--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_HighConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_HighConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1687"/>
+  <dimension ref="A1:K1751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49374,6 +49374,1862 @@
       </c>
       <c r="K1687" t="inlineStr"/>
     </row>
+    <row r="1688">
+      <c r="A1688" s="1" t="n">
+        <v>1686</v>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0006.png</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr"/>
+      <c r="D1688" t="inlineStr"/>
+      <c r="E1688" t="inlineStr"/>
+      <c r="F1688" t="inlineStr">
+        <is>
+          <t>O=C(NC(Cc1ccc(OCc2ccccc2)nc1)C(=O)N1CCC(N2CCCCC2)CC1)N1CCC(N2Cc3ccccc3NC2=O)CC1</t>
+        </is>
+      </c>
+      <c r="G1688" t="inlineStr"/>
+      <c r="H1688" t="inlineStr"/>
+      <c r="I1688" t="n">
+        <v>0.9142170765838024</v>
+      </c>
+      <c r="J1688" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1688" t="inlineStr"/>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="1" t="n">
+        <v>1687</v>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0008.png</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr"/>
+      <c r="D1689" t="inlineStr"/>
+      <c r="E1689" t="inlineStr"/>
+      <c r="F1689" t="inlineStr">
+        <is>
+          <t>C=C[C@@H]1CC1(NC(=O)[C@@H]1C[C@@H](Oc2cc(-c3ccccc3)nc3cc(OC)ccc23)CN1C(=O)[C@@H](OC(=O)NC(C)(C)C)C(C)(C)C)C(=O)NS(=O)(=O)C1(CC2CC2)CC1</t>
+        </is>
+      </c>
+      <c r="G1689" t="inlineStr"/>
+      <c r="H1689" t="inlineStr"/>
+      <c r="I1689" t="n">
+        <v>0.9008674185420836</v>
+      </c>
+      <c r="J1689" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1689" t="inlineStr"/>
+    </row>
+    <row r="1690">
+      <c r="A1690" s="1" t="n">
+        <v>1688</v>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0009.png</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr"/>
+      <c r="D1690" t="inlineStr"/>
+      <c r="E1690" t="inlineStr"/>
+      <c r="F1690" t="inlineStr">
+        <is>
+          <t>C=C[C@@H]1C[C@]1(NC(=O)[C@@H]1C[C@@H](Oc2nccc3ccccc23)CN1C(=O)[C@@H](OC(=O)Nc1ccc(C(C)(C)C)cc1)C(C)(C)C)C(=O)NS(=O)(=O)C1CC1</t>
+        </is>
+      </c>
+      <c r="G1690" t="inlineStr"/>
+      <c r="H1690" t="inlineStr"/>
+      <c r="I1690" t="n">
+        <v>0.9131192918353959</v>
+      </c>
+      <c r="J1690" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1690" t="inlineStr"/>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="1" t="n">
+        <v>1689</v>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0011.png</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr"/>
+      <c r="D1691" t="inlineStr"/>
+      <c r="E1691" t="inlineStr"/>
+      <c r="F1691" t="inlineStr">
+        <is>
+          <t>NC(CCC(=O)NCCCC(=O)N[C@@H](CNC(=O)c1ccc2c(cnn2CCCNc2ncc[nH]2)c1)C(=O)O)C(=O)NCCCCCC(=O)N[C@@H](CNC(=O)c1ccc2c(cnn2CCCNc2ncc[nH]2)c1)C(=O)O</t>
+        </is>
+      </c>
+      <c r="G1691" t="inlineStr"/>
+      <c r="H1691" t="inlineStr"/>
+      <c r="I1691" t="n">
+        <v>0.9059905721446931</v>
+      </c>
+      <c r="J1691" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1691" t="inlineStr"/>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="1" t="n">
+        <v>1690</v>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0013.png</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr"/>
+      <c r="D1692" t="inlineStr"/>
+      <c r="E1692" t="inlineStr"/>
+      <c r="F1692" t="inlineStr">
+        <is>
+          <t>Cc1cc(OCCCC(=O)NCCNC(=O)C(CCC(=O)OC(C)(C)C)NC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)OCc2ccccc2)cc(C)c1S(=O)(=O)N[C@@H](CNC(=O)c1ccc2c(cnn2CCCNc2ncc[nH]2)c1)C(=O)O</t>
+        </is>
+      </c>
+      <c r="G1692" t="inlineStr"/>
+      <c r="H1692" t="inlineStr"/>
+      <c r="I1692" t="n">
+        <v>0.8972030700707886</v>
+      </c>
+      <c r="J1692" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1692" t="inlineStr"/>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="1" t="n">
+        <v>1691</v>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0014.png</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr"/>
+      <c r="D1693" t="inlineStr"/>
+      <c r="E1693" t="inlineStr"/>
+      <c r="F1693" t="inlineStr">
+        <is>
+          <t>C=C[C@@H]1C[C@]1(NC(=O)[C@@H]1C[C@H](Oc2cc(-c3ccccc3)nc3cc(OC)ccc23)CN1C(=O)[C@@H](OC(=O)Nc1ccc(OC)cc1)C(C)(C)C)C(=O)NS(=O)(=O)C1CC1</t>
+        </is>
+      </c>
+      <c r="G1693" t="inlineStr"/>
+      <c r="H1693" t="inlineStr"/>
+      <c r="I1693" t="n">
+        <v>0.9073033447622657</v>
+      </c>
+      <c r="J1693" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1693" t="inlineStr"/>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="1" t="n">
+        <v>1692</v>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0015.png</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr"/>
+      <c r="D1694" t="inlineStr"/>
+      <c r="E1694" t="inlineStr"/>
+      <c r="F1694" t="inlineStr">
+        <is>
+          <t>c1cc(-c2ccc3ccc4cccnc4c3n2)cc(-c2ccccc2-c2ccccc2-c2cccc(-c3ccc4ccc5cccnc5c4n3)c2)c1</t>
+        </is>
+      </c>
+      <c r="G1694" t="inlineStr"/>
+      <c r="H1694" t="inlineStr"/>
+      <c r="I1694" t="n">
+        <v>0.9210780030190178</v>
+      </c>
+      <c r="J1694" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1694" t="inlineStr"/>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="1" t="n">
+        <v>1693</v>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0016.png</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr"/>
+      <c r="D1695" t="inlineStr"/>
+      <c r="E1695" t="inlineStr"/>
+      <c r="F1695" t="inlineStr">
+        <is>
+          <t>C=C[C@@H]1C[C@]1(NC(=O)[C@@H]1C[C@H](Oc2cc(-c3ccccc3)nc3cc(OC)ccc23)CN1C(=O)[C@@H](OC(=O)Nc1ccc(N(C)C)cc1)C(C)(C)C)C(=O)NS(=O)(=O)C1CC1</t>
+        </is>
+      </c>
+      <c r="G1695" t="inlineStr"/>
+      <c r="H1695" t="inlineStr"/>
+      <c r="I1695" t="n">
+        <v>0.8969342911597011</v>
+      </c>
+      <c r="J1695" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1695" t="inlineStr"/>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="1" t="n">
+        <v>1694</v>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0019.png</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr"/>
+      <c r="D1696" t="inlineStr"/>
+      <c r="E1696" t="inlineStr"/>
+      <c r="F1696" t="inlineStr">
+        <is>
+          <t>CC1=C(/C=C/C=C/C=C/C=C/C=C/C=C/C=C/C=C(C)/C=C/C2=C(C)C(=O)C(OP(=O)(O)O)CC2(C)C)C(C)(C)CC(OP(=O)(O)O)C1=O</t>
+        </is>
+      </c>
+      <c r="G1696" t="inlineStr"/>
+      <c r="H1696" t="inlineStr"/>
+      <c r="I1696" t="n">
+        <v>0.8858947752673534</v>
+      </c>
+      <c r="J1696" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1696" t="inlineStr"/>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="1" t="n">
+        <v>1695</v>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0020.png</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr"/>
+      <c r="D1697" t="inlineStr"/>
+      <c r="E1697" t="inlineStr"/>
+      <c r="F1697" t="inlineStr">
+        <is>
+          <t>C=C[C@@H]1C[C@@]1(NC(=O)[C@@H]1CC(Oc2cc(-c3ccccc3)nc3cc(OC)ccc23)CN1C(=O)[C@@H](O)C(C)(C)C)C(=O)NS(=O)(=O)C1(CC2CC2)CC1</t>
+        </is>
+      </c>
+      <c r="G1697" t="inlineStr"/>
+      <c r="H1697" t="inlineStr"/>
+      <c r="I1697" t="n">
+        <v>0.8890468321032035</v>
+      </c>
+      <c r="J1697" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1697" t="inlineStr"/>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="1" t="n">
+        <v>1696</v>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0021.png</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr"/>
+      <c r="D1698" t="inlineStr"/>
+      <c r="E1698" t="inlineStr"/>
+      <c r="F1698" t="inlineStr">
+        <is>
+          <t>[H][C@]1(Oc2cc(-c3ccccc3)nc3cc(OC)ccc23)CN(C(=O)[C@]([H])(O)c2ccccc2)[C@]([H])(C(=O)N[C@]2(C(=O)NS(=O)(=O)C3CC3)C[C@@]2([H])C=C)C1</t>
+        </is>
+      </c>
+      <c r="G1698" t="inlineStr"/>
+      <c r="H1698" t="inlineStr"/>
+      <c r="I1698" t="n">
+        <v>0.8899591704481401</v>
+      </c>
+      <c r="J1698" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1698" t="inlineStr"/>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="1" t="n">
+        <v>1697</v>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0022.png</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr"/>
+      <c r="D1699" t="inlineStr"/>
+      <c r="E1699" t="inlineStr"/>
+      <c r="F1699" t="inlineStr">
+        <is>
+          <t>COC(=O)[C@H](CNC(=O)c1ccc2c(cnn2CCCNc2ncccn2)c1)NS(=O)(=O)c1c(C)cc(OCCCC(=O)NCCNC(=O)OCc2ccccc2)cc1C</t>
+        </is>
+      </c>
+      <c r="G1699" t="inlineStr"/>
+      <c r="H1699" t="inlineStr"/>
+      <c r="I1699" t="n">
+        <v>0.8942836240659651</v>
+      </c>
+      <c r="J1699" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1699" t="inlineStr"/>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="1" t="n">
+        <v>1698</v>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0023.png</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr"/>
+      <c r="D1700" t="inlineStr"/>
+      <c r="E1700" t="inlineStr"/>
+      <c r="F1700" t="inlineStr">
+        <is>
+          <t>COC(=O)[C@H](CNC(=O)c1ccc2c(CCCNC3=NCCCC3)nn(C)c2c1)NS(=O)(=O)c1c(C)cc(OCCCC(=O)NCCNC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)OCc2ccccc2)cc1C</t>
+        </is>
+      </c>
+      <c r="G1700" t="inlineStr"/>
+      <c r="H1700" t="inlineStr"/>
+      <c r="I1700" t="n">
+        <v>0.8938599646997502</v>
+      </c>
+      <c r="J1700" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1700" t="inlineStr"/>
+    </row>
+    <row r="1701">
+      <c r="A1701" s="1" t="n">
+        <v>1699</v>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0024.png</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr"/>
+      <c r="D1701" t="inlineStr"/>
+      <c r="E1701" t="inlineStr"/>
+      <c r="F1701" t="inlineStr">
+        <is>
+          <t>C=CC1CC1(NC(=O)[C@@H]1CC(Oc2cc(-c3ccccc3)nc3cc(OC)ccc23)CN1C(=O)[C@@H](OC(=O)Nc1ccc(OC)cc1C)C(C)(C)C)C(=O)NS(=O)(=O)C1CC1</t>
+        </is>
+      </c>
+      <c r="G1701" t="inlineStr"/>
+      <c r="H1701" t="inlineStr"/>
+      <c r="I1701" t="n">
+        <v>0.9159639749347586</v>
+      </c>
+      <c r="J1701" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1701" t="inlineStr"/>
+    </row>
+    <row r="1702">
+      <c r="A1702" s="1" t="n">
+        <v>1700</v>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0025.png</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr"/>
+      <c r="D1702" t="inlineStr"/>
+      <c r="E1702" t="inlineStr"/>
+      <c r="F1702" t="inlineStr">
+        <is>
+          <t>CC1(C)O[C@@H]2[C@H](O1)[C@@H](/C=C/CNC(=O)c1cc(C(=O)c3ccncc3)cc3c1OC(c1ccccc1)(c1ccccc1)O3)O[C@H]2n1cnc2c(N)ncnc21</t>
+        </is>
+      </c>
+      <c r="G1702" t="inlineStr"/>
+      <c r="H1702" t="inlineStr"/>
+      <c r="I1702" t="n">
+        <v>0.896823333093274</v>
+      </c>
+      <c r="J1702" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1702" t="inlineStr"/>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="1" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0026.png</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr"/>
+      <c r="D1703" t="inlineStr"/>
+      <c r="E1703" t="inlineStr"/>
+      <c r="F1703" t="inlineStr">
+        <is>
+          <t>CC1(C)O[C@@H]2[C@H](O1)[C@@H](/C=C/CNC(=O)c1cc(-c3nccs3)cc3c1OC(c1ccccc1)(c1ccccc1)O3)O[C@H]2n1cnc2c(N)ncnc21</t>
+        </is>
+      </c>
+      <c r="G1703" t="inlineStr"/>
+      <c r="H1703" t="inlineStr"/>
+      <c r="I1703" t="n">
+        <v>0.8915959474653408</v>
+      </c>
+      <c r="J1703" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1703" t="inlineStr"/>
+    </row>
+    <row r="1704">
+      <c r="A1704" s="1" t="n">
+        <v>1702</v>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0030.png</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr"/>
+      <c r="D1704" t="inlineStr"/>
+      <c r="E1704" t="inlineStr"/>
+      <c r="F1704" t="inlineStr">
+        <is>
+          <t>CC1(C)O[C@@H]2[C@H](O1)[C@H](n1cnc3c(N)ncnc31)O[C@@H]2/C=C/CNC(=O)c1cc(-c2nc3ccccc3s2)cc2c1OC(c1ccccc1)(c1ccccc1)O2</t>
+        </is>
+      </c>
+      <c r="G1704" t="inlineStr"/>
+      <c r="H1704" t="inlineStr"/>
+      <c r="I1704" t="n">
+        <v>0.8870881154821409</v>
+      </c>
+      <c r="J1704" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1704" t="inlineStr"/>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="1" t="n">
+        <v>1703</v>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0031.png</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr"/>
+      <c r="D1705" t="inlineStr"/>
+      <c r="E1705" t="inlineStr"/>
+      <c r="F1705" t="inlineStr">
+        <is>
+          <t>C=C[C@@H]1C[C@]1(NC(=O)[C@@H]1C[C@@H](Oc2nccc3ccccc23)CN1C(=O)[C@@H](OC(=O)Nc1ccc(F)cc1)C(C)(C)C)C(=O)NS(=O)(=O)C1CC1</t>
+        </is>
+      </c>
+      <c r="G1705" t="inlineStr"/>
+      <c r="H1705" t="inlineStr"/>
+      <c r="I1705" t="n">
+        <v>0.9097663454707612</v>
+      </c>
+      <c r="J1705" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1705" t="inlineStr"/>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="1" t="n">
+        <v>1704</v>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0032.png</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr"/>
+      <c r="D1706" t="inlineStr"/>
+      <c r="E1706" t="inlineStr"/>
+      <c r="F1706" t="inlineStr">
+        <is>
+          <t>COC(=O)[C@H](CNC(=O)c1ccc2c(cnn2CCNC2=NCCCC2)c1)NS(=O)(=O)c1ccc(-c2ccc(S(=O)(=O)NCCNC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)OCc3ccccc3)cc2)cc1</t>
+        </is>
+      </c>
+      <c r="G1706" t="inlineStr"/>
+      <c r="H1706" t="inlineStr"/>
+      <c r="I1706" t="n">
+        <v>0.8847456761217281</v>
+      </c>
+      <c r="J1706" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1706" t="inlineStr"/>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="1" t="n">
+        <v>1705</v>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0033.png</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr"/>
+      <c r="D1707" t="inlineStr"/>
+      <c r="E1707" t="inlineStr"/>
+      <c r="F1707" t="inlineStr">
+        <is>
+          <t>Cc1cc(OCCCC(=O)NCCNC(=O)C(CCC(=O)OC(C)(C)C)NC(=O)[C@@H](N)CCC(=O)OC(C)(C)C)cc(C)c1S(=O)(=O)N[C@@H](CNC(=O)c1ccc2c(cnn2CCCNc2ncc[nH]2)c1)C(=O)O</t>
+        </is>
+      </c>
+      <c r="G1707" t="inlineStr"/>
+      <c r="H1707" t="inlineStr"/>
+      <c r="I1707" t="n">
+        <v>0.880686318362027</v>
+      </c>
+      <c r="J1707" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1707" t="inlineStr"/>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="1" t="n">
+        <v>1706</v>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0035.png</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr"/>
+      <c r="D1708" t="inlineStr"/>
+      <c r="E1708" t="inlineStr"/>
+      <c r="F1708" t="inlineStr">
+        <is>
+          <t>Cc1ccc(Cc2cc3c(c(C(=O)NC/C=C/[C@H]4O[C@@H](n5cnc6c(N)ncnc65)[C@@H]5OC(C)(C)OC54)c2)OC(c2ccccc2)(c2ccccc2)O3)cc1</t>
+        </is>
+      </c>
+      <c r="G1708" t="inlineStr"/>
+      <c r="H1708" t="inlineStr"/>
+      <c r="I1708" t="n">
+        <v>0.902444519862141</v>
+      </c>
+      <c r="J1708" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1708" t="inlineStr"/>
+    </row>
+    <row r="1709">
+      <c r="A1709" s="1" t="n">
+        <v>1707</v>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0036.png</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr"/>
+      <c r="D1709" t="inlineStr"/>
+      <c r="E1709" t="inlineStr"/>
+      <c r="F1709" t="inlineStr">
+        <is>
+          <t>COC(=O)[C@H](CNC(=O)c1ccc2c(cnn2CCCNC2=NCCCN2)c1)NS(=O)(=O)c1ccc(-c2ccc(S(=O)(=O)NCCNC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)OCc3ccccc3)cc2)cc1</t>
+        </is>
+      </c>
+      <c r="G1709" t="inlineStr"/>
+      <c r="H1709" t="inlineStr"/>
+      <c r="I1709" t="n">
+        <v>0.8955557204829121</v>
+      </c>
+      <c r="J1709" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1709" t="inlineStr"/>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="1" t="n">
+        <v>1708</v>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0037.png</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr"/>
+      <c r="D1710" t="inlineStr"/>
+      <c r="E1710" t="inlineStr"/>
+      <c r="F1710" t="inlineStr">
+        <is>
+          <t>COC(=O)[C@H](CNC(=O)c1ccc2c(cnn2CCCNC2=NCCCN2)c1)NS(=O)(=O)c1c(C)cc(OCCCC(=O)NCCNC(=O)C(N)CCC(=O)OC(C)(C)C)cc1C</t>
+        </is>
+      </c>
+      <c r="G1710" t="inlineStr"/>
+      <c r="H1710" t="inlineStr"/>
+      <c r="I1710" t="n">
+        <v>0.8892282666557172</v>
+      </c>
+      <c r="J1710" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1710" t="inlineStr"/>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="1" t="n">
+        <v>1709</v>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0038.png</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr"/>
+      <c r="D1711" t="inlineStr"/>
+      <c r="E1711" t="inlineStr"/>
+      <c r="F1711" t="inlineStr">
+        <is>
+          <t>CC1(C)O[C@@H]2[C@H](O1)[C@@H](/C=C/CNC(=O)c1cc(-c3ccncc3)cc3c1OC(c1ccccc1)(c1ccccc1)O3)O[C@H]2n1cnc2c(N)ncnc21</t>
+        </is>
+      </c>
+      <c r="G1711" t="inlineStr"/>
+      <c r="H1711" t="inlineStr"/>
+      <c r="I1711" t="n">
+        <v>0.8944543207967235</v>
+      </c>
+      <c r="J1711" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1711" t="inlineStr"/>
+    </row>
+    <row r="1712">
+      <c r="A1712" s="1" t="n">
+        <v>1710</v>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0041.png</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr"/>
+      <c r="D1712" t="inlineStr"/>
+      <c r="E1712" t="inlineStr"/>
+      <c r="F1712" t="inlineStr">
+        <is>
+          <t>CC(C)(C)OC(=O)n1ncc2cc(CC(CC(=O)N3CCC(N4Cc5ccccc5NC4=O)CC3)C(=O)N3CCC(N4CCCCC4)CC3)ccc21</t>
+        </is>
+      </c>
+      <c r="G1712" t="inlineStr"/>
+      <c r="H1712" t="inlineStr"/>
+      <c r="I1712" t="n">
+        <v>0.9199019996272951</v>
+      </c>
+      <c r="J1712" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1712" t="inlineStr"/>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="1" t="n">
+        <v>1711</v>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0042.png</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr"/>
+      <c r="D1713" t="inlineStr"/>
+      <c r="E1713" t="inlineStr"/>
+      <c r="F1713" t="inlineStr">
+        <is>
+          <t>Cc1cc(C)cc(-c2[nH]c3sc(C(C)(C)C(=O)N4C5CCC4CC5)cc3c2[C@H](C)CN/C(=N/C(=O)OC(C)C)N2CCN(c3ccncc3)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G1713" t="inlineStr"/>
+      <c r="H1713" t="inlineStr"/>
+      <c r="I1713" t="n">
+        <v>0.8949040905954962</v>
+      </c>
+      <c r="J1713" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1713" t="inlineStr"/>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="1" t="n">
+        <v>1712</v>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0046.png</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr"/>
+      <c r="D1714" t="inlineStr"/>
+      <c r="E1714" t="inlineStr"/>
+      <c r="F1714" t="inlineStr">
+        <is>
+          <t>CC[C@H]1C[C@]1(NC(=O)[C@@H]1C[C@@H](Oc2cc(-c3ccccc3)nc3cc(OC)ccc23)CN1C(=O)C(O)Cc1c[nH]cn1)C(=O)NS(=O)(=O)C1CC1</t>
+        </is>
+      </c>
+      <c r="G1714" t="inlineStr"/>
+      <c r="H1714" t="inlineStr"/>
+      <c r="I1714" t="n">
+        <v>0.9076067119803672</v>
+      </c>
+      <c r="J1714" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1714" t="inlineStr"/>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="1" t="n">
+        <v>1713</v>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0047.png</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr"/>
+      <c r="D1715" t="inlineStr"/>
+      <c r="E1715" t="inlineStr"/>
+      <c r="F1715" t="inlineStr">
+        <is>
+          <t>Cc1cc(C)cc(-c2[nH]c3sc(C(C)(C)C(=O)N4C5CCC4CC5)cc3c2CCN/C(=N/C(=O)OC(C)C)N2CCC(c3ccncc3)C2)c1</t>
+        </is>
+      </c>
+      <c r="G1715" t="inlineStr"/>
+      <c r="H1715" t="inlineStr"/>
+      <c r="I1715" t="n">
+        <v>0.889653278681565</v>
+      </c>
+      <c r="J1715" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1715" t="inlineStr"/>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="1" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0048.png</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr"/>
+      <c r="D1716" t="inlineStr"/>
+      <c r="E1716" t="inlineStr"/>
+      <c r="F1716" t="inlineStr">
+        <is>
+          <t>COC(=O)[C@H](CNC(=O)c1ccc2c(cnn2CCCNc2ncccn2)c1)NS(=O)(=O)c1ccc(-c2ccc(S(=O)(=O)NCCNC(=O)OCc3ccccc3)cc2)cc1</t>
+        </is>
+      </c>
+      <c r="G1716" t="inlineStr"/>
+      <c r="H1716" t="inlineStr"/>
+      <c r="I1716" t="n">
+        <v>0.893672977762292</v>
+      </c>
+      <c r="J1716" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1716" t="inlineStr"/>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="1" t="n">
+        <v>1715</v>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0049.png</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr"/>
+      <c r="D1717" t="inlineStr"/>
+      <c r="E1717" t="inlineStr"/>
+      <c r="F1717" t="inlineStr">
+        <is>
+          <t>Cc1cc(OCCCC(=O)NCCNC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)OCc2ccccc2)cc(C)c1S(=O)(=O)N[C@@H](CNC(=O)c1ccc2c(cnn2CCNC2=NCCCC2)c1)C(=O)O</t>
+        </is>
+      </c>
+      <c r="G1717" t="inlineStr"/>
+      <c r="H1717" t="inlineStr"/>
+      <c r="I1717" t="n">
+        <v>0.884760816211659</v>
+      </c>
+      <c r="J1717" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1717" t="inlineStr"/>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="1" t="n">
+        <v>1716</v>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0050.png</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr"/>
+      <c r="D1718" t="inlineStr"/>
+      <c r="E1718" t="inlineStr"/>
+      <c r="F1718" t="inlineStr">
+        <is>
+          <t>[H][C@]1(Oc2cc(-c3ccccc3)nc3cc(OC)ccc23)CN(C(=O)C(O)c2ccccc2)[C@]([H])(C(=O)N[C@]2(C(=O)NS(=O)(=O)C3CC3)C[C@@]2([H])C=C)C1</t>
+        </is>
+      </c>
+      <c r="G1718" t="inlineStr"/>
+      <c r="H1718" t="inlineStr"/>
+      <c r="I1718" t="n">
+        <v>0.8953091419398913</v>
+      </c>
+      <c r="J1718" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1718" t="inlineStr"/>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="1" t="n">
+        <v>1717</v>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0052.png</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr"/>
+      <c r="D1719" t="inlineStr"/>
+      <c r="E1719" t="inlineStr"/>
+      <c r="F1719" t="inlineStr">
+        <is>
+          <t>C=CC1CC1(NC(=O)[C@@H]1CC(Oc2cc(-c3ccccc3)nc3cc(OC)ccc23)CN1C(=O)[C@@H](OC(=O)Nc1ccc(OC)cc1)C(C)(C)C)C(=O)NS(=O)(=O)C1CC1</t>
+        </is>
+      </c>
+      <c r="G1719" t="inlineStr"/>
+      <c r="H1719" t="inlineStr"/>
+      <c r="I1719" t="n">
+        <v>0.9160497383125208</v>
+      </c>
+      <c r="J1719" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1719" t="inlineStr"/>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="1" t="n">
+        <v>1718</v>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0053.png</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr"/>
+      <c r="D1720" t="inlineStr"/>
+      <c r="E1720" t="inlineStr"/>
+      <c r="F1720" t="inlineStr">
+        <is>
+          <t>COC(=O)[C@H](CNC(=O)c1ccc2c(cnn2CCCNC2=NCCCN2)c1)NS(=O)(=O)c1c(C)cc(OCCCC(=O)NCCNC(=O)C(CCC(=O)OC(C)(C)C)NC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)OCc2ccccc2)cc1C</t>
+        </is>
+      </c>
+      <c r="G1720" t="inlineStr"/>
+      <c r="H1720" t="inlineStr"/>
+      <c r="I1720" t="n">
+        <v>0.8792676041129015</v>
+      </c>
+      <c r="J1720" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1720" t="inlineStr"/>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="1" t="n">
+        <v>1719</v>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0054.png</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr"/>
+      <c r="D1721" t="inlineStr"/>
+      <c r="E1721" t="inlineStr"/>
+      <c r="F1721" t="inlineStr">
+        <is>
+          <t>O=C(NC(Cc1ccc2[nH]ncc2c1)C(=O)N1CCC(N2Cc3ccccc3NC2=O)CC1)N1CCC(N2Cc3ccccc3NC2=O)CC1</t>
+        </is>
+      </c>
+      <c r="G1721" t="inlineStr"/>
+      <c r="H1721" t="inlineStr"/>
+      <c r="I1721" t="n">
+        <v>0.9207033166920465</v>
+      </c>
+      <c r="J1721" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1721" t="inlineStr"/>
+    </row>
+    <row r="1722">
+      <c r="A1722" s="1" t="n">
+        <v>1720</v>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0056.png</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr"/>
+      <c r="D1722" t="inlineStr"/>
+      <c r="E1722" t="inlineStr"/>
+      <c r="F1722" t="inlineStr">
+        <is>
+          <t>Cc1cc(C)cc(-c2[nH]c3sc(C(C)(C)C(=O)N4C5CCC4CC5)cc3c2[C@H](C)CN/C(=N/C(=O)OC(C)C)N2CCC(c3ccncc3)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G1722" t="inlineStr"/>
+      <c r="H1722" t="inlineStr"/>
+      <c r="I1722" t="n">
+        <v>0.8960723402285682</v>
+      </c>
+      <c r="J1722" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1722" t="inlineStr"/>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="1" t="n">
+        <v>1721</v>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0057.png</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr"/>
+      <c r="D1723" t="inlineStr"/>
+      <c r="E1723" t="inlineStr"/>
+      <c r="F1723" t="inlineStr">
+        <is>
+          <t>CC(=O)c1ccc2c(c1)C1(c3cc(-c4ccc5ccc6ccccc6c5n4)ccc3-2)c2cc(-c3ccc4ccc5ccccc5c4n3)ccc2-c2ccc(-c3ccc4ccc5ccccc5c4n3)cc21</t>
+        </is>
+      </c>
+      <c r="G1723" t="inlineStr"/>
+      <c r="H1723" t="inlineStr"/>
+      <c r="I1723" t="n">
+        <v>0.894957416468548</v>
+      </c>
+      <c r="J1723" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1723" t="inlineStr"/>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="1" t="n">
+        <v>1722</v>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0058.png</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr"/>
+      <c r="D1724" t="inlineStr"/>
+      <c r="E1724" t="inlineStr"/>
+      <c r="F1724" t="inlineStr">
+        <is>
+          <t>COC(=O)[C@H](CNC(=O)c1ccc2c(CCCNc3ccccn3)nn(C)c2c1)NS(=O)(=O)c1c(C)cc(OCCCC(=O)NCCNC(=O)OCc2ccccc2)cc1C</t>
+        </is>
+      </c>
+      <c r="G1724" t="inlineStr"/>
+      <c r="H1724" t="inlineStr"/>
+      <c r="I1724" t="n">
+        <v>0.9033998893373066</v>
+      </c>
+      <c r="J1724" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1724" t="inlineStr"/>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="1" t="n">
+        <v>1723</v>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0060.png</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr"/>
+      <c r="D1725" t="inlineStr"/>
+      <c r="E1725" t="inlineStr"/>
+      <c r="F1725" t="inlineStr">
+        <is>
+          <t>C=C[C@@H]1C[C@]1(NC(=O)[C@@H]1C[C@@H](Oc2nccc3ccccc23)CN1C(=O)[C@@H](OC(=O)Nc1ccccc1OC)C(C)(C)C)C(=O)NS(=O)(=O)C1CC1</t>
+        </is>
+      </c>
+      <c r="G1725" t="inlineStr"/>
+      <c r="H1725" t="inlineStr"/>
+      <c r="I1725" t="n">
+        <v>0.9023607108190183</v>
+      </c>
+      <c r="J1725" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1725" t="inlineStr"/>
+    </row>
+    <row r="1726">
+      <c r="A1726" s="1" t="n">
+        <v>1724</v>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0062.png</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr"/>
+      <c r="D1726" t="inlineStr"/>
+      <c r="E1726" t="inlineStr"/>
+      <c r="F1726" t="inlineStr">
+        <is>
+          <t>C=C[C@@H]1C[C@]1(NC(=O)[C@@H]1C[C@@H](Oc2cc(-c3cccs3)cc(-c3ccccc3)n2)CN1C(=O)[C@@H](OC(=O)NC(C)(C)C)C(C)C)C(=O)NS(=O)(=O)C1CC1</t>
+        </is>
+      </c>
+      <c r="G1726" t="inlineStr"/>
+      <c r="H1726" t="inlineStr"/>
+      <c r="I1726" t="n">
+        <v>0.9001725000769537</v>
+      </c>
+      <c r="J1726" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1726" t="inlineStr"/>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="1" t="n">
+        <v>1725</v>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0065.png</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr"/>
+      <c r="D1727" t="inlineStr"/>
+      <c r="E1727" t="inlineStr"/>
+      <c r="F1727" t="inlineStr">
+        <is>
+          <t>C=C[C@@H]1C[C@]1(NC(=O)[C@@H]1C[C@H](Oc2cc(-c3ccccc3)nc3cc(OC)ccc23)CN1C(=O)[C@@H](OC(=O)Nc1ccc(OC)cc1C)C(C)(C)C)C(=O)NS(=O)(=O)C1CC1</t>
+        </is>
+      </c>
+      <c r="G1727" t="inlineStr"/>
+      <c r="H1727" t="inlineStr"/>
+      <c r="I1727" t="n">
+        <v>0.9065342442348568</v>
+      </c>
+      <c r="J1727" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1727" t="inlineStr"/>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="1" t="n">
+        <v>1726</v>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0067.png</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr"/>
+      <c r="D1728" t="inlineStr"/>
+      <c r="E1728" t="inlineStr"/>
+      <c r="F1728" t="inlineStr">
+        <is>
+          <t>C=C[C@@H]1C[C@]1(NC(=O)[C@@H]1C[C@@H](Oc2nccc3ccccc23)CN1C(=O)[C@@H](OC(=O)Nc1ccc(OC)cc1)C(C)(C)C)C(=O)NS(=O)(=O)C1CC1</t>
+        </is>
+      </c>
+      <c r="G1728" t="inlineStr"/>
+      <c r="H1728" t="inlineStr"/>
+      <c r="I1728" t="n">
+        <v>0.9083649568773515</v>
+      </c>
+      <c r="J1728" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1728" t="inlineStr"/>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="1" t="n">
+        <v>1727</v>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0068.png</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr"/>
+      <c r="D1729" t="inlineStr"/>
+      <c r="E1729" t="inlineStr"/>
+      <c r="F1729" t="inlineStr">
+        <is>
+          <t>C=C[C@@H]1C[C@]1(NC(=O)[C@@H]1C[C@@H](Oc2nc(-c3ccc(OC(F)(F)F)cc3)cc3cc(OC)ccc23)CN1C(=O)[C@@H](OC(=O)NC(C)(C)C)C(C)(C)C)C(=O)NS(=O)(=O)C1CC1</t>
+        </is>
+      </c>
+      <c r="G1729" t="inlineStr"/>
+      <c r="H1729" t="inlineStr"/>
+      <c r="I1729" t="n">
+        <v>0.8955345356250366</v>
+      </c>
+      <c r="J1729" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1729" t="inlineStr"/>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="1" t="n">
+        <v>1728</v>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0069.png</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr"/>
+      <c r="D1730" t="inlineStr"/>
+      <c r="E1730" t="inlineStr"/>
+      <c r="F1730" t="inlineStr">
+        <is>
+          <t>Cc1cc(C)cc(-c2[nH]c3sc(C(C)(C)C(=O)N4C5CCC4CC5)cc3c2[C@H](C)CN/C(=N/C(=O)OC(C)C)N2CCC(c3ccccn3)C2)c1</t>
+        </is>
+      </c>
+      <c r="G1730" t="inlineStr"/>
+      <c r="H1730" t="inlineStr"/>
+      <c r="I1730" t="n">
+        <v>0.8951914024924019</v>
+      </c>
+      <c r="J1730" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1730" t="inlineStr"/>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="1" t="n">
+        <v>1729</v>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0070.png</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr"/>
+      <c r="D1731" t="inlineStr"/>
+      <c r="E1731" t="inlineStr"/>
+      <c r="F1731" t="inlineStr">
+        <is>
+          <t>C=C[C@@H]1C[C@]1(NC(=O)[C@@H]1C[C@@H](Oc2nccc3ccccc23)CN1C(=O)[C@@H](OC(=O)Nc1ccccc1C(C)C)C(C)(C)C)C(=O)NS(=O)(=O)C1CC1</t>
+        </is>
+      </c>
+      <c r="G1731" t="inlineStr"/>
+      <c r="H1731" t="inlineStr"/>
+      <c r="I1731" t="n">
+        <v>0.881482076679066</v>
+      </c>
+      <c r="J1731" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1731" t="inlineStr"/>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="1" t="n">
+        <v>1730</v>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0071.png</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr"/>
+      <c r="D1732" t="inlineStr"/>
+      <c r="E1732" t="inlineStr"/>
+      <c r="F1732" t="inlineStr">
+        <is>
+          <t>[H]O[C@]([H])(C(=O)N1C[C@H](Oc2cc(-c3ccccc3)nc3cc(OC)ccc23)C[C@H]1C(=O)N[C@]1(C(=O)NS(=O)(=O)C2CC2)C[C@@H]1CC)C1CCCCC1</t>
+        </is>
+      </c>
+      <c r="G1732" t="inlineStr"/>
+      <c r="H1732" t="inlineStr"/>
+      <c r="I1732" t="n">
+        <v>0.8964078813953507</v>
+      </c>
+      <c r="J1732" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1732" t="inlineStr"/>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="1" t="n">
+        <v>1731</v>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0072.png</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr"/>
+      <c r="D1733" t="inlineStr"/>
+      <c r="E1733" t="inlineStr"/>
+      <c r="F1733" t="inlineStr">
+        <is>
+          <t>O=C(NC(Cn1ccc(OCc2ccccc2)cc1=O)C(=O)N1CCC(N2CCCCC2)CC1)N1CCC(N2Cc3ccccc3NC2=O)CC1</t>
+        </is>
+      </c>
+      <c r="G1733" t="inlineStr"/>
+      <c r="H1733" t="inlineStr"/>
+      <c r="I1733" t="n">
+        <v>0.9173066312951518</v>
+      </c>
+      <c r="J1733" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1733" t="inlineStr"/>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="1" t="n">
+        <v>1732</v>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0073.png</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr"/>
+      <c r="D1734" t="inlineStr"/>
+      <c r="E1734" t="inlineStr"/>
+      <c r="F1734" t="inlineStr">
+        <is>
+          <t>c1ccc(-c2ccc(-c3ccccc3)c3c2-c2ccc4c5ccc6c7c(ccc(c8ccc-3c2c48)c75)-c2c(-c3ccccc3)ccc(-c3ccccc3)c2-6)cc1</t>
+        </is>
+      </c>
+      <c r="G1734" t="inlineStr"/>
+      <c r="H1734" t="inlineStr"/>
+      <c r="I1734" t="n">
+        <v>0.8780214396204282</v>
+      </c>
+      <c r="J1734" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1734" t="inlineStr"/>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="1" t="n">
+        <v>1733</v>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0074.png</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr"/>
+      <c r="D1735" t="inlineStr"/>
+      <c r="E1735" t="inlineStr"/>
+      <c r="F1735" t="inlineStr">
+        <is>
+          <t>c1ccc(-n2c(-c3cccc(-c4nc5c6ccccc6c6ccccc6c5n4-c4ccccc4)c3)nc3c4ccccc4c4ccccc4c32)cc1</t>
+        </is>
+      </c>
+      <c r="G1735" t="inlineStr"/>
+      <c r="H1735" t="inlineStr"/>
+      <c r="I1735" t="n">
+        <v>0.9079417429555183</v>
+      </c>
+      <c r="J1735" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1735" t="inlineStr"/>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="1" t="n">
+        <v>1734</v>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0075.png</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr"/>
+      <c r="D1736" t="inlineStr"/>
+      <c r="E1736" t="inlineStr"/>
+      <c r="F1736" t="inlineStr">
+        <is>
+          <t>CC1(C)O[C@@H]2[C@H](O1)[C@H](n1cnc3c(N)ncnc31)O[C@@H]2/C=C/CNC(=O)c1cc(C(=O)C2CCCCC2)cc2c1OC(c1ccccc1)(c1ccccc1)O2</t>
+        </is>
+      </c>
+      <c r="G1736" t="inlineStr"/>
+      <c r="H1736" t="inlineStr"/>
+      <c r="I1736" t="n">
+        <v>0.8940487163380083</v>
+      </c>
+      <c r="J1736" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1736" t="inlineStr"/>
+    </row>
+    <row r="1737">
+      <c r="A1737" s="1" t="n">
+        <v>1735</v>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0076.png</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr"/>
+      <c r="D1737" t="inlineStr"/>
+      <c r="E1737" t="inlineStr"/>
+      <c r="F1737" t="inlineStr">
+        <is>
+          <t>CCN(CC)c1ccc(C(CC)(c2ccccc2)c2ccc(N(c3ccc(C)cc3)c3ccc4ccc5cccc6ccc3c4c56)cc2)cc1</t>
+        </is>
+      </c>
+      <c r="G1737" t="inlineStr"/>
+      <c r="H1737" t="inlineStr"/>
+      <c r="I1737" t="n">
+        <v>0.8823876040549724</v>
+      </c>
+      <c r="J1737" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1737" t="inlineStr"/>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="1" t="n">
+        <v>1736</v>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0077.png</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr"/>
+      <c r="D1738" t="inlineStr"/>
+      <c r="E1738" t="inlineStr"/>
+      <c r="F1738" t="inlineStr">
+        <is>
+          <t>Cc1cc(C)cc(-c2[nH]c3sc(C(C)(C)C(=O)N4C5CCC4CC5)cc3c2[C@H](C)CN/C(=N/C(=O)OC(C)C)N2CCN(CC(=O)NC(C)C)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G1738" t="inlineStr"/>
+      <c r="H1738" t="inlineStr"/>
+      <c r="I1738" t="n">
+        <v>0.8852134504598471</v>
+      </c>
+      <c r="J1738" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1738" t="inlineStr"/>
+    </row>
+    <row r="1739">
+      <c r="A1739" s="1" t="n">
+        <v>1737</v>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0078.png</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr"/>
+      <c r="D1739" t="inlineStr"/>
+      <c r="E1739" t="inlineStr"/>
+      <c r="F1739" t="inlineStr">
+        <is>
+          <t>COC(=O)[C@H](CNC(=O)c1ccc2c(cnn2CCCNC2=NCCCN2)c1)NS(=O)(=O)c1c(C)cc(OCCCC(=O)NCCNC(=O)C(CCC(=O)OC(C)(C)C)NC(=O)[C@@H](N)CCC(=O)OC(C)(C)C)cc1C</t>
+        </is>
+      </c>
+      <c r="G1739" t="inlineStr"/>
+      <c r="H1739" t="inlineStr"/>
+      <c r="I1739" t="n">
+        <v>0.8658121158163138</v>
+      </c>
+      <c r="J1739" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1739" t="inlineStr"/>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="1" t="n">
+        <v>1738</v>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0080.png</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr"/>
+      <c r="D1740" t="inlineStr"/>
+      <c r="E1740" t="inlineStr"/>
+      <c r="F1740" t="inlineStr">
+        <is>
+          <t>COC(=O)[C@H](CNC(=O)c1ccc2c(CNc3nccn3C(c3ccccc3)(c3ccccc3)c3ccccc3)nn(C)c2c1)NS(=O)(=O)c1ccc(-c2ccc(S(=O)(=O)NCCN)cc2)cc1</t>
+        </is>
+      </c>
+      <c r="G1740" t="inlineStr"/>
+      <c r="H1740" t="inlineStr"/>
+      <c r="I1740" t="n">
+        <v>0.8905611427299589</v>
+      </c>
+      <c r="J1740" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1740" t="inlineStr"/>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="1" t="n">
+        <v>1739</v>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0082.png</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr"/>
+      <c r="D1741" t="inlineStr"/>
+      <c r="E1741" t="inlineStr"/>
+      <c r="F1741" t="inlineStr">
+        <is>
+          <t>C=C[C@@H]1C[C@]1(NC(=O)[C@@H]1C[C@H](Oc2nc(-c3ccc(OC(F)(F)F)cc3)cc3cc(OC)ccc23)CN1C(=O)[C@@H](O)C(C)(C)C)C(=O)NS(=O)(=O)C1CC1</t>
+        </is>
+      </c>
+      <c r="G1741" t="inlineStr"/>
+      <c r="H1741" t="inlineStr"/>
+      <c r="I1741" t="n">
+        <v>0.8813345128149159</v>
+      </c>
+      <c r="J1741" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1741" t="inlineStr"/>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="1" t="n">
+        <v>1740</v>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0083.png</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr"/>
+      <c r="D1742" t="inlineStr"/>
+      <c r="E1742" t="inlineStr"/>
+      <c r="F1742" t="inlineStr">
+        <is>
+          <t>Cc1cc(C)cc(-c2[nH]c3sc(C(C)(C)C(=O)N4C5CCC4CC5)cc3c2[C@H](C)CN/C(=N/C(=O)OC(C)C)N2CCN(c3ccccn3)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G1742" t="inlineStr"/>
+      <c r="H1742" t="inlineStr"/>
+      <c r="I1742" t="n">
+        <v>0.894047375489725</v>
+      </c>
+      <c r="J1742" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1742" t="inlineStr"/>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="1" t="n">
+        <v>1741</v>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0084.png</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr"/>
+      <c r="D1743" t="inlineStr"/>
+      <c r="E1743" t="inlineStr"/>
+      <c r="F1743" t="inlineStr">
+        <is>
+          <t>Cc1cc(OCCCC(=O)NCCNC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)OCc2ccccc2)cc(C)c1S(=O)(=O)N[C@@H](CNC(=O)c1ccc2c(cnn2CCNC2=NCCCC2)c1)C(=O)O</t>
+        </is>
+      </c>
+      <c r="G1743" t="inlineStr"/>
+      <c r="H1743" t="inlineStr"/>
+      <c r="I1743" t="n">
+        <v>0.8897775592653683</v>
+      </c>
+      <c r="J1743" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1743" t="inlineStr"/>
+    </row>
+    <row r="1744">
+      <c r="A1744" s="1" t="n">
+        <v>1742</v>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0087.png</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr"/>
+      <c r="D1744" t="inlineStr"/>
+      <c r="E1744" t="inlineStr"/>
+      <c r="F1744" t="inlineStr">
+        <is>
+          <t>Cc1cc(C)cc(-c2[nH]c3sc(C(C)(C)C(=O)N4C5CCC4CC5)cc3c2[C@H](C)CN/C(=N/C(=O)OC(C)C)N2CCC(C3CCOCC3)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G1744" t="inlineStr"/>
+      <c r="H1744" t="inlineStr"/>
+      <c r="I1744" t="n">
+        <v>0.9032333236516835</v>
+      </c>
+      <c r="J1744" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1744" t="inlineStr"/>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="1" t="n">
+        <v>1743</v>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0090.png</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr"/>
+      <c r="D1745" t="inlineStr"/>
+      <c r="E1745" t="inlineStr"/>
+      <c r="F1745" t="inlineStr">
+        <is>
+          <t>COC(=O)[C@H](CNC(=O)c1ccc2c(cnn2CCCNC2=NCCCN2)c1)NS(=O)(=O)c1ccc(-c2ccc(S(=O)(=O)NCCNC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)OCc3ccccc3)cc2)cc1</t>
+        </is>
+      </c>
+      <c r="G1745" t="inlineStr"/>
+      <c r="H1745" t="inlineStr"/>
+      <c r="I1745" t="n">
+        <v>0.8887643997989498</v>
+      </c>
+      <c r="J1745" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1745" t="inlineStr"/>
+    </row>
+    <row r="1746">
+      <c r="A1746" s="1" t="n">
+        <v>1744</v>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0091.png</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr"/>
+      <c r="D1746" t="inlineStr"/>
+      <c r="E1746" t="inlineStr"/>
+      <c r="F1746" t="inlineStr">
+        <is>
+          <t>C=CCCCCCC(O)C(=O)N1C[C@H](Oc2nc(-c3ccccc3)cc3cc(OC)ccc23)CC1C(=O)N[C@]1(C(=O)NS(=O)(=O)C2CC2)C[C@H]1C=C</t>
+        </is>
+      </c>
+      <c r="G1746" t="inlineStr"/>
+      <c r="H1746" t="inlineStr"/>
+      <c r="I1746" t="n">
+        <v>0.9051356984152785</v>
+      </c>
+      <c r="J1746" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1746" t="inlineStr"/>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="1" t="n">
+        <v>1745</v>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0094.png</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr"/>
+      <c r="D1747" t="inlineStr"/>
+      <c r="E1747" t="inlineStr"/>
+      <c r="F1747" t="inlineStr">
+        <is>
+          <t>c1ccc2c(c1)-c1ccc(-c3ccc4ccc5cccnc5c4n3)cc1C21c2ccccc2-c2ccc(-c3ccc4ccc5cccnc5c4n3)cc21</t>
+        </is>
+      </c>
+      <c r="G1747" t="inlineStr"/>
+      <c r="H1747" t="inlineStr"/>
+      <c r="I1747" t="n">
+        <v>0.8941462661658132</v>
+      </c>
+      <c r="J1747" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1747" t="inlineStr"/>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="1" t="n">
+        <v>1746</v>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0097.png</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr"/>
+      <c r="D1748" t="inlineStr"/>
+      <c r="E1748" t="inlineStr"/>
+      <c r="F1748" t="inlineStr">
+        <is>
+          <t>CN(C)C(=O)c1cc2c(c(C(=O)NC/C=C/[C@H]3O[C@@H](n4cnc5c(N)ncnc54)[C@@H]4OC(C)(C)OC43)c1)OC(c1ccccc1)(c1ccccc1)O2</t>
+        </is>
+      </c>
+      <c r="G1748" t="inlineStr"/>
+      <c r="H1748" t="inlineStr"/>
+      <c r="I1748" t="n">
+        <v>0.9007253525525214</v>
+      </c>
+      <c r="J1748" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1748" t="inlineStr"/>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="1" t="n">
+        <v>1747</v>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0098.png</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr"/>
+      <c r="D1749" t="inlineStr"/>
+      <c r="E1749" t="inlineStr"/>
+      <c r="F1749" t="inlineStr">
+        <is>
+          <t>c1ccc2c(c1)-c1ccc(-c3ccc4ccc5ccccc5c4n3)cc1C21c2ccccc2-c2ccc(-c3ccc4ccc5ccccc5c4n3)cc21</t>
+        </is>
+      </c>
+      <c r="G1749" t="inlineStr"/>
+      <c r="H1749" t="inlineStr"/>
+      <c r="I1749" t="n">
+        <v>0.8852024857200894</v>
+      </c>
+      <c r="J1749" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1749" t="inlineStr"/>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="1" t="n">
+        <v>1748</v>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0099.png</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr"/>
+      <c r="D1750" t="inlineStr"/>
+      <c r="E1750" t="inlineStr"/>
+      <c r="F1750" t="inlineStr">
+        <is>
+          <t>CCc1ccc(-c2ccc(CN(C)c3ccc(-c4cccc(-c5ccc(N(C)Cc6ccc(-c7ccc(C)cc7)cc6)cc5)c4)cc3)cc2)cc1</t>
+        </is>
+      </c>
+      <c r="G1750" t="inlineStr"/>
+      <c r="H1750" t="inlineStr"/>
+      <c r="I1750" t="n">
+        <v>0.8692438665110074</v>
+      </c>
+      <c r="J1750" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1750" t="inlineStr"/>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="1" t="n">
+        <v>1749</v>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0100.png</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr"/>
+      <c r="D1751" t="inlineStr"/>
+      <c r="E1751" t="inlineStr"/>
+      <c r="F1751" t="inlineStr">
+        <is>
+          <t>[H][C@@](NC(=O)N(C)Cc1csc(C(C)C)n1)(C(=O)N[C@@](C)(Cc1ccccc1)C[C@H](O)[C@]([H])(Cc1ccccc1)NC(=O)OCc1cncs1)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1751" t="inlineStr"/>
+      <c r="H1751" t="inlineStr"/>
+      <c r="I1751" t="n">
+        <v>0.8913209820059446</v>
+      </c>
+      <c r="J1751" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1751" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_HighConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_HighConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1751"/>
+  <dimension ref="A1:K1906"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51230,6 +51230,4501 @@
       </c>
       <c r="K1751" t="inlineStr"/>
     </row>
+    <row r="1752">
+      <c r="A1752" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0101.png</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr"/>
+      <c r="D1752" t="inlineStr"/>
+      <c r="E1752" t="inlineStr"/>
+      <c r="F1752" t="inlineStr">
+        <is>
+          <t>Cc1[nH]c2ccccc2c1C[C@H]1C(=O)NCc2c(-c3ccn(CC(=O)O)c(=O)c3)ccc(Cl)c2Sc2ncccc2CN[C@@H](CCCN)C(=O)N[C@@H](CCCCN)C(=O)N1C</t>
+        </is>
+      </c>
+      <c r="G1752" t="inlineStr"/>
+      <c r="H1752" t="inlineStr"/>
+      <c r="I1752" t="n">
+        <v>0.890906805239708</v>
+      </c>
+      <c r="J1752" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1752" t="inlineStr"/>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="1" t="n">
+        <v>1751</v>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0102.png</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr"/>
+      <c r="D1753" t="inlineStr"/>
+      <c r="E1753" t="inlineStr"/>
+      <c r="F1753" t="inlineStr">
+        <is>
+          <t>CC(C)(S)[C@H](NC(=O)[C@H](CC(=O)O)NC(=O)[C@H](CCCCN)NC(=O)[C@H](CC(=O)O)NC(=O)CCC(=O)Nc1cccc2c(C(=O)NCC(=O)N3CC(F)(F)C[C@H]3C#N)ccnc12)C(=O)O</t>
+        </is>
+      </c>
+      <c r="G1753" t="inlineStr"/>
+      <c r="H1753" t="inlineStr"/>
+      <c r="I1753" t="n">
+        <v>0.8890425487913143</v>
+      </c>
+      <c r="J1753" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1753" t="inlineStr"/>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="1" t="n">
+        <v>1752</v>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0105.png</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr"/>
+      <c r="D1754" t="inlineStr"/>
+      <c r="E1754" t="inlineStr"/>
+      <c r="F1754" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)c4ccc(CN[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)N[C@@H](C)c5ccc(-c6scnc6C)cc5)C(C)(C)C)cc4)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1754" t="inlineStr"/>
+      <c r="H1754" t="inlineStr"/>
+      <c r="I1754" t="n">
+        <v>0.8887266634880251</v>
+      </c>
+      <c r="J1754" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1754" t="inlineStr"/>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="1" t="n">
+        <v>1753</v>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0106.png</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr"/>
+      <c r="D1755" t="inlineStr"/>
+      <c r="E1755" t="inlineStr"/>
+      <c r="F1755" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)CCC(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1755" t="inlineStr"/>
+      <c r="H1755" t="inlineStr"/>
+      <c r="I1755" t="n">
+        <v>0.8928162500331304</v>
+      </c>
+      <c r="J1755" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1755" t="inlineStr"/>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="1" t="n">
+        <v>1754</v>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0107.png</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr"/>
+      <c r="D1756" t="inlineStr"/>
+      <c r="E1756" t="inlineStr"/>
+      <c r="F1756" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)[C@@H]4C[C@@H](C(=O)N[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)N[C@@H](C)c5ccc(-c6scnc6C)cc5)C(C)(C)C)C4)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1756" t="inlineStr"/>
+      <c r="H1756" t="inlineStr"/>
+      <c r="I1756" t="n">
+        <v>0.9035510515789659</v>
+      </c>
+      <c r="J1756" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1756" t="inlineStr"/>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="1" t="n">
+        <v>1755</v>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0108.png</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr"/>
+      <c r="D1757" t="inlineStr"/>
+      <c r="E1757" t="inlineStr"/>
+      <c r="F1757" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2ccc(C3=C4C=c5ccccc5=[N+]4[B-](F)(F)n4c3cc3ccccc34)cc2OC)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1757" t="inlineStr"/>
+      <c r="H1757" t="inlineStr"/>
+      <c r="I1757" t="n">
+        <v>0.9050060473668353</v>
+      </c>
+      <c r="J1757" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1757" t="inlineStr"/>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="1" t="n">
+        <v>1756</v>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0109.png</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr"/>
+      <c r="D1758" t="inlineStr"/>
+      <c r="E1758" t="inlineStr"/>
+      <c r="F1758" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCN7CC8CCC7C8)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1758" t="inlineStr"/>
+      <c r="H1758" t="inlineStr"/>
+      <c r="I1758" t="n">
+        <v>0.8876300268363819</v>
+      </c>
+      <c r="J1758" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1758" t="inlineStr"/>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="1" t="n">
+        <v>1757</v>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0110.png</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr"/>
+      <c r="D1759" t="inlineStr"/>
+      <c r="E1759" t="inlineStr"/>
+      <c r="F1759" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)c4ccc(C(=O)N[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)N[C@@H](C)c5ccc(-c6scnc6C)cc5)C(C)(C)C)cc4)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1759" t="inlineStr"/>
+      <c r="H1759" t="inlineStr"/>
+      <c r="I1759" t="n">
+        <v>0.9027908563676383</v>
+      </c>
+      <c r="J1759" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1759" t="inlineStr"/>
+    </row>
+    <row r="1760">
+      <c r="A1760" s="1" t="n">
+        <v>1758</v>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0111.png</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr"/>
+      <c r="D1760" t="inlineStr"/>
+      <c r="E1760" t="inlineStr"/>
+      <c r="F1760" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)c2ccc(N3CCN(c4cc(-c5ccccc5O)nnc4N)CC3)s2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1760" t="inlineStr"/>
+      <c r="H1760" t="inlineStr"/>
+      <c r="I1760" t="n">
+        <v>0.8918146782755171</v>
+      </c>
+      <c r="J1760" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1760" t="inlineStr"/>
+    </row>
+    <row r="1761">
+      <c r="A1761" s="1" t="n">
+        <v>1759</v>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0112.png</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr"/>
+      <c r="D1761" t="inlineStr"/>
+      <c r="E1761" t="inlineStr"/>
+      <c r="F1761" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)N(CCCCNC[C@@H]2CC[C@@H](n3cc4cc(NC(=O)c5cccc(C(F)(F)F)n5)c(C(C)(C)O)cc4n3)CC2)CCCCN2CCC(c3ccc(Nc4nc(N5CCCCC5)cnc4C(N)=O)cc3)CC2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1761" t="inlineStr"/>
+      <c r="H1761" t="inlineStr"/>
+      <c r="I1761" t="n">
+        <v>0.8835469944379127</v>
+      </c>
+      <c r="J1761" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1761" t="inlineStr"/>
+    </row>
+    <row r="1762">
+      <c r="A1762" s="1" t="n">
+        <v>1760</v>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0114.png</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr"/>
+      <c r="D1762" t="inlineStr"/>
+      <c r="E1762" t="inlineStr"/>
+      <c r="F1762" t="inlineStr">
+        <is>
+          <t>N[C@@H](Cc1ccc(NS(=O)(=O)c2ccc(C3CCCCC3)cc2)cc1)C(=O)N1CCC(CCC#Cc2cccc3c2CN(C2CCC(=O)NC2=O)C3=O)CC1</t>
+        </is>
+      </c>
+      <c r="G1762" t="inlineStr"/>
+      <c r="H1762" t="inlineStr"/>
+      <c r="I1762" t="n">
+        <v>0.9037736828754294</v>
+      </c>
+      <c r="J1762" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1762" t="inlineStr"/>
+    </row>
+    <row r="1763">
+      <c r="A1763" s="1" t="n">
+        <v>1761</v>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0116.png</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr"/>
+      <c r="D1763" t="inlineStr"/>
+      <c r="E1763" t="inlineStr"/>
+      <c r="F1763" t="inlineStr">
+        <is>
+          <t>CCOP(=O)(O)C(F)(F)c1ccc2[nH]c(C(=O)N[C@H]3CN(CCOCCOCCOCCNc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)CC[C@H]4CC[C@@H](C(=O)NCCCC(N)=O)N4C3=O)cc2c1</t>
+        </is>
+      </c>
+      <c r="G1763" t="inlineStr"/>
+      <c r="H1763" t="inlineStr"/>
+      <c r="I1763" t="n">
+        <v>0.8793957597443802</v>
+      </c>
+      <c r="J1763" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1763" t="inlineStr"/>
+    </row>
+    <row r="1764">
+      <c r="A1764" s="1" t="n">
+        <v>1762</v>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0117.png</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr"/>
+      <c r="D1764" t="inlineStr"/>
+      <c r="E1764" t="inlineStr"/>
+      <c r="F1764" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)CCC(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1764" t="inlineStr"/>
+      <c r="H1764" t="inlineStr"/>
+      <c r="I1764" t="n">
+        <v>0.8875698715321245</v>
+      </c>
+      <c r="J1764" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1764" t="inlineStr"/>
+    </row>
+    <row r="1765">
+      <c r="A1765" s="1" t="n">
+        <v>1763</v>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0118.png</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr"/>
+      <c r="D1765" t="inlineStr"/>
+      <c r="E1765" t="inlineStr"/>
+      <c r="F1765" t="inlineStr">
+        <is>
+          <t>C#C[Br-]1(C#C)N2C(C)=CC(C)=C2C(C2=CC=C(N3CCOCCOCCN(C4=C(OC)C=CC=C4)CCOCCOCC3)C(OC)=C2)=C2C(C)=CC(C)=[N+]21</t>
+        </is>
+      </c>
+      <c r="G1765" t="inlineStr"/>
+      <c r="H1765" t="inlineStr"/>
+      <c r="I1765" t="n">
+        <v>0.8863642561670542</v>
+      </c>
+      <c r="J1765" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1765" t="inlineStr"/>
+    </row>
+    <row r="1766">
+      <c r="A1766" s="1" t="n">
+        <v>1764</v>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0119.png</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr"/>
+      <c r="D1766" t="inlineStr"/>
+      <c r="E1766" t="inlineStr"/>
+      <c r="F1766" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)c4cc(C(=O)N[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)N[C@@H](C)c5ccc(-c6scnc6C)cc5)C(C)(C)C)ncn4)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1766" t="inlineStr"/>
+      <c r="H1766" t="inlineStr"/>
+      <c r="I1766" t="n">
+        <v>0.8823817498528365</v>
+      </c>
+      <c r="J1766" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1766" t="inlineStr"/>
+    </row>
+    <row r="1767">
+      <c r="A1767" s="1" t="n">
+        <v>1765</v>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0121.png</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr"/>
+      <c r="D1767" t="inlineStr"/>
+      <c r="E1767" t="inlineStr"/>
+      <c r="F1767" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCN(c2cc(C3=C4C=CC(=[N+](C)C)C=C4C(C)(C)c4cc(N(C)C)ccc43)c(C(=O)[O-])cc2OC)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1767" t="inlineStr"/>
+      <c r="H1767" t="inlineStr"/>
+      <c r="I1767" t="n">
+        <v>0.8940898481672558</v>
+      </c>
+      <c r="J1767" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1767" t="inlineStr"/>
+    </row>
+    <row r="1768">
+      <c r="A1768" s="1" t="n">
+        <v>1766</v>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0122.png</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr"/>
+      <c r="D1768" t="inlineStr"/>
+      <c r="E1768" t="inlineStr"/>
+      <c r="F1768" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2cc3c(cc2OC)C2(OC3=O)c3ccc(OC(C)=O)cc3S(=O)(=O)c3cc(OC(C)=O)ccc32)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1768" t="inlineStr"/>
+      <c r="H1768" t="inlineStr"/>
+      <c r="I1768" t="n">
+        <v>0.9000330186341481</v>
+      </c>
+      <c r="J1768" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1768" t="inlineStr"/>
+    </row>
+    <row r="1769">
+      <c r="A1769" s="1" t="n">
+        <v>1767</v>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0123.png</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr"/>
+      <c r="D1769" t="inlineStr"/>
+      <c r="E1769" t="inlineStr"/>
+      <c r="F1769" t="inlineStr">
+        <is>
+          <t>O=C(O)c1cccc(CN2CCOCCOCCN(Cc3cc(OCCc4ccc(N=C=S)cc4)cc(C(=O)O)n3)CCOCCOCC2)n1</t>
+        </is>
+      </c>
+      <c r="G1769" t="inlineStr"/>
+      <c r="H1769" t="inlineStr"/>
+      <c r="I1769" t="n">
+        <v>0.8437937674634005</v>
+      </c>
+      <c r="J1769" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1769" t="inlineStr"/>
+    </row>
+    <row r="1770">
+      <c r="A1770" s="1" t="n">
+        <v>1768</v>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0126.png</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr"/>
+      <c r="D1770" t="inlineStr"/>
+      <c r="E1770" t="inlineStr"/>
+      <c r="F1770" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCN7CCCCCC7)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1770" t="inlineStr"/>
+      <c r="H1770" t="inlineStr"/>
+      <c r="I1770" t="n">
+        <v>0.8881306513092286</v>
+      </c>
+      <c r="J1770" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1770" t="inlineStr"/>
+    </row>
+    <row r="1771">
+      <c r="A1771" s="1" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0127.png</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr"/>
+      <c r="D1771" t="inlineStr"/>
+      <c r="E1771" t="inlineStr"/>
+      <c r="F1771" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CN2CCN(c3cc(-c4cccc(F)c4O)nnc3N)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1771" t="inlineStr"/>
+      <c r="H1771" t="inlineStr"/>
+      <c r="I1771" t="n">
+        <v>0.8992640380749422</v>
+      </c>
+      <c r="J1771" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1771" t="inlineStr"/>
+    </row>
+    <row r="1772">
+      <c r="A1772" s="1" t="n">
+        <v>1770</v>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0129.png</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr"/>
+      <c r="D1772" t="inlineStr"/>
+      <c r="E1772" t="inlineStr"/>
+      <c r="F1772" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2cc(C(=O)O)c(C3=C4C=C(F)C(=O)C=C4B(O)c4cc(O)c(F)cc43)cc2OC)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1772" t="inlineStr"/>
+      <c r="H1772" t="inlineStr"/>
+      <c r="I1772" t="n">
+        <v>0.9087582354940286</v>
+      </c>
+      <c r="J1772" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1772" t="inlineStr"/>
+    </row>
+    <row r="1773">
+      <c r="A1773" s="1" t="n">
+        <v>1771</v>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0131.png</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr"/>
+      <c r="D1773" t="inlineStr"/>
+      <c r="E1773" t="inlineStr"/>
+      <c r="F1773" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2cc3c(cc2OC)C2(OC3=O)c3ccc(OC(C)=O)cc3P(C)(=O)c3cc(OC(C)=O)ccc32)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1773" t="inlineStr"/>
+      <c r="H1773" t="inlineStr"/>
+      <c r="I1773" t="n">
+        <v>0.9031096149582338</v>
+      </c>
+      <c r="J1773" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1773" t="inlineStr"/>
+    </row>
+    <row r="1774">
+      <c r="A1774" s="1" t="n">
+        <v>1772</v>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0133.png</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr"/>
+      <c r="D1774" t="inlineStr"/>
+      <c r="E1774" t="inlineStr"/>
+      <c r="F1774" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2ccc(C3=C4C(C)=CC(C)=[N+]4[B-](OC)(OC)n4c(C)cc(C)c43)cc2OC)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1774" t="inlineStr"/>
+      <c r="H1774" t="inlineStr"/>
+      <c r="I1774" t="n">
+        <v>0.9067113547843993</v>
+      </c>
+      <c r="J1774" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1774" t="inlineStr"/>
+    </row>
+    <row r="1775">
+      <c r="A1775" s="1" t="n">
+        <v>1773</v>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0135.png</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr"/>
+      <c r="D1775" t="inlineStr"/>
+      <c r="E1775" t="inlineStr"/>
+      <c r="F1775" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccc2c(c1)CCCOc1cc(ccc1Cc1nc3c(OCCOC)cc(C(=O)OC)cc3n1C[C@@H]1CCO1)-c1cccc(n1)OC2</t>
+        </is>
+      </c>
+      <c r="G1775" t="inlineStr"/>
+      <c r="H1775" t="inlineStr"/>
+      <c r="I1775" t="n">
+        <v>0.8796212786983971</v>
+      </c>
+      <c r="J1775" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1775" t="inlineStr"/>
+    </row>
+    <row r="1776">
+      <c r="A1776" s="1" t="n">
+        <v>1774</v>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0138.png</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr"/>
+      <c r="D1776" t="inlineStr"/>
+      <c r="E1776" t="inlineStr"/>
+      <c r="F1776" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2cc3c(cc2OC)C2(OC3=O)c3ccc(OC(C)=O)cc3[Si](C)(C)c3cc(OC(C)=O)ccc32)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1776" t="inlineStr"/>
+      <c r="H1776" t="inlineStr"/>
+      <c r="I1776" t="n">
+        <v>0.9029322857220686</v>
+      </c>
+      <c r="J1776" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1776" t="inlineStr"/>
+    </row>
+    <row r="1777">
+      <c r="A1777" s="1" t="n">
+        <v>1775</v>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0141.png</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr"/>
+      <c r="D1777" t="inlineStr"/>
+      <c r="E1777" t="inlineStr"/>
+      <c r="F1777" t="inlineStr">
+        <is>
+          <t>Cc1cnc(Nc2cc(C3CCN(C(=O)C4CC(C(=O)Nc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)CC3)cc(N3CCC(F)(F)C3)n2)cn1</t>
+        </is>
+      </c>
+      <c r="G1777" t="inlineStr"/>
+      <c r="H1777" t="inlineStr"/>
+      <c r="I1777" t="n">
+        <v>0.888462048485224</v>
+      </c>
+      <c r="J1777" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1777" t="inlineStr"/>
+    </row>
+    <row r="1778">
+      <c r="A1778" s="1" t="n">
+        <v>1776</v>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0142.png</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr"/>
+      <c r="D1778" t="inlineStr"/>
+      <c r="E1778" t="inlineStr"/>
+      <c r="F1778" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCCCCCCCCCCOc2ccc3c(-c4ccc(C(=O)O)c(C5CCCC5)c4)ncnc3c2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1778" t="inlineStr"/>
+      <c r="H1778" t="inlineStr"/>
+      <c r="I1778" t="n">
+        <v>0.8798559839417448</v>
+      </c>
+      <c r="J1778" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1778" t="inlineStr"/>
+    </row>
+    <row r="1779">
+      <c r="A1779" s="1" t="n">
+        <v>1777</v>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0144.png</t>
+        </is>
+      </c>
+      <c r="C1779" t="inlineStr"/>
+      <c r="D1779" t="inlineStr"/>
+      <c r="E1779" t="inlineStr"/>
+      <c r="F1779" t="inlineStr">
+        <is>
+          <t>NC(=O)c1c(-c2ccc(Oc3ccccc3)cc2)nn2c1Nc1ccc(NCC3CCN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)cc1CC2</t>
+        </is>
+      </c>
+      <c r="G1779" t="inlineStr"/>
+      <c r="H1779" t="inlineStr"/>
+      <c r="I1779" t="n">
+        <v>0.8864810231225339</v>
+      </c>
+      <c r="J1779" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1779" t="inlineStr"/>
+    </row>
+    <row r="1780">
+      <c r="A1780" s="1" t="n">
+        <v>1778</v>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0145.png</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr"/>
+      <c r="D1780" t="inlineStr"/>
+      <c r="E1780" t="inlineStr"/>
+      <c r="F1780" t="inlineStr">
+        <is>
+          <t>COCCOc1cc(C(=O)O)cc2c1nc(Cc1cc(F)c3cc1COCCc1cc(C#N)cc(F)c1COc1cccc-3n1)n2C[C@@H]1CCO1</t>
+        </is>
+      </c>
+      <c r="G1780" t="inlineStr"/>
+      <c r="H1780" t="inlineStr"/>
+      <c r="I1780" t="n">
+        <v>0.898045312028382</v>
+      </c>
+      <c r="J1780" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1780" t="inlineStr"/>
+    </row>
+    <row r="1781">
+      <c r="A1781" s="1" t="n">
+        <v>1779</v>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0146.png</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr"/>
+      <c r="D1781" t="inlineStr"/>
+      <c r="E1781" t="inlineStr"/>
+      <c r="F1781" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCCN)NC(=O)[C@H](CCCN)NCc2nccnc2Sc2c(Cl)ccc(-c3ccc(C(=O)O)cc3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G1781" t="inlineStr"/>
+      <c r="H1781" t="inlineStr"/>
+      <c r="I1781" t="n">
+        <v>0.8907545307378212</v>
+      </c>
+      <c r="J1781" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1781" t="inlineStr"/>
+    </row>
+    <row r="1782">
+      <c r="A1782" s="1" t="n">
+        <v>1780</v>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0149.png</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr"/>
+      <c r="D1782" t="inlineStr"/>
+      <c r="E1782" t="inlineStr"/>
+      <c r="F1782" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(O)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1782" t="inlineStr"/>
+      <c r="H1782" t="inlineStr"/>
+      <c r="I1782" t="n">
+        <v>0.8762769975916448</v>
+      </c>
+      <c r="J1782" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1782" t="inlineStr"/>
+    </row>
+    <row r="1783">
+      <c r="A1783" s="1" t="n">
+        <v>1781</v>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0150.png</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr"/>
+      <c r="D1783" t="inlineStr"/>
+      <c r="E1783" t="inlineStr"/>
+      <c r="F1783" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)[C@@H]2C[C@@H](C(=O)N3CCC(c4cc(Nc5cnccn5)nc(N5CCC(F)(F)C5)c4)CC3)C2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1783" t="inlineStr"/>
+      <c r="H1783" t="inlineStr"/>
+      <c r="I1783" t="n">
+        <v>0.8978856498306861</v>
+      </c>
+      <c r="J1783" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1783" t="inlineStr"/>
+    </row>
+    <row r="1784">
+      <c r="A1784" s="1" t="n">
+        <v>1782</v>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0151.png</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr"/>
+      <c r="D1784" t="inlineStr"/>
+      <c r="E1784" t="inlineStr"/>
+      <c r="F1784" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCN)NC(=O)[C@H](CCN)NCc2cccnc2Sc2c(Cl)ccc(-c3ccc(C(=O)O)cc3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G1784" t="inlineStr"/>
+      <c r="H1784" t="inlineStr"/>
+      <c r="I1784" t="n">
+        <v>0.8987201279751899</v>
+      </c>
+      <c r="J1784" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1784" t="inlineStr"/>
+    </row>
+    <row r="1785">
+      <c r="A1785" s="1" t="n">
+        <v>1783</v>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0152.png</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr"/>
+      <c r="D1785" t="inlineStr"/>
+      <c r="E1785" t="inlineStr"/>
+      <c r="F1785" t="inlineStr">
+        <is>
+          <t>CC[C@@]1(O)C(=O)OCc2c1cc1n(c2=O)Cc2c-1nc1cc(F)c(C)cc1c2CCCCOCNC(=O)[C@H](C)NC(=O)[C@H](C)NC(=O)[C@H](C)NC(=O)[C@H](CCC(=O)N(C)C[C@H](O)[C@@H](O)[C@H](O)[C@H](O)CO)NC(=O)CCN1C(=O)C=CC1=O</t>
+        </is>
+      </c>
+      <c r="G1785" t="inlineStr"/>
+      <c r="H1785" t="inlineStr"/>
+      <c r="I1785" t="n">
+        <v>0.8844931128978811</v>
+      </c>
+      <c r="J1785" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1785" t="inlineStr"/>
+    </row>
+    <row r="1786">
+      <c r="A1786" s="1" t="n">
+        <v>1784</v>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0157.png</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr"/>
+      <c r="D1786" t="inlineStr"/>
+      <c r="E1786" t="inlineStr"/>
+      <c r="F1786" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)c4ccc(-c5ccc(C(=O)N[C@H](C(=O)N6C[C@H](O)C[C@H]6C(=O)N[C@@H](C)c6ccc(-c7scnc7C)cc6)C(C)(C)C)cc5)cc4)C3C)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1786" t="inlineStr"/>
+      <c r="H1786" t="inlineStr"/>
+      <c r="I1786" t="n">
+        <v>0.8559881206764496</v>
+      </c>
+      <c r="J1786" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1786" t="inlineStr"/>
+    </row>
+    <row r="1787">
+      <c r="A1787" s="1" t="n">
+        <v>1785</v>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0159.png</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr"/>
+      <c r="D1787" t="inlineStr"/>
+      <c r="E1787" t="inlineStr"/>
+      <c r="F1787" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)CCCCCN[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1787" t="inlineStr"/>
+      <c r="H1787" t="inlineStr"/>
+      <c r="I1787" t="n">
+        <v>0.8849592370387845</v>
+      </c>
+      <c r="J1787" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1787" t="inlineStr"/>
+    </row>
+    <row r="1788">
+      <c r="A1788" s="1" t="n">
+        <v>1786</v>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0165.png</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr"/>
+      <c r="D1788" t="inlineStr"/>
+      <c r="E1788" t="inlineStr"/>
+      <c r="F1788" t="inlineStr">
+        <is>
+          <t>COC(=O)c1cc(NC[C@@H]2CCO2)c(NC(=O)Cc2ccc3cc2COCCc2cc(Cl)ccc2COc2cccc-3n2)c(OCCO[Si](C)(C)C(C)(C)C)c1</t>
+        </is>
+      </c>
+      <c r="G1788" t="inlineStr"/>
+      <c r="H1788" t="inlineStr"/>
+      <c r="I1788" t="n">
+        <v>0.894287291088156</v>
+      </c>
+      <c r="J1788" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1788" t="inlineStr"/>
+    </row>
+    <row r="1789">
+      <c r="A1789" s="1" t="n">
+        <v>1787</v>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0166.png</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr"/>
+      <c r="D1789" t="inlineStr"/>
+      <c r="E1789" t="inlineStr"/>
+      <c r="F1789" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCNC(=O)OC(C)(C)C)NC(=O)[C@H](CCCNC(=O)OC(C)(C)C)NCc2cccnc2Sc2c(F)ccc(Br)c2CNC(=O)[C@@H]1Cc1cn(C(=O)OC(C)(C)C)c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G1789" t="inlineStr"/>
+      <c r="H1789" t="inlineStr"/>
+      <c r="I1789" t="n">
+        <v>0.9065416330662514</v>
+      </c>
+      <c r="J1789" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1789" t="inlineStr"/>
+    </row>
+    <row r="1790">
+      <c r="A1790" s="1" t="n">
+        <v>1788</v>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0167.png</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr"/>
+      <c r="D1790" t="inlineStr"/>
+      <c r="E1790" t="inlineStr"/>
+      <c r="F1790" t="inlineStr">
+        <is>
+          <t>CC(C)c1cnn2c(NCc3ccccc3-c3nccc4cc(NCC5CCN(CC6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)ccc34)nc(N[C@@H]3CCCNC3)nc12</t>
+        </is>
+      </c>
+      <c r="G1790" t="inlineStr"/>
+      <c r="H1790" t="inlineStr"/>
+      <c r="I1790" t="n">
+        <v>0.8975483277394064</v>
+      </c>
+      <c r="J1790" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1790" t="inlineStr"/>
+    </row>
+    <row r="1791">
+      <c r="A1791" s="1" t="n">
+        <v>1789</v>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0168.png</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr"/>
+      <c r="D1791" t="inlineStr"/>
+      <c r="E1791" t="inlineStr"/>
+      <c r="F1791" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCN(C)c7ccccn7)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1791" t="inlineStr"/>
+      <c r="H1791" t="inlineStr"/>
+      <c r="I1791" t="n">
+        <v>0.8929740635843338</v>
+      </c>
+      <c r="J1791" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1791" t="inlineStr"/>
+    </row>
+    <row r="1792">
+      <c r="A1792" s="1" t="n">
+        <v>1790</v>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0169.png</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr"/>
+      <c r="D1792" t="inlineStr"/>
+      <c r="E1792" t="inlineStr"/>
+      <c r="F1792" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCOCCN(C)C)cc(O)c6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1792" t="inlineStr"/>
+      <c r="H1792" t="inlineStr"/>
+      <c r="I1792" t="n">
+        <v>0.8925505129153195</v>
+      </c>
+      <c r="J1792" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1792" t="inlineStr"/>
+    </row>
+    <row r="1793">
+      <c r="A1793" s="1" t="n">
+        <v>1791</v>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0170.png</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr"/>
+      <c r="D1793" t="inlineStr"/>
+      <c r="E1793" t="inlineStr"/>
+      <c r="F1793" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCC7CCCN(C)C7)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1793" t="inlineStr"/>
+      <c r="H1793" t="inlineStr"/>
+      <c r="I1793" t="n">
+        <v>0.9028196903080433</v>
+      </c>
+      <c r="J1793" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1793" t="inlineStr"/>
+    </row>
+    <row r="1794">
+      <c r="A1794" s="1" t="n">
+        <v>1792</v>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0172.png</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr"/>
+      <c r="D1794" t="inlineStr"/>
+      <c r="E1794" t="inlineStr"/>
+      <c r="F1794" t="inlineStr">
+        <is>
+          <t>COc1ccc(CCN(CCOCCNc2cccc3c2C(=O)N(C2CCC(=O)NC2=O)C3=O)Cc2ccc(OCc3ccc(Cl)nc3)c(OC)c2)cc1OC</t>
+        </is>
+      </c>
+      <c r="G1794" t="inlineStr"/>
+      <c r="H1794" t="inlineStr"/>
+      <c r="I1794" t="n">
+        <v>0.9138843826444728</v>
+      </c>
+      <c r="J1794" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1794" t="inlineStr"/>
+    </row>
+    <row r="1795">
+      <c r="A1795" s="1" t="n">
+        <v>1793</v>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0173.png</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr"/>
+      <c r="D1795" t="inlineStr"/>
+      <c r="E1795" t="inlineStr"/>
+      <c r="F1795" t="inlineStr">
+        <is>
+          <t>CN(CCOc1cc(C(=O)O)cc2c1nc(Cc1ccc3cc1COCCc1cc(Cl)ccc1COc1cccc-3n1)n2C[C@@H]1CCO1)C(=O)OC(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G1795" t="inlineStr"/>
+      <c r="H1795" t="inlineStr"/>
+      <c r="I1795" t="n">
+        <v>0.8779687317387704</v>
+      </c>
+      <c r="J1795" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1795" t="inlineStr"/>
+    </row>
+    <row r="1796">
+      <c r="A1796" s="1" t="n">
+        <v>1794</v>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0174.png</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr"/>
+      <c r="D1796" t="inlineStr"/>
+      <c r="E1796" t="inlineStr"/>
+      <c r="F1796" t="inlineStr">
+        <is>
+          <t>CC(C)c1cnn2c(NCc3ccccc3-c3nccc4cc(N5CCC(CN6CCN(c7cc8c(cc7F)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)ccc34)nc(O[C@@H]3CCCNC3)nc12</t>
+        </is>
+      </c>
+      <c r="G1796" t="inlineStr"/>
+      <c r="H1796" t="inlineStr"/>
+      <c r="I1796" t="n">
+        <v>0.8766044480162879</v>
+      </c>
+      <c r="J1796" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1796" t="inlineStr"/>
+    </row>
+    <row r="1797">
+      <c r="A1797" s="1" t="n">
+        <v>1795</v>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0175.png</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr"/>
+      <c r="D1797" t="inlineStr"/>
+      <c r="E1797" t="inlineStr"/>
+      <c r="F1797" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCCN)NC(=O)[C@H](CCCN)NCc2cccnc2Sc2c(Cl)ccc(-c3ccc(C(=O)O)cc3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G1797" t="inlineStr"/>
+      <c r="H1797" t="inlineStr"/>
+      <c r="I1797" t="n">
+        <v>0.8904165011997766</v>
+      </c>
+      <c r="J1797" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1797" t="inlineStr"/>
+    </row>
+    <row r="1798">
+      <c r="A1798" s="1" t="n">
+        <v>1796</v>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0176.png</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr"/>
+      <c r="D1798" t="inlineStr"/>
+      <c r="E1798" t="inlineStr"/>
+      <c r="F1798" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)[C@H]4C[C@@H](C(=O)N[C@@H](C(=O)N5C[C@H](O)C[C@@H]5C(=O)N[C@@H](C)c5ccc(-c6scnc6C)cc5)C(C)(C)C)C4)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1798" t="inlineStr"/>
+      <c r="H1798" t="inlineStr"/>
+      <c r="I1798" t="n">
+        <v>0.8881256975318474</v>
+      </c>
+      <c r="J1798" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1798" t="inlineStr"/>
+    </row>
+    <row r="1799">
+      <c r="A1799" s="1" t="n">
+        <v>1797</v>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0177.png</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr"/>
+      <c r="D1799" t="inlineStr"/>
+      <c r="E1799" t="inlineStr"/>
+      <c r="F1799" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)c4cnc(C(=O)N[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)N[C@@H](C)c5ccc(-c6scnc6C)cc5)C(C)C)cn4)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1799" t="inlineStr"/>
+      <c r="H1799" t="inlineStr"/>
+      <c r="I1799" t="n">
+        <v>0.8731453405423427</v>
+      </c>
+      <c r="J1799" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1799" t="inlineStr"/>
+    </row>
+    <row r="1800">
+      <c r="A1800" s="1" t="n">
+        <v>1798</v>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0181.png</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr"/>
+      <c r="D1800" t="inlineStr"/>
+      <c r="E1800" t="inlineStr"/>
+      <c r="F1800" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCN(C)C)cc(SC)c6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1800" t="inlineStr"/>
+      <c r="H1800" t="inlineStr"/>
+      <c r="I1800" t="n">
+        <v>0.8759651474609226</v>
+      </c>
+      <c r="J1800" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1800" t="inlineStr"/>
+    </row>
+    <row r="1801">
+      <c r="A1801" s="1" t="n">
+        <v>1799</v>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0183.png</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr"/>
+      <c r="D1801" t="inlineStr"/>
+      <c r="E1801" t="inlineStr"/>
+      <c r="F1801" t="inlineStr">
+        <is>
+          <t>COC(=O)c1cc(NC[C@@H]2CCO2)c(NC(=O)Cc2ccc3cc2COCCc2cc(Cl)ccc2COc2cccc-3n2)c(OCCN(C)C(=O)OC(C)(C)C)c1</t>
+        </is>
+      </c>
+      <c r="G1801" t="inlineStr"/>
+      <c r="H1801" t="inlineStr"/>
+      <c r="I1801" t="n">
+        <v>0.8944119519992774</v>
+      </c>
+      <c r="J1801" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1801" t="inlineStr"/>
+    </row>
+    <row r="1802">
+      <c r="A1802" s="1" t="n">
+        <v>1800</v>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0184.png</t>
+        </is>
+      </c>
+      <c r="C1802" t="inlineStr"/>
+      <c r="D1802" t="inlineStr"/>
+      <c r="E1802" t="inlineStr"/>
+      <c r="F1802" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)c2csc(N3CCN(c4cc(-c5ccccc5O)nnc4N)CC3)n2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1802" t="inlineStr"/>
+      <c r="H1802" t="inlineStr"/>
+      <c r="I1802" t="n">
+        <v>0.8943015243906124</v>
+      </c>
+      <c r="J1802" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1802" t="inlineStr"/>
+    </row>
+    <row r="1803">
+      <c r="A1803" s="1" t="n">
+        <v>1801</v>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0185.png</t>
+        </is>
+      </c>
+      <c r="C1803" t="inlineStr"/>
+      <c r="D1803" t="inlineStr"/>
+      <c r="E1803" t="inlineStr"/>
+      <c r="F1803" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)CN[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1803" t="inlineStr"/>
+      <c r="H1803" t="inlineStr"/>
+      <c r="I1803" t="n">
+        <v>0.8762426746106197</v>
+      </c>
+      <c r="J1803" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1803" t="inlineStr"/>
+    </row>
+    <row r="1804">
+      <c r="A1804" s="1" t="n">
+        <v>1802</v>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0186.png</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr"/>
+      <c r="D1804" t="inlineStr"/>
+      <c r="E1804" t="inlineStr"/>
+      <c r="F1804" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCOCCN(C)C)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1804" t="inlineStr"/>
+      <c r="H1804" t="inlineStr"/>
+      <c r="I1804" t="n">
+        <v>0.8926495640948178</v>
+      </c>
+      <c r="J1804" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1804" t="inlineStr"/>
+    </row>
+    <row r="1805">
+      <c r="A1805" s="1" t="n">
+        <v>1803</v>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0187.png</t>
+        </is>
+      </c>
+      <c r="C1805" t="inlineStr"/>
+      <c r="D1805" t="inlineStr"/>
+      <c r="E1805" t="inlineStr"/>
+      <c r="F1805" t="inlineStr">
+        <is>
+          <t>Cc1cc(-c2ncnc3[nH]c(-c4ccc(C5CCN(CCCC6CN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)CC5)cc4)cc23)ccc1CNC(=O)c1nc(C(C)(C)C)no1</t>
+        </is>
+      </c>
+      <c r="G1805" t="inlineStr"/>
+      <c r="H1805" t="inlineStr"/>
+      <c r="I1805" t="n">
+        <v>0.8475143245797137</v>
+      </c>
+      <c r="J1805" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1805" t="inlineStr"/>
+    </row>
+    <row r="1806">
+      <c r="A1806" s="1" t="n">
+        <v>1804</v>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0189.png</t>
+        </is>
+      </c>
+      <c r="C1806" t="inlineStr"/>
+      <c r="D1806" t="inlineStr"/>
+      <c r="E1806" t="inlineStr"/>
+      <c r="F1806" t="inlineStr">
+        <is>
+          <t>NC(=O)c1c(-c2ccc(Oc3ccccc3)cc2)nn2c1Nc1ccc(C(=O)NC3CCN(CC4CCN(c5cc6c(cc5F)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)CC3)cc1CC2</t>
+        </is>
+      </c>
+      <c r="G1806" t="inlineStr"/>
+      <c r="H1806" t="inlineStr"/>
+      <c r="I1806" t="n">
+        <v>0.8915134122491665</v>
+      </c>
+      <c r="J1806" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1806" t="inlineStr"/>
+    </row>
+    <row r="1807">
+      <c r="A1807" s="1" t="n">
+        <v>1805</v>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0190.png</t>
+        </is>
+      </c>
+      <c r="C1807" t="inlineStr"/>
+      <c r="D1807" t="inlineStr"/>
+      <c r="E1807" t="inlineStr"/>
+      <c r="F1807" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCN)NC(=O)[C@H](CCCN)NCc2cccnc2Sc2c(Cl)ccc(-c3ccc(C(=O)O)cc3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G1807" t="inlineStr"/>
+      <c r="H1807" t="inlineStr"/>
+      <c r="I1807" t="n">
+        <v>0.8964843053195026</v>
+      </c>
+      <c r="J1807" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1807" t="inlineStr"/>
+    </row>
+    <row r="1808">
+      <c r="A1808" s="1" t="n">
+        <v>1806</v>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0191.png</t>
+        </is>
+      </c>
+      <c r="C1808" t="inlineStr"/>
+      <c r="D1808" t="inlineStr"/>
+      <c r="E1808" t="inlineStr"/>
+      <c r="F1808" t="inlineStr">
+        <is>
+          <t>Cc1cnc(Nc2cc(C3CCN(C(=O)c4cnc(C(=O)Nc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)cn4)CC3)cc(N3CCC(F)(F)C3)n2)cn1</t>
+        </is>
+      </c>
+      <c r="G1808" t="inlineStr"/>
+      <c r="H1808" t="inlineStr"/>
+      <c r="I1808" t="n">
+        <v>0.8970650205306012</v>
+      </c>
+      <c r="J1808" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1808" t="inlineStr"/>
+    </row>
+    <row r="1809">
+      <c r="A1809" s="1" t="n">
+        <v>1807</v>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0192.png</t>
+        </is>
+      </c>
+      <c r="C1809" t="inlineStr"/>
+      <c r="D1809" t="inlineStr"/>
+      <c r="E1809" t="inlineStr"/>
+      <c r="F1809" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)[C@@H]4CC[C@@H]4C(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1809" t="inlineStr"/>
+      <c r="H1809" t="inlineStr"/>
+      <c r="I1809" t="n">
+        <v>0.8901290210565896</v>
+      </c>
+      <c r="J1809" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1809" t="inlineStr"/>
+    </row>
+    <row r="1810">
+      <c r="A1810" s="1" t="n">
+        <v>1808</v>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0196.png</t>
+        </is>
+      </c>
+      <c r="C1810" t="inlineStr"/>
+      <c r="D1810" t="inlineStr"/>
+      <c r="E1810" t="inlineStr"/>
+      <c r="F1810" t="inlineStr">
+        <is>
+          <t>NC(=O)CN1CCN(CC(N)=O)CCN(CC(=O)NCC2CCC(C(=O)NC(Cc3ccc4ccccc4c3)C(=O)NCCCCC(NC(=O)NC(CCC(=O)O)C(=O)O)C(=O)O)CC2)CCN(CC(N)=O)CC1</t>
+        </is>
+      </c>
+      <c r="G1810" t="inlineStr"/>
+      <c r="H1810" t="inlineStr"/>
+      <c r="I1810" t="n">
+        <v>0.8865682031703374</v>
+      </c>
+      <c r="J1810" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1810" t="inlineStr"/>
+    </row>
+    <row r="1811">
+      <c r="A1811" s="1" t="n">
+        <v>1809</v>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0197.png</t>
+        </is>
+      </c>
+      <c r="C1811" t="inlineStr"/>
+      <c r="D1811" t="inlineStr"/>
+      <c r="E1811" t="inlineStr"/>
+      <c r="F1811" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(O)cc(F)c6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1811" t="inlineStr"/>
+      <c r="H1811" t="inlineStr"/>
+      <c r="I1811" t="n">
+        <v>0.8936711567255069</v>
+      </c>
+      <c r="J1811" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1811" t="inlineStr"/>
+    </row>
+    <row r="1812">
+      <c r="A1812" s="1" t="n">
+        <v>1810</v>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0199.png</t>
+        </is>
+      </c>
+      <c r="C1812" t="inlineStr"/>
+      <c r="D1812" t="inlineStr"/>
+      <c r="E1812" t="inlineStr"/>
+      <c r="F1812" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)c4ccc(CN[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)N[C@@H](C)c5ccc(-c6scnc6C)cc5)C(C)(C)C)cc4)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1812" t="inlineStr"/>
+      <c r="H1812" t="inlineStr"/>
+      <c r="I1812" t="n">
+        <v>0.9021786926100969</v>
+      </c>
+      <c r="J1812" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1812" t="inlineStr"/>
+    </row>
+    <row r="1813">
+      <c r="A1813" s="1" t="n">
+        <v>1811</v>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0200.png</t>
+        </is>
+      </c>
+      <c r="C1813" t="inlineStr"/>
+      <c r="D1813" t="inlineStr"/>
+      <c r="E1813" t="inlineStr"/>
+      <c r="F1813" t="inlineStr">
+        <is>
+          <t>NC(=O)c1c(-c2ccc(Oc3ccccc3)cc2)nn2c1Nc1ccc(C(=O)N[C@@H]3CC[C@@H](CN4CCN(c5cc6c(cc5F)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)CC3)cc1CC2</t>
+        </is>
+      </c>
+      <c r="G1813" t="inlineStr"/>
+      <c r="H1813" t="inlineStr"/>
+      <c r="I1813" t="n">
+        <v>0.8939187520780157</v>
+      </c>
+      <c r="J1813" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1813" t="inlineStr"/>
+    </row>
+    <row r="1814">
+      <c r="A1814" s="1" t="n">
+        <v>1812</v>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0201.png</t>
+        </is>
+      </c>
+      <c r="C1814" t="inlineStr"/>
+      <c r="D1814" t="inlineStr"/>
+      <c r="E1814" t="inlineStr"/>
+      <c r="F1814" t="inlineStr">
+        <is>
+          <t>CN1CC[C@H]2CC[C@@H](C(=O)N[C@@H](CCC(N)=O)C(=O)NC(CCC(=O)N3CCC(C#Cc4cccc5c4CN(C4CCC(=O)NC4=O)C5=O)CC3)c3ccccc3)N2C(=O)[C@@H](NC(=O)c2cc3cc(C(F)(F)P(=O)(O)O)ccc3s2)C1</t>
+        </is>
+      </c>
+      <c r="G1814" t="inlineStr"/>
+      <c r="H1814" t="inlineStr"/>
+      <c r="I1814" t="n">
+        <v>0.845426429024724</v>
+      </c>
+      <c r="J1814" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1814" t="inlineStr"/>
+    </row>
+    <row r="1815">
+      <c r="A1815" s="1" t="n">
+        <v>1813</v>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0203.png</t>
+        </is>
+      </c>
+      <c r="C1815" t="inlineStr"/>
+      <c r="D1815" t="inlineStr"/>
+      <c r="E1815" t="inlineStr"/>
+      <c r="F1815" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCNC(=O)OC(C)(C)C)NC(=O)[C@H](CCCNC(=O)OC(C)(C)C)NCc2cccnc2Sc2c(Cl)ccc(Br)c2CNC(=O)[C@@H]1Cc1cn(C(=O)OC(C)(C)C)c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G1815" t="inlineStr"/>
+      <c r="H1815" t="inlineStr"/>
+      <c r="I1815" t="n">
+        <v>0.8953788666047585</v>
+      </c>
+      <c r="J1815" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1815" t="inlineStr"/>
+    </row>
+    <row r="1816">
+      <c r="A1816" s="1" t="n">
+        <v>1814</v>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0205.png</t>
+        </is>
+      </c>
+      <c r="C1816" t="inlineStr"/>
+      <c r="D1816" t="inlineStr"/>
+      <c r="E1816" t="inlineStr"/>
+      <c r="F1816" t="inlineStr">
+        <is>
+          <t>NC(=O)c1c(-c2ccc(Oc3ccccc3)cc2)nn2c1Nc1ccc(C(=O)N3CCN(CC4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)CC3)cc1CC2</t>
+        </is>
+      </c>
+      <c r="G1816" t="inlineStr"/>
+      <c r="H1816" t="inlineStr"/>
+      <c r="I1816" t="n">
+        <v>0.8770286103694482</v>
+      </c>
+      <c r="J1816" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1816" t="inlineStr"/>
+    </row>
+    <row r="1817">
+      <c r="A1817" s="1" t="n">
+        <v>1815</v>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0206.png</t>
+        </is>
+      </c>
+      <c r="C1817" t="inlineStr"/>
+      <c r="D1817" t="inlineStr"/>
+      <c r="E1817" t="inlineStr"/>
+      <c r="F1817" t="inlineStr">
+        <is>
+          <t>Cc1[nH]c2ccccc2c1C[C@H]1C(=O)NCc2c(-c3ccc(C(=O)O)cc3)ccc(Cl)c2Sc2ncccc2CN[C@@H](CCCN)C(=O)N[C@@H](CCCCN)C(=O)N1C</t>
+        </is>
+      </c>
+      <c r="G1817" t="inlineStr"/>
+      <c r="H1817" t="inlineStr"/>
+      <c r="I1817" t="n">
+        <v>0.9082435204872276</v>
+      </c>
+      <c r="J1817" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1817" t="inlineStr"/>
+    </row>
+    <row r="1818">
+      <c r="A1818" s="1" t="n">
+        <v>1816</v>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0207.png</t>
+        </is>
+      </c>
+      <c r="C1818" t="inlineStr"/>
+      <c r="D1818" t="inlineStr"/>
+      <c r="E1818" t="inlineStr"/>
+      <c r="F1818" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2ccc3c(c2)CCCOc2cc(ccc2Cc2nc4ccc(C(=O)O)cc4n2C[C@@H]2CCO2)-c2cccc(n2)OC3)ccn1</t>
+        </is>
+      </c>
+      <c r="G1818" t="inlineStr"/>
+      <c r="H1818" t="inlineStr"/>
+      <c r="I1818" t="n">
+        <v>0.8825812792317952</v>
+      </c>
+      <c r="J1818" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1818" t="inlineStr"/>
+    </row>
+    <row r="1819">
+      <c r="A1819" s="1" t="n">
+        <v>1817</v>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0208.png</t>
+        </is>
+      </c>
+      <c r="C1819" t="inlineStr"/>
+      <c r="D1819" t="inlineStr"/>
+      <c r="E1819" t="inlineStr"/>
+      <c r="F1819" t="inlineStr">
+        <is>
+          <t>NC(=O)c1c(-c2ccc(Oc3ccccc3)cc2)nn2c1Nc1ccc(C(=O)N3CCC(CN4CCN(c5cc6c(cc5F)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)CC3)cc1CC2</t>
+        </is>
+      </c>
+      <c r="G1819" t="inlineStr"/>
+      <c r="H1819" t="inlineStr"/>
+      <c r="I1819" t="n">
+        <v>0.872482261620968</v>
+      </c>
+      <c r="J1819" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1819" t="inlineStr"/>
+    </row>
+    <row r="1820">
+      <c r="A1820" s="1" t="n">
+        <v>1818</v>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0209.png</t>
+        </is>
+      </c>
+      <c r="C1820" t="inlineStr"/>
+      <c r="D1820" t="inlineStr"/>
+      <c r="E1820" t="inlineStr"/>
+      <c r="F1820" t="inlineStr">
+        <is>
+          <t>COc1cc(C(=O)NS(=O)(=O)CC2CC2)cc2c1nc(Cc1cc(C)c3cc1OCCCc1cc(F)ccc1COc1cccc-3n1)n2C[C@@H]1CCO1</t>
+        </is>
+      </c>
+      <c r="G1820" t="inlineStr"/>
+      <c r="H1820" t="inlineStr"/>
+      <c r="I1820" t="n">
+        <v>0.8983863462880408</v>
+      </c>
+      <c r="J1820" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1820" t="inlineStr"/>
+    </row>
+    <row r="1821">
+      <c r="A1821" s="1" t="n">
+        <v>1819</v>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0211.png</t>
+        </is>
+      </c>
+      <c r="C1821" t="inlineStr"/>
+      <c r="D1821" t="inlineStr"/>
+      <c r="E1821" t="inlineStr"/>
+      <c r="F1821" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCN7CCCCC7)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1821" t="inlineStr"/>
+      <c r="H1821" t="inlineStr"/>
+      <c r="I1821" t="n">
+        <v>0.8959538706212233</v>
+      </c>
+      <c r="J1821" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1821" t="inlineStr"/>
+    </row>
+    <row r="1822">
+      <c r="A1822" s="1" t="n">
+        <v>1820</v>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0213.png</t>
+        </is>
+      </c>
+      <c r="C1822" t="inlineStr"/>
+      <c r="D1822" t="inlineStr"/>
+      <c r="E1822" t="inlineStr"/>
+      <c r="F1822" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(c3C2=O)C(=O)C=C(NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C)C4=O</t>
+        </is>
+      </c>
+      <c r="G1822" t="inlineStr"/>
+      <c r="H1822" t="inlineStr"/>
+      <c r="I1822" t="n">
+        <v>0.8658190715344175</v>
+      </c>
+      <c r="J1822" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1822" t="inlineStr"/>
+    </row>
+    <row r="1823">
+      <c r="A1823" s="1" t="n">
+        <v>1821</v>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0216.png</t>
+        </is>
+      </c>
+      <c r="C1823" t="inlineStr"/>
+      <c r="D1823" t="inlineStr"/>
+      <c r="E1823" t="inlineStr"/>
+      <c r="F1823" t="inlineStr">
+        <is>
+          <t>NC(=O)c1ncc(N2CCCCC2)nc1Nc1ccc(C2CCN(CCCCN(CCC3CCN(C[C@@H]4CC[C@@H](n5cc(NC(=O)c6cnn7ccc(N8CCOCC8)nc67)c(C(F)F)n5)CC4)CC3)c3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)CC2)cc1</t>
+        </is>
+      </c>
+      <c r="G1823" t="inlineStr"/>
+      <c r="H1823" t="inlineStr"/>
+      <c r="I1823" t="n">
+        <v>0.8993106927911703</v>
+      </c>
+      <c r="J1823" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1823" t="inlineStr"/>
+    </row>
+    <row r="1824">
+      <c r="A1824" s="1" t="n">
+        <v>1822</v>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0218.png</t>
+        </is>
+      </c>
+      <c r="C1824" t="inlineStr"/>
+      <c r="D1824" t="inlineStr"/>
+      <c r="E1824" t="inlineStr"/>
+      <c r="F1824" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccc2c(c1)CCCOc1cc(ccc1Cc1nc3c(OCC(=O)N(C)C)cc(C(=O)O)cc3n1C[C@@H]1CCO1)-c1cccc(n1)OC2</t>
+        </is>
+      </c>
+      <c r="G1824" t="inlineStr"/>
+      <c r="H1824" t="inlineStr"/>
+      <c r="I1824" t="n">
+        <v>0.8698908539938425</v>
+      </c>
+      <c r="J1824" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1824" t="inlineStr"/>
+    </row>
+    <row r="1825">
+      <c r="A1825" s="1" t="n">
+        <v>1823</v>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0219.png</t>
+        </is>
+      </c>
+      <c r="C1825" t="inlineStr"/>
+      <c r="D1825" t="inlineStr"/>
+      <c r="E1825" t="inlineStr"/>
+      <c r="F1825" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCN)NC(=O)[C@H](CCCN)NCc2cccnc2Sc2c(Cl)ccc(-c3ccc(C(=O)O)cc3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G1825" t="inlineStr"/>
+      <c r="H1825" t="inlineStr"/>
+      <c r="I1825" t="n">
+        <v>0.8862883111479054</v>
+      </c>
+      <c r="J1825" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1825" t="inlineStr"/>
+    </row>
+    <row r="1826">
+      <c r="A1826" s="1" t="n">
+        <v>1824</v>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0221.png</t>
+        </is>
+      </c>
+      <c r="C1826" t="inlineStr"/>
+      <c r="D1826" t="inlineStr"/>
+      <c r="E1826" t="inlineStr"/>
+      <c r="F1826" t="inlineStr">
+        <is>
+          <t>CC(C)c1cnn2c(NCc3ccccc3-c3nccc4cc(NC(=O)/C=C/CN(C)CCOCCOCCOCCNC(=O)CNc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)ccc34)nc(N3CCC(N)CC3)nc12</t>
+        </is>
+      </c>
+      <c r="G1826" t="inlineStr"/>
+      <c r="H1826" t="inlineStr"/>
+      <c r="I1826" t="n">
+        <v>0.888811140587797</v>
+      </c>
+      <c r="J1826" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1826" t="inlineStr"/>
+    </row>
+    <row r="1827">
+      <c r="A1827" s="1" t="n">
+        <v>1825</v>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0227.png</t>
+        </is>
+      </c>
+      <c r="C1827" t="inlineStr"/>
+      <c r="D1827" t="inlineStr"/>
+      <c r="E1827" t="inlineStr"/>
+      <c r="F1827" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2cc3c(cc2OC)C2(OC3=O)c3cc(-c4ccccc4)c(OC(C)=O)cc3Oc3cc(OC(C)=O)c(-c4ccccc4)cc32)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1827" t="inlineStr"/>
+      <c r="H1827" t="inlineStr"/>
+      <c r="I1827" t="n">
+        <v>0.8860820415074333</v>
+      </c>
+      <c r="J1827" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1827" t="inlineStr"/>
+    </row>
+    <row r="1828">
+      <c r="A1828" s="1" t="n">
+        <v>1826</v>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0228.png</t>
+        </is>
+      </c>
+      <c r="C1828" t="inlineStr"/>
+      <c r="D1828" t="inlineStr"/>
+      <c r="E1828" t="inlineStr"/>
+      <c r="F1828" t="inlineStr">
+        <is>
+          <t>COCCOc1cc(C(=O)OC)cc2c1nc(Cc1cc(F)c3cc1CCOCc1cc(ccc1Cl)COc1cccc-3n1)n2C[C@H]1CCO1</t>
+        </is>
+      </c>
+      <c r="G1828" t="inlineStr"/>
+      <c r="H1828" t="inlineStr"/>
+      <c r="I1828" t="n">
+        <v>0.8813598458127065</v>
+      </c>
+      <c r="J1828" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1828" t="inlineStr"/>
+    </row>
+    <row r="1829">
+      <c r="A1829" s="1" t="n">
+        <v>1827</v>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0229.png</t>
+        </is>
+      </c>
+      <c r="C1829" t="inlineStr"/>
+      <c r="D1829" t="inlineStr"/>
+      <c r="E1829" t="inlineStr"/>
+      <c r="F1829" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCCNC(=O)OC(C)(C)C)NC(=O)[C@H](CCNC(=O)C(C)(C)C)NCc2cccnc2Sc2c(Cl)ccc(Br)c2CNC(=O)[C@@H]1Cc1cn(C(=O)OC(C)(C)C)c2ccccc12.[HH].[HH]</t>
+        </is>
+      </c>
+      <c r="G1829" t="inlineStr"/>
+      <c r="H1829" t="inlineStr"/>
+      <c r="I1829" t="n">
+        <v>0.8983537709777016</v>
+      </c>
+      <c r="J1829" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1829" t="inlineStr"/>
+    </row>
+    <row r="1830">
+      <c r="A1830" s="1" t="n">
+        <v>1828</v>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0232.png</t>
+        </is>
+      </c>
+      <c r="C1830" t="inlineStr"/>
+      <c r="D1830" t="inlineStr"/>
+      <c r="E1830" t="inlineStr"/>
+      <c r="F1830" t="inlineStr">
+        <is>
+          <t>COC(=O)c1cc(OCCO[Si](C)(C)C(C)(C)C)c2nc(Cc3ccc4cc3COCCc3cc(Cl)ccc3COc3cccc-4n3)n(C[C@@H]3CCO3)c2c1</t>
+        </is>
+      </c>
+      <c r="G1830" t="inlineStr"/>
+      <c r="H1830" t="inlineStr"/>
+      <c r="I1830" t="n">
+        <v>0.8976589131581323</v>
+      </c>
+      <c r="J1830" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1830" t="inlineStr"/>
+    </row>
+    <row r="1831">
+      <c r="A1831" s="1" t="n">
+        <v>1829</v>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0234.png</t>
+        </is>
+      </c>
+      <c r="C1831" t="inlineStr"/>
+      <c r="D1831" t="inlineStr"/>
+      <c r="E1831" t="inlineStr"/>
+      <c r="F1831" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2cc3c(cc2OC)C2(OC3=O)c3cc(F)c(OC(C)=O)cc3Oc3cc(OC(C)=O)c(F)cc32)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1831" t="inlineStr"/>
+      <c r="H1831" t="inlineStr"/>
+      <c r="I1831" t="n">
+        <v>0.8973909389775973</v>
+      </c>
+      <c r="J1831" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1831" t="inlineStr"/>
+    </row>
+    <row r="1832">
+      <c r="A1832" s="1" t="n">
+        <v>1830</v>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0235.png</t>
+        </is>
+      </c>
+      <c r="C1832" t="inlineStr"/>
+      <c r="D1832" t="inlineStr"/>
+      <c r="E1832" t="inlineStr"/>
+      <c r="F1832" t="inlineStr">
+        <is>
+          <t>N#C[C@@H]1CC(F)(F)CN1C(=O)CNC(=O)c1ccnc2c(NC(=O)CCC(=O)NCCNC(=O)CCC(C(=O)O)N3CCN(CC(=O)O)CCN(CC(=O)O)CCN(CC(=O)O)CC3)cccc12</t>
+        </is>
+      </c>
+      <c r="G1832" t="inlineStr"/>
+      <c r="H1832" t="inlineStr"/>
+      <c r="I1832" t="n">
+        <v>0.8740124077418417</v>
+      </c>
+      <c r="J1832" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1832" t="inlineStr"/>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="1" t="n">
+        <v>1831</v>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0238.png</t>
+        </is>
+      </c>
+      <c r="C1833" t="inlineStr"/>
+      <c r="D1833" t="inlineStr"/>
+      <c r="E1833" t="inlineStr"/>
+      <c r="F1833" t="inlineStr">
+        <is>
+          <t>Cc1ccc(S(=O)(=O)Nc2ccc(C[C@H](N)C(=O)N3CCC(CCC#Cc4cccc5c4CN(C4CCC(=O)NC4=O)C5=O)CC3)cc2)cc1</t>
+        </is>
+      </c>
+      <c r="G1833" t="inlineStr"/>
+      <c r="H1833" t="inlineStr"/>
+      <c r="I1833" t="n">
+        <v>0.8923162527711789</v>
+      </c>
+      <c r="J1833" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1833" t="inlineStr"/>
+    </row>
+    <row r="1834">
+      <c r="A1834" s="1" t="n">
+        <v>1832</v>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0239.png</t>
+        </is>
+      </c>
+      <c r="C1834" t="inlineStr"/>
+      <c r="D1834" t="inlineStr"/>
+      <c r="E1834" t="inlineStr"/>
+      <c r="F1834" t="inlineStr">
+        <is>
+          <t>Cc1[nH]c2ccccc2c1C[C@H]1C(=O)NCc2c(cccc2-c2ccc(C(=O)O)cc2)Sc2ncccc2CN[C@@H](CCCN)C(=O)N[C@@H](CCCCN)C(=O)N1C</t>
+        </is>
+      </c>
+      <c r="G1834" t="inlineStr"/>
+      <c r="H1834" t="inlineStr"/>
+      <c r="I1834" t="n">
+        <v>0.9116286421505283</v>
+      </c>
+      <c r="J1834" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1834" t="inlineStr"/>
+    </row>
+    <row r="1835">
+      <c r="A1835" s="1" t="n">
+        <v>1833</v>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0240.png</t>
+        </is>
+      </c>
+      <c r="C1835" t="inlineStr"/>
+      <c r="D1835" t="inlineStr"/>
+      <c r="E1835" t="inlineStr"/>
+      <c r="F1835" t="inlineStr">
+        <is>
+          <t>CN1CCC(CNC(=O)c2ccc(C[C@H](N)C(=O)N3CCC(CCC#Cc4cccc5c4CN(C4CCC(=O)NC4=O)C5=O)CC3)cc2)CC1</t>
+        </is>
+      </c>
+      <c r="G1835" t="inlineStr"/>
+      <c r="H1835" t="inlineStr"/>
+      <c r="I1835" t="n">
+        <v>0.8821742390197592</v>
+      </c>
+      <c r="J1835" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1835" t="inlineStr"/>
+    </row>
+    <row r="1836">
+      <c r="A1836" s="1" t="n">
+        <v>1834</v>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0241.png</t>
+        </is>
+      </c>
+      <c r="C1836" t="inlineStr"/>
+      <c r="D1836" t="inlineStr"/>
+      <c r="E1836" t="inlineStr"/>
+      <c r="F1836" t="inlineStr">
+        <is>
+          <t>COCCOc1cc(C(=O)OC)cc2c1nc(Cc1ccc3cc1COCCc1cc(ccc1C#N)COc1cccc-3n1)n2C[C@@H]1CCO1</t>
+        </is>
+      </c>
+      <c r="G1836" t="inlineStr"/>
+      <c r="H1836" t="inlineStr"/>
+      <c r="I1836" t="n">
+        <v>0.895511138065637</v>
+      </c>
+      <c r="J1836" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1836" t="inlineStr"/>
+    </row>
+    <row r="1837">
+      <c r="A1837" s="1" t="n">
+        <v>1835</v>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0242.png</t>
+        </is>
+      </c>
+      <c r="C1837" t="inlineStr"/>
+      <c r="D1837" t="inlineStr"/>
+      <c r="E1837" t="inlineStr"/>
+      <c r="F1837" t="inlineStr">
+        <is>
+          <t>COCCOc1cc(C(=O)OC)cc2c1nc(Cc1ccc3cc1COCCc1nc(ccc1C#N)COc1cccc-3n1)n2C[C@@H]1CCO1</t>
+        </is>
+      </c>
+      <c r="G1837" t="inlineStr"/>
+      <c r="H1837" t="inlineStr"/>
+      <c r="I1837" t="n">
+        <v>0.8627408265652562</v>
+      </c>
+      <c r="J1837" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1837" t="inlineStr"/>
+    </row>
+    <row r="1838">
+      <c r="A1838" s="1" t="n">
+        <v>1836</v>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0243.png</t>
+        </is>
+      </c>
+      <c r="C1838" t="inlineStr"/>
+      <c r="D1838" t="inlineStr"/>
+      <c r="E1838" t="inlineStr"/>
+      <c r="F1838" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCN(C)C)cc(S(C)(=O)=O)c6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1838" t="inlineStr"/>
+      <c r="H1838" t="inlineStr"/>
+      <c r="I1838" t="n">
+        <v>0.8732411923641403</v>
+      </c>
+      <c r="J1838" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1838" t="inlineStr"/>
+    </row>
+    <row r="1839">
+      <c r="A1839" s="1" t="n">
+        <v>1837</v>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0245.png</t>
+        </is>
+      </c>
+      <c r="C1839" t="inlineStr"/>
+      <c r="D1839" t="inlineStr"/>
+      <c r="E1839" t="inlineStr"/>
+      <c r="F1839" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCn7ccnc7)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1839" t="inlineStr"/>
+      <c r="H1839" t="inlineStr"/>
+      <c r="I1839" t="n">
+        <v>0.8955935207794978</v>
+      </c>
+      <c r="J1839" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1839" t="inlineStr"/>
+    </row>
+    <row r="1840">
+      <c r="A1840" s="1" t="n">
+        <v>1838</v>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0246.png</t>
+        </is>
+      </c>
+      <c r="C1840" t="inlineStr"/>
+      <c r="D1840" t="inlineStr"/>
+      <c r="E1840" t="inlineStr"/>
+      <c r="F1840" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCCN)NC(=O)[C@H](CCC(N)=O)NCc2cccnc2Sc2c(Cl)ccc(-c3ccc(C(=O)O)cc3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G1840" t="inlineStr"/>
+      <c r="H1840" t="inlineStr"/>
+      <c r="I1840" t="n">
+        <v>0.9060925574269924</v>
+      </c>
+      <c r="J1840" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1840" t="inlineStr"/>
+    </row>
+    <row r="1841">
+      <c r="A1841" s="1" t="n">
+        <v>1839</v>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0247.png</t>
+        </is>
+      </c>
+      <c r="C1841" t="inlineStr"/>
+      <c r="D1841" t="inlineStr"/>
+      <c r="E1841" t="inlineStr"/>
+      <c r="F1841" t="inlineStr">
+        <is>
+          <t>C[CH][C@H](O)[C@H](C)[C@@H](O)[C@@H](C)/C=C/C=C(/C)C(=O)Nc1c2oc3cc(OCCNC(C)=O)ccc3nc-2c2c3c(c(C)c(O)c2c1=O)O[C@](C)(O/C=C/[CH]OC)C3=O |^1:1,52|</t>
+        </is>
+      </c>
+      <c r="G1841" t="inlineStr"/>
+      <c r="H1841" t="inlineStr"/>
+      <c r="I1841" t="n">
+        <v>0.8871420559330476</v>
+      </c>
+      <c r="J1841" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1841" t="inlineStr"/>
+    </row>
+    <row r="1842">
+      <c r="A1842" s="1" t="n">
+        <v>1840</v>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0250.png</t>
+        </is>
+      </c>
+      <c r="C1842" t="inlineStr"/>
+      <c r="D1842" t="inlineStr"/>
+      <c r="E1842" t="inlineStr"/>
+      <c r="F1842" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2cc3c(cc2OC)C2(OC3=O)c3cc(OC)c(OC(C)=O)c(Cl)c3Oc3c2cc(OC)c(OC(C)=O)c3Cl)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1842" t="inlineStr"/>
+      <c r="H1842" t="inlineStr"/>
+      <c r="I1842" t="n">
+        <v>0.8620903665103316</v>
+      </c>
+      <c r="J1842" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1842" t="inlineStr"/>
+    </row>
+    <row r="1843">
+      <c r="A1843" s="1" t="n">
+        <v>1841</v>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0252.png</t>
+        </is>
+      </c>
+      <c r="C1843" t="inlineStr"/>
+      <c r="D1843" t="inlineStr"/>
+      <c r="E1843" t="inlineStr"/>
+      <c r="F1843" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5n(C)c6cc(O)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1843" t="inlineStr"/>
+      <c r="H1843" t="inlineStr"/>
+      <c r="I1843" t="n">
+        <v>0.8687157644785235</v>
+      </c>
+      <c r="J1843" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1843" t="inlineStr"/>
+    </row>
+    <row r="1844">
+      <c r="A1844" s="1" t="n">
+        <v>1842</v>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0254.png</t>
+        </is>
+      </c>
+      <c r="C1844" t="inlineStr"/>
+      <c r="D1844" t="inlineStr"/>
+      <c r="E1844" t="inlineStr"/>
+      <c r="F1844" t="inlineStr">
+        <is>
+          <t>O=C(O)c1ccc2nc(Cc3ccc4cc3OCCCc3cc(-c5cnn(C6COC6)c5)ccc3COc3cccc-4n3)n(C[C@@H]3CCO3)c2c1</t>
+        </is>
+      </c>
+      <c r="G1844" t="inlineStr"/>
+      <c r="H1844" t="inlineStr"/>
+      <c r="I1844" t="n">
+        <v>0.8904506807236929</v>
+      </c>
+      <c r="J1844" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1844" t="inlineStr"/>
+    </row>
+    <row r="1845">
+      <c r="A1845" s="1" t="n">
+        <v>1843</v>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0255.png</t>
+        </is>
+      </c>
+      <c r="C1845" t="inlineStr"/>
+      <c r="D1845" t="inlineStr"/>
+      <c r="E1845" t="inlineStr"/>
+      <c r="F1845" t="inlineStr">
+        <is>
+          <t>CC(C)c1cnn2c(NCc3ccccc3-c3nccc4cc(NC(=O)/C=C/CN(C)CCOCCNC(=O)CNc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)ccc34)nc(N3CCC(N)CC3)nc12</t>
+        </is>
+      </c>
+      <c r="G1845" t="inlineStr"/>
+      <c r="H1845" t="inlineStr"/>
+      <c r="I1845" t="n">
+        <v>0.892078137247225</v>
+      </c>
+      <c r="J1845" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1845" t="inlineStr"/>
+    </row>
+    <row r="1846">
+      <c r="A1846" s="1" t="n">
+        <v>1844</v>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0256.png</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr"/>
+      <c r="D1846" t="inlineStr"/>
+      <c r="E1846" t="inlineStr"/>
+      <c r="F1846" t="inlineStr">
+        <is>
+          <t>CC(C)(O)c1cc2nn(C3CCC(CN4CC5(CC(C(CNc6cccc7c6C(=O)N(C6CCC(=O)NC6=O)C7=O)CN6CCC(c7ccc(Nc8nc(N9CCCCC9)cnc8C(N)=O)cc7)CC6)C5)C4)CC3)cc2cc1NC(=O)c1cccc(C(F)(F)F)n1</t>
+        </is>
+      </c>
+      <c r="G1846" t="inlineStr"/>
+      <c r="H1846" t="inlineStr"/>
+      <c r="I1846" t="n">
+        <v>0.8763772623109352</v>
+      </c>
+      <c r="J1846" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1846" t="inlineStr"/>
+    </row>
+    <row r="1847">
+      <c r="A1847" s="1" t="n">
+        <v>1845</v>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0259.png</t>
+        </is>
+      </c>
+      <c r="C1847" t="inlineStr"/>
+      <c r="D1847" t="inlineStr"/>
+      <c r="E1847" t="inlineStr"/>
+      <c r="F1847" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCNC(=O)OC(C)(C)C)NC(=O)[C@H](CCNC(=O)C(C)(C)C)NCc2cccnc2Sc2c(Cl)ccc(Br)c2CNC(=O)[C@@H]1Cc1cn(C(=O)OC(C)(C)C)c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G1847" t="inlineStr"/>
+      <c r="H1847" t="inlineStr"/>
+      <c r="I1847" t="n">
+        <v>0.9010334931058321</v>
+      </c>
+      <c r="J1847" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1847" t="inlineStr"/>
+    </row>
+    <row r="1848">
+      <c r="A1848" s="1" t="n">
+        <v>1846</v>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0260.png</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr"/>
+      <c r="D1848" t="inlineStr"/>
+      <c r="E1848" t="inlineStr"/>
+      <c r="F1848" t="inlineStr">
+        <is>
+          <t>CN[C@@H](C)C(=O)N[C@H]1CN(S(=O)(=O)c2cccc(S(=O)(=O)N3CC[C@H]4CC[C@@H](C(=O)NC(c5ccccc5)c5ccccc5)N4C(=O)[C@@H](NC(=O)[C@H](C)NC)C3)c2)CC[C@H]2CC[C@@H](C(=O)NC(c3ccccc3)c3ccccc3)N2C1=O</t>
+        </is>
+      </c>
+      <c r="G1848" t="inlineStr"/>
+      <c r="H1848" t="inlineStr"/>
+      <c r="I1848" t="n">
+        <v>0.8686951276643128</v>
+      </c>
+      <c r="J1848" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1848" t="inlineStr"/>
+    </row>
+    <row r="1849">
+      <c r="A1849" s="1" t="n">
+        <v>1847</v>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0262.png</t>
+        </is>
+      </c>
+      <c r="C1849" t="inlineStr"/>
+      <c r="D1849" t="inlineStr"/>
+      <c r="E1849" t="inlineStr"/>
+      <c r="F1849" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCCCCCC(=O)N2CCC(c3cc(Nc4cnccn4)nc(N4CCC(F)(F)C4)c3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1849" t="inlineStr"/>
+      <c r="H1849" t="inlineStr"/>
+      <c r="I1849" t="n">
+        <v>0.887019591997399</v>
+      </c>
+      <c r="J1849" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1849" t="inlineStr"/>
+    </row>
+    <row r="1850">
+      <c r="A1850" s="1" t="n">
+        <v>1848</v>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0263.png</t>
+        </is>
+      </c>
+      <c r="C1850" t="inlineStr"/>
+      <c r="D1850" t="inlineStr"/>
+      <c r="E1850" t="inlineStr"/>
+      <c r="F1850" t="inlineStr">
+        <is>
+          <t>COc1ccc(-c2ccc(C(=O)O)cc2)c2c1Sc1ncccc1CN[C@@H](CCCN)C(=O)N[C@@H](CCCCN)C(=O)N(C)[C@@H](Cc1c[nH]c3ccccc13)C(=O)NC2</t>
+        </is>
+      </c>
+      <c r="G1850" t="inlineStr"/>
+      <c r="H1850" t="inlineStr"/>
+      <c r="I1850" t="n">
+        <v>0.8653530536302241</v>
+      </c>
+      <c r="J1850" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1850" t="inlineStr"/>
+    </row>
+    <row r="1851">
+      <c r="A1851" s="1" t="n">
+        <v>1849</v>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0264.png</t>
+        </is>
+      </c>
+      <c r="C1851" t="inlineStr"/>
+      <c r="D1851" t="inlineStr"/>
+      <c r="E1851" t="inlineStr"/>
+      <c r="F1851" t="inlineStr">
+        <is>
+          <t>Cc1cnc(Nc2cc(C3CCN(C(=O)COc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)cc(N3CCC(F)(F)C3)n2)cn1</t>
+        </is>
+      </c>
+      <c r="G1851" t="inlineStr"/>
+      <c r="H1851" t="inlineStr"/>
+      <c r="I1851" t="n">
+        <v>0.8901492951147394</v>
+      </c>
+      <c r="J1851" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1851" t="inlineStr"/>
+    </row>
+    <row r="1852">
+      <c r="A1852" s="1" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0268.png</t>
+        </is>
+      </c>
+      <c r="C1852" t="inlineStr"/>
+      <c r="D1852" t="inlineStr"/>
+      <c r="E1852" t="inlineStr"/>
+      <c r="F1852" t="inlineStr">
+        <is>
+          <t>CO[C@H]1C[C@@H]2CC[C@@H](C)[C@@](O)(O2)C(=O)C(=O)N2CCCC[C@H]2C(=O)O[C@H]([C@H](C)C[C@@H]2CC[C@H](n3cnnn3)[C@H](OC)C2)CC(=O)[C@H](C)/C=C(\C)[C@@H](O)[C@@H](OC)C(=O)[C@H](C)C[C@H](C)/C=C/C=C/C=C/1C</t>
+        </is>
+      </c>
+      <c r="G1852" t="inlineStr"/>
+      <c r="H1852" t="inlineStr"/>
+      <c r="I1852" t="n">
+        <v>0.8823610976819186</v>
+      </c>
+      <c r="J1852" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1852" t="inlineStr"/>
+    </row>
+    <row r="1853">
+      <c r="A1853" s="1" t="n">
+        <v>1851</v>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0269.png</t>
+        </is>
+      </c>
+      <c r="C1853" t="inlineStr"/>
+      <c r="D1853" t="inlineStr"/>
+      <c r="E1853" t="inlineStr"/>
+      <c r="F1853" t="inlineStr">
+        <is>
+          <t>NC(=O)c1c(-c2ccc(Oc3ccccc3)cc2)nn2c1Nc1ccc(NC(=O)C3CCN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)cc1CC2</t>
+        </is>
+      </c>
+      <c r="G1853" t="inlineStr"/>
+      <c r="H1853" t="inlineStr"/>
+      <c r="I1853" t="n">
+        <v>0.8922588532817833</v>
+      </c>
+      <c r="J1853" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1853" t="inlineStr"/>
+    </row>
+    <row r="1854">
+      <c r="A1854" s="1" t="n">
+        <v>1852</v>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0270.png</t>
+        </is>
+      </c>
+      <c r="C1854" t="inlineStr"/>
+      <c r="D1854" t="inlineStr"/>
+      <c r="E1854" t="inlineStr"/>
+      <c r="F1854" t="inlineStr">
+        <is>
+          <t>CC(C)c1cnn2c(NCc3ccccc3-c3nccc4c3C=CC(N3CCN(CC5CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)CC3)C4)nc(O[C@@H]3CCCNC3)nc12</t>
+        </is>
+      </c>
+      <c r="G1854" t="inlineStr"/>
+      <c r="H1854" t="inlineStr"/>
+      <c r="I1854" t="n">
+        <v>0.9028264859906784</v>
+      </c>
+      <c r="J1854" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1854" t="inlineStr"/>
+    </row>
+    <row r="1855">
+      <c r="A1855" s="1" t="n">
+        <v>1853</v>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0271.png</t>
+        </is>
+      </c>
+      <c r="C1855" t="inlineStr"/>
+      <c r="D1855" t="inlineStr"/>
+      <c r="E1855" t="inlineStr"/>
+      <c r="F1855" t="inlineStr">
+        <is>
+          <t>Cn1cc(-c2ccc3c(c2)CCCOc2cc(ccc2Cc2nc4ccc(C(=O)O)cc4n2C[C@@H]2CCO2)-c2cccc(n2)OC3)ccc1=O</t>
+        </is>
+      </c>
+      <c r="G1855" t="inlineStr"/>
+      <c r="H1855" t="inlineStr"/>
+      <c r="I1855" t="n">
+        <v>0.8748284702461027</v>
+      </c>
+      <c r="J1855" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1855" t="inlineStr"/>
+    </row>
+    <row r="1856">
+      <c r="A1856" s="1" t="n">
+        <v>1854</v>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0272.png</t>
+        </is>
+      </c>
+      <c r="C1856" t="inlineStr"/>
+      <c r="D1856" t="inlineStr"/>
+      <c r="E1856" t="inlineStr"/>
+      <c r="F1856" t="inlineStr">
+        <is>
+          <t>COCCOc1cc(C(=O)OC)cc2c1nc(Cc1cc(F)c3cc1COCCc1cc(ccc1C#N)COc1cccc-3n1)n2C[C@@H]1CCO1</t>
+        </is>
+      </c>
+      <c r="G1856" t="inlineStr"/>
+      <c r="H1856" t="inlineStr"/>
+      <c r="I1856" t="n">
+        <v>0.9039156002199558</v>
+      </c>
+      <c r="J1856" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1856" t="inlineStr"/>
+    </row>
+    <row r="1857">
+      <c r="A1857" s="1" t="n">
+        <v>1855</v>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0274.png</t>
+        </is>
+      </c>
+      <c r="C1857" t="inlineStr"/>
+      <c r="D1857" t="inlineStr"/>
+      <c r="E1857" t="inlineStr"/>
+      <c r="F1857" t="inlineStr">
+        <is>
+          <t>O=C(O)COC1=CC(C2=C3C=CC(C=CC4=CC=CC=C4)=N3Br(F)(F)N3C(C=CC4=CC=CC=C4)=CC=C23)=CC=C1N1CCOCCOCCN(C2=C(OCC(=O)O)C=CC=C2)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1857" t="inlineStr"/>
+      <c r="H1857" t="inlineStr"/>
+      <c r="I1857" t="n">
+        <v>0.8881617555437529</v>
+      </c>
+      <c r="J1857" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1857" t="inlineStr"/>
+    </row>
+    <row r="1858">
+      <c r="A1858" s="1" t="n">
+        <v>1856</v>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0277.png</t>
+        </is>
+      </c>
+      <c r="C1858" t="inlineStr"/>
+      <c r="D1858" t="inlineStr"/>
+      <c r="E1858" t="inlineStr"/>
+      <c r="F1858" t="inlineStr">
+        <is>
+          <t>CC(C)(O)c1cc2nc([C@@H]3CC[C@@H](CN4CCC(CCN(CCCCN5CCC(c6ccc(Nc7nc(N8CCCCC8)cnc7C(N)=O)cc6)CC5)c5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)CC3)sc2cc1NC(=O)c1cccc(C(F)(F)F)n1</t>
+        </is>
+      </c>
+      <c r="G1858" t="inlineStr"/>
+      <c r="H1858" t="inlineStr"/>
+      <c r="I1858" t="n">
+        <v>0.9032043512469488</v>
+      </c>
+      <c r="J1858" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1858" t="inlineStr"/>
+    </row>
+    <row r="1859">
+      <c r="A1859" s="1" t="n">
+        <v>1857</v>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0278.png</t>
+        </is>
+      </c>
+      <c r="C1859" t="inlineStr"/>
+      <c r="D1859" t="inlineStr"/>
+      <c r="E1859" t="inlineStr"/>
+      <c r="F1859" t="inlineStr">
+        <is>
+          <t>O=C(CCOCCOCCOCCOCCC(=O)N1CCC(c2cc(Nc3cc(C(F)(F)F)ccn3)nc(N3CCC(F)(F)C3)c2)CC1)NCCCCNC(=O)CNc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O</t>
+        </is>
+      </c>
+      <c r="G1859" t="inlineStr"/>
+      <c r="H1859" t="inlineStr"/>
+      <c r="I1859" t="n">
+        <v>0.8569970886044792</v>
+      </c>
+      <c r="J1859" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1859" t="inlineStr"/>
+    </row>
+    <row r="1860">
+      <c r="A1860" s="1" t="n">
+        <v>1858</v>
+      </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0279.png</t>
+        </is>
+      </c>
+      <c r="C1860" t="inlineStr"/>
+      <c r="D1860" t="inlineStr"/>
+      <c r="E1860" t="inlineStr"/>
+      <c r="F1860" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)[C@H]4CC[C@@H]4C(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1860" t="inlineStr"/>
+      <c r="H1860" t="inlineStr"/>
+      <c r="I1860" t="n">
+        <v>0.8922005901509127</v>
+      </c>
+      <c r="J1860" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1860" t="inlineStr"/>
+    </row>
+    <row r="1861">
+      <c r="A1861" s="1" t="n">
+        <v>1859</v>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0281.png</t>
+        </is>
+      </c>
+      <c r="C1861" t="inlineStr"/>
+      <c r="D1861" t="inlineStr"/>
+      <c r="E1861" t="inlineStr"/>
+      <c r="F1861" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)c4ccc(C(=O)N[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)N[C@@H](C)c5ccc(-c6scnc6C)cc5)C(C)(C)C)cc4)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1861" t="inlineStr"/>
+      <c r="H1861" t="inlineStr"/>
+      <c r="I1861" t="n">
+        <v>0.8851429028936981</v>
+      </c>
+      <c r="J1861" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1861" t="inlineStr"/>
+    </row>
+    <row r="1862">
+      <c r="A1862" s="1" t="n">
+        <v>1860</v>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0282.png</t>
+        </is>
+      </c>
+      <c r="C1862" t="inlineStr"/>
+      <c r="D1862" t="inlineStr"/>
+      <c r="E1862" t="inlineStr"/>
+      <c r="F1862" t="inlineStr">
+        <is>
+          <t>NC(=O)c1c(-c2ccc(Oc3ccccc3)cc2)nn2c1Nc1cc(C(=O)N3CCN(CC4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)CC3)ccc1CC2</t>
+        </is>
+      </c>
+      <c r="G1862" t="inlineStr"/>
+      <c r="H1862" t="inlineStr"/>
+      <c r="I1862" t="n">
+        <v>0.8768779745590215</v>
+      </c>
+      <c r="J1862" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1862" t="inlineStr"/>
+    </row>
+    <row r="1863">
+      <c r="A1863" s="1" t="n">
+        <v>1861</v>
+      </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0283.png</t>
+        </is>
+      </c>
+      <c r="C1863" t="inlineStr"/>
+      <c r="D1863" t="inlineStr"/>
+      <c r="E1863" t="inlineStr"/>
+      <c r="F1863" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(CCCCCCN[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1863" t="inlineStr"/>
+      <c r="H1863" t="inlineStr"/>
+      <c r="I1863" t="n">
+        <v>0.8866901792044894</v>
+      </c>
+      <c r="J1863" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1863" t="inlineStr"/>
+    </row>
+    <row r="1864">
+      <c r="A1864" s="1" t="n">
+        <v>1862</v>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0284.png</t>
+        </is>
+      </c>
+      <c r="C1864" t="inlineStr"/>
+      <c r="D1864" t="inlineStr"/>
+      <c r="E1864" t="inlineStr"/>
+      <c r="F1864" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCN(c2cc(C3=C4C=CC(=[N+](C)C)C=C4[Si](C)(C)c4cc(N(C)C)ccc43)c(C(=O)[O-])cc2OC)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1864" t="inlineStr"/>
+      <c r="H1864" t="inlineStr"/>
+      <c r="I1864" t="n">
+        <v>0.8959128187785722</v>
+      </c>
+      <c r="J1864" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1864" t="inlineStr"/>
+    </row>
+    <row r="1865">
+      <c r="A1865" s="1" t="n">
+        <v>1863</v>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0285.png</t>
+        </is>
+      </c>
+      <c r="C1865" t="inlineStr"/>
+      <c r="D1865" t="inlineStr"/>
+      <c r="E1865" t="inlineStr"/>
+      <c r="F1865" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCC7CCN(C)C7)cc(O)c6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1865" t="inlineStr"/>
+      <c r="H1865" t="inlineStr"/>
+      <c r="I1865" t="n">
+        <v>0.8788828533668392</v>
+      </c>
+      <c r="J1865" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1865" t="inlineStr"/>
+    </row>
+    <row r="1866">
+      <c r="A1866" s="1" t="n">
+        <v>1864</v>
+      </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0287.png</t>
+        </is>
+      </c>
+      <c r="C1866" t="inlineStr"/>
+      <c r="D1866" t="inlineStr"/>
+      <c r="E1866" t="inlineStr"/>
+      <c r="F1866" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccc2c(c1)CCCOc1cc(ccc1CC(=O)Nc1c(NC[C@H]3CCO3)cc(C(=O)OC)cc1OCCN(CC(F)(F)F)C(=O)OC(C)(C)C)-c1cccc(n1)OC2</t>
+        </is>
+      </c>
+      <c r="G1866" t="inlineStr"/>
+      <c r="H1866" t="inlineStr"/>
+      <c r="I1866" t="n">
+        <v>0.9034924523410569</v>
+      </c>
+      <c r="J1866" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1866" t="inlineStr"/>
+    </row>
+    <row r="1867">
+      <c r="A1867" s="1" t="n">
+        <v>1865</v>
+      </c>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0289.png</t>
+        </is>
+      </c>
+      <c r="C1867" t="inlineStr"/>
+      <c r="D1867" t="inlineStr"/>
+      <c r="E1867" t="inlineStr"/>
+      <c r="F1867" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCCN)NC(=O)[C@H](CCCN)NCc2cccnc2Sc2c(F)ccc(-c3ccc(C(=O)O)cc3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G1867" t="inlineStr"/>
+      <c r="H1867" t="inlineStr"/>
+      <c r="I1867" t="n">
+        <v>0.8959456555453144</v>
+      </c>
+      <c r="J1867" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1867" t="inlineStr"/>
+    </row>
+    <row r="1868">
+      <c r="A1868" s="1" t="n">
+        <v>1866</v>
+      </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0290.png</t>
+        </is>
+      </c>
+      <c r="C1868" t="inlineStr"/>
+      <c r="D1868" t="inlineStr"/>
+      <c r="E1868" t="inlineStr"/>
+      <c r="F1868" t="inlineStr">
+        <is>
+          <t>CC(C)c1cnn2c(NCc3ccccc3-c3nccc4cc(N5CCC(CN6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)ccc34)nc(O[C@@H]3CCCNC3)nc12</t>
+        </is>
+      </c>
+      <c r="G1868" t="inlineStr"/>
+      <c r="H1868" t="inlineStr"/>
+      <c r="I1868" t="n">
+        <v>0.8714307708154391</v>
+      </c>
+      <c r="J1868" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1868" t="inlineStr"/>
+    </row>
+    <row r="1869">
+      <c r="A1869" s="1" t="n">
+        <v>1867</v>
+      </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0291.png</t>
+        </is>
+      </c>
+      <c r="C1869" t="inlineStr"/>
+      <c r="D1869" t="inlineStr"/>
+      <c r="E1869" t="inlineStr"/>
+      <c r="F1869" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)c2cnc(C(=O)N3CCC(c4cc(Nc5cnccn5)nc(N5CCC(F)(F)C5)c4)CC3)cn2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1869" t="inlineStr"/>
+      <c r="H1869" t="inlineStr"/>
+      <c r="I1869" t="n">
+        <v>0.8966867677829597</v>
+      </c>
+      <c r="J1869" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1869" t="inlineStr"/>
+    </row>
+    <row r="1870">
+      <c r="A1870" s="1" t="n">
+        <v>1868</v>
+      </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0292.png</t>
+        </is>
+      </c>
+      <c r="C1870" t="inlineStr"/>
+      <c r="D1870" t="inlineStr"/>
+      <c r="E1870" t="inlineStr"/>
+      <c r="F1870" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CN2CCN(c3cc(-c4ccccc4O)nnc3N)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1870" t="inlineStr"/>
+      <c r="H1870" t="inlineStr"/>
+      <c r="I1870" t="n">
+        <v>0.8852395984020427</v>
+      </c>
+      <c r="J1870" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1870" t="inlineStr"/>
+    </row>
+    <row r="1871">
+      <c r="A1871" s="1" t="n">
+        <v>1869</v>
+      </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0293.png</t>
+        </is>
+      </c>
+      <c r="C1871" t="inlineStr"/>
+      <c r="D1871" t="inlineStr"/>
+      <c r="E1871" t="inlineStr"/>
+      <c r="F1871" t="inlineStr">
+        <is>
+          <t>CC(C)c1cnn2c(NCc3ccccc3-c3nccc4cc(NC(=O)/C=C/CNCCOCCOCCNC(=O)CNc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)ccc34)nc(N3CCC(N)CC3)nc12</t>
+        </is>
+      </c>
+      <c r="G1871" t="inlineStr"/>
+      <c r="H1871" t="inlineStr"/>
+      <c r="I1871" t="n">
+        <v>0.894083720269331</v>
+      </c>
+      <c r="J1871" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1871" t="inlineStr"/>
+    </row>
+    <row r="1872">
+      <c r="A1872" s="1" t="n">
+        <v>1870</v>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0296.png</t>
+        </is>
+      </c>
+      <c r="C1872" t="inlineStr"/>
+      <c r="D1872" t="inlineStr"/>
+      <c r="E1872" t="inlineStr"/>
+      <c r="F1872" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccc2c(c1)CCCOc1cc(ccc1Cc1nc3c(OC4CCN(C)C4)cc(C(=O)OC)cc3n1C[C@@H]1CCO1)-c1cccc(n1)OC2</t>
+        </is>
+      </c>
+      <c r="G1872" t="inlineStr"/>
+      <c r="H1872" t="inlineStr"/>
+      <c r="I1872" t="n">
+        <v>0.9030797539313467</v>
+      </c>
+      <c r="J1872" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1872" t="inlineStr"/>
+    </row>
+    <row r="1873">
+      <c r="A1873" s="1" t="n">
+        <v>1871</v>
+      </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0297.png</t>
+        </is>
+      </c>
+      <c r="C1873" t="inlineStr"/>
+      <c r="D1873" t="inlineStr"/>
+      <c r="E1873" t="inlineStr"/>
+      <c r="F1873" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCCN)NC(=O)[C@H](CCCN)NCc2nccnc2Sc2c(Cl)ccc(-c3ccc(C(=O)O)c(Cl)c3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G1873" t="inlineStr"/>
+      <c r="H1873" t="inlineStr"/>
+      <c r="I1873" t="n">
+        <v>0.8959412946662736</v>
+      </c>
+      <c r="J1873" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1873" t="inlineStr"/>
+    </row>
+    <row r="1874">
+      <c r="A1874" s="1" t="n">
+        <v>1872</v>
+      </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0298.png</t>
+        </is>
+      </c>
+      <c r="C1874" t="inlineStr"/>
+      <c r="D1874" t="inlineStr"/>
+      <c r="E1874" t="inlineStr"/>
+      <c r="F1874" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2ccc(C3=C4C=CC(c5ccsc5)=[N+]4[B-](F)(F)n4c3ccc4-c3cccs3)cc2OC)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1874" t="inlineStr"/>
+      <c r="H1874" t="inlineStr"/>
+      <c r="I1874" t="n">
+        <v>0.8981512823968641</v>
+      </c>
+      <c r="J1874" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1874" t="inlineStr"/>
+    </row>
+    <row r="1875">
+      <c r="A1875" s="1" t="n">
+        <v>1873</v>
+      </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0300.png</t>
+        </is>
+      </c>
+      <c r="C1875" t="inlineStr"/>
+      <c r="D1875" t="inlineStr"/>
+      <c r="E1875" t="inlineStr"/>
+      <c r="F1875" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCN7CCOCC7)cc(O)c6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1875" t="inlineStr"/>
+      <c r="H1875" t="inlineStr"/>
+      <c r="I1875" t="n">
+        <v>0.8729541865878038</v>
+      </c>
+      <c r="J1875" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1875" t="inlineStr"/>
+    </row>
+    <row r="1876">
+      <c r="A1876" s="1" t="n">
+        <v>1874</v>
+      </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0302.png</t>
+        </is>
+      </c>
+      <c r="C1876" t="inlineStr"/>
+      <c r="D1876" t="inlineStr"/>
+      <c r="E1876" t="inlineStr"/>
+      <c r="F1876" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCN)NC(=O)[C@H](CCCN)NCc2cccnc2Sc2c(F)ccc(-c3ccc(C(=O)O)nc3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G1876" t="inlineStr"/>
+      <c r="H1876" t="inlineStr"/>
+      <c r="I1876" t="n">
+        <v>0.8923639235173411</v>
+      </c>
+      <c r="J1876" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1876" t="inlineStr"/>
+    </row>
+    <row r="1877">
+      <c r="A1877" s="1" t="n">
+        <v>1875</v>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0303.png</t>
+        </is>
+      </c>
+      <c r="C1877" t="inlineStr"/>
+      <c r="D1877" t="inlineStr"/>
+      <c r="E1877" t="inlineStr"/>
+      <c r="F1877" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)[C@@H]4C[C@@H]4C(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1877" t="inlineStr"/>
+      <c r="H1877" t="inlineStr"/>
+      <c r="I1877" t="n">
+        <v>0.8993212450228709</v>
+      </c>
+      <c r="J1877" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1877" t="inlineStr"/>
+    </row>
+    <row r="1878">
+      <c r="A1878" s="1" t="n">
+        <v>1876</v>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0311.png</t>
+        </is>
+      </c>
+      <c r="C1878" t="inlineStr"/>
+      <c r="D1878" t="inlineStr"/>
+      <c r="E1878" t="inlineStr"/>
+      <c r="F1878" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCCN)NC(=O)[C@H](CCCN)NCc2cccnc2Sc2c(Cl)ccc(-c3ccc(C(=O)O)c(S(C)(=O)=O)c3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G1878" t="inlineStr"/>
+      <c r="H1878" t="inlineStr"/>
+      <c r="I1878" t="n">
+        <v>0.8776819532721607</v>
+      </c>
+      <c r="J1878" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1878" t="inlineStr"/>
+    </row>
+    <row r="1879">
+      <c r="A1879" s="1" t="n">
+        <v>1877</v>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0312.png</t>
+        </is>
+      </c>
+      <c r="C1879" t="inlineStr"/>
+      <c r="D1879" t="inlineStr"/>
+      <c r="E1879" t="inlineStr"/>
+      <c r="F1879" t="inlineStr">
+        <is>
+          <t>COc1cc2cc(c1OC)OCCCC(OC(=O)c1cc(Cl)c3cnn(Cc4ccccc4)c3c1)CCN1CCCN(CCCOC2=O)CC1</t>
+        </is>
+      </c>
+      <c r="G1879" t="inlineStr"/>
+      <c r="H1879" t="inlineStr"/>
+      <c r="I1879" t="n">
+        <v>0.9122290538689991</v>
+      </c>
+      <c r="J1879" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1879" t="inlineStr"/>
+    </row>
+    <row r="1880">
+      <c r="A1880" s="1" t="n">
+        <v>1878</v>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0315.png</t>
+        </is>
+      </c>
+      <c r="C1880" t="inlineStr"/>
+      <c r="D1880" t="inlineStr"/>
+      <c r="E1880" t="inlineStr"/>
+      <c r="F1880" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCN7CCOCC7)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1880" t="inlineStr"/>
+      <c r="H1880" t="inlineStr"/>
+      <c r="I1880" t="n">
+        <v>0.888994569840926</v>
+      </c>
+      <c r="J1880" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1880" t="inlineStr"/>
+    </row>
+    <row r="1881">
+      <c r="A1881" s="1" t="n">
+        <v>1879</v>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0316.png</t>
+        </is>
+      </c>
+      <c r="C1881" t="inlineStr"/>
+      <c r="D1881" t="inlineStr"/>
+      <c r="E1881" t="inlineStr"/>
+      <c r="F1881" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1881" t="inlineStr"/>
+      <c r="H1881" t="inlineStr"/>
+      <c r="I1881" t="n">
+        <v>0.853807921961285</v>
+      </c>
+      <c r="J1881" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1881" t="inlineStr"/>
+    </row>
+    <row r="1882">
+      <c r="A1882" s="1" t="n">
+        <v>1880</v>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0317.png</t>
+        </is>
+      </c>
+      <c r="C1882" t="inlineStr"/>
+      <c r="D1882" t="inlineStr"/>
+      <c r="E1882" t="inlineStr"/>
+      <c r="F1882" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)[C@@H]4CC[C@@H]4C(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1882" t="inlineStr"/>
+      <c r="H1882" t="inlineStr"/>
+      <c r="I1882" t="n">
+        <v>0.876555218355371</v>
+      </c>
+      <c r="J1882" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1882" t="inlineStr"/>
+    </row>
+    <row r="1883">
+      <c r="A1883" s="1" t="n">
+        <v>1881</v>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0318.png</t>
+        </is>
+      </c>
+      <c r="C1883" t="inlineStr"/>
+      <c r="D1883" t="inlineStr"/>
+      <c r="E1883" t="inlineStr"/>
+      <c r="F1883" t="inlineStr">
+        <is>
+          <t>Cc1cc(-c2ncnc3[nH]c(-c4ccc(C5CCN(CC6CCN(c7ccc8c(c7)CN(C7CCC(=O)NC7=O)C8=O)CC6)CC5)cc4)cc23)ccc1CNC(=O)c1nc(C(C)(C)C)no1</t>
+        </is>
+      </c>
+      <c r="G1883" t="inlineStr"/>
+      <c r="H1883" t="inlineStr"/>
+      <c r="I1883" t="n">
+        <v>0.8790419124287648</v>
+      </c>
+      <c r="J1883" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1883" t="inlineStr"/>
+    </row>
+    <row r="1884">
+      <c r="A1884" s="1" t="n">
+        <v>1882</v>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0321.png</t>
+        </is>
+      </c>
+      <c r="C1884" t="inlineStr"/>
+      <c r="D1884" t="inlineStr"/>
+      <c r="E1884" t="inlineStr"/>
+      <c r="F1884" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)c4cccc(CN[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)N[C@@H](C)c5ccc(-c6scnc6C)cc5)C(C)(C)C)c4)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1884" t="inlineStr"/>
+      <c r="H1884" t="inlineStr"/>
+      <c r="I1884" t="n">
+        <v>0.8633785271140404</v>
+      </c>
+      <c r="J1884" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1884" t="inlineStr"/>
+    </row>
+    <row r="1885">
+      <c r="A1885" s="1" t="n">
+        <v>1883</v>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0322.png</t>
+        </is>
+      </c>
+      <c r="C1885" t="inlineStr"/>
+      <c r="D1885" t="inlineStr"/>
+      <c r="E1885" t="inlineStr"/>
+      <c r="F1885" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(Br)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1885" t="inlineStr"/>
+      <c r="H1885" t="inlineStr"/>
+      <c r="I1885" t="n">
+        <v>0.8913975425739714</v>
+      </c>
+      <c r="J1885" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1885" t="inlineStr"/>
+    </row>
+    <row r="1886">
+      <c r="A1886" s="1" t="n">
+        <v>1884</v>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0323.png</t>
+        </is>
+      </c>
+      <c r="C1886" t="inlineStr"/>
+      <c r="D1886" t="inlineStr"/>
+      <c r="E1886" t="inlineStr"/>
+      <c r="F1886" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)c4cncc(C(=O)N[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)N[C@@H](C)c5ccc(-c6scnc6C)cc5)C(C)(C)C)c4)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1886" t="inlineStr"/>
+      <c r="H1886" t="inlineStr"/>
+      <c r="I1886" t="n">
+        <v>0.8834369905332535</v>
+      </c>
+      <c r="J1886" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1886" t="inlineStr"/>
+    </row>
+    <row r="1887">
+      <c r="A1887" s="1" t="n">
+        <v>1885</v>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0324.png</t>
+        </is>
+      </c>
+      <c r="C1887" t="inlineStr"/>
+      <c r="D1887" t="inlineStr"/>
+      <c r="E1887" t="inlineStr"/>
+      <c r="F1887" t="inlineStr">
+        <is>
+          <t>NC(=O)c1c(-c2ccc(Oc3ccccc3)cc2)nn2c1Nc1ccc(NC(=O)COCCOCCOCCOCCNc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)cc1CC2</t>
+        </is>
+      </c>
+      <c r="G1887" t="inlineStr"/>
+      <c r="H1887" t="inlineStr"/>
+      <c r="I1887" t="n">
+        <v>0.8721398559650142</v>
+      </c>
+      <c r="J1887" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1887" t="inlineStr"/>
+    </row>
+    <row r="1888">
+      <c r="A1888" s="1" t="n">
+        <v>1886</v>
+      </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0326.png</t>
+        </is>
+      </c>
+      <c r="C1888" t="inlineStr"/>
+      <c r="D1888" t="inlineStr"/>
+      <c r="E1888" t="inlineStr"/>
+      <c r="F1888" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)[C@H]4C[C@H]4C(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1888" t="inlineStr"/>
+      <c r="H1888" t="inlineStr"/>
+      <c r="I1888" t="n">
+        <v>0.8996855566791238</v>
+      </c>
+      <c r="J1888" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1888" t="inlineStr"/>
+    </row>
+    <row r="1889">
+      <c r="A1889" s="1" t="n">
+        <v>1887</v>
+      </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0328.png</t>
+        </is>
+      </c>
+      <c r="C1889" t="inlineStr"/>
+      <c r="D1889" t="inlineStr"/>
+      <c r="E1889" t="inlineStr"/>
+      <c r="F1889" t="inlineStr">
+        <is>
+          <t>Cc1cnc(Nc2cc(C3CCN(C4CC5(C4)CN(c4ccc6c(c4)C(=O)N(C4CCC(=O)NC4=O)C6=O)C5)CC3)cc(N3CCC(F)(F)C3)n2)cn1</t>
+        </is>
+      </c>
+      <c r="G1889" t="inlineStr"/>
+      <c r="H1889" t="inlineStr"/>
+      <c r="I1889" t="n">
+        <v>0.8873212995284203</v>
+      </c>
+      <c r="J1889" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1889" t="inlineStr"/>
+    </row>
+    <row r="1890">
+      <c r="A1890" s="1" t="n">
+        <v>1888</v>
+      </c>
+      <c r="B1890" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0330.png</t>
+        </is>
+      </c>
+      <c r="C1890" t="inlineStr"/>
+      <c r="D1890" t="inlineStr"/>
+      <c r="E1890" t="inlineStr"/>
+      <c r="F1890" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6ccc(Br)cc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1890" t="inlineStr"/>
+      <c r="H1890" t="inlineStr"/>
+      <c r="I1890" t="n">
+        <v>0.8769640720733435</v>
+      </c>
+      <c r="J1890" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1890" t="inlineStr"/>
+    </row>
+    <row r="1891">
+      <c r="A1891" s="1" t="n">
+        <v>1889</v>
+      </c>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0333.png</t>
+        </is>
+      </c>
+      <c r="C1891" t="inlineStr"/>
+      <c r="D1891" t="inlineStr"/>
+      <c r="E1891" t="inlineStr"/>
+      <c r="F1891" t="inlineStr">
+        <is>
+          <t>CCOP(=O)(O)C(F)(F)c1ccc2[nH]c(C(=O)N[C@H]3CN(CCOCCOCCOCCNc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)CC[C@H]4CC[C@@H](C(=O)NCCNC(N)=O)N4C3=O)cc2c1</t>
+        </is>
+      </c>
+      <c r="G1891" t="inlineStr"/>
+      <c r="H1891" t="inlineStr"/>
+      <c r="I1891" t="n">
+        <v>0.8788099186918795</v>
+      </c>
+      <c r="J1891" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1891" t="inlineStr"/>
+    </row>
+    <row r="1892">
+      <c r="A1892" s="1" t="n">
+        <v>1890</v>
+      </c>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0334.png</t>
+        </is>
+      </c>
+      <c r="C1892" t="inlineStr"/>
+      <c r="D1892" t="inlineStr"/>
+      <c r="E1892" t="inlineStr"/>
+      <c r="F1892" t="inlineStr">
+        <is>
+          <t>Cc1cc(-c2ncnc3[nH]c(-c4ccc(C5CCN(CC6CCN(c7cc8c(cc7F)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)cc4)cc23)ccc1CNC(=O)c1nc(C(C)(C)C)no1</t>
+        </is>
+      </c>
+      <c r="G1892" t="inlineStr"/>
+      <c r="H1892" t="inlineStr"/>
+      <c r="I1892" t="n">
+        <v>0.8996394718333315</v>
+      </c>
+      <c r="J1892" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1892" t="inlineStr"/>
+    </row>
+    <row r="1893">
+      <c r="A1893" s="1" t="n">
+        <v>1891</v>
+      </c>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0335.png</t>
+        </is>
+      </c>
+      <c r="C1893" t="inlineStr"/>
+      <c r="D1893" t="inlineStr"/>
+      <c r="E1893" t="inlineStr"/>
+      <c r="F1893" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCN(C)C)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1893" t="inlineStr"/>
+      <c r="H1893" t="inlineStr"/>
+      <c r="I1893" t="n">
+        <v>0.8820637082942988</v>
+      </c>
+      <c r="J1893" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1893" t="inlineStr"/>
+    </row>
+    <row r="1894">
+      <c r="A1894" s="1" t="n">
+        <v>1892</v>
+      </c>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0336.png</t>
+        </is>
+      </c>
+      <c r="C1894" t="inlineStr"/>
+      <c r="D1894" t="inlineStr"/>
+      <c r="E1894" t="inlineStr"/>
+      <c r="F1894" t="inlineStr">
+        <is>
+          <t>Cc1cnc(Nc2cc(C3CCN(CC4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)CC3)cc(N3CCC(F)(F)C3)n2)cn1</t>
+        </is>
+      </c>
+      <c r="G1894" t="inlineStr"/>
+      <c r="H1894" t="inlineStr"/>
+      <c r="I1894" t="n">
+        <v>0.9112476441011469</v>
+      </c>
+      <c r="J1894" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1894" t="inlineStr"/>
+    </row>
+    <row r="1895">
+      <c r="A1895" s="1" t="n">
+        <v>1893</v>
+      </c>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0337.png</t>
+        </is>
+      </c>
+      <c r="C1895" t="inlineStr"/>
+      <c r="D1895" t="inlineStr"/>
+      <c r="E1895" t="inlineStr"/>
+      <c r="F1895" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccc2c(c1)CCCOc1cc(ccc1Cc1nc3c(OCC(=O)N(C)C)cc(C(=O)OC)cc3n1C[C@@H]1CCO1)-c1cccc(n1)OC2</t>
+        </is>
+      </c>
+      <c r="G1895" t="inlineStr"/>
+      <c r="H1895" t="inlineStr"/>
+      <c r="I1895" t="n">
+        <v>0.9058743949788565</v>
+      </c>
+      <c r="J1895" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1895" t="inlineStr"/>
+    </row>
+    <row r="1896">
+      <c r="A1896" s="1" t="n">
+        <v>1894</v>
+      </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0338.png</t>
+        </is>
+      </c>
+      <c r="C1896" t="inlineStr"/>
+      <c r="D1896" t="inlineStr"/>
+      <c r="E1896" t="inlineStr"/>
+      <c r="F1896" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCN)NC(=O)[C@H](CCCN)NCc2cccnc2Sc2cccc(-c3ccc(C(=O)O)cc3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G1896" t="inlineStr"/>
+      <c r="H1896" t="inlineStr"/>
+      <c r="I1896" t="n">
+        <v>0.8862036901303013</v>
+      </c>
+      <c r="J1896" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1896" t="inlineStr"/>
+    </row>
+    <row r="1897">
+      <c r="A1897" s="1" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0339.png</t>
+        </is>
+      </c>
+      <c r="C1897" t="inlineStr"/>
+      <c r="D1897" t="inlineStr"/>
+      <c r="E1897" t="inlineStr"/>
+      <c r="F1897" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2cc3c(cc2OC)C2(OC3=O)c3cc(-c4ccncc4)c(OC(C)=O)cc3Oc3cc(OC(C)=O)c(-c4ccncc4)cc32)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1897" t="inlineStr"/>
+      <c r="H1897" t="inlineStr"/>
+      <c r="I1897" t="n">
+        <v>0.8872907072455989</v>
+      </c>
+      <c r="J1897" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1897" t="inlineStr"/>
+    </row>
+    <row r="1898">
+      <c r="A1898" s="1" t="n">
+        <v>1896</v>
+      </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0341.png</t>
+        </is>
+      </c>
+      <c r="C1898" t="inlineStr"/>
+      <c r="D1898" t="inlineStr"/>
+      <c r="E1898" t="inlineStr"/>
+      <c r="F1898" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCN(C)C)cc(OCc7ccccc7)c6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1898" t="inlineStr"/>
+      <c r="H1898" t="inlineStr"/>
+      <c r="I1898" t="n">
+        <v>0.8805210170181467</v>
+      </c>
+      <c r="J1898" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1898" t="inlineStr"/>
+    </row>
+    <row r="1899">
+      <c r="A1899" s="1" t="n">
+        <v>1897</v>
+      </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0343.png</t>
+        </is>
+      </c>
+      <c r="C1899" t="inlineStr"/>
+      <c r="D1899" t="inlineStr"/>
+      <c r="E1899" t="inlineStr"/>
+      <c r="F1899" t="inlineStr">
+        <is>
+          <t>CCn1cncc1Cn1c(Cc2ccc3cc2OCCCc2cc(C#N)ccc2COc2cccc-3n2)nc2c(OC)cc(C(=O)OC)cc21</t>
+        </is>
+      </c>
+      <c r="G1899" t="inlineStr"/>
+      <c r="H1899" t="inlineStr"/>
+      <c r="I1899" t="n">
+        <v>0.907073236231128</v>
+      </c>
+      <c r="J1899" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1899" t="inlineStr"/>
+    </row>
+    <row r="1900">
+      <c r="A1900" s="1" t="n">
+        <v>1898</v>
+      </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0344.png</t>
+        </is>
+      </c>
+      <c r="C1900" t="inlineStr"/>
+      <c r="D1900" t="inlineStr"/>
+      <c r="E1900" t="inlineStr"/>
+      <c r="F1900" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OC7CCNCC7)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1900" t="inlineStr"/>
+      <c r="H1900" t="inlineStr"/>
+      <c r="I1900" t="n">
+        <v>0.8897699710431715</v>
+      </c>
+      <c r="J1900" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1900" t="inlineStr"/>
+    </row>
+    <row r="1901">
+      <c r="A1901" s="1" t="n">
+        <v>1899</v>
+      </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0345.png</t>
+        </is>
+      </c>
+      <c r="C1901" t="inlineStr"/>
+      <c r="D1901" t="inlineStr"/>
+      <c r="E1901" t="inlineStr"/>
+      <c r="F1901" t="inlineStr">
+        <is>
+          <t>Cc1ccc(-c2ccn(CC(=O)O)c(=O)c2)c2c1Sc1ncccc1CN[C@@H](CCCN)C(=O)N[C@@H](CCCCN)C(=O)N(C)[C@@H](Cc1c[nH]c3ccccc13)C(=O)NC2</t>
+        </is>
+      </c>
+      <c r="G1901" t="inlineStr"/>
+      <c r="H1901" t="inlineStr"/>
+      <c r="I1901" t="n">
+        <v>0.8799245958082826</v>
+      </c>
+      <c r="J1901" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1901" t="inlineStr"/>
+    </row>
+    <row r="1902">
+      <c r="A1902" s="1" t="n">
+        <v>1900</v>
+      </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0346.png</t>
+        </is>
+      </c>
+      <c r="C1902" t="inlineStr"/>
+      <c r="D1902" t="inlineStr"/>
+      <c r="E1902" t="inlineStr"/>
+      <c r="F1902" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)[C@@H]4C[C@H]4C(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G1902" t="inlineStr"/>
+      <c r="H1902" t="inlineStr"/>
+      <c r="I1902" t="n">
+        <v>0.8823923113070917</v>
+      </c>
+      <c r="J1902" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1902" t="inlineStr"/>
+    </row>
+    <row r="1903">
+      <c r="A1903" s="1" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0347.png</t>
+        </is>
+      </c>
+      <c r="C1903" t="inlineStr"/>
+      <c r="D1903" t="inlineStr"/>
+      <c r="E1903" t="inlineStr"/>
+      <c r="F1903" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCN(C)C(C)=O)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1903" t="inlineStr"/>
+      <c r="H1903" t="inlineStr"/>
+      <c r="I1903" t="n">
+        <v>0.8967818979303619</v>
+      </c>
+      <c r="J1903" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1903" t="inlineStr"/>
+    </row>
+    <row r="1904">
+      <c r="A1904" s="1" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0348.png</t>
+        </is>
+      </c>
+      <c r="C1904" t="inlineStr"/>
+      <c r="D1904" t="inlineStr"/>
+      <c r="E1904" t="inlineStr"/>
+      <c r="F1904" t="inlineStr">
+        <is>
+          <t>CC(C)c1cnn2c(NCc3ccccc3-c3nccc4cc(NCCOCCOCCNC(=O)CNc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)ccc34)nc(O[C@@H]3CCCNC3)nc12</t>
+        </is>
+      </c>
+      <c r="G1904" t="inlineStr"/>
+      <c r="H1904" t="inlineStr"/>
+      <c r="I1904" t="n">
+        <v>0.8531231849430729</v>
+      </c>
+      <c r="J1904" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1904" t="inlineStr"/>
+    </row>
+    <row r="1905">
+      <c r="A1905" s="1" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0349.png</t>
+        </is>
+      </c>
+      <c r="C1905" t="inlineStr"/>
+      <c r="D1905" t="inlineStr"/>
+      <c r="E1905" t="inlineStr"/>
+      <c r="F1905" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)c2ccnc(N3CCN(c4cc(-c5ccccc5O)nnc4N)CC3)c2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1905" t="inlineStr"/>
+      <c r="H1905" t="inlineStr"/>
+      <c r="I1905" t="n">
+        <v>0.899499190477738</v>
+      </c>
+      <c r="J1905" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1905" t="inlineStr"/>
+    </row>
+    <row r="1906">
+      <c r="A1906" s="1" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0350.png</t>
+        </is>
+      </c>
+      <c r="C1906" t="inlineStr"/>
+      <c r="D1906" t="inlineStr"/>
+      <c r="E1906" t="inlineStr"/>
+      <c r="F1906" t="inlineStr">
+        <is>
+          <t>O=C(O)c1ccc2nc(Cc3ccc4cc3OCCCc3cc(-n5ccc(=O)c(F)c5)ccc3COc3cccc-4n3)n(C[C@@H]3CCO3)c2c1</t>
+        </is>
+      </c>
+      <c r="G1906" t="inlineStr"/>
+      <c r="H1906" t="inlineStr"/>
+      <c r="I1906" t="n">
+        <v>0.9063762358982737</v>
+      </c>
+      <c r="J1906" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1906" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_HighConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_HighConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1906"/>
+  <dimension ref="A1:K1962"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55725,6 +55725,1630 @@
       </c>
       <c r="K1906" t="inlineStr"/>
     </row>
+    <row r="1907">
+      <c r="A1907" s="1" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0001.png</t>
+        </is>
+      </c>
+      <c r="C1907" t="inlineStr"/>
+      <c r="D1907" t="inlineStr"/>
+      <c r="E1907" t="inlineStr"/>
+      <c r="F1907" t="inlineStr">
+        <is>
+          <t>CC(C)(C)Nc1cccc2c(C(=O)NCC(=O)N3CC(F)(F)C[C@H]3C#N)ccnc12</t>
+        </is>
+      </c>
+      <c r="G1907" t="inlineStr"/>
+      <c r="H1907" t="inlineStr"/>
+      <c r="I1907" t="n">
+        <v>0.890425560510111</v>
+      </c>
+      <c r="J1907" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1907" t="inlineStr"/>
+    </row>
+    <row r="1908">
+      <c r="A1908" s="1" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0002.png</t>
+        </is>
+      </c>
+      <c r="C1908" t="inlineStr"/>
+      <c r="D1908" t="inlineStr"/>
+      <c r="E1908" t="inlineStr"/>
+      <c r="F1908" t="inlineStr">
+        <is>
+          <t>CC(C)(C)C1CC2(CCN(C(C)(C)C)CC2)C1</t>
+        </is>
+      </c>
+      <c r="G1908" t="inlineStr"/>
+      <c r="H1908" t="inlineStr"/>
+      <c r="I1908" t="n">
+        <v>0.8792665332884626</v>
+      </c>
+      <c r="J1908" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1908" t="inlineStr"/>
+    </row>
+    <row r="1909">
+      <c r="A1909" s="1" t="n">
+        <v>1907</v>
+      </c>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0004.png</t>
+        </is>
+      </c>
+      <c r="C1909" t="inlineStr"/>
+      <c r="D1909" t="inlineStr"/>
+      <c r="E1909" t="inlineStr"/>
+      <c r="F1909" t="inlineStr">
+        <is>
+          <t>CCCCC/C=C\C/C=C\CCCCCCC(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G1909" t="inlineStr"/>
+      <c r="H1909" t="inlineStr"/>
+      <c r="I1909" t="n">
+        <v>0.8476269490494855</v>
+      </c>
+      <c r="J1909" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1909" t="inlineStr"/>
+    </row>
+    <row r="1910">
+      <c r="A1910" s="1" t="n">
+        <v>1908</v>
+      </c>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0005.png</t>
+        </is>
+      </c>
+      <c r="C1910" t="inlineStr"/>
+      <c r="D1910" t="inlineStr"/>
+      <c r="E1910" t="inlineStr"/>
+      <c r="F1910" t="inlineStr">
+        <is>
+          <t>CC(C)(C)CCCCCC(=O)C(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G1910" t="inlineStr"/>
+      <c r="H1910" t="inlineStr"/>
+      <c r="I1910" t="n">
+        <v>0.8906175425581678</v>
+      </c>
+      <c r="J1910" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1910" t="inlineStr"/>
+    </row>
+    <row r="1911">
+      <c r="A1911" s="1" t="n">
+        <v>1909</v>
+      </c>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0006.png</t>
+        </is>
+      </c>
+      <c r="C1911" t="inlineStr"/>
+      <c r="D1911" t="inlineStr"/>
+      <c r="E1911" t="inlineStr"/>
+      <c r="F1911" t="inlineStr">
+        <is>
+          <t>CC(O)COC(C)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1911" t="inlineStr"/>
+      <c r="H1911" t="inlineStr"/>
+      <c r="I1911" t="n">
+        <v>0.8721278171920418</v>
+      </c>
+      <c r="J1911" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1911" t="inlineStr"/>
+    </row>
+    <row r="1912">
+      <c r="A1912" s="1" t="n">
+        <v>1910</v>
+      </c>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0007.png</t>
+        </is>
+      </c>
+      <c r="C1912" t="inlineStr"/>
+      <c r="D1912" t="inlineStr"/>
+      <c r="E1912" t="inlineStr"/>
+      <c r="F1912" t="inlineStr">
+        <is>
+          <t>CC(C)C(=O)C1(c2ccccc2)CC1</t>
+        </is>
+      </c>
+      <c r="G1912" t="inlineStr"/>
+      <c r="H1912" t="inlineStr"/>
+      <c r="I1912" t="n">
+        <v>0.8864692045491774</v>
+      </c>
+      <c r="J1912" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1912" t="inlineStr"/>
+    </row>
+    <row r="1913">
+      <c r="A1913" s="1" t="n">
+        <v>1911</v>
+      </c>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0009.png</t>
+        </is>
+      </c>
+      <c r="C1913" t="inlineStr"/>
+      <c r="D1913" t="inlineStr"/>
+      <c r="E1913" t="inlineStr"/>
+      <c r="F1913" t="inlineStr">
+        <is>
+          <t>CN(C)C(=O)CC(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G1913" t="inlineStr"/>
+      <c r="H1913" t="inlineStr"/>
+      <c r="I1913" t="n">
+        <v>0.8755240394523718</v>
+      </c>
+      <c r="J1913" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1913" t="inlineStr"/>
+    </row>
+    <row r="1914">
+      <c r="A1914" s="1" t="n">
+        <v>1912</v>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0010.png</t>
+        </is>
+      </c>
+      <c r="C1914" t="inlineStr"/>
+      <c r="D1914" t="inlineStr"/>
+      <c r="E1914" t="inlineStr"/>
+      <c r="F1914" t="inlineStr">
+        <is>
+          <t>CC(C)C(=O)[C@@H]1CCC(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1914" t="inlineStr"/>
+      <c r="H1914" t="inlineStr"/>
+      <c r="I1914" t="n">
+        <v>0.8680043197835354</v>
+      </c>
+      <c r="J1914" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1914" t="inlineStr"/>
+    </row>
+    <row r="1915">
+      <c r="A1915" s="1" t="n">
+        <v>1913</v>
+      </c>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0011.png</t>
+        </is>
+      </c>
+      <c r="C1915" t="inlineStr"/>
+      <c r="D1915" t="inlineStr"/>
+      <c r="E1915" t="inlineStr"/>
+      <c r="F1915" t="inlineStr">
+        <is>
+          <t>CC(C)CCc1ccn(C)n1</t>
+        </is>
+      </c>
+      <c r="G1915" t="inlineStr"/>
+      <c r="H1915" t="inlineStr"/>
+      <c r="I1915" t="n">
+        <v>0.8700329976849509</v>
+      </c>
+      <c r="J1915" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1915" t="inlineStr"/>
+    </row>
+    <row r="1916">
+      <c r="A1916" s="1" t="n">
+        <v>1914</v>
+      </c>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0012.png</t>
+        </is>
+      </c>
+      <c r="C1916" t="inlineStr"/>
+      <c r="D1916" t="inlineStr"/>
+      <c r="E1916" t="inlineStr"/>
+      <c r="F1916" t="inlineStr">
+        <is>
+          <t>CCCCCCC(CCCCCC)CCC(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G1916" t="inlineStr"/>
+      <c r="H1916" t="inlineStr"/>
+      <c r="I1916" t="n">
+        <v>0.8880744163690831</v>
+      </c>
+      <c r="J1916" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1916" t="inlineStr"/>
+    </row>
+    <row r="1917">
+      <c r="A1917" s="1" t="n">
+        <v>1915</v>
+      </c>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0014.png</t>
+        </is>
+      </c>
+      <c r="C1917" t="inlineStr"/>
+      <c r="D1917" t="inlineStr"/>
+      <c r="E1917" t="inlineStr"/>
+      <c r="F1917" t="inlineStr">
+        <is>
+          <t>CC(C)(C)CCN1CCCC1=O</t>
+        </is>
+      </c>
+      <c r="G1917" t="inlineStr"/>
+      <c r="H1917" t="inlineStr"/>
+      <c r="I1917" t="n">
+        <v>0.8709039836184956</v>
+      </c>
+      <c r="J1917" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1917" t="inlineStr"/>
+    </row>
+    <row r="1918">
+      <c r="A1918" s="1" t="n">
+        <v>1916</v>
+      </c>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0015.png</t>
+        </is>
+      </c>
+      <c r="C1918" t="inlineStr"/>
+      <c r="D1918" t="inlineStr"/>
+      <c r="E1918" t="inlineStr"/>
+      <c r="F1918" t="inlineStr">
+        <is>
+          <t>CC(C)(C)c1cc(F)ccc1F</t>
+        </is>
+      </c>
+      <c r="G1918" t="inlineStr"/>
+      <c r="H1918" t="inlineStr"/>
+      <c r="I1918" t="n">
+        <v>0.8781241146077132</v>
+      </c>
+      <c r="J1918" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1918" t="inlineStr"/>
+    </row>
+    <row r="1919">
+      <c r="A1919" s="1" t="n">
+        <v>1917</v>
+      </c>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0016.png</t>
+        </is>
+      </c>
+      <c r="C1919" t="inlineStr"/>
+      <c r="D1919" t="inlineStr"/>
+      <c r="E1919" t="inlineStr"/>
+      <c r="F1919" t="inlineStr">
+        <is>
+          <t>CC(C)(C)C(=O)CCl</t>
+        </is>
+      </c>
+      <c r="G1919" t="inlineStr"/>
+      <c r="H1919" t="inlineStr"/>
+      <c r="I1919" t="n">
+        <v>0.8566773886195536</v>
+      </c>
+      <c r="J1919" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1919" t="inlineStr"/>
+    </row>
+    <row r="1920">
+      <c r="A1920" s="1" t="n">
+        <v>1918</v>
+      </c>
+      <c r="B1920" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0017.png</t>
+        </is>
+      </c>
+      <c r="C1920" t="inlineStr"/>
+      <c r="D1920" t="inlineStr"/>
+      <c r="E1920" t="inlineStr"/>
+      <c r="F1920" t="inlineStr">
+        <is>
+          <t>CC(C)c1ccc([N+](=O)[O-])cc1Cl</t>
+        </is>
+      </c>
+      <c r="G1920" t="inlineStr"/>
+      <c r="H1920" t="inlineStr"/>
+      <c r="I1920" t="n">
+        <v>0.8958684899003649</v>
+      </c>
+      <c r="J1920" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1920" t="inlineStr"/>
+    </row>
+    <row r="1921">
+      <c r="A1921" s="1" t="n">
+        <v>1919</v>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0018.png</t>
+        </is>
+      </c>
+      <c r="C1921" t="inlineStr"/>
+      <c r="D1921" t="inlineStr"/>
+      <c r="E1921" t="inlineStr"/>
+      <c r="F1921" t="inlineStr">
+        <is>
+          <t>CC(C)C(=O)COCCOCCN1CCN(C(=O)C(C)C)CC1</t>
+        </is>
+      </c>
+      <c r="G1921" t="inlineStr"/>
+      <c r="H1921" t="inlineStr"/>
+      <c r="I1921" t="n">
+        <v>0.8528561468196261</v>
+      </c>
+      <c r="J1921" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1921" t="inlineStr"/>
+    </row>
+    <row r="1922">
+      <c r="A1922" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0020.png</t>
+        </is>
+      </c>
+      <c r="C1922" t="inlineStr"/>
+      <c r="D1922" t="inlineStr"/>
+      <c r="E1922" t="inlineStr"/>
+      <c r="F1922" t="inlineStr">
+        <is>
+          <t>CC(C)N1C[C@H](C)O[C@@H](C)C1</t>
+        </is>
+      </c>
+      <c r="G1922" t="inlineStr"/>
+      <c r="H1922" t="inlineStr"/>
+      <c r="I1922" t="n">
+        <v>0.8471395841001044</v>
+      </c>
+      <c r="J1922" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1922" t="inlineStr"/>
+    </row>
+    <row r="1923">
+      <c r="A1923" s="1" t="n">
+        <v>1921</v>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0021.png</t>
+        </is>
+      </c>
+      <c r="C1923" t="inlineStr"/>
+      <c r="D1923" t="inlineStr"/>
+      <c r="E1923" t="inlineStr"/>
+      <c r="F1923" t="inlineStr">
+        <is>
+          <t>CC(C)CCC1CCN(C(C)C)CC1</t>
+        </is>
+      </c>
+      <c r="G1923" t="inlineStr"/>
+      <c r="H1923" t="inlineStr"/>
+      <c r="I1923" t="n">
+        <v>0.8669099143239484</v>
+      </c>
+      <c r="J1923" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1923" t="inlineStr"/>
+    </row>
+    <row r="1924">
+      <c r="A1924" s="1" t="n">
+        <v>1922</v>
+      </c>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0022.png</t>
+        </is>
+      </c>
+      <c r="C1924" t="inlineStr"/>
+      <c r="D1924" t="inlineStr"/>
+      <c r="E1924" t="inlineStr"/>
+      <c r="F1924" t="inlineStr">
+        <is>
+          <t>CC(C)N1CCc2ccccc2C1</t>
+        </is>
+      </c>
+      <c r="G1924" t="inlineStr"/>
+      <c r="H1924" t="inlineStr"/>
+      <c r="I1924" t="n">
+        <v>0.9063207027506207</v>
+      </c>
+      <c r="J1924" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1924" t="inlineStr"/>
+    </row>
+    <row r="1925">
+      <c r="A1925" s="1" t="n">
+        <v>1923</v>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0023.png</t>
+        </is>
+      </c>
+      <c r="C1925" t="inlineStr"/>
+      <c r="D1925" t="inlineStr"/>
+      <c r="E1925" t="inlineStr"/>
+      <c r="F1925" t="inlineStr">
+        <is>
+          <t>CC(C)(C)N1CC2(COC2)C1</t>
+        </is>
+      </c>
+      <c r="G1925" t="inlineStr"/>
+      <c r="H1925" t="inlineStr"/>
+      <c r="I1925" t="n">
+        <v>0.8583332623610674</v>
+      </c>
+      <c r="J1925" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1925" t="inlineStr"/>
+    </row>
+    <row r="1926">
+      <c r="A1926" s="1" t="n">
+        <v>1924</v>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0024.png</t>
+        </is>
+      </c>
+      <c r="C1926" t="inlineStr"/>
+      <c r="D1926" t="inlineStr"/>
+      <c r="E1926" t="inlineStr"/>
+      <c r="F1926" t="inlineStr">
+        <is>
+          <t>CC(C)c1ccc(Br)c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G1926" t="inlineStr"/>
+      <c r="H1926" t="inlineStr"/>
+      <c r="I1926" t="n">
+        <v>0.9042401260952247</v>
+      </c>
+      <c r="J1926" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1926" t="inlineStr"/>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="1" t="n">
+        <v>1925</v>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0026.png</t>
+        </is>
+      </c>
+      <c r="C1927" t="inlineStr"/>
+      <c r="D1927" t="inlineStr"/>
+      <c r="E1927" t="inlineStr"/>
+      <c r="F1927" t="inlineStr">
+        <is>
+          <t>CC(C)C(N)=O</t>
+        </is>
+      </c>
+      <c r="G1927" t="inlineStr"/>
+      <c r="H1927" t="inlineStr"/>
+      <c r="I1927" t="n">
+        <v>0.8581194135667869</v>
+      </c>
+      <c r="J1927" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1927" t="inlineStr"/>
+    </row>
+    <row r="1928">
+      <c r="A1928" s="1" t="n">
+        <v>1926</v>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0027.png</t>
+        </is>
+      </c>
+      <c r="C1928" t="inlineStr"/>
+      <c r="D1928" t="inlineStr"/>
+      <c r="E1928" t="inlineStr"/>
+      <c r="F1928" t="inlineStr">
+        <is>
+          <t>CC(C)(C)C1CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1928" t="inlineStr"/>
+      <c r="H1928" t="inlineStr"/>
+      <c r="I1928" t="n">
+        <v>0.889460827552064</v>
+      </c>
+      <c r="J1928" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1928" t="inlineStr"/>
+    </row>
+    <row r="1929">
+      <c r="A1929" s="1" t="n">
+        <v>1927</v>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0029.png</t>
+        </is>
+      </c>
+      <c r="C1929" t="inlineStr"/>
+      <c r="D1929" t="inlineStr"/>
+      <c r="E1929" t="inlineStr"/>
+      <c r="F1929" t="inlineStr">
+        <is>
+          <t>CC(C)C1c2ccccc2-c2ccccc21</t>
+        </is>
+      </c>
+      <c r="G1929" t="inlineStr"/>
+      <c r="H1929" t="inlineStr"/>
+      <c r="I1929" t="n">
+        <v>0.8696497710748888</v>
+      </c>
+      <c r="J1929" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1929" t="inlineStr"/>
+    </row>
+    <row r="1930">
+      <c r="A1930" s="1" t="n">
+        <v>1928</v>
+      </c>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0032.png</t>
+        </is>
+      </c>
+      <c r="C1930" t="inlineStr"/>
+      <c r="D1930" t="inlineStr"/>
+      <c r="E1930" t="inlineStr"/>
+      <c r="F1930" t="inlineStr">
+        <is>
+          <t>CN1CCN(CCC(C)(C)C)CC1</t>
+        </is>
+      </c>
+      <c r="G1930" t="inlineStr"/>
+      <c r="H1930" t="inlineStr"/>
+      <c r="I1930" t="n">
+        <v>0.8987030519332201</v>
+      </c>
+      <c r="J1930" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1930" t="inlineStr"/>
+    </row>
+    <row r="1931">
+      <c r="A1931" s="1" t="n">
+        <v>1929</v>
+      </c>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0033.png</t>
+        </is>
+      </c>
+      <c r="C1931" t="inlineStr"/>
+      <c r="D1931" t="inlineStr"/>
+      <c r="E1931" t="inlineStr"/>
+      <c r="F1931" t="inlineStr">
+        <is>
+          <t>Cc1ccc(C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1931" t="inlineStr"/>
+      <c r="H1931" t="inlineStr"/>
+      <c r="I1931" t="n">
+        <v>0.9145990164302414</v>
+      </c>
+      <c r="J1931" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1931" t="inlineStr"/>
+    </row>
+    <row r="1932">
+      <c r="A1932" s="1" t="n">
+        <v>1930</v>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0034.png</t>
+        </is>
+      </c>
+      <c r="C1932" t="inlineStr"/>
+      <c r="D1932" t="inlineStr"/>
+      <c r="E1932" t="inlineStr"/>
+      <c r="F1932" t="inlineStr">
+        <is>
+          <t>CC(C)Cc1nccc2ccccc12</t>
+        </is>
+      </c>
+      <c r="G1932" t="inlineStr"/>
+      <c r="H1932" t="inlineStr"/>
+      <c r="I1932" t="n">
+        <v>0.8893230723231054</v>
+      </c>
+      <c r="J1932" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1932" t="inlineStr"/>
+    </row>
+    <row r="1933">
+      <c r="A1933" s="1" t="n">
+        <v>1931</v>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0035.png</t>
+        </is>
+      </c>
+      <c r="C1933" t="inlineStr"/>
+      <c r="D1933" t="inlineStr"/>
+      <c r="E1933" t="inlineStr"/>
+      <c r="F1933" t="inlineStr">
+        <is>
+          <t>CC(C)SSc1ccccn1</t>
+        </is>
+      </c>
+      <c r="G1933" t="inlineStr"/>
+      <c r="H1933" t="inlineStr"/>
+      <c r="I1933" t="n">
+        <v>0.8879527228978943</v>
+      </c>
+      <c r="J1933" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1933" t="inlineStr"/>
+    </row>
+    <row r="1934">
+      <c r="A1934" s="1" t="n">
+        <v>1932</v>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0036.png</t>
+        </is>
+      </c>
+      <c r="C1934" t="inlineStr"/>
+      <c r="D1934" t="inlineStr"/>
+      <c r="E1934" t="inlineStr"/>
+      <c r="F1934" t="inlineStr">
+        <is>
+          <t>CC(C)(C)CCOCCC(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G1934" t="inlineStr"/>
+      <c r="H1934" t="inlineStr"/>
+      <c r="I1934" t="n">
+        <v>0.87172996196632</v>
+      </c>
+      <c r="J1934" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1934" t="inlineStr"/>
+    </row>
+    <row r="1935">
+      <c r="A1935" s="1" t="n">
+        <v>1933</v>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0037.png</t>
+        </is>
+      </c>
+      <c r="C1935" t="inlineStr"/>
+      <c r="D1935" t="inlineStr"/>
+      <c r="E1935" t="inlineStr"/>
+      <c r="F1935" t="inlineStr">
+        <is>
+          <t>C#CCOCCOCCOCCC(C)C</t>
+        </is>
+      </c>
+      <c r="G1935" t="inlineStr"/>
+      <c r="H1935" t="inlineStr"/>
+      <c r="I1935" t="n">
+        <v>0.861481098246221</v>
+      </c>
+      <c r="J1935" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1935" t="inlineStr"/>
+    </row>
+    <row r="1936">
+      <c r="A1936" s="1" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0038.png</t>
+        </is>
+      </c>
+      <c r="C1936" t="inlineStr"/>
+      <c r="D1936" t="inlineStr"/>
+      <c r="E1936" t="inlineStr"/>
+      <c r="F1936" t="inlineStr">
+        <is>
+          <t>COC(=O)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1936" t="inlineStr"/>
+      <c r="H1936" t="inlineStr"/>
+      <c r="I1936" t="n">
+        <v>0.8446285525486495</v>
+      </c>
+      <c r="J1936" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1936" t="inlineStr"/>
+    </row>
+    <row r="1937">
+      <c r="A1937" s="1" t="n">
+        <v>1935</v>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0041.png</t>
+        </is>
+      </c>
+      <c r="C1937" t="inlineStr"/>
+      <c r="D1937" t="inlineStr"/>
+      <c r="E1937" t="inlineStr"/>
+      <c r="F1937" t="inlineStr">
+        <is>
+          <t>CC(C)c1cnc2c(c1)CCC2</t>
+        </is>
+      </c>
+      <c r="G1937" t="inlineStr"/>
+      <c r="H1937" t="inlineStr"/>
+      <c r="I1937" t="n">
+        <v>0.864964974256196</v>
+      </c>
+      <c r="J1937" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1937" t="inlineStr"/>
+    </row>
+    <row r="1938">
+      <c r="A1938" s="1" t="n">
+        <v>1936</v>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0046.png</t>
+        </is>
+      </c>
+      <c r="C1938" t="inlineStr"/>
+      <c r="D1938" t="inlineStr"/>
+      <c r="E1938" t="inlineStr"/>
+      <c r="F1938" t="inlineStr">
+        <is>
+          <t>CCCCC/C=C\C/C=C\CCCCCCCC(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G1938" t="inlineStr"/>
+      <c r="H1938" t="inlineStr"/>
+      <c r="I1938" t="n">
+        <v>0.8696466738396037</v>
+      </c>
+      <c r="J1938" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1938" t="inlineStr"/>
+    </row>
+    <row r="1939">
+      <c r="A1939" s="1" t="n">
+        <v>1937</v>
+      </c>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0047.png</t>
+        </is>
+      </c>
+      <c r="C1939" t="inlineStr"/>
+      <c r="D1939" t="inlineStr"/>
+      <c r="E1939" t="inlineStr"/>
+      <c r="F1939" t="inlineStr">
+        <is>
+          <t>CC(C)Cc1cccn1C</t>
+        </is>
+      </c>
+      <c r="G1939" t="inlineStr"/>
+      <c r="H1939" t="inlineStr"/>
+      <c r="I1939" t="n">
+        <v>0.8833163741035787</v>
+      </c>
+      <c r="J1939" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1939" t="inlineStr"/>
+    </row>
+    <row r="1940">
+      <c r="A1940" s="1" t="n">
+        <v>1938</v>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0048.png</t>
+        </is>
+      </c>
+      <c r="C1940" t="inlineStr"/>
+      <c r="D1940" t="inlineStr"/>
+      <c r="E1940" t="inlineStr"/>
+      <c r="F1940" t="inlineStr">
+        <is>
+          <t>CC(C)c1cc(C(C)C)n(C(C)C)c1</t>
+        </is>
+      </c>
+      <c r="G1940" t="inlineStr"/>
+      <c r="H1940" t="inlineStr"/>
+      <c r="I1940" t="n">
+        <v>0.8612395257432265</v>
+      </c>
+      <c r="J1940" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1940" t="inlineStr"/>
+    </row>
+    <row r="1941">
+      <c r="A1941" s="1" t="n">
+        <v>1939</v>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0049.png</t>
+        </is>
+      </c>
+      <c r="C1941" t="inlineStr"/>
+      <c r="D1941" t="inlineStr"/>
+      <c r="E1941" t="inlineStr"/>
+      <c r="F1941" t="inlineStr">
+        <is>
+          <t>CC(C)Nc1cccc2[nH]ncc12</t>
+        </is>
+      </c>
+      <c r="G1941" t="inlineStr"/>
+      <c r="H1941" t="inlineStr"/>
+      <c r="I1941" t="n">
+        <v>0.9029995310767223</v>
+      </c>
+      <c r="J1941" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1941" t="inlineStr"/>
+    </row>
+    <row r="1942">
+      <c r="A1942" s="1" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0051.png</t>
+        </is>
+      </c>
+      <c r="C1942" t="inlineStr"/>
+      <c r="D1942" t="inlineStr"/>
+      <c r="E1942" t="inlineStr"/>
+      <c r="F1942" t="inlineStr">
+        <is>
+          <t>CC(C)c1cccc(C(C)C)c1</t>
+        </is>
+      </c>
+      <c r="G1942" t="inlineStr"/>
+      <c r="H1942" t="inlineStr"/>
+      <c r="I1942" t="n">
+        <v>0.9010618681883864</v>
+      </c>
+      <c r="J1942" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1942" t="inlineStr"/>
+    </row>
+    <row r="1943">
+      <c r="A1943" s="1" t="n">
+        <v>1941</v>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0052.png</t>
+        </is>
+      </c>
+      <c r="C1943" t="inlineStr"/>
+      <c r="D1943" t="inlineStr"/>
+      <c r="E1943" t="inlineStr"/>
+      <c r="F1943" t="inlineStr">
+        <is>
+          <t>CC(C)(C)CNC(=O)NCNc1nc(N)nc(NC(C)(C)C)n1</t>
+        </is>
+      </c>
+      <c r="G1943" t="inlineStr"/>
+      <c r="H1943" t="inlineStr"/>
+      <c r="I1943" t="n">
+        <v>0.8524547220116637</v>
+      </c>
+      <c r="J1943" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1943" t="inlineStr"/>
+    </row>
+    <row r="1944">
+      <c r="A1944" s="1" t="n">
+        <v>1942</v>
+      </c>
+      <c r="B1944" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0053.png</t>
+        </is>
+      </c>
+      <c r="C1944" t="inlineStr"/>
+      <c r="D1944" t="inlineStr"/>
+      <c r="E1944" t="inlineStr"/>
+      <c r="F1944" t="inlineStr">
+        <is>
+          <t>CC(C)c1cccnc1</t>
+        </is>
+      </c>
+      <c r="G1944" t="inlineStr"/>
+      <c r="H1944" t="inlineStr"/>
+      <c r="I1944" t="n">
+        <v>0.87674330943896</v>
+      </c>
+      <c r="J1944" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1944" t="inlineStr"/>
+    </row>
+    <row r="1945">
+      <c r="A1945" s="1" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0054.png</t>
+        </is>
+      </c>
+      <c r="C1945" t="inlineStr"/>
+      <c r="D1945" t="inlineStr"/>
+      <c r="E1945" t="inlineStr"/>
+      <c r="F1945" t="inlineStr">
+        <is>
+          <t>CC(C)(C)CCCN1C(=O)C=CC1=O</t>
+        </is>
+      </c>
+      <c r="G1945" t="inlineStr"/>
+      <c r="H1945" t="inlineStr"/>
+      <c r="I1945" t="n">
+        <v>0.8691925633132703</v>
+      </c>
+      <c r="J1945" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1945" t="inlineStr"/>
+    </row>
+    <row r="1946">
+      <c r="A1946" s="1" t="n">
+        <v>1944</v>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0056.png</t>
+        </is>
+      </c>
+      <c r="C1946" t="inlineStr"/>
+      <c r="D1946" t="inlineStr"/>
+      <c r="E1946" t="inlineStr"/>
+      <c r="F1946" t="inlineStr">
+        <is>
+          <t>CC(C)c1ccccc1F</t>
+        </is>
+      </c>
+      <c r="G1946" t="inlineStr"/>
+      <c r="H1946" t="inlineStr"/>
+      <c r="I1946" t="n">
+        <v>0.9026471941361747</v>
+      </c>
+      <c r="J1946" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1946" t="inlineStr"/>
+    </row>
+    <row r="1947">
+      <c r="A1947" s="1" t="n">
+        <v>1945</v>
+      </c>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0057.png</t>
+        </is>
+      </c>
+      <c r="C1947" t="inlineStr"/>
+      <c r="D1947" t="inlineStr"/>
+      <c r="E1947" t="inlineStr"/>
+      <c r="F1947" t="inlineStr">
+        <is>
+          <t>CC(C)c1cccnc1OC1CC1</t>
+        </is>
+      </c>
+      <c r="G1947" t="inlineStr"/>
+      <c r="H1947" t="inlineStr"/>
+      <c r="I1947" t="n">
+        <v>0.8770475226431689</v>
+      </c>
+      <c r="J1947" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1947" t="inlineStr"/>
+    </row>
+    <row r="1948">
+      <c r="A1948" s="1" t="n">
+        <v>1946</v>
+      </c>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0058.png</t>
+        </is>
+      </c>
+      <c r="C1948" t="inlineStr"/>
+      <c r="D1948" t="inlineStr"/>
+      <c r="E1948" t="inlineStr"/>
+      <c r="F1948" t="inlineStr">
+        <is>
+          <t>CC(C)/C=C/C1=Nc2ccccc2C1</t>
+        </is>
+      </c>
+      <c r="G1948" t="inlineStr"/>
+      <c r="H1948" t="inlineStr"/>
+      <c r="I1948" t="n">
+        <v>0.8791164323752999</v>
+      </c>
+      <c r="J1948" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1948" t="inlineStr"/>
+    </row>
+    <row r="1949">
+      <c r="A1949" s="1" t="n">
+        <v>1947</v>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0059.png</t>
+        </is>
+      </c>
+      <c r="C1949" t="inlineStr"/>
+      <c r="D1949" t="inlineStr"/>
+      <c r="E1949" t="inlineStr"/>
+      <c r="F1949" t="inlineStr">
+        <is>
+          <t>CC(C)c1ccc(C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1949" t="inlineStr"/>
+      <c r="H1949" t="inlineStr"/>
+      <c r="I1949" t="n">
+        <v>0.9003497849539289</v>
+      </c>
+      <c r="J1949" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1949" t="inlineStr"/>
+    </row>
+    <row r="1950">
+      <c r="A1950" s="1" t="n">
+        <v>1948</v>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0061.png</t>
+        </is>
+      </c>
+      <c r="C1950" t="inlineStr"/>
+      <c r="D1950" t="inlineStr"/>
+      <c r="E1950" t="inlineStr"/>
+      <c r="F1950" t="inlineStr">
+        <is>
+          <t>CC(C)(C)CCCCCC(O)CC(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G1950" t="inlineStr"/>
+      <c r="H1950" t="inlineStr"/>
+      <c r="I1950" t="n">
+        <v>0.878979904889825</v>
+      </c>
+      <c r="J1950" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1950" t="inlineStr"/>
+    </row>
+    <row r="1951">
+      <c r="A1951" s="1" t="n">
+        <v>1949</v>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0062.png</t>
+        </is>
+      </c>
+      <c r="C1951" t="inlineStr"/>
+      <c r="D1951" t="inlineStr"/>
+      <c r="E1951" t="inlineStr"/>
+      <c r="F1951" t="inlineStr">
+        <is>
+          <t>CCCCCCCCC(CCCC)C(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G1951" t="inlineStr"/>
+      <c r="H1951" t="inlineStr"/>
+      <c r="I1951" t="n">
+        <v>0.8996285896650024</v>
+      </c>
+      <c r="J1951" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1951" t="inlineStr"/>
+    </row>
+    <row r="1952">
+      <c r="A1952" s="1" t="n">
+        <v>1950</v>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0063.png</t>
+        </is>
+      </c>
+      <c r="C1952" t="inlineStr"/>
+      <c r="D1952" t="inlineStr"/>
+      <c r="E1952" t="inlineStr"/>
+      <c r="F1952" t="inlineStr">
+        <is>
+          <t>CC(C)c1ccc(Oc2ccc(Cl)cc2)c(Cl)c1</t>
+        </is>
+      </c>
+      <c r="G1952" t="inlineStr"/>
+      <c r="H1952" t="inlineStr"/>
+      <c r="I1952" t="n">
+        <v>0.9050962421655079</v>
+      </c>
+      <c r="J1952" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1952" t="inlineStr"/>
+    </row>
+    <row r="1953">
+      <c r="A1953" s="1" t="n">
+        <v>1951</v>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0064.png</t>
+        </is>
+      </c>
+      <c r="C1953" t="inlineStr"/>
+      <c r="D1953" t="inlineStr"/>
+      <c r="E1953" t="inlineStr"/>
+      <c r="F1953" t="inlineStr">
+        <is>
+          <t>CC(C)c1ccc(Cc2ccccc2)cc1</t>
+        </is>
+      </c>
+      <c r="G1953" t="inlineStr"/>
+      <c r="H1953" t="inlineStr"/>
+      <c r="I1953" t="n">
+        <v>0.9113743955042727</v>
+      </c>
+      <c r="J1953" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1953" t="inlineStr"/>
+    </row>
+    <row r="1954">
+      <c r="A1954" s="1" t="n">
+        <v>1952</v>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0065.png</t>
+        </is>
+      </c>
+      <c r="C1954" t="inlineStr"/>
+      <c r="D1954" t="inlineStr"/>
+      <c r="E1954" t="inlineStr"/>
+      <c r="F1954" t="inlineStr">
+        <is>
+          <t>CCCCCCCC/C=C\C(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G1954" t="inlineStr"/>
+      <c r="H1954" t="inlineStr"/>
+      <c r="I1954" t="n">
+        <v>0.8655983492185698</v>
+      </c>
+      <c r="J1954" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1954" t="inlineStr"/>
+    </row>
+    <row r="1955">
+      <c r="A1955" s="1" t="n">
+        <v>1953</v>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0066.png</t>
+        </is>
+      </c>
+      <c r="C1955" t="inlineStr"/>
+      <c r="D1955" t="inlineStr"/>
+      <c r="E1955" t="inlineStr"/>
+      <c r="F1955" t="inlineStr">
+        <is>
+          <t>CC(C)O[C@H]1CCN2C(=O)OC[C@@H]2C1</t>
+        </is>
+      </c>
+      <c r="G1955" t="inlineStr"/>
+      <c r="H1955" t="inlineStr"/>
+      <c r="I1955" t="n">
+        <v>0.8583853687499077</v>
+      </c>
+      <c r="J1955" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1955" t="inlineStr"/>
+    </row>
+    <row r="1956">
+      <c r="A1956" s="1" t="n">
+        <v>1954</v>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0071.png</t>
+        </is>
+      </c>
+      <c r="C1956" t="inlineStr"/>
+      <c r="D1956" t="inlineStr"/>
+      <c r="E1956" t="inlineStr"/>
+      <c r="F1956" t="inlineStr">
+        <is>
+          <t>CC(C)[C@H](O)C(C)(C)CO</t>
+        </is>
+      </c>
+      <c r="G1956" t="inlineStr"/>
+      <c r="H1956" t="inlineStr"/>
+      <c r="I1956" t="n">
+        <v>0.8445659975586018</v>
+      </c>
+      <c r="J1956" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1956" t="inlineStr"/>
+    </row>
+    <row r="1957">
+      <c r="A1957" s="1" t="n">
+        <v>1955</v>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0072.png</t>
+        </is>
+      </c>
+      <c r="C1957" t="inlineStr"/>
+      <c r="D1957" t="inlineStr"/>
+      <c r="E1957" t="inlineStr"/>
+      <c r="F1957" t="inlineStr">
+        <is>
+          <t>CCCCCCCC/C=C\CCCCCCC(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G1957" t="inlineStr"/>
+      <c r="H1957" t="inlineStr"/>
+      <c r="I1957" t="n">
+        <v>0.8980828613457111</v>
+      </c>
+      <c r="J1957" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1957" t="inlineStr"/>
+    </row>
+    <row r="1958">
+      <c r="A1958" s="1" t="n">
+        <v>1956</v>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0076.png</t>
+        </is>
+      </c>
+      <c r="C1958" t="inlineStr"/>
+      <c r="D1958" t="inlineStr"/>
+      <c r="E1958" t="inlineStr"/>
+      <c r="F1958" t="inlineStr">
+        <is>
+          <t>CC(C)(C)/C=C/c1ccc(C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1958" t="inlineStr"/>
+      <c r="H1958" t="inlineStr"/>
+      <c r="I1958" t="n">
+        <v>0.9043903739256073</v>
+      </c>
+      <c r="J1958" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1958" t="inlineStr"/>
+    </row>
+    <row r="1959">
+      <c r="A1959" s="1" t="n">
+        <v>1957</v>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0077.png</t>
+        </is>
+      </c>
+      <c r="C1959" t="inlineStr"/>
+      <c r="D1959" t="inlineStr"/>
+      <c r="E1959" t="inlineStr"/>
+      <c r="F1959" t="inlineStr">
+        <is>
+          <t>CN[C@H](C)C(=O)N[C@H](C)C(=O)N1C[C@H](NC(C)(C)C)C[C@@H]1C(=O)N[C@H]1CCCc2ccccc21</t>
+        </is>
+      </c>
+      <c r="G1959" t="inlineStr"/>
+      <c r="H1959" t="inlineStr"/>
+      <c r="I1959" t="n">
+        <v>0.8931805570779713</v>
+      </c>
+      <c r="J1959" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1959" t="inlineStr"/>
+    </row>
+    <row r="1960">
+      <c r="A1960" s="1" t="n">
+        <v>1958</v>
+      </c>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0078.png</t>
+        </is>
+      </c>
+      <c r="C1960" t="inlineStr"/>
+      <c r="D1960" t="inlineStr"/>
+      <c r="E1960" t="inlineStr"/>
+      <c r="F1960" t="inlineStr">
+        <is>
+          <t>CC(C)(C)CCCc1ccc(I)cc1</t>
+        </is>
+      </c>
+      <c r="G1960" t="inlineStr"/>
+      <c r="H1960" t="inlineStr"/>
+      <c r="I1960" t="n">
+        <v>0.9020062766805423</v>
+      </c>
+      <c r="J1960" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1960" t="inlineStr"/>
+    </row>
+    <row r="1961">
+      <c r="A1961" s="1" t="n">
+        <v>1959</v>
+      </c>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0079.png</t>
+        </is>
+      </c>
+      <c r="C1961" t="inlineStr"/>
+      <c r="D1961" t="inlineStr"/>
+      <c r="E1961" t="inlineStr"/>
+      <c r="F1961" t="inlineStr">
+        <is>
+          <t>CC(C)(C)P(=O)(O)OP(=O)(O)OP(=O)(O)O</t>
+        </is>
+      </c>
+      <c r="G1961" t="inlineStr"/>
+      <c r="H1961" t="inlineStr"/>
+      <c r="I1961" t="n">
+        <v>0.901999848713983</v>
+      </c>
+      <c r="J1961" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1961" t="inlineStr"/>
+    </row>
+    <row r="1962">
+      <c r="A1962" s="1" t="n">
+        <v>1960</v>
+      </c>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0082.png</t>
+        </is>
+      </c>
+      <c r="C1962" t="inlineStr"/>
+      <c r="D1962" t="inlineStr"/>
+      <c r="E1962" t="inlineStr"/>
+      <c r="F1962" t="inlineStr">
+        <is>
+          <t>CC(C)C(=O)NCCNC(=O)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1962" t="inlineStr"/>
+      <c r="H1962" t="inlineStr"/>
+      <c r="I1962" t="n">
+        <v>0.8628898683263105</v>
+      </c>
+      <c r="J1962" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1962" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_HighConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_HighConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1962"/>
+  <dimension ref="A1:K2136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57349,6 +57349,5052 @@
       </c>
       <c r="K1962" t="inlineStr"/>
     </row>
+    <row r="1963">
+      <c r="A1963" s="1" t="n">
+        <v>1961</v>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0351.png</t>
+        </is>
+      </c>
+      <c r="C1963" t="inlineStr"/>
+      <c r="D1963" t="inlineStr"/>
+      <c r="E1963" t="inlineStr"/>
+      <c r="F1963" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCN(C)C(C)=O)cc(O)c6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1963" t="inlineStr"/>
+      <c r="H1963" t="inlineStr"/>
+      <c r="I1963" t="n">
+        <v>0.8924713295782715</v>
+      </c>
+      <c r="J1963" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1963" t="inlineStr"/>
+    </row>
+    <row r="1964">
+      <c r="A1964" s="1" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0352.png</t>
+        </is>
+      </c>
+      <c r="C1964" t="inlineStr"/>
+      <c r="D1964" t="inlineStr"/>
+      <c r="E1964" t="inlineStr"/>
+      <c r="F1964" t="inlineStr">
+        <is>
+          <t>N=C(N)NCCC[C@@H]1NC(=O)[C@@H](Cc2cccc3ccccc23)NC(=O)[C@H](Cc2c[nH]cn2)NC(=O)[C@@H](NC(=O)CC2CCCC2)CC(=O)NCCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1964" t="inlineStr"/>
+      <c r="H1964" t="inlineStr"/>
+      <c r="I1964" t="n">
+        <v>0.8903266018351721</v>
+      </c>
+      <c r="J1964" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1964" t="inlineStr"/>
+    </row>
+    <row r="1965">
+      <c r="A1965" s="1" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0353.png</t>
+        </is>
+      </c>
+      <c r="C1965" t="inlineStr"/>
+      <c r="D1965" t="inlineStr"/>
+      <c r="E1965" t="inlineStr"/>
+      <c r="F1965" t="inlineStr">
+        <is>
+          <t>CC(=O)N[C@H]1CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccc(F)cc2)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1965" t="inlineStr"/>
+      <c r="H1965" t="inlineStr"/>
+      <c r="I1965" t="n">
+        <v>0.873496045800523</v>
+      </c>
+      <c r="J1965" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1965" t="inlineStr"/>
+    </row>
+    <row r="1966">
+      <c r="A1966" s="1" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0354.png</t>
+        </is>
+      </c>
+      <c r="C1966" t="inlineStr"/>
+      <c r="D1966" t="inlineStr"/>
+      <c r="E1966" t="inlineStr"/>
+      <c r="F1966" t="inlineStr">
+        <is>
+          <t>O=C(O)c1ccc2nc(Cc3ccc4cc3OCCCc3cc(-c5ccc(CO)cc5)ccc3COc3cccc-4n3)n(C[C@@H]3CCO3)c2c1</t>
+        </is>
+      </c>
+      <c r="G1966" t="inlineStr"/>
+      <c r="H1966" t="inlineStr"/>
+      <c r="I1966" t="n">
+        <v>0.8796550326891555</v>
+      </c>
+      <c r="J1966" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1966" t="inlineStr"/>
+    </row>
+    <row r="1967">
+      <c r="A1967" s="1" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0355.png</t>
+        </is>
+      </c>
+      <c r="C1967" t="inlineStr"/>
+      <c r="D1967" t="inlineStr"/>
+      <c r="E1967" t="inlineStr"/>
+      <c r="F1967" t="inlineStr">
+        <is>
+          <t>CC(C)[C@H](NC(=O)CCCCCCCCCCC(=O)N1CCN(C(=O)c2ccc(Nc3nc(C4CC4)cn4c(-c5cn[nH]c5)cnc34)c(F)c2)CC1)C(=O)N1C[C@H](O)C[C@H]1C(=O)NCc1ccc(-c2cncs2)cc1</t>
+        </is>
+      </c>
+      <c r="G1967" t="inlineStr"/>
+      <c r="H1967" t="inlineStr"/>
+      <c r="I1967" t="n">
+        <v>0.893359706950335</v>
+      </c>
+      <c r="J1967" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1967" t="inlineStr"/>
+    </row>
+    <row r="1968">
+      <c r="A1968" s="1" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B1968" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0356.png</t>
+        </is>
+      </c>
+      <c r="C1968" t="inlineStr"/>
+      <c r="D1968" t="inlineStr"/>
+      <c r="E1968" t="inlineStr"/>
+      <c r="F1968" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCc7ccccc7)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1968" t="inlineStr"/>
+      <c r="H1968" t="inlineStr"/>
+      <c r="I1968" t="n">
+        <v>0.8763657578400854</v>
+      </c>
+      <c r="J1968" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1968" t="inlineStr"/>
+    </row>
+    <row r="1969">
+      <c r="A1969" s="1" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0357.png</t>
+        </is>
+      </c>
+      <c r="C1969" t="inlineStr"/>
+      <c r="D1969" t="inlineStr"/>
+      <c r="E1969" t="inlineStr"/>
+      <c r="F1969" t="inlineStr">
+        <is>
+          <t>CCCCCCC(=O)N[C@H]1CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccc(F)cc2)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1969" t="inlineStr"/>
+      <c r="H1969" t="inlineStr"/>
+      <c r="I1969" t="n">
+        <v>0.8875974997602584</v>
+      </c>
+      <c r="J1969" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1969" t="inlineStr"/>
+    </row>
+    <row r="1970">
+      <c r="A1970" s="1" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0358.png</t>
+        </is>
+      </c>
+      <c r="C1970" t="inlineStr"/>
+      <c r="D1970" t="inlineStr"/>
+      <c r="E1970" t="inlineStr"/>
+      <c r="F1970" t="inlineStr">
+        <is>
+          <t>CC(=O)N[C@@H](CCCNC(=N)N)C(=O)N[C@H]1CC(=O)NCCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccccc2)NC(=O)[C@H](COCc2ccccc2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1970" t="inlineStr"/>
+      <c r="H1970" t="inlineStr"/>
+      <c r="I1970" t="n">
+        <v>0.8746741659517021</v>
+      </c>
+      <c r="J1970" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1970" t="inlineStr"/>
+    </row>
+    <row r="1971">
+      <c r="A1971" s="1" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0359.png</t>
+        </is>
+      </c>
+      <c r="C1971" t="inlineStr"/>
+      <c r="D1971" t="inlineStr"/>
+      <c r="E1971" t="inlineStr"/>
+      <c r="F1971" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3ccsc23)cc(OC)c1CN1CCC(CN2CCC3(CC2)CC(Oc2ccc4c(c2)CN(C2CCC(=O)NC2=O)C4=O)C3)CC1</t>
+        </is>
+      </c>
+      <c r="G1971" t="inlineStr"/>
+      <c r="H1971" t="inlineStr"/>
+      <c r="I1971" t="n">
+        <v>0.9114669386075319</v>
+      </c>
+      <c r="J1971" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1971" t="inlineStr"/>
+    </row>
+    <row r="1972">
+      <c r="A1972" s="1" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0360.png</t>
+        </is>
+      </c>
+      <c r="C1972" t="inlineStr"/>
+      <c r="D1972" t="inlineStr"/>
+      <c r="E1972" t="inlineStr"/>
+      <c r="F1972" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCC(=O)N2CCN(C(=O)c3ccc(Nc4nc(C5CC5)cn5c(-c6cn[nH]c6)cnc45)c(F)c3)CC2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1972" t="inlineStr"/>
+      <c r="H1972" t="inlineStr"/>
+      <c r="I1972" t="n">
+        <v>0.9040536334138783</v>
+      </c>
+      <c r="J1972" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1972" t="inlineStr"/>
+    </row>
+    <row r="1973">
+      <c r="A1973" s="1" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0361.png</t>
+        </is>
+      </c>
+      <c r="C1973" t="inlineStr"/>
+      <c r="D1973" t="inlineStr"/>
+      <c r="E1973" t="inlineStr"/>
+      <c r="F1973" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(N)=O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CC)nc2cc(C(N)=O)cc(c21)OCC(N1CCC(C#N)C1)CO3</t>
+        </is>
+      </c>
+      <c r="G1973" t="inlineStr"/>
+      <c r="H1973" t="inlineStr"/>
+      <c r="I1973" t="n">
+        <v>0.9028646505000495</v>
+      </c>
+      <c r="J1973" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1973" t="inlineStr"/>
+    </row>
+    <row r="1974">
+      <c r="A1974" s="1" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0363.png</t>
+        </is>
+      </c>
+      <c r="C1974" t="inlineStr"/>
+      <c r="D1974" t="inlineStr"/>
+      <c r="E1974" t="inlineStr"/>
+      <c r="F1974" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1cc2c(cc1OC(C)=O)Oc1cc(OC(C)=O)c([N+]#[C-])cc1C21OC(=O)c2cc(N3CCOCCOCCN(c4ccccc4OC)CCOCCOCC3)c(OC)cc21</t>
+        </is>
+      </c>
+      <c r="G1974" t="inlineStr"/>
+      <c r="H1974" t="inlineStr"/>
+      <c r="I1974" t="n">
+        <v>0.865204166790979</v>
+      </c>
+      <c r="J1974" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1974" t="inlineStr"/>
+    </row>
+    <row r="1975">
+      <c r="A1975" s="1" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0365.png</t>
+        </is>
+      </c>
+      <c r="C1975" t="inlineStr"/>
+      <c r="D1975" t="inlineStr"/>
+      <c r="E1975" t="inlineStr"/>
+      <c r="F1975" t="inlineStr">
+        <is>
+          <t>CO[C@]1(CN2CCN3CCCC[C@@H]3C2)/C=C/C[C@H](C)[C@@H](C)S(=O)(=O)NC(=O)c2ccc3c(c2)N(C[C@@H]2CC[C@H]21)C[C@@]1(CCCc2cc(Cl)ccc21)CO3</t>
+        </is>
+      </c>
+      <c r="G1975" t="inlineStr"/>
+      <c r="H1975" t="inlineStr"/>
+      <c r="I1975" t="n">
+        <v>0.8529773906503014</v>
+      </c>
+      <c r="J1975" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1975" t="inlineStr"/>
+    </row>
+    <row r="1976">
+      <c r="A1976" s="1" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0368.png</t>
+        </is>
+      </c>
+      <c r="C1976" t="inlineStr"/>
+      <c r="D1976" t="inlineStr"/>
+      <c r="E1976" t="inlineStr"/>
+      <c r="F1976" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NC4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6)CC4(F)F)sc23)cc(F)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G1976" t="inlineStr"/>
+      <c r="H1976" t="inlineStr"/>
+      <c r="I1976" t="n">
+        <v>0.9139359860736135</v>
+      </c>
+      <c r="J1976" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1976" t="inlineStr"/>
+    </row>
+    <row r="1977">
+      <c r="A1977" s="1" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0369.png</t>
+        </is>
+      </c>
+      <c r="C1977" t="inlineStr"/>
+      <c r="D1977" t="inlineStr"/>
+      <c r="E1977" t="inlineStr"/>
+      <c r="F1977" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2cc3c(cc2OC)C2(OC3=O)c3ccc(OC(C)=O)cc3C(C)(C)c3cc(OC(C)=O)ccc32)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1977" t="inlineStr"/>
+      <c r="H1977" t="inlineStr"/>
+      <c r="I1977" t="n">
+        <v>0.903812783907507</v>
+      </c>
+      <c r="J1977" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1977" t="inlineStr"/>
+    </row>
+    <row r="1978">
+      <c r="A1978" s="1" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0370.png</t>
+        </is>
+      </c>
+      <c r="C1978" t="inlineStr"/>
+      <c r="D1978" t="inlineStr"/>
+      <c r="E1978" t="inlineStr"/>
+      <c r="F1978" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2c(C)n(C)c(=O)c3ccsc23)cc(OC)c1CN1CCC2(CC1)CN(c1ccc3c(c1)C(=O)N(C1CCC(=O)NC1=O)C3)C2</t>
+        </is>
+      </c>
+      <c r="G1978" t="inlineStr"/>
+      <c r="H1978" t="inlineStr"/>
+      <c r="I1978" t="n">
+        <v>0.911571018148045</v>
+      </c>
+      <c r="J1978" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1978" t="inlineStr"/>
+    </row>
+    <row r="1979">
+      <c r="A1979" s="1" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0371.png</t>
+        </is>
+      </c>
+      <c r="C1979" t="inlineStr"/>
+      <c r="D1979" t="inlineStr"/>
+      <c r="E1979" t="inlineStr"/>
+      <c r="F1979" t="inlineStr">
+        <is>
+          <t>CC(=O)N[C@@H](CCCNC(=N)N)C(=O)N[C@H]1CC(=O)NCCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccccc2)NC(=O)[C@H](CC(N)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1979" t="inlineStr"/>
+      <c r="H1979" t="inlineStr"/>
+      <c r="I1979" t="n">
+        <v>0.8618308133792784</v>
+      </c>
+      <c r="J1979" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1979" t="inlineStr"/>
+    </row>
+    <row r="1980">
+      <c r="A1980" s="1" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0372.png</t>
+        </is>
+      </c>
+      <c r="C1980" t="inlineStr"/>
+      <c r="D1980" t="inlineStr"/>
+      <c r="E1980" t="inlineStr"/>
+      <c r="F1980" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NCC4CC5CN(CCN6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5C4)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G1980" t="inlineStr"/>
+      <c r="H1980" t="inlineStr"/>
+      <c r="I1980" t="n">
+        <v>0.8744846656031208</v>
+      </c>
+      <c r="J1980" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1980" t="inlineStr"/>
+    </row>
+    <row r="1981">
+      <c r="A1981" s="1" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0373.png</t>
+        </is>
+      </c>
+      <c r="C1981" t="inlineStr"/>
+      <c r="D1981" t="inlineStr"/>
+      <c r="E1981" t="inlineStr"/>
+      <c r="F1981" t="inlineStr">
+        <is>
+          <t>O=C(CN1CCN(C(=O)c2ccc(Nc3nc(C4CC4)cn4c(-c5cn[nH]c5)cnc34)c(F)c2)CC1)NCCOCCNc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O</t>
+        </is>
+      </c>
+      <c r="G1981" t="inlineStr"/>
+      <c r="H1981" t="inlineStr"/>
+      <c r="I1981" t="n">
+        <v>0.9050318249155687</v>
+      </c>
+      <c r="J1981" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1981" t="inlineStr"/>
+    </row>
+    <row r="1982">
+      <c r="A1982" s="1" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0374.png</t>
+        </is>
+      </c>
+      <c r="C1982" t="inlineStr"/>
+      <c r="D1982" t="inlineStr"/>
+      <c r="E1982" t="inlineStr"/>
+      <c r="F1982" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)N[C@@H]4CCN(C5CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7)CC5)CC4(F)I)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G1982" t="inlineStr"/>
+      <c r="H1982" t="inlineStr"/>
+      <c r="I1982" t="n">
+        <v>0.8853873734020375</v>
+      </c>
+      <c r="J1982" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1982" t="inlineStr"/>
+    </row>
+    <row r="1983">
+      <c r="A1983" s="1" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0375.png</t>
+        </is>
+      </c>
+      <c r="C1983" t="inlineStr"/>
+      <c r="D1983" t="inlineStr"/>
+      <c r="E1983" t="inlineStr"/>
+      <c r="F1983" t="inlineStr">
+        <is>
+          <t>COc1cc2c(cc1N1CCOCCOCCN(c3ccccc3Oc3ccccc3)CCOCC1)C(=O)OC21c2cc(-c3c(F)c(F)c(F)c(F)c3F)c(OC(C)=O)cc2Oc2cc(OC(C)=O)c(-c3c(F)c(F)c(F)c(F)c3F)cc21</t>
+        </is>
+      </c>
+      <c r="G1983" t="inlineStr"/>
+      <c r="H1983" t="inlineStr"/>
+      <c r="I1983" t="n">
+        <v>0.8935581716940159</v>
+      </c>
+      <c r="J1983" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1983" t="inlineStr"/>
+    </row>
+    <row r="1984">
+      <c r="A1984" s="1" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0376.png</t>
+        </is>
+      </c>
+      <c r="C1984" t="inlineStr"/>
+      <c r="D1984" t="inlineStr"/>
+      <c r="E1984" t="inlineStr"/>
+      <c r="F1984" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccc2c(c1)CCCOc1cc(ccc1Cc1nc3c(OCCN(CC(F)(F)F)C(=O)OC(C)(C)C)cc(C(=O)O)cc3n1C[C@@H]1CCO1)-c1cccc(n1)OC2</t>
+        </is>
+      </c>
+      <c r="G1984" t="inlineStr"/>
+      <c r="H1984" t="inlineStr"/>
+      <c r="I1984" t="n">
+        <v>0.8823693886361508</v>
+      </c>
+      <c r="J1984" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1984" t="inlineStr"/>
+    </row>
+    <row r="1985">
+      <c r="A1985" s="1" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0377.png</t>
+        </is>
+      </c>
+      <c r="C1985" t="inlineStr"/>
+      <c r="D1985" t="inlineStr"/>
+      <c r="E1985" t="inlineStr"/>
+      <c r="F1985" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccc(F)cc2)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1985" t="inlineStr"/>
+      <c r="H1985" t="inlineStr"/>
+      <c r="I1985" t="n">
+        <v>0.8858385419431706</v>
+      </c>
+      <c r="J1985" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1985" t="inlineStr"/>
+    </row>
+    <row r="1986">
+      <c r="A1986" s="1" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0378.png</t>
+        </is>
+      </c>
+      <c r="C1986" t="inlineStr"/>
+      <c r="D1986" t="inlineStr"/>
+      <c r="E1986" t="inlineStr"/>
+      <c r="F1986" t="inlineStr">
+        <is>
+          <t>CC(C)(C)Cc1cc(CSCCNC(=O)CN2CCN(CC(=O)O)CCN(CC(=O)O)CCN(CC(=O)O)CC2)cc(CSC[C@H](N)C(=O)O)c1</t>
+        </is>
+      </c>
+      <c r="G1986" t="inlineStr"/>
+      <c r="H1986" t="inlineStr"/>
+      <c r="I1986" t="n">
+        <v>0.876920654731052</v>
+      </c>
+      <c r="J1986" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1986" t="inlineStr"/>
+    </row>
+    <row r="1987">
+      <c r="A1987" s="1" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0380.png</t>
+        </is>
+      </c>
+      <c r="C1987" t="inlineStr"/>
+      <c r="D1987" t="inlineStr"/>
+      <c r="E1987" t="inlineStr"/>
+      <c r="F1987" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccc3ccccc3c2)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1987" t="inlineStr"/>
+      <c r="H1987" t="inlineStr"/>
+      <c r="I1987" t="n">
+        <v>0.8872361807738042</v>
+      </c>
+      <c r="J1987" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1987" t="inlineStr"/>
+    </row>
+    <row r="1988">
+      <c r="A1988" s="1" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0381.png</t>
+        </is>
+      </c>
+      <c r="C1988" t="inlineStr"/>
+      <c r="D1988" t="inlineStr"/>
+      <c r="E1988" t="inlineStr"/>
+      <c r="F1988" t="inlineStr">
+        <is>
+          <t>COC(=O)c1cc(OCCN(C)C(=O)OC(C)(C)C)c2nc(Cc3ccc4cc3COCCc3cc(Cl)ccc3COc3cccc-4n3)n(C[C@@H]3CCO3)c2c1</t>
+        </is>
+      </c>
+      <c r="G1988" t="inlineStr"/>
+      <c r="H1988" t="inlineStr"/>
+      <c r="I1988" t="n">
+        <v>0.9008766647523581</v>
+      </c>
+      <c r="J1988" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1988" t="inlineStr"/>
+    </row>
+    <row r="1989">
+      <c r="A1989" s="1" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0382.png</t>
+        </is>
+      </c>
+      <c r="C1989" t="inlineStr"/>
+      <c r="D1989" t="inlineStr"/>
+      <c r="E1989" t="inlineStr"/>
+      <c r="F1989" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2cccc3ccccc23)NC(=O)[C@H](CC(N)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1989" t="inlineStr"/>
+      <c r="H1989" t="inlineStr"/>
+      <c r="I1989" t="n">
+        <v>0.8919358648650831</v>
+      </c>
+      <c r="J1989" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1989" t="inlineStr"/>
+    </row>
+    <row r="1990">
+      <c r="A1990" s="1" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0383.png</t>
+        </is>
+      </c>
+      <c r="C1990" t="inlineStr"/>
+      <c r="D1990" t="inlineStr"/>
+      <c r="E1990" t="inlineStr"/>
+      <c r="F1990" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)N(C)C)sc23)cc(OC)c1CN1CCC2(CC1)CN(c1ccc3c(c1)C(=O)N(C1CCC(=O)NC1=O)C3)C2</t>
+        </is>
+      </c>
+      <c r="G1990" t="inlineStr"/>
+      <c r="H1990" t="inlineStr"/>
+      <c r="I1990" t="n">
+        <v>0.9094989898799667</v>
+      </c>
+      <c r="J1990" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1990" t="inlineStr"/>
+    </row>
+    <row r="1991">
+      <c r="A1991" s="1" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0384.png</t>
+        </is>
+      </c>
+      <c r="C1991" t="inlineStr"/>
+      <c r="D1991" t="inlineStr"/>
+      <c r="E1991" t="inlineStr"/>
+      <c r="F1991" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(N)=O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CC)nc2cc(C(N)=O)cc(c21)OCCCO3</t>
+        </is>
+      </c>
+      <c r="G1991" t="inlineStr"/>
+      <c r="H1991" t="inlineStr"/>
+      <c r="I1991" t="n">
+        <v>0.8971573283053585</v>
+      </c>
+      <c r="J1991" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1991" t="inlineStr"/>
+    </row>
+    <row r="1992">
+      <c r="A1992" s="1" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0385.png</t>
+        </is>
+      </c>
+      <c r="C1992" t="inlineStr"/>
+      <c r="D1992" t="inlineStr"/>
+      <c r="E1992" t="inlineStr"/>
+      <c r="F1992" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(=O)O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CC)nc2cc(C(=O)O)cc(c21)OCC(N1C2CCC1COC2)CO3</t>
+        </is>
+      </c>
+      <c r="G1992" t="inlineStr"/>
+      <c r="H1992" t="inlineStr"/>
+      <c r="I1992" t="n">
+        <v>0.8757477615157473</v>
+      </c>
+      <c r="J1992" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1992" t="inlineStr"/>
+    </row>
+    <row r="1993">
+      <c r="A1993" s="1" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0387.png</t>
+        </is>
+      </c>
+      <c r="C1993" t="inlineStr"/>
+      <c r="D1993" t="inlineStr"/>
+      <c r="E1993" t="inlineStr"/>
+      <c r="F1993" t="inlineStr">
+        <is>
+          <t>COC1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCC7CCN(C)CC7)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H]([O][Ac])[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1993" t="inlineStr"/>
+      <c r="H1993" t="inlineStr"/>
+      <c r="I1993" t="n">
+        <v>0.8620724037771722</v>
+      </c>
+      <c r="J1993" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1993" t="inlineStr"/>
+    </row>
+    <row r="1994">
+      <c r="A1994" s="1" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0389.png</t>
+        </is>
+      </c>
+      <c r="C1994" t="inlineStr"/>
+      <c r="D1994" t="inlineStr"/>
+      <c r="E1994" t="inlineStr"/>
+      <c r="F1994" t="inlineStr">
+        <is>
+          <t>CCCC[C@@H](NC(C)=O)C(=O)N[C@H]1CC(=O)NCCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2cccc3ccccc23)NC(=O)[C@H](CCS(C)(=O)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1994" t="inlineStr"/>
+      <c r="H1994" t="inlineStr"/>
+      <c r="I1994" t="n">
+        <v>0.8770723760187015</v>
+      </c>
+      <c r="J1994" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1994" t="inlineStr"/>
+    </row>
+    <row r="1995">
+      <c r="A1995" s="1" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0390.png</t>
+        </is>
+      </c>
+      <c r="C1995" t="inlineStr"/>
+      <c r="D1995" t="inlineStr"/>
+      <c r="E1995" t="inlineStr"/>
+      <c r="F1995" t="inlineStr">
+        <is>
+          <t>NC(=O)c1cc(-c2cn(CCCC(=O)NCCCCCNc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)cn2)cnc1O[C@@H]1CCN(C(=O)Cc2ccc(OC(F)(F)F)cc2)C[C@H]1F</t>
+        </is>
+      </c>
+      <c r="G1995" t="inlineStr"/>
+      <c r="H1995" t="inlineStr"/>
+      <c r="I1995" t="n">
+        <v>0.8470830977281747</v>
+      </c>
+      <c r="J1995" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1995" t="inlineStr"/>
+    </row>
+    <row r="1996">
+      <c r="A1996" s="1" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0391.png</t>
+        </is>
+      </c>
+      <c r="C1996" t="inlineStr"/>
+      <c r="D1996" t="inlineStr"/>
+      <c r="E1996" t="inlineStr"/>
+      <c r="F1996" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2cc(C(=O)O)c(-c3c4cc(-c5cccs5)c(=O)cc-4oc4cc(O)c(-c5ccsc5)cc34)cc2OC)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1996" t="inlineStr"/>
+      <c r="H1996" t="inlineStr"/>
+      <c r="I1996" t="n">
+        <v>0.8975292361090668</v>
+      </c>
+      <c r="J1996" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1996" t="inlineStr"/>
+    </row>
+    <row r="1997">
+      <c r="A1997" s="1" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0392.png</t>
+        </is>
+      </c>
+      <c r="C1997" t="inlineStr"/>
+      <c r="D1997" t="inlineStr"/>
+      <c r="E1997" t="inlineStr"/>
+      <c r="F1997" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(NC(=O)[C@H]4CCCN(C(=O)CCCCOc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G1997" t="inlineStr"/>
+      <c r="H1997" t="inlineStr"/>
+      <c r="I1997" t="n">
+        <v>0.9121083753252237</v>
+      </c>
+      <c r="J1997" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1997" t="inlineStr"/>
+    </row>
+    <row r="1998">
+      <c r="A1998" s="1" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0393.png</t>
+        </is>
+      </c>
+      <c r="C1998" t="inlineStr"/>
+      <c r="D1998" t="inlineStr"/>
+      <c r="E1998" t="inlineStr"/>
+      <c r="F1998" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(N)=O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CC)nc2cc(C(N)=O)cc(c21)OCC(N1CCC1)CO3</t>
+        </is>
+      </c>
+      <c r="G1998" t="inlineStr"/>
+      <c r="H1998" t="inlineStr"/>
+      <c r="I1998" t="n">
+        <v>0.882076970493115</v>
+      </c>
+      <c r="J1998" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1998" t="inlineStr"/>
+    </row>
+    <row r="1999">
+      <c r="A1999" s="1" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0394.png</t>
+        </is>
+      </c>
+      <c r="C1999" t="inlineStr"/>
+      <c r="D1999" t="inlineStr"/>
+      <c r="E1999" t="inlineStr"/>
+      <c r="F1999" t="inlineStr">
+        <is>
+          <t>CCCCC(NC(C)=O)C(=O)NC1CCC(=O)NCCCCNC(=O)C(CC2=CNC3=C2C=CC=C3)NC(=O)C(CCCNC(=N)N)NC(=O)C(CC2=C(N(=O)O)C=CC=C2)NC(=O)C(CC2=CNC=N2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1999" t="inlineStr"/>
+      <c r="H1999" t="inlineStr"/>
+      <c r="I1999" t="n">
+        <v>0.8752275992991595</v>
+      </c>
+      <c r="J1999" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K1999" t="inlineStr"/>
+    </row>
+    <row r="2000">
+      <c r="A2000" s="1" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0395.png</t>
+        </is>
+      </c>
+      <c r="C2000" t="inlineStr"/>
+      <c r="D2000" t="inlineStr"/>
+      <c r="E2000" t="inlineStr"/>
+      <c r="F2000" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(NC(=O)C4CCN(C(=O)CCCCOc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2000" t="inlineStr"/>
+      <c r="H2000" t="inlineStr"/>
+      <c r="I2000" t="n">
+        <v>0.9079872583285036</v>
+      </c>
+      <c r="J2000" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2000" t="inlineStr"/>
+    </row>
+    <row r="2001">
+      <c r="A2001" s="1" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0396.png</t>
+        </is>
+      </c>
+      <c r="C2001" t="inlineStr"/>
+      <c r="D2001" t="inlineStr"/>
+      <c r="E2001" t="inlineStr"/>
+      <c r="F2001" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCN7CCN(C)CC7)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G2001" t="inlineStr"/>
+      <c r="H2001" t="inlineStr"/>
+      <c r="I2001" t="n">
+        <v>0.8958139674716522</v>
+      </c>
+      <c r="J2001" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2001" t="inlineStr"/>
+    </row>
+    <row r="2002">
+      <c r="A2002" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0397.png</t>
+        </is>
+      </c>
+      <c r="C2002" t="inlineStr"/>
+      <c r="D2002" t="inlineStr"/>
+      <c r="E2002" t="inlineStr"/>
+      <c r="F2002" t="inlineStr">
+        <is>
+          <t>N=C(N)NCCC[C@@H]1NC(=O)[C@@H](Cc2ccc(F)cc2)NC(=O)[C@H](Cc2c[nH]cn2)NC(=O)[C@@H](NC(=O)CC2CCCC2)CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2002" t="inlineStr"/>
+      <c r="H2002" t="inlineStr"/>
+      <c r="I2002" t="n">
+        <v>0.8838225847936426</v>
+      </c>
+      <c r="J2002" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2002" t="inlineStr"/>
+    </row>
+    <row r="2003">
+      <c r="A2003" s="1" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0398.png</t>
+        </is>
+      </c>
+      <c r="C2003" t="inlineStr"/>
+      <c r="D2003" t="inlineStr"/>
+      <c r="E2003" t="inlineStr"/>
+      <c r="F2003" t="inlineStr">
+        <is>
+          <t>CO[C@H]1C[C@@H]2CC[C@@H](C)[C@@](O)(O2)C(=O)C(=O)N2CCCC[C@H]2C(=O)C[C@H]([C@H](C)C[C@@H]2CC[C@@H](O)[C@H](OC)C2)CC(=O)[C@H](C)/C=C(\C)[C@@H](O)[C@@H](OC)C(=O)[C@H](C)C[C@H](C)/C=C/C=C/C=C/1C</t>
+        </is>
+      </c>
+      <c r="G2003" t="inlineStr"/>
+      <c r="H2003" t="inlineStr"/>
+      <c r="I2003" t="n">
+        <v>0.9020690945270304</v>
+      </c>
+      <c r="J2003" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2003" t="inlineStr"/>
+    </row>
+    <row r="2004">
+      <c r="A2004" s="1" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0400.png</t>
+        </is>
+      </c>
+      <c r="C2004" t="inlineStr"/>
+      <c r="D2004" t="inlineStr"/>
+      <c r="E2004" t="inlineStr"/>
+      <c r="F2004" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCCN)NC(=O)[C@H](CCN)NCc2cccnc2Sc2c(Cl)ccc(-c3ccc(C(=O)O)cc3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G2004" t="inlineStr"/>
+      <c r="H2004" t="inlineStr"/>
+      <c r="I2004" t="n">
+        <v>0.8946680328585113</v>
+      </c>
+      <c r="J2004" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2004" t="inlineStr"/>
+    </row>
+    <row r="2005">
+      <c r="A2005" s="1" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0401.png</t>
+        </is>
+      </c>
+      <c r="C2005" t="inlineStr"/>
+      <c r="D2005" t="inlineStr"/>
+      <c r="E2005" t="inlineStr"/>
+      <c r="F2005" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3sccc23)cc(OC)c1CN1CCC(CN2CCC3(CC2)CC(Oc2ccc4c(c2)CN(C2CCC(=O)NC2=O)C4=O)C3)CC1</t>
+        </is>
+      </c>
+      <c r="G2005" t="inlineStr"/>
+      <c r="H2005" t="inlineStr"/>
+      <c r="I2005" t="n">
+        <v>0.9037881669689727</v>
+      </c>
+      <c r="J2005" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2005" t="inlineStr"/>
+    </row>
+    <row r="2006">
+      <c r="A2006" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0404.png</t>
+        </is>
+      </c>
+      <c r="C2006" t="inlineStr"/>
+      <c r="D2006" t="inlineStr"/>
+      <c r="E2006" t="inlineStr"/>
+      <c r="F2006" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CCC(=O)NCCCCNC(=O)[C@@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccc3ccccc3c2)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2006" t="inlineStr"/>
+      <c r="H2006" t="inlineStr"/>
+      <c r="I2006" t="n">
+        <v>0.8953514706212504</v>
+      </c>
+      <c r="J2006" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2006" t="inlineStr"/>
+    </row>
+    <row r="2007">
+      <c r="A2007" s="1" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0406.png</t>
+        </is>
+      </c>
+      <c r="C2007" t="inlineStr"/>
+      <c r="D2007" t="inlineStr"/>
+      <c r="E2007" t="inlineStr"/>
+      <c r="F2007" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(N)=O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CC)nc2cc(C(N)=O)cc(c21)OCC(C1CN(C)C1)CO3</t>
+        </is>
+      </c>
+      <c r="G2007" t="inlineStr"/>
+      <c r="H2007" t="inlineStr"/>
+      <c r="I2007" t="n">
+        <v>0.9029138362181804</v>
+      </c>
+      <c r="J2007" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2007" t="inlineStr"/>
+    </row>
+    <row r="2008">
+      <c r="A2008" s="1" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0407.png</t>
+        </is>
+      </c>
+      <c r="C2008" t="inlineStr"/>
+      <c r="D2008" t="inlineStr"/>
+      <c r="E2008" t="inlineStr"/>
+      <c r="F2008" t="inlineStr">
+        <is>
+          <t>CCCCCC(=O)N[C@H]1CCC(=O)NCCNC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccccc2)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2008" t="inlineStr"/>
+      <c r="H2008" t="inlineStr"/>
+      <c r="I2008" t="n">
+        <v>0.8896294842125557</v>
+      </c>
+      <c r="J2008" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2008" t="inlineStr"/>
+    </row>
+    <row r="2009">
+      <c r="A2009" s="1" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0409.png</t>
+        </is>
+      </c>
+      <c r="C2009" t="inlineStr"/>
+      <c r="D2009" t="inlineStr"/>
+      <c r="E2009" t="inlineStr"/>
+      <c r="F2009" t="inlineStr">
+        <is>
+          <t>CN(C)C(=O)c1ccc(-c2ccc3c(c2)CCCOc2cc(ccc2Cc2nc4ccc(C(=O)O)cc4n2C[C@@H]2CCO2)-c2cccc(n2)OC3)cc1</t>
+        </is>
+      </c>
+      <c r="G2009" t="inlineStr"/>
+      <c r="H2009" t="inlineStr"/>
+      <c r="I2009" t="n">
+        <v>0.8962443635778076</v>
+      </c>
+      <c r="J2009" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2009" t="inlineStr"/>
+    </row>
+    <row r="2010">
+      <c r="A2010" s="1" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0410.png</t>
+        </is>
+      </c>
+      <c r="C2010" t="inlineStr"/>
+      <c r="D2010" t="inlineStr"/>
+      <c r="E2010" t="inlineStr"/>
+      <c r="F2010" t="inlineStr">
+        <is>
+          <t>[H][C@]12CC(C)(C)[C@@H](C(=O)N[C@H]3c4ccccc4C[C@H]3OCCS(=O)(=O)CCO[C@@H]3Cc4ccccc4[C@@H]3NC(=O)[C@H]3N4C(=O)[C@@H](NC(=O)[C@H](C)NC)CCS[C@@]4([H])CC3(C)C)N1C(=O)[C@@H](NC(=O)[C@H](C)NC)CCS2</t>
+        </is>
+      </c>
+      <c r="G2010" t="inlineStr"/>
+      <c r="H2010" t="inlineStr"/>
+      <c r="I2010" t="n">
+        <v>0.8788776161884838</v>
+      </c>
+      <c r="J2010" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2010" t="inlineStr"/>
+    </row>
+    <row r="2011">
+      <c r="A2011" s="1" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0411.png</t>
+        </is>
+      </c>
+      <c r="C2011" t="inlineStr"/>
+      <c r="D2011" t="inlineStr"/>
+      <c r="E2011" t="inlineStr"/>
+      <c r="F2011" t="inlineStr">
+        <is>
+          <t>COc1cc(Cn2ncc3ccc(C(=O)OC4CCCOc5cc(cc(OC)c5OC)C(=O)OCCCN5CCCN(CC4)CC5)cc32)cc(OC)c1OC</t>
+        </is>
+      </c>
+      <c r="G2011" t="inlineStr"/>
+      <c r="H2011" t="inlineStr"/>
+      <c r="I2011" t="n">
+        <v>0.9066057327622368</v>
+      </c>
+      <c r="J2011" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2011" t="inlineStr"/>
+    </row>
+    <row r="2012">
+      <c r="A2012" s="1" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0412.png</t>
+        </is>
+      </c>
+      <c r="C2012" t="inlineStr"/>
+      <c r="D2012" t="inlineStr"/>
+      <c r="E2012" t="inlineStr"/>
+      <c r="F2012" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NC4CCC5CN(CCCN6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC54)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2012" t="inlineStr"/>
+      <c r="H2012" t="inlineStr"/>
+      <c r="I2012" t="n">
+        <v>0.8928467076268894</v>
+      </c>
+      <c r="J2012" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2012" t="inlineStr"/>
+    </row>
+    <row r="2013">
+      <c r="A2013" s="1" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0413.png</t>
+        </is>
+      </c>
+      <c r="C2013" t="inlineStr"/>
+      <c r="D2013" t="inlineStr"/>
+      <c r="E2013" t="inlineStr"/>
+      <c r="F2013" t="inlineStr">
+        <is>
+          <t>CC(=O)N[C@@H](CCCNC(=N)N)C(=O)N[C@H]1CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccccc2)NC(=O)[C@H](CC(N)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2013" t="inlineStr"/>
+      <c r="H2013" t="inlineStr"/>
+      <c r="I2013" t="n">
+        <v>0.8847969220256467</v>
+      </c>
+      <c r="J2013" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2013" t="inlineStr"/>
+    </row>
+    <row r="2014">
+      <c r="A2014" s="1" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0414.png</t>
+        </is>
+      </c>
+      <c r="C2014" t="inlineStr"/>
+      <c r="D2014" t="inlineStr"/>
+      <c r="E2014" t="inlineStr"/>
+      <c r="F2014" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3ncsc23)cc(OC)c1CN1CCC2(CC1)CN(c1ccc3c(c1)C(=O)N(C1CCC(=O)NC1=O)C3=O)C2</t>
+        </is>
+      </c>
+      <c r="G2014" t="inlineStr"/>
+      <c r="H2014" t="inlineStr"/>
+      <c r="I2014" t="n">
+        <v>0.9103401730128133</v>
+      </c>
+      <c r="J2014" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2014" t="inlineStr"/>
+    </row>
+    <row r="2015">
+      <c r="A2015" s="1" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0415.png</t>
+        </is>
+      </c>
+      <c r="C2015" t="inlineStr"/>
+      <c r="D2015" t="inlineStr"/>
+      <c r="E2015" t="inlineStr"/>
+      <c r="F2015" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccc2c(c1)CCCOc1cc(ccc1Cc1nc3c(OCCN(CC(F)(F)F)C(=O)OC(C)(C)C)cc(C(=O)OC)cc3n1C[C@@H]1CCO1)-c1cccc(n1)OC2</t>
+        </is>
+      </c>
+      <c r="G2015" t="inlineStr"/>
+      <c r="H2015" t="inlineStr"/>
+      <c r="I2015" t="n">
+        <v>0.8890849056879688</v>
+      </c>
+      <c r="J2015" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2015" t="inlineStr"/>
+    </row>
+    <row r="2016">
+      <c r="A2016" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0418.png</t>
+        </is>
+      </c>
+      <c r="C2016" t="inlineStr"/>
+      <c r="D2016" t="inlineStr"/>
+      <c r="E2016" t="inlineStr"/>
+      <c r="F2016" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(N)=O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CC)nc2cc(C(N)=O)cc(c21)OCC(N1CC[C@H](OC)C1)CO3.S</t>
+        </is>
+      </c>
+      <c r="G2016" t="inlineStr"/>
+      <c r="H2016" t="inlineStr"/>
+      <c r="I2016" t="n">
+        <v>0.8724792007154151</v>
+      </c>
+      <c r="J2016" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2016" t="inlineStr"/>
+    </row>
+    <row r="2017">
+      <c r="A2017" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0419.png</t>
+        </is>
+      </c>
+      <c r="C2017" t="inlineStr"/>
+      <c r="D2017" t="inlineStr"/>
+      <c r="E2017" t="inlineStr"/>
+      <c r="F2017" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NC4CCN(C5CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7)CC5)CC4)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2017" t="inlineStr"/>
+      <c r="H2017" t="inlineStr"/>
+      <c r="I2017" t="n">
+        <v>0.9038214529776569</v>
+      </c>
+      <c r="J2017" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2017" t="inlineStr"/>
+    </row>
+    <row r="2018">
+      <c r="A2018" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B2018" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0420.png</t>
+        </is>
+      </c>
+      <c r="C2018" t="inlineStr"/>
+      <c r="D2018" t="inlineStr"/>
+      <c r="E2018" t="inlineStr"/>
+      <c r="F2018" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCC7CCCN7C)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G2018" t="inlineStr"/>
+      <c r="H2018" t="inlineStr"/>
+      <c r="I2018" t="n">
+        <v>0.8908079686822975</v>
+      </c>
+      <c r="J2018" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2018" t="inlineStr"/>
+    </row>
+    <row r="2019">
+      <c r="A2019" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B2019" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0421.png</t>
+        </is>
+      </c>
+      <c r="C2019" t="inlineStr"/>
+      <c r="D2019" t="inlineStr"/>
+      <c r="E2019" t="inlineStr"/>
+      <c r="F2019" t="inlineStr">
+        <is>
+          <t>Cc1cc(-c2nc(-c3ccc(N4CCC(CN5CC=C(c6ccc7c(c6F)CN(C6CCC(=O)NC6=O)C7=O)CC5)CC4)nc3)cn3nccc23)ccc1[C@@H](C)NC(=O)c1nnn(C(C)(C)C)n1</t>
+        </is>
+      </c>
+      <c r="G2019" t="inlineStr"/>
+      <c r="H2019" t="inlineStr"/>
+      <c r="I2019" t="n">
+        <v>0.9150126193014807</v>
+      </c>
+      <c r="J2019" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2019" t="inlineStr"/>
+    </row>
+    <row r="2020">
+      <c r="A2020" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B2020" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0424.png</t>
+        </is>
+      </c>
+      <c r="C2020" t="inlineStr"/>
+      <c r="D2020" t="inlineStr"/>
+      <c r="E2020" t="inlineStr"/>
+      <c r="F2020" t="inlineStr">
+        <is>
+          <t>O=C(CN1CCN(C(=O)c2ccc(Nc3nc(C4CC4)cn4c(-c5cn[nH]c5)cnc34)c(F)c2)CC1)NCCOCCOCCOCCOCCOCCNc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O</t>
+        </is>
+      </c>
+      <c r="G2020" t="inlineStr"/>
+      <c r="H2020" t="inlineStr"/>
+      <c r="I2020" t="n">
+        <v>0.8896225357610409</v>
+      </c>
+      <c r="J2020" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2020" t="inlineStr"/>
+    </row>
+    <row r="2021">
+      <c r="A2021" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0425.png</t>
+        </is>
+      </c>
+      <c r="C2021" t="inlineStr"/>
+      <c r="D2021" t="inlineStr"/>
+      <c r="E2021" t="inlineStr"/>
+      <c r="F2021" t="inlineStr">
+        <is>
+          <t>Cc1cc([C@H](C(=O)N2C[C@H](O)C[C@H]2C(=O)N[C@@H](CC(=O)NCCOCCNC(=O)CN2CCN(C(=O)c3ccc(Nc4nc(C5CC5)cn5c(-c6cn[nH]c6)cnc45)c(F)c3)CC2)c2ccc(-c3scnc3C)cc2)C(C)C)on1</t>
+        </is>
+      </c>
+      <c r="G2021" t="inlineStr"/>
+      <c r="H2021" t="inlineStr"/>
+      <c r="I2021" t="n">
+        <v>0.8654634168001581</v>
+      </c>
+      <c r="J2021" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2021" t="inlineStr"/>
+    </row>
+    <row r="2022">
+      <c r="A2022" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B2022" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0426.png</t>
+        </is>
+      </c>
+      <c r="C2022" t="inlineStr"/>
+      <c r="D2022" t="inlineStr"/>
+      <c r="E2022" t="inlineStr"/>
+      <c r="F2022" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCNC(=O)OC(C)(C)C)NC(=O)[C@H](CCCNC(=O)OC(C)(C)C)NCc2cccnc2Sc2cccc(Br)c2CNC(=O)[C@@H]1Cc1cn(C(=O)OC(C)(C)C)c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G2022" t="inlineStr"/>
+      <c r="H2022" t="inlineStr"/>
+      <c r="I2022" t="n">
+        <v>0.9038079969425942</v>
+      </c>
+      <c r="J2022" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2022" t="inlineStr"/>
+    </row>
+    <row r="2023">
+      <c r="A2023" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0427.png</t>
+        </is>
+      </c>
+      <c r="C2023" t="inlineStr"/>
+      <c r="D2023" t="inlineStr"/>
+      <c r="E2023" t="inlineStr"/>
+      <c r="F2023" t="inlineStr">
+        <is>
+          <t>COc1cc2c(=O)n(C)cc(-c3cc(OC)c(CN4CCC5(CC4)CN(c4ccc6c(c4)C(=O)N(C4CCC(=O)NC4=O)C6)C5)c(OC)c3)c2s1</t>
+        </is>
+      </c>
+      <c r="G2023" t="inlineStr"/>
+      <c r="H2023" t="inlineStr"/>
+      <c r="I2023" t="n">
+        <v>0.9135400592919903</v>
+      </c>
+      <c r="J2023" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2023" t="inlineStr"/>
+    </row>
+    <row r="2024">
+      <c r="A2024" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B2024" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0429.png</t>
+        </is>
+      </c>
+      <c r="C2024" t="inlineStr"/>
+      <c r="D2024" t="inlineStr"/>
+      <c r="E2024" t="inlineStr"/>
+      <c r="F2024" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3ccsc23)cc(OC)c1CN1CCC(CN2CCC3(CC2)CN(c2ccc4c(c2)C(=O)N(C2CCC(=O)NC2=O)C4)C3)CC1</t>
+        </is>
+      </c>
+      <c r="G2024" t="inlineStr"/>
+      <c r="H2024" t="inlineStr"/>
+      <c r="I2024" t="n">
+        <v>0.9147530437322202</v>
+      </c>
+      <c r="J2024" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2024" t="inlineStr"/>
+    </row>
+    <row r="2025">
+      <c r="A2025" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0430.png</t>
+        </is>
+      </c>
+      <c r="C2025" t="inlineStr"/>
+      <c r="D2025" t="inlineStr"/>
+      <c r="E2025" t="inlineStr"/>
+      <c r="F2025" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCCN)NC(=O)[C@H](CCCN)NCc2cccnc2Sc2cncc(-c3ccc(C(=O)O)cc3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G2025" t="inlineStr"/>
+      <c r="H2025" t="inlineStr"/>
+      <c r="I2025" t="n">
+        <v>0.8981760576827169</v>
+      </c>
+      <c r="J2025" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2025" t="inlineStr"/>
+    </row>
+    <row r="2026">
+      <c r="A2026" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0431.png</t>
+        </is>
+      </c>
+      <c r="C2026" t="inlineStr"/>
+      <c r="D2026" t="inlineStr"/>
+      <c r="E2026" t="inlineStr"/>
+      <c r="F2026" t="inlineStr">
+        <is>
+          <t>CC(C)(C)[C@H](NC(=O)CCOCCOCCNC(=O)CN1CCN(C(=O)c2ccc(Nc3nc(C4CC4)cn4c(-c5cn[nH]c5)cnc34)c(F)c2)CC1)C(=O)N1C[C@H](O)C[C@H]1C(=O)NCc1ccc(-c2cncs2)cc1</t>
+        </is>
+      </c>
+      <c r="G2026" t="inlineStr"/>
+      <c r="H2026" t="inlineStr"/>
+      <c r="I2026" t="n">
+        <v>0.8886850333091036</v>
+      </c>
+      <c r="J2026" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2026" t="inlineStr"/>
+    </row>
+    <row r="2027">
+      <c r="A2027" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0432.png</t>
+        </is>
+      </c>
+      <c r="C2027" t="inlineStr"/>
+      <c r="D2027" t="inlineStr"/>
+      <c r="E2027" t="inlineStr"/>
+      <c r="F2027" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NCC4=CC5CN(CCCN6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5C4)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2027" t="inlineStr"/>
+      <c r="H2027" t="inlineStr"/>
+      <c r="I2027" t="n">
+        <v>0.8866885784880298</v>
+      </c>
+      <c r="J2027" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2027" t="inlineStr"/>
+    </row>
+    <row r="2028">
+      <c r="A2028" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0433.png</t>
+        </is>
+      </c>
+      <c r="C2028" t="inlineStr"/>
+      <c r="D2028" t="inlineStr"/>
+      <c r="E2028" t="inlineStr"/>
+      <c r="F2028" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CC(=O)NCCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2cccc3ccccc23)NC(=O)[C@H](CCS(C)(=O)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2028" t="inlineStr"/>
+      <c r="H2028" t="inlineStr"/>
+      <c r="I2028" t="n">
+        <v>0.8877573761421035</v>
+      </c>
+      <c r="J2028" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2028" t="inlineStr"/>
+    </row>
+    <row r="2029">
+      <c r="A2029" s="1" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0434.png</t>
+        </is>
+      </c>
+      <c r="C2029" t="inlineStr"/>
+      <c r="D2029" t="inlineStr"/>
+      <c r="E2029" t="inlineStr"/>
+      <c r="F2029" t="inlineStr">
+        <is>
+          <t>COCc1cc2c(=O)n(C)cc(-c3cc(OC)c(CN4CCC5(CC4)CN(c4ccc6c(c4)C(=O)N(C4CCC(=O)NC4=O)C6)C5)c(OC)c3)c2s1</t>
+        </is>
+      </c>
+      <c r="G2029" t="inlineStr"/>
+      <c r="H2029" t="inlineStr"/>
+      <c r="I2029" t="n">
+        <v>0.9072962288554161</v>
+      </c>
+      <c r="J2029" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2029" t="inlineStr"/>
+    </row>
+    <row r="2030">
+      <c r="A2030" s="1" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0435.png</t>
+        </is>
+      </c>
+      <c r="C2030" t="inlineStr"/>
+      <c r="D2030" t="inlineStr"/>
+      <c r="E2030" t="inlineStr"/>
+      <c r="F2030" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccccc2Br)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2030" t="inlineStr"/>
+      <c r="H2030" t="inlineStr"/>
+      <c r="I2030" t="n">
+        <v>0.873304295245954</v>
+      </c>
+      <c r="J2030" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2030" t="inlineStr"/>
+    </row>
+    <row r="2031">
+      <c r="A2031" s="1" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B2031" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0437.png</t>
+        </is>
+      </c>
+      <c r="C2031" t="inlineStr"/>
+      <c r="D2031" t="inlineStr"/>
+      <c r="E2031" t="inlineStr"/>
+      <c r="F2031" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CC(=O)NCCCCCNC(=O)[C@H](Cc2ccc3ccccc3c2)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2cccc3ccccc23)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2031" t="inlineStr"/>
+      <c r="H2031" t="inlineStr"/>
+      <c r="I2031" t="n">
+        <v>0.8923699085275</v>
+      </c>
+      <c r="J2031" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2031" t="inlineStr"/>
+    </row>
+    <row r="2032">
+      <c r="A2032" s="1" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B2032" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0438.png</t>
+        </is>
+      </c>
+      <c r="C2032" t="inlineStr"/>
+      <c r="D2032" t="inlineStr"/>
+      <c r="E2032" t="inlineStr"/>
+      <c r="F2032" t="inlineStr">
+        <is>
+          <t>NCCn1cnc2c(ncn2[C@@H]2O[C@@H]3COP(=O)(S)O[C@H]4[C@@H](F)[C@H](n5cc6c7c(ncnc75)SCCC6)O[C@@H]4COP(=O)(S)O[C@@H]2[C@@H]3O)c1=O</t>
+        </is>
+      </c>
+      <c r="G2032" t="inlineStr"/>
+      <c r="H2032" t="inlineStr"/>
+      <c r="I2032" t="n">
+        <v>0.8698058710087215</v>
+      </c>
+      <c r="J2032" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2032" t="inlineStr"/>
+    </row>
+    <row r="2033">
+      <c r="A2033" s="1" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0440.png</t>
+        </is>
+      </c>
+      <c r="C2033" t="inlineStr"/>
+      <c r="D2033" t="inlineStr"/>
+      <c r="E2033" t="inlineStr"/>
+      <c r="F2033" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NC4CC5(CCN(CCN6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2033" t="inlineStr"/>
+      <c r="H2033" t="inlineStr"/>
+      <c r="I2033" t="n">
+        <v>0.8831297832229849</v>
+      </c>
+      <c r="J2033" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2033" t="inlineStr"/>
+    </row>
+    <row r="2034">
+      <c r="A2034" s="1" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B2034" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0441.png</t>
+        </is>
+      </c>
+      <c r="C2034" t="inlineStr"/>
+      <c r="D2034" t="inlineStr"/>
+      <c r="E2034" t="inlineStr"/>
+      <c r="F2034" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(N)=O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CC)nc2cc(C(N)=O)cc(c21)OCC(N1CCOCC1)CO3</t>
+        </is>
+      </c>
+      <c r="G2034" t="inlineStr"/>
+      <c r="H2034" t="inlineStr"/>
+      <c r="I2034" t="n">
+        <v>0.8896406268893796</v>
+      </c>
+      <c r="J2034" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2034" t="inlineStr"/>
+    </row>
+    <row r="2035">
+      <c r="A2035" s="1" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B2035" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0442.png</t>
+        </is>
+      </c>
+      <c r="C2035" t="inlineStr"/>
+      <c r="D2035" t="inlineStr"/>
+      <c r="E2035" t="inlineStr"/>
+      <c r="F2035" t="inlineStr">
+        <is>
+          <t>N=C(N)NCCC[C@@H]1NC(=O)[C@@H](Cc2ccc(F)cc2)NC(=O)[C@H](Cc2c[nH]cn2)NC(=O)[C@@H](NC(=O)Cc2ccc3ccccc3c2)CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2035" t="inlineStr"/>
+      <c r="H2035" t="inlineStr"/>
+      <c r="I2035" t="n">
+        <v>0.8899681464688129</v>
+      </c>
+      <c r="J2035" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2035" t="inlineStr"/>
+    </row>
+    <row r="2036">
+      <c r="A2036" s="1" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B2036" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0443.png</t>
+        </is>
+      </c>
+      <c r="C2036" t="inlineStr"/>
+      <c r="D2036" t="inlineStr"/>
+      <c r="E2036" t="inlineStr"/>
+      <c r="F2036" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NC4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6)CC4)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2036" t="inlineStr"/>
+      <c r="H2036" t="inlineStr"/>
+      <c r="I2036" t="n">
+        <v>0.9096150023265964</v>
+      </c>
+      <c r="J2036" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2036" t="inlineStr"/>
+    </row>
+    <row r="2037">
+      <c r="A2037" s="1" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B2037" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0444.png</t>
+        </is>
+      </c>
+      <c r="C2037" t="inlineStr"/>
+      <c r="D2037" t="inlineStr"/>
+      <c r="E2037" t="inlineStr"/>
+      <c r="F2037" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NC4CCN(C5CC6(C5)CN(c5ccc7c(c5)CN(C5CCC(=O)NC5=O)C7=O)C6)CC4(F)F)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2037" t="inlineStr"/>
+      <c r="H2037" t="inlineStr"/>
+      <c r="I2037" t="n">
+        <v>0.9073214705671779</v>
+      </c>
+      <c r="J2037" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2037" t="inlineStr"/>
+    </row>
+    <row r="2038">
+      <c r="A2038" s="1" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B2038" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0445.png</t>
+        </is>
+      </c>
+      <c r="C2038" t="inlineStr"/>
+      <c r="D2038" t="inlineStr"/>
+      <c r="E2038" t="inlineStr"/>
+      <c r="F2038" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NC4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6)C4)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2038" t="inlineStr"/>
+      <c r="H2038" t="inlineStr"/>
+      <c r="I2038" t="n">
+        <v>0.9072660151059722</v>
+      </c>
+      <c r="J2038" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2038" t="inlineStr"/>
+    </row>
+    <row r="2039">
+      <c r="A2039" s="1" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B2039" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0446.png</t>
+        </is>
+      </c>
+      <c r="C2039" t="inlineStr"/>
+      <c r="D2039" t="inlineStr"/>
+      <c r="E2039" t="inlineStr"/>
+      <c r="F2039" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccc2c(c1)C(F)(F)COCc1cc(ccc1Cc1nc3c(OCCOC)cc(C(=O)O)cc3n1C[C@@H]1CCO1)-c1cccc(n1)OC2</t>
+        </is>
+      </c>
+      <c r="G2039" t="inlineStr"/>
+      <c r="H2039" t="inlineStr"/>
+      <c r="I2039" t="n">
+        <v>0.9080019053154275</v>
+      </c>
+      <c r="J2039" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2039" t="inlineStr"/>
+    </row>
+    <row r="2040">
+      <c r="A2040" s="1" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B2040" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0447.png</t>
+        </is>
+      </c>
+      <c r="C2040" t="inlineStr"/>
+      <c r="D2040" t="inlineStr"/>
+      <c r="E2040" t="inlineStr"/>
+      <c r="F2040" t="inlineStr">
+        <is>
+          <t>[H][C@]12CC(C)(C)[C@@H](C(=O)N[C@H]3c4ccccc4C[C@H]3OCC#Cc3ccc(CO[C@@H]4Cc5ccccc5[C@@H]4NC(=O)[C@H]4N5C(=O)[C@@H](NC(=O)[C@H](C)NC)CCS[C@@]5([H])CC4(C)C)cc3)N1C(=O)[C@@H](NC(=O)[C@H](C)NC)CCS2</t>
+        </is>
+      </c>
+      <c r="G2040" t="inlineStr"/>
+      <c r="H2040" t="inlineStr"/>
+      <c r="I2040" t="n">
+        <v>0.8835853774476584</v>
+      </c>
+      <c r="J2040" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2040" t="inlineStr"/>
+    </row>
+    <row r="2041">
+      <c r="A2041" s="1" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B2041" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0448.png</t>
+        </is>
+      </c>
+      <c r="C2041" t="inlineStr"/>
+      <c r="D2041" t="inlineStr"/>
+      <c r="E2041" t="inlineStr"/>
+      <c r="F2041" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CCC(=O)NCCCNC(=O)[C@@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccc3ccccc3c2)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2041" t="inlineStr"/>
+      <c r="H2041" t="inlineStr"/>
+      <c r="I2041" t="n">
+        <v>0.8952041228307925</v>
+      </c>
+      <c r="J2041" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2041" t="inlineStr"/>
+    </row>
+    <row r="2042">
+      <c r="A2042" s="1" t="n">
+        <v>2040</v>
+      </c>
+      <c r="B2042" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0450.png</t>
+        </is>
+      </c>
+      <c r="C2042" t="inlineStr"/>
+      <c r="D2042" t="inlineStr"/>
+      <c r="E2042" t="inlineStr"/>
+      <c r="F2042" t="inlineStr">
+        <is>
+          <t>Cc1ccc(-c2ccc(C(=O)O)cc2)c2c1Sc1ncccc1CN[C@@H](CCCN)C(=O)N[C@@H](CCCCN)C(=O)N(C)[C@@H](Cc1c[nH]c3ccccc13)C(=O)NC2</t>
+        </is>
+      </c>
+      <c r="G2042" t="inlineStr"/>
+      <c r="H2042" t="inlineStr"/>
+      <c r="I2042" t="n">
+        <v>0.8862205076160492</v>
+      </c>
+      <c r="J2042" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2042" t="inlineStr"/>
+    </row>
+    <row r="2043">
+      <c r="A2043" s="1" t="n">
+        <v>2041</v>
+      </c>
+      <c r="B2043" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0451.png</t>
+        </is>
+      </c>
+      <c r="C2043" t="inlineStr"/>
+      <c r="D2043" t="inlineStr"/>
+      <c r="E2043" t="inlineStr"/>
+      <c r="F2043" t="inlineStr">
+        <is>
+          <t>*C1CCN(C2COc3cc(C(N)=O)cc4nc(NC(=O)c5cc(C)nn5CC)n(c34)C/C=C/Cn3c(NC(=O)c4cc(C)nn4CC)nc4cc(C(N)=O)cc(c43)OC2)C1 |$CO2Me;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2043" t="inlineStr"/>
+      <c r="H2043" t="inlineStr"/>
+      <c r="I2043" t="n">
+        <v>0.8818781721516568</v>
+      </c>
+      <c r="J2043" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2043" t="inlineStr"/>
+    </row>
+    <row r="2044">
+      <c r="A2044" s="1" t="n">
+        <v>2042</v>
+      </c>
+      <c r="B2044" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0453.png</t>
+        </is>
+      </c>
+      <c r="C2044" t="inlineStr"/>
+      <c r="D2044" t="inlineStr"/>
+      <c r="E2044" t="inlineStr"/>
+      <c r="F2044" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccc2c(c1)CCCOc1cc(ccc1Cc1nc3ccc(-c4nnnn4COCC[Si](C)(C)C)cc3n1C[C@@H]1CCO1)-c1cccc(n1)OC2</t>
+        </is>
+      </c>
+      <c r="G2044" t="inlineStr"/>
+      <c r="H2044" t="inlineStr"/>
+      <c r="I2044" t="n">
+        <v>0.8814423636020786</v>
+      </c>
+      <c r="J2044" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2044" t="inlineStr"/>
+    </row>
+    <row r="2045">
+      <c r="A2045" s="1" t="n">
+        <v>2043</v>
+      </c>
+      <c r="B2045" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0454.png</t>
+        </is>
+      </c>
+      <c r="C2045" t="inlineStr"/>
+      <c r="D2045" t="inlineStr"/>
+      <c r="E2045" t="inlineStr"/>
+      <c r="F2045" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2cccc(Cl)c2)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2045" t="inlineStr"/>
+      <c r="H2045" t="inlineStr"/>
+      <c r="I2045" t="n">
+        <v>0.8951033186734441</v>
+      </c>
+      <c r="J2045" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2045" t="inlineStr"/>
+    </row>
+    <row r="2046">
+      <c r="A2046" s="1" t="n">
+        <v>2044</v>
+      </c>
+      <c r="B2046" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0455.png</t>
+        </is>
+      </c>
+      <c r="C2046" t="inlineStr"/>
+      <c r="D2046" t="inlineStr"/>
+      <c r="E2046" t="inlineStr"/>
+      <c r="F2046" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(N)=O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CC)nc2cc(C(N)=O)cc(c21)OCC(N1CCCCC1)CO3</t>
+        </is>
+      </c>
+      <c r="G2046" t="inlineStr"/>
+      <c r="H2046" t="inlineStr"/>
+      <c r="I2046" t="n">
+        <v>0.8875119931507812</v>
+      </c>
+      <c r="J2046" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2046" t="inlineStr"/>
+    </row>
+    <row r="2047">
+      <c r="A2047" s="1" t="n">
+        <v>2045</v>
+      </c>
+      <c r="B2047" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0460.png</t>
+        </is>
+      </c>
+      <c r="C2047" t="inlineStr"/>
+      <c r="D2047" t="inlineStr"/>
+      <c r="E2047" t="inlineStr"/>
+      <c r="F2047" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)COCCOCC(=O)N2CCN(C(=O)c3ccc(Nc4nc(C5CC5)cn5c(-c6cn[nH]c6)cnc45)c(F)c3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2047" t="inlineStr"/>
+      <c r="H2047" t="inlineStr"/>
+      <c r="I2047" t="n">
+        <v>0.8569297986682728</v>
+      </c>
+      <c r="J2047" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2047" t="inlineStr"/>
+    </row>
+    <row r="2048">
+      <c r="A2048" s="1" t="n">
+        <v>2046</v>
+      </c>
+      <c r="B2048" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0461.png</t>
+        </is>
+      </c>
+      <c r="C2048" t="inlineStr"/>
+      <c r="D2048" t="inlineStr"/>
+      <c r="E2048" t="inlineStr"/>
+      <c r="F2048" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCCCCC(=O)NCCN2CCN(C(=O)c3ccc(Nc4nc(C5CC5)cn5c(-c6cn[nH]c6)cnc45)c(F)c3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2048" t="inlineStr"/>
+      <c r="H2048" t="inlineStr"/>
+      <c r="I2048" t="n">
+        <v>0.8778329193239222</v>
+      </c>
+      <c r="J2048" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2048" t="inlineStr"/>
+    </row>
+    <row r="2049">
+      <c r="A2049" s="1" t="n">
+        <v>2047</v>
+      </c>
+      <c r="B2049" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0462.png</t>
+        </is>
+      </c>
+      <c r="C2049" t="inlineStr"/>
+      <c r="D2049" t="inlineStr"/>
+      <c r="E2049" t="inlineStr"/>
+      <c r="F2049" t="inlineStr">
+        <is>
+          <t>N=C(N)NCCC[C@@H]1NC(=O)[C@@H](Cc2ccc(F)cc2)NC(=O)[C@H](Cc2c[nH]cn2)NC(=O)[C@@H](NC(=O)CCc2ccccc2)CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2049" t="inlineStr"/>
+      <c r="H2049" t="inlineStr"/>
+      <c r="I2049" t="n">
+        <v>0.8882790571041943</v>
+      </c>
+      <c r="J2049" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2049" t="inlineStr"/>
+    </row>
+    <row r="2050">
+      <c r="A2050" s="1" t="n">
+        <v>2048</v>
+      </c>
+      <c r="B2050" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0463.png</t>
+        </is>
+      </c>
+      <c r="C2050" t="inlineStr"/>
+      <c r="D2050" t="inlineStr"/>
+      <c r="E2050" t="inlineStr"/>
+      <c r="F2050" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(NC(=O)C4CCN(CCCCCOc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4(F)F)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2050" t="inlineStr"/>
+      <c r="H2050" t="inlineStr"/>
+      <c r="I2050" t="n">
+        <v>0.9106544888788559</v>
+      </c>
+      <c r="J2050" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2050" t="inlineStr"/>
+    </row>
+    <row r="2051">
+      <c r="A2051" s="1" t="n">
+        <v>2049</v>
+      </c>
+      <c r="B2051" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0467.png</t>
+        </is>
+      </c>
+      <c r="C2051" t="inlineStr"/>
+      <c r="D2051" t="inlineStr"/>
+      <c r="E2051" t="inlineStr"/>
+      <c r="F2051" t="inlineStr">
+        <is>
+          <t>COCCOc1cc(C(=O)O)cc2c1nc(Cc1cc(F)c3cc1COCCc1cc(Cl)cc(F)c1COc1cccc-3n1)n2C[C@@H]1CCO1</t>
+        </is>
+      </c>
+      <c r="G2051" t="inlineStr"/>
+      <c r="H2051" t="inlineStr"/>
+      <c r="I2051" t="n">
+        <v>0.8950524676939927</v>
+      </c>
+      <c r="J2051" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2051" t="inlineStr"/>
+    </row>
+    <row r="2052">
+      <c r="A2052" s="1" t="n">
+        <v>2050</v>
+      </c>
+      <c r="B2052" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0468.png</t>
+        </is>
+      </c>
+      <c r="C2052" t="inlineStr"/>
+      <c r="D2052" t="inlineStr"/>
+      <c r="E2052" t="inlineStr"/>
+      <c r="F2052" t="inlineStr">
+        <is>
+          <t>Cn1ccc(-c2ccc3c(c2)CCCOc2cc(ccc2Cc2nc4ccc(C(=O)O)cc4n2C[C@@H]2CCO2)-c2cccc(n2)OC3)cc1=O</t>
+        </is>
+      </c>
+      <c r="G2052" t="inlineStr"/>
+      <c r="H2052" t="inlineStr"/>
+      <c r="I2052" t="n">
+        <v>0.8959625730113659</v>
+      </c>
+      <c r="J2052" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2052" t="inlineStr"/>
+    </row>
+    <row r="2053">
+      <c r="A2053" s="1" t="n">
+        <v>2051</v>
+      </c>
+      <c r="B2053" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0469.png</t>
+        </is>
+      </c>
+      <c r="C2053" t="inlineStr"/>
+      <c r="D2053" t="inlineStr"/>
+      <c r="E2053" t="inlineStr"/>
+      <c r="F2053" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCNCCOCCN7CC7)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H]([O][Ac])[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G2053" t="inlineStr"/>
+      <c r="H2053" t="inlineStr"/>
+      <c r="I2053" t="n">
+        <v>0.85725877073111</v>
+      </c>
+      <c r="J2053" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2053" t="inlineStr"/>
+    </row>
+    <row r="2054">
+      <c r="A2054" s="1" t="n">
+        <v>2052</v>
+      </c>
+      <c r="B2054" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0472.png</t>
+        </is>
+      </c>
+      <c r="C2054" t="inlineStr"/>
+      <c r="D2054" t="inlineStr"/>
+      <c r="E2054" t="inlineStr"/>
+      <c r="F2054" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)COCCNC(=O)CN2CCN(C(=O)c3ccc(Nc4nc(C5CC5)cn5c(-c6cn[nH]c6)cnc45)c(F)c3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2054" t="inlineStr"/>
+      <c r="H2054" t="inlineStr"/>
+      <c r="I2054" t="n">
+        <v>0.8926005215256786</v>
+      </c>
+      <c r="J2054" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2054" t="inlineStr"/>
+    </row>
+    <row r="2055">
+      <c r="A2055" s="1" t="n">
+        <v>2053</v>
+      </c>
+      <c r="B2055" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0474.png</t>
+        </is>
+      </c>
+      <c r="C2055" t="inlineStr"/>
+      <c r="D2055" t="inlineStr"/>
+      <c r="E2055" t="inlineStr"/>
+      <c r="F2055" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C)sc23)cc(OC)c1CN1CCC(CN2CCC3(CC2)CC(Oc2ccc4c(c2)C(=O)N(C2CCC(=O)NC2=O)C4=O)C3)CC1</t>
+        </is>
+      </c>
+      <c r="G2055" t="inlineStr"/>
+      <c r="H2055" t="inlineStr"/>
+      <c r="I2055" t="n">
+        <v>0.9170772009932301</v>
+      </c>
+      <c r="J2055" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2055" t="inlineStr"/>
+    </row>
+    <row r="2056">
+      <c r="A2056" s="1" t="n">
+        <v>2054</v>
+      </c>
+      <c r="B2056" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0475.png</t>
+        </is>
+      </c>
+      <c r="C2056" t="inlineStr"/>
+      <c r="D2056" t="inlineStr"/>
+      <c r="E2056" t="inlineStr"/>
+      <c r="F2056" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NC4CCN(C5CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7)CC5(F)F)CC4)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2056" t="inlineStr"/>
+      <c r="H2056" t="inlineStr"/>
+      <c r="I2056" t="n">
+        <v>0.8698624277958193</v>
+      </c>
+      <c r="J2056" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2056" t="inlineStr"/>
+    </row>
+    <row r="2057">
+      <c r="A2057" s="1" t="n">
+        <v>2055</v>
+      </c>
+      <c r="B2057" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0477.png</t>
+        </is>
+      </c>
+      <c r="C2057" t="inlineStr"/>
+      <c r="D2057" t="inlineStr"/>
+      <c r="E2057" t="inlineStr"/>
+      <c r="F2057" t="inlineStr">
+        <is>
+          <t>COc1cccc(OC)c1CN(C)C.Cc1cn(C)c(=O)c2cc(C(=O)NC3CCCN(CCCCCOc4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)sc12</t>
+        </is>
+      </c>
+      <c r="G2057" t="inlineStr"/>
+      <c r="H2057" t="inlineStr"/>
+      <c r="I2057" t="n">
+        <v>0.8662974271423202</v>
+      </c>
+      <c r="J2057" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2057" t="inlineStr"/>
+    </row>
+    <row r="2058">
+      <c r="A2058" s="1" t="n">
+        <v>2056</v>
+      </c>
+      <c r="B2058" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0478.png</t>
+        </is>
+      </c>
+      <c r="C2058" t="inlineStr"/>
+      <c r="D2058" t="inlineStr"/>
+      <c r="E2058" t="inlineStr"/>
+      <c r="F2058" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3cccc(NCCOCCOCCOCCOCCOCCC(=O)N4CCN(C(=O)c5ccc(Nc6nc(C7CC7)cn7c(-c8cn[nH]c8)cnc67)c(F)c5)CC4)c3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2058" t="inlineStr"/>
+      <c r="H2058" t="inlineStr"/>
+      <c r="I2058" t="n">
+        <v>0.8817907353838522</v>
+      </c>
+      <c r="J2058" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2058" t="inlineStr"/>
+    </row>
+    <row r="2059">
+      <c r="A2059" s="1" t="n">
+        <v>2057</v>
+      </c>
+      <c r="B2059" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0479.png</t>
+        </is>
+      </c>
+      <c r="C2059" t="inlineStr"/>
+      <c r="D2059" t="inlineStr"/>
+      <c r="E2059" t="inlineStr"/>
+      <c r="F2059" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(N)=O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CC)nc2cc(C(N)=O)cc(c21)OCC(C1CCOCN1)CO3</t>
+        </is>
+      </c>
+      <c r="G2059" t="inlineStr"/>
+      <c r="H2059" t="inlineStr"/>
+      <c r="I2059" t="n">
+        <v>0.8859857708865383</v>
+      </c>
+      <c r="J2059" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2059" t="inlineStr"/>
+    </row>
+    <row r="2060">
+      <c r="A2060" s="1" t="n">
+        <v>2058</v>
+      </c>
+      <c r="B2060" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0481.png</t>
+        </is>
+      </c>
+      <c r="C2060" t="inlineStr"/>
+      <c r="D2060" t="inlineStr"/>
+      <c r="E2060" t="inlineStr"/>
+      <c r="F2060" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccccc2F)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2060" t="inlineStr"/>
+      <c r="H2060" t="inlineStr"/>
+      <c r="I2060" t="n">
+        <v>0.8862628050851487</v>
+      </c>
+      <c r="J2060" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2060" t="inlineStr"/>
+    </row>
+    <row r="2061">
+      <c r="A2061" s="1" t="n">
+        <v>2059</v>
+      </c>
+      <c r="B2061" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0482.png</t>
+        </is>
+      </c>
+      <c r="C2061" t="inlineStr"/>
+      <c r="D2061" t="inlineStr"/>
+      <c r="E2061" t="inlineStr"/>
+      <c r="F2061" t="inlineStr">
+        <is>
+          <t>N=C(N)NCCC[C@@H]1NC(=O)[C@@H](Cc2ccc(F)cc2)NC(=O)[C@H](Cc2c[nH]cn2)NC(=O)[C@@H](NC(=O)CCc2cccc3ccccc23)CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2061" t="inlineStr"/>
+      <c r="H2061" t="inlineStr"/>
+      <c r="I2061" t="n">
+        <v>0.8917619638335045</v>
+      </c>
+      <c r="J2061" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2061" t="inlineStr"/>
+    </row>
+    <row r="2062">
+      <c r="A2062" s="1" t="n">
+        <v>2060</v>
+      </c>
+      <c r="B2062" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0483.png</t>
+        </is>
+      </c>
+      <c r="C2062" t="inlineStr"/>
+      <c r="D2062" t="inlineStr"/>
+      <c r="E2062" t="inlineStr"/>
+      <c r="F2062" t="inlineStr">
+        <is>
+          <t>[H]C12CC(C)(C)C(C(=O)NC3C4=C(C=CC=C4)CC3OCC#CC3=CC=C(C#CCO[CH]4=CC5=C(C=CC=C5)C4OC(=O)C4N5C(=O)C(NC(=O)C(C)NC)CCSC5([H])CC4(C)C)C=C3)N1C(=O)C(NC(=O)C(C)NC)CCS2</t>
+        </is>
+      </c>
+      <c r="G2062" t="inlineStr"/>
+      <c r="H2062" t="inlineStr"/>
+      <c r="I2062" t="n">
+        <v>0.8653289585821933</v>
+      </c>
+      <c r="J2062" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2062" t="inlineStr"/>
+    </row>
+    <row r="2063">
+      <c r="A2063" s="1" t="n">
+        <v>2061</v>
+      </c>
+      <c r="B2063" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0484.png</t>
+        </is>
+      </c>
+      <c r="C2063" t="inlineStr"/>
+      <c r="D2063" t="inlineStr"/>
+      <c r="E2063" t="inlineStr"/>
+      <c r="F2063" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(N)=O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CC)nc2cc(C(N)=O)cc(c21)OCC(N1CCC(N)C1)CO3</t>
+        </is>
+      </c>
+      <c r="G2063" t="inlineStr"/>
+      <c r="H2063" t="inlineStr"/>
+      <c r="I2063" t="n">
+        <v>0.9040539041396517</v>
+      </c>
+      <c r="J2063" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2063" t="inlineStr"/>
+    </row>
+    <row r="2064">
+      <c r="A2064" s="1" t="n">
+        <v>2062</v>
+      </c>
+      <c r="B2064" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0485.png</t>
+        </is>
+      </c>
+      <c r="C2064" t="inlineStr"/>
+      <c r="D2064" t="inlineStr"/>
+      <c r="E2064" t="inlineStr"/>
+      <c r="F2064" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OC7CCN(C)CC7)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G2064" t="inlineStr"/>
+      <c r="H2064" t="inlineStr"/>
+      <c r="I2064" t="n">
+        <v>0.8800786313345839</v>
+      </c>
+      <c r="J2064" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2064" t="inlineStr"/>
+    </row>
+    <row r="2065">
+      <c r="A2065" s="1" t="n">
+        <v>2063</v>
+      </c>
+      <c r="B2065" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0486.png</t>
+        </is>
+      </c>
+      <c r="C2065" t="inlineStr"/>
+      <c r="D2065" t="inlineStr"/>
+      <c r="E2065" t="inlineStr"/>
+      <c r="F2065" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CC(=O)NCCCCCNC(=O)[C@H](Cc2cccc3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2cccc3ccccc23)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2065" t="inlineStr"/>
+      <c r="H2065" t="inlineStr"/>
+      <c r="I2065" t="n">
+        <v>0.8768631084504218</v>
+      </c>
+      <c r="J2065" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2065" t="inlineStr"/>
+    </row>
+    <row r="2066">
+      <c r="A2066" s="1" t="n">
+        <v>2064</v>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0488.png</t>
+        </is>
+      </c>
+      <c r="C2066" t="inlineStr"/>
+      <c r="D2066" t="inlineStr"/>
+      <c r="E2066" t="inlineStr"/>
+      <c r="F2066" t="inlineStr">
+        <is>
+          <t>CC(=O)N[C@@H](CCCNC(=N)N)C(=O)N[C@H]1CCC(=O)NCCCCNC(=O)[C@@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccc3ccccc3c2)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2066" t="inlineStr"/>
+      <c r="H2066" t="inlineStr"/>
+      <c r="I2066" t="n">
+        <v>0.8796699676320288</v>
+      </c>
+      <c r="J2066" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2066" t="inlineStr"/>
+    </row>
+    <row r="2067">
+      <c r="A2067" s="1" t="n">
+        <v>2065</v>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0489.png</t>
+        </is>
+      </c>
+      <c r="C2067" t="inlineStr"/>
+      <c r="D2067" t="inlineStr"/>
+      <c r="E2067" t="inlineStr"/>
+      <c r="F2067" t="inlineStr">
+        <is>
+          <t>[H]C12CC(C)(C)C(C(=O)NC3C4=C(C=CC=C4)CC3OCCCCCCO[CH]3=CC4=C(C=CC=C4)C3NC(=O)C3N4C(=O)C(NC(=O)C(C)NC)CCSC4([H])CC3(C)C)N1C(=O)C(NC(=O)C(C)NC)CCS2</t>
+        </is>
+      </c>
+      <c r="G2067" t="inlineStr"/>
+      <c r="H2067" t="inlineStr"/>
+      <c r="I2067" t="n">
+        <v>0.8636278066209404</v>
+      </c>
+      <c r="J2067" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2067" t="inlineStr"/>
+    </row>
+    <row r="2068">
+      <c r="A2068" s="1" t="n">
+        <v>2066</v>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0490.png</t>
+        </is>
+      </c>
+      <c r="C2068" t="inlineStr"/>
+      <c r="D2068" t="inlineStr"/>
+      <c r="E2068" t="inlineStr"/>
+      <c r="F2068" t="inlineStr">
+        <is>
+          <t>COC(=O)c1cccc(CN2CCOCCOCCN(Cc3cc(OCCc4ccc(N)cc4)cc(C(=O)OC)n3)CCOCCOCC2)n1</t>
+        </is>
+      </c>
+      <c r="G2068" t="inlineStr"/>
+      <c r="H2068" t="inlineStr"/>
+      <c r="I2068" t="n">
+        <v>0.9028705712557346</v>
+      </c>
+      <c r="J2068" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2068" t="inlineStr"/>
+    </row>
+    <row r="2069">
+      <c r="A2069" s="1" t="n">
+        <v>2067</v>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0491.png</t>
+        </is>
+      </c>
+      <c r="C2069" t="inlineStr"/>
+      <c r="D2069" t="inlineStr"/>
+      <c r="E2069" t="inlineStr"/>
+      <c r="F2069" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccccc2Cl)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2069" t="inlineStr"/>
+      <c r="H2069" t="inlineStr"/>
+      <c r="I2069" t="n">
+        <v>0.8764042086294964</v>
+      </c>
+      <c r="J2069" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2069" t="inlineStr"/>
+    </row>
+    <row r="2070">
+      <c r="A2070" s="1" t="n">
+        <v>2068</v>
+      </c>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0492.png</t>
+        </is>
+      </c>
+      <c r="C2070" t="inlineStr"/>
+      <c r="D2070" t="inlineStr"/>
+      <c r="E2070" t="inlineStr"/>
+      <c r="F2070" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(N)=O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CCF)nc2cc(C(N)=O)cc(c21)OCC(N1CCOCC1)CO3</t>
+        </is>
+      </c>
+      <c r="G2070" t="inlineStr"/>
+      <c r="H2070" t="inlineStr"/>
+      <c r="I2070" t="n">
+        <v>0.8968177182673071</v>
+      </c>
+      <c r="J2070" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2070" t="inlineStr"/>
+    </row>
+    <row r="2071">
+      <c r="A2071" s="1" t="n">
+        <v>2069</v>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0493.png</t>
+        </is>
+      </c>
+      <c r="C2071" t="inlineStr"/>
+      <c r="D2071" t="inlineStr"/>
+      <c r="E2071" t="inlineStr"/>
+      <c r="F2071" t="inlineStr">
+        <is>
+          <t>CCCc1cn2c(-c3cn[nH]c3)cnc2c(Nc2ccc(C(=O)N3CCN(CC(=O)N4CCC(N5CCC(C(=O)N[C@H](C(=O)N6C[C@H](O)C[C@H]6C(=O)NCc6ccc(-c7scnc7C)cc6)C(C)(C)C)CC5)CC4)CC3)cc2I)n1</t>
+        </is>
+      </c>
+      <c r="G2071" t="inlineStr"/>
+      <c r="H2071" t="inlineStr"/>
+      <c r="I2071" t="n">
+        <v>0.8908083458492735</v>
+      </c>
+      <c r="J2071" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2071" t="inlineStr"/>
+    </row>
+    <row r="2072">
+      <c r="A2072" s="1" t="n">
+        <v>2070</v>
+      </c>
+      <c r="B2072" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0495.png</t>
+        </is>
+      </c>
+      <c r="C2072" t="inlineStr"/>
+      <c r="D2072" t="inlineStr"/>
+      <c r="E2072" t="inlineStr"/>
+      <c r="F2072" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NCC4CC5(C4)CN(CCCN4CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC4)C5)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2072" t="inlineStr"/>
+      <c r="H2072" t="inlineStr"/>
+      <c r="I2072" t="n">
+        <v>0.8938427511051256</v>
+      </c>
+      <c r="J2072" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2072" t="inlineStr"/>
+    </row>
+    <row r="2073">
+      <c r="A2073" s="1" t="n">
+        <v>2071</v>
+      </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0497.png</t>
+        </is>
+      </c>
+      <c r="C2073" t="inlineStr"/>
+      <c r="D2073" t="inlineStr"/>
+      <c r="E2073" t="inlineStr"/>
+      <c r="F2073" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(N)=O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CC)nc2cc(C(N)=O)cc(c21)OCC(N1CCC(F)(F)CC1)CO3</t>
+        </is>
+      </c>
+      <c r="G2073" t="inlineStr"/>
+      <c r="H2073" t="inlineStr"/>
+      <c r="I2073" t="n">
+        <v>0.9023266631623299</v>
+      </c>
+      <c r="J2073" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2073" t="inlineStr"/>
+    </row>
+    <row r="2074">
+      <c r="A2074" s="1" t="n">
+        <v>2072</v>
+      </c>
+      <c r="B2074" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0499.png</t>
+        </is>
+      </c>
+      <c r="C2074" t="inlineStr"/>
+      <c r="D2074" t="inlineStr"/>
+      <c r="E2074" t="inlineStr"/>
+      <c r="F2074" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(N)=O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CC)nc2cc(C(N)=O)cc(c21)OCC(C1CCN(C)CC1)CO3</t>
+        </is>
+      </c>
+      <c r="G2074" t="inlineStr"/>
+      <c r="H2074" t="inlineStr"/>
+      <c r="I2074" t="n">
+        <v>0.9092299005895257</v>
+      </c>
+      <c r="J2074" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2074" t="inlineStr"/>
+    </row>
+    <row r="2075">
+      <c r="A2075" s="1" t="n">
+        <v>2073</v>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0502.png</t>
+        </is>
+      </c>
+      <c r="C2075" t="inlineStr"/>
+      <c r="D2075" t="inlineStr"/>
+      <c r="E2075" t="inlineStr"/>
+      <c r="F2075" t="inlineStr">
+        <is>
+          <t>[H][C@]12CC(C)(C)[C@@H](C(=O)N[C@H]3c4ccccc4C[C@H]3OCC#Cc3cccc(C#CCO[C@@H]4Cc5ccccc5[C@@H]4NC(=O)[C@H]4N5C(=O)[C@@H](NC(=O)[C@H](C)NC)CCS[C@@]5([H])CC4(C)C)c3)N1C(=O)[C@@H](NC(=O)[C@H](C)NC)CCS2</t>
+        </is>
+      </c>
+      <c r="G2075" t="inlineStr"/>
+      <c r="H2075" t="inlineStr"/>
+      <c r="I2075" t="n">
+        <v>0.8485232848117054</v>
+      </c>
+      <c r="J2075" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2075" t="inlineStr"/>
+    </row>
+    <row r="2076">
+      <c r="A2076" s="1" t="n">
+        <v>2074</v>
+      </c>
+      <c r="B2076" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0503.png</t>
+        </is>
+      </c>
+      <c r="C2076" t="inlineStr"/>
+      <c r="D2076" t="inlineStr"/>
+      <c r="E2076" t="inlineStr"/>
+      <c r="F2076" t="inlineStr">
+        <is>
+          <t>CCCC[C@@H](NC(C)=O)C(=O)N[C@H]1CCC(=O)NCCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2cccc3ccccc23)NC(=O)[C@H](CCS(C)(=O)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2076" t="inlineStr"/>
+      <c r="H2076" t="inlineStr"/>
+      <c r="I2076" t="n">
+        <v>0.883404152634032</v>
+      </c>
+      <c r="J2076" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2076" t="inlineStr"/>
+    </row>
+    <row r="2077">
+      <c r="A2077" s="1" t="n">
+        <v>2075</v>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0504.png</t>
+        </is>
+      </c>
+      <c r="C2077" t="inlineStr"/>
+      <c r="D2077" t="inlineStr"/>
+      <c r="E2077" t="inlineStr"/>
+      <c r="F2077" t="inlineStr">
+        <is>
+          <t>CC(=O)N[C@H](CCCNC(=N)N)C(=O)N[C@H]1CCC(=O)NCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccc3ccccc3c2)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2077" t="inlineStr"/>
+      <c r="H2077" t="inlineStr"/>
+      <c r="I2077" t="n">
+        <v>0.8798616315212483</v>
+      </c>
+      <c r="J2077" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2077" t="inlineStr"/>
+    </row>
+    <row r="2078">
+      <c r="A2078" s="1" t="n">
+        <v>2076</v>
+      </c>
+      <c r="B2078" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0505.png</t>
+        </is>
+      </c>
+      <c r="C2078" t="inlineStr"/>
+      <c r="D2078" t="inlineStr"/>
+      <c r="E2078" t="inlineStr"/>
+      <c r="F2078" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3cccc(NCC(=O)N4CCN(C(=O)c5ccc(Nc6nc(C7CC7)cn7c(-c8cn[nH]c8)cnc67)c(F)c5)CC4)c3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2078" t="inlineStr"/>
+      <c r="H2078" t="inlineStr"/>
+      <c r="I2078" t="n">
+        <v>0.9006855418743446</v>
+      </c>
+      <c r="J2078" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2078" t="inlineStr"/>
+    </row>
+    <row r="2079">
+      <c r="A2079" s="1" t="n">
+        <v>2077</v>
+      </c>
+      <c r="B2079" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0506.png</t>
+        </is>
+      </c>
+      <c r="C2079" t="inlineStr"/>
+      <c r="D2079" t="inlineStr"/>
+      <c r="E2079" t="inlineStr"/>
+      <c r="F2079" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NC4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)N(C)C5=O)C6)CC4(F)F)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2079" t="inlineStr"/>
+      <c r="H2079" t="inlineStr"/>
+      <c r="I2079" t="n">
+        <v>0.9129416424909843</v>
+      </c>
+      <c r="J2079" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2079" t="inlineStr"/>
+    </row>
+    <row r="2080">
+      <c r="A2080" s="1" t="n">
+        <v>2078</v>
+      </c>
+      <c r="B2080" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0507.png</t>
+        </is>
+      </c>
+      <c r="C2080" t="inlineStr"/>
+      <c r="D2080" t="inlineStr"/>
+      <c r="E2080" t="inlineStr"/>
+      <c r="F2080" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2cc(-c3c4ccc(=[N+](C)C)cc-4[nH]c4cc(N(C)C)ccc34)c(C(=O)O)cc2OC)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G2080" t="inlineStr"/>
+      <c r="H2080" t="inlineStr"/>
+      <c r="I2080" t="n">
+        <v>0.8993683895909104</v>
+      </c>
+      <c r="J2080" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2080" t="inlineStr"/>
+    </row>
+    <row r="2081">
+      <c r="A2081" s="1" t="n">
+        <v>2079</v>
+      </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0508.png</t>
+        </is>
+      </c>
+      <c r="C2081" t="inlineStr"/>
+      <c r="D2081" t="inlineStr"/>
+      <c r="E2081" t="inlineStr"/>
+      <c r="F2081" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCNC(=O)OC(C)(C)C)NC(=O)[C@H](CCCNC(=O)OC(C)(C)C)NCc2cccnc2Sc2c(Cl)ccc(Br)c2CNC(=O)[C@@H]1Cc1cn(C(=O)OC(C)(C)C)c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G2081" t="inlineStr"/>
+      <c r="H2081" t="inlineStr"/>
+      <c r="I2081" t="n">
+        <v>0.9065743007950289</v>
+      </c>
+      <c r="J2081" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2081" t="inlineStr"/>
+    </row>
+    <row r="2082">
+      <c r="A2082" s="1" t="n">
+        <v>2080</v>
+      </c>
+      <c r="B2082" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0511.png</t>
+        </is>
+      </c>
+      <c r="C2082" t="inlineStr"/>
+      <c r="D2082" t="inlineStr"/>
+      <c r="E2082" t="inlineStr"/>
+      <c r="F2082" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCCN)NC(=O)[C@H](CCCN)NCc2cccnc2Sc2c(Cl)ccc(-c3ccc(C(=O)O)c(O)c3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G2082" t="inlineStr"/>
+      <c r="H2082" t="inlineStr"/>
+      <c r="I2082" t="n">
+        <v>0.9084594884622367</v>
+      </c>
+      <c r="J2082" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2082" t="inlineStr"/>
+    </row>
+    <row r="2083">
+      <c r="A2083" s="1" t="n">
+        <v>2081</v>
+      </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0512.png</t>
+        </is>
+      </c>
+      <c r="C2083" t="inlineStr"/>
+      <c r="D2083" t="inlineStr"/>
+      <c r="E2083" t="inlineStr"/>
+      <c r="F2083" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2ccc(Cl)c3c2CNC(=O)[C@H](Cc2c[nH]c4ccccc24)N(C)C(=O)[C@H](CCCCN)NC(=O)[C@H](CCCN)NCc2nccnc2S3)ccc1C(=O)O</t>
+        </is>
+      </c>
+      <c r="G2083" t="inlineStr"/>
+      <c r="H2083" t="inlineStr"/>
+      <c r="I2083" t="n">
+        <v>0.8967031848743746</v>
+      </c>
+      <c r="J2083" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2083" t="inlineStr"/>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="1" t="n">
+        <v>2082</v>
+      </c>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0513.png</t>
+        </is>
+      </c>
+      <c r="C2084" t="inlineStr"/>
+      <c r="D2084" t="inlineStr"/>
+      <c r="E2084" t="inlineStr"/>
+      <c r="F2084" t="inlineStr">
+        <is>
+          <t>CC(C)(C)[C@H](NC(=O)COCCOCCOCC(=O)NCCN1CCN(C(=O)c2ccc(Nc3nc(C4CC4)cn4c(-c5cn[nH]c5)cnc34)c(F)c2)CC1)C(=O)N1C[C@H](O)C[C@H]1C(=O)NCc1ccc(-c2cncs2)cc1</t>
+        </is>
+      </c>
+      <c r="G2084" t="inlineStr"/>
+      <c r="H2084" t="inlineStr"/>
+      <c r="I2084" t="n">
+        <v>0.8768886291917787</v>
+      </c>
+      <c r="J2084" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2084" t="inlineStr"/>
+    </row>
+    <row r="2085">
+      <c r="A2085" s="1" t="n">
+        <v>2083</v>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0514.png</t>
+        </is>
+      </c>
+      <c r="C2085" t="inlineStr"/>
+      <c r="D2085" t="inlineStr"/>
+      <c r="E2085" t="inlineStr"/>
+      <c r="F2085" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCN(C)C)cc(F)c6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G2085" t="inlineStr"/>
+      <c r="H2085" t="inlineStr"/>
+      <c r="I2085" t="n">
+        <v>0.8777802034974267</v>
+      </c>
+      <c r="J2085" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2085" t="inlineStr"/>
+    </row>
+    <row r="2086">
+      <c r="A2086" s="1" t="n">
+        <v>2084</v>
+      </c>
+      <c r="B2086" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0515.png</t>
+        </is>
+      </c>
+      <c r="C2086" t="inlineStr"/>
+      <c r="D2086" t="inlineStr"/>
+      <c r="E2086" t="inlineStr"/>
+      <c r="F2086" t="inlineStr">
+        <is>
+          <t>[H][C@]12CC(C)(C)[C@@H](C(=O)N[C@H]3c4ccccc4C[C@H]3OCC#CCO[C@@H]3Cc4ccccc4[C@@H]3NC(=O)[C@H]3N4C(=O)[C@@H](NC(=O)[C@H](C)NC)CCS[C@@]4([H])CC3(C)C)N1C(=O)[C@@H](NC(=O)[C@H](C)NC)CCS2</t>
+        </is>
+      </c>
+      <c r="G2086" t="inlineStr"/>
+      <c r="H2086" t="inlineStr"/>
+      <c r="I2086" t="n">
+        <v>0.8882632630491002</v>
+      </c>
+      <c r="J2086" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2086" t="inlineStr"/>
+    </row>
+    <row r="2087">
+      <c r="A2087" s="1" t="n">
+        <v>2085</v>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0516.png</t>
+        </is>
+      </c>
+      <c r="C2087" t="inlineStr"/>
+      <c r="D2087" t="inlineStr"/>
+      <c r="E2087" t="inlineStr"/>
+      <c r="F2087" t="inlineStr">
+        <is>
+          <t>CC(=O)N[C@@H](CCCNC(=N)N)C(=O)N[C@H]1CC(=O)NCCOCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccccc2)NC(=O)[C@H](CC(N)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2087" t="inlineStr"/>
+      <c r="H2087" t="inlineStr"/>
+      <c r="I2087" t="n">
+        <v>0.8809940870397838</v>
+      </c>
+      <c r="J2087" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2087" t="inlineStr"/>
+    </row>
+    <row r="2088">
+      <c r="A2088" s="1" t="n">
+        <v>2086</v>
+      </c>
+      <c r="B2088" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0518.png</t>
+        </is>
+      </c>
+      <c r="C2088" t="inlineStr"/>
+      <c r="D2088" t="inlineStr"/>
+      <c r="E2088" t="inlineStr"/>
+      <c r="F2088" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(C#CCN(C)C)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G2088" t="inlineStr"/>
+      <c r="H2088" t="inlineStr"/>
+      <c r="I2088" t="n">
+        <v>0.8911927314197339</v>
+      </c>
+      <c r="J2088" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2088" t="inlineStr"/>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="1" t="n">
+        <v>2087</v>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0519.png</t>
+        </is>
+      </c>
+      <c r="C2089" t="inlineStr"/>
+      <c r="D2089" t="inlineStr"/>
+      <c r="E2089" t="inlineStr"/>
+      <c r="F2089" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCCN7CCC7)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G2089" t="inlineStr"/>
+      <c r="H2089" t="inlineStr"/>
+      <c r="I2089" t="n">
+        <v>0.88978855443353</v>
+      </c>
+      <c r="J2089" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2089" t="inlineStr"/>
+    </row>
+    <row r="2090">
+      <c r="A2090" s="1" t="n">
+        <v>2088</v>
+      </c>
+      <c r="B2090" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0521.png</t>
+        </is>
+      </c>
+      <c r="C2090" t="inlineStr"/>
+      <c r="D2090" t="inlineStr"/>
+      <c r="E2090" t="inlineStr"/>
+      <c r="F2090" t="inlineStr">
+        <is>
+          <t>[H][C@]12CC(C)(C)[C@@H](C(=O)N[C@H]3c4ccccc4C[C@H]3OCc3ccc(-c4ccc(CO[C@@H]5Cc6ccccc6[C@@H]5NC(=O)[C@H]5N6C(=O)[C@@H](NC(=O)[C@H](C)NC)CCS[C@@]6([H])CC5(C)C)cc4)cc3)N1C(=O)[C@@H](NC(=O)[C@H](C)NC)CCS2</t>
+        </is>
+      </c>
+      <c r="G2090" t="inlineStr"/>
+      <c r="H2090" t="inlineStr"/>
+      <c r="I2090" t="n">
+        <v>0.880068583404181</v>
+      </c>
+      <c r="J2090" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2090" t="inlineStr"/>
+    </row>
+    <row r="2091">
+      <c r="A2091" s="1" t="n">
+        <v>2089</v>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0523.png</t>
+        </is>
+      </c>
+      <c r="C2091" t="inlineStr"/>
+      <c r="D2091" t="inlineStr"/>
+      <c r="E2091" t="inlineStr"/>
+      <c r="F2091" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCCN)NC(=O)[C@H](CCCN)NCc2nccnc2Sc2c(Cl)ccc(-c3ccc(C(=O)O)c(F)c3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G2091" t="inlineStr"/>
+      <c r="H2091" t="inlineStr"/>
+      <c r="I2091" t="n">
+        <v>0.8955786035902198</v>
+      </c>
+      <c r="J2091" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2091" t="inlineStr"/>
+    </row>
+    <row r="2092">
+      <c r="A2092" s="1" t="n">
+        <v>2090</v>
+      </c>
+      <c r="B2092" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0525.png</t>
+        </is>
+      </c>
+      <c r="C2092" t="inlineStr"/>
+      <c r="D2092" t="inlineStr"/>
+      <c r="E2092" t="inlineStr"/>
+      <c r="F2092" t="inlineStr">
+        <is>
+          <t>N=C(N)NCCC[C@@H]1NC(=O)[C@@H](Cc2ccc(F)cc2)NC(=O)[C@@H](Cc2c[nH]cn2)NC(=O)[C@@H](NC(=O)Cc2cccc3ccccc23)CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2092" t="inlineStr"/>
+      <c r="H2092" t="inlineStr"/>
+      <c r="I2092" t="n">
+        <v>0.8897917602937508</v>
+      </c>
+      <c r="J2092" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2092" t="inlineStr"/>
+    </row>
+    <row r="2093">
+      <c r="A2093" s="1" t="n">
+        <v>2091</v>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0527.png</t>
+        </is>
+      </c>
+      <c r="C2093" t="inlineStr"/>
+      <c r="D2093" t="inlineStr"/>
+      <c r="E2093" t="inlineStr"/>
+      <c r="F2093" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccc2c(c1)CCOCc1cc(ccc1Cc1nc3c(OCCOC)cc(C(=O)OC)cc3n1C[C@@H]1CCO1)-c1cccc(n1)OC2</t>
+        </is>
+      </c>
+      <c r="G2093" t="inlineStr"/>
+      <c r="H2093" t="inlineStr"/>
+      <c r="I2093" t="n">
+        <v>0.8920694624568657</v>
+      </c>
+      <c r="J2093" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2093" t="inlineStr"/>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="1" t="n">
+        <v>2092</v>
+      </c>
+      <c r="B2094" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0528.png</t>
+        </is>
+      </c>
+      <c r="C2094" t="inlineStr"/>
+      <c r="D2094" t="inlineStr"/>
+      <c r="E2094" t="inlineStr"/>
+      <c r="F2094" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NC4CCN(C5CC6(C5)CN(c5ccc7c(c5)C(=O)N(C5CCC(=O)NC5=O)C7)C6)CC4(F)F)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2094" t="inlineStr"/>
+      <c r="H2094" t="inlineStr"/>
+      <c r="I2094" t="n">
+        <v>0.8899798338530339</v>
+      </c>
+      <c r="J2094" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2094" t="inlineStr"/>
+    </row>
+    <row r="2095">
+      <c r="A2095" s="1" t="n">
+        <v>2093</v>
+      </c>
+      <c r="B2095" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0531.png</t>
+        </is>
+      </c>
+      <c r="C2095" t="inlineStr"/>
+      <c r="D2095" t="inlineStr"/>
+      <c r="E2095" t="inlineStr"/>
+      <c r="F2095" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCCN)NC(=O)[C@H](CCCN)NCc2cccnc2Sc2c(Cl)ccc(-c3ccc(C(=O)O)nc3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G2095" t="inlineStr"/>
+      <c r="H2095" t="inlineStr"/>
+      <c r="I2095" t="n">
+        <v>0.9093102288543945</v>
+      </c>
+      <c r="J2095" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2095" t="inlineStr"/>
+    </row>
+    <row r="2096">
+      <c r="A2096" s="1" t="n">
+        <v>2094</v>
+      </c>
+      <c r="B2096" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0534.png</t>
+        </is>
+      </c>
+      <c r="C2096" t="inlineStr"/>
+      <c r="D2096" t="inlineStr"/>
+      <c r="E2096" t="inlineStr"/>
+      <c r="F2096" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(N)=O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CC)nc2cc(C(N)=O)cc(c21)OCC(N1C2CCC1COC2)CO3</t>
+        </is>
+      </c>
+      <c r="G2096" t="inlineStr"/>
+      <c r="H2096" t="inlineStr"/>
+      <c r="I2096" t="n">
+        <v>0.8868582239629101</v>
+      </c>
+      <c r="J2096" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2096" t="inlineStr"/>
+    </row>
+    <row r="2097">
+      <c r="A2097" s="1" t="n">
+        <v>2095</v>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0537.png</t>
+        </is>
+      </c>
+      <c r="C2097" t="inlineStr"/>
+      <c r="D2097" t="inlineStr"/>
+      <c r="E2097" t="inlineStr"/>
+      <c r="F2097" t="inlineStr">
+        <is>
+          <t>COCCOc1cc(C(=O)OC)cc2c1nc(Cc1cc(F)c3cc1COCCc1cc(Cl)cc(F)c1COc1cccc-3n1)n2C[C@@H]1CCO1</t>
+        </is>
+      </c>
+      <c r="G2097" t="inlineStr"/>
+      <c r="H2097" t="inlineStr"/>
+      <c r="I2097" t="n">
+        <v>0.8782259910325526</v>
+      </c>
+      <c r="J2097" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2097" t="inlineStr"/>
+    </row>
+    <row r="2098">
+      <c r="A2098" s="1" t="n">
+        <v>2096</v>
+      </c>
+      <c r="B2098" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0542.png</t>
+        </is>
+      </c>
+      <c r="C2098" t="inlineStr"/>
+      <c r="D2098" t="inlineStr"/>
+      <c r="E2098" t="inlineStr"/>
+      <c r="F2098" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CC(=O)NCCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccc(Cl)c(Cl)c2)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2098" t="inlineStr"/>
+      <c r="H2098" t="inlineStr"/>
+      <c r="I2098" t="n">
+        <v>0.8899475111128585</v>
+      </c>
+      <c r="J2098" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2098" t="inlineStr"/>
+    </row>
+    <row r="2099">
+      <c r="A2099" s="1" t="n">
+        <v>2097</v>
+      </c>
+      <c r="B2099" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0543.png</t>
+        </is>
+      </c>
+      <c r="C2099" t="inlineStr"/>
+      <c r="D2099" t="inlineStr"/>
+      <c r="E2099" t="inlineStr"/>
+      <c r="F2099" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](CC(=O)NCCCNC(=O)CN2CCN(C(=O)c3ccc(Nc4nc(C5CC5)cn5c(-c6cn[nH]c6)cnc45)c(F)c3)CC2)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2(F)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2099" t="inlineStr"/>
+      <c r="H2099" t="inlineStr"/>
+      <c r="I2099" t="n">
+        <v>0.8859773532227807</v>
+      </c>
+      <c r="J2099" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2099" t="inlineStr"/>
+    </row>
+    <row r="2100">
+      <c r="A2100" s="1" t="n">
+        <v>2098</v>
+      </c>
+      <c r="B2100" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0544.png</t>
+        </is>
+      </c>
+      <c r="C2100" t="inlineStr"/>
+      <c r="D2100" t="inlineStr"/>
+      <c r="E2100" t="inlineStr"/>
+      <c r="F2100" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCCCCCCCCN2CCN(C(=O)c3ccc(Nc4nc(C5CC5)cn5c(-c6cn[nH]c6)cnc45)c(F)c3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2100" t="inlineStr"/>
+      <c r="H2100" t="inlineStr"/>
+      <c r="I2100" t="n">
+        <v>0.8808743666851485</v>
+      </c>
+      <c r="J2100" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2100" t="inlineStr"/>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="1" t="n">
+        <v>2099</v>
+      </c>
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0545.png</t>
+        </is>
+      </c>
+      <c r="C2101" t="inlineStr"/>
+      <c r="D2101" t="inlineStr"/>
+      <c r="E2101" t="inlineStr"/>
+      <c r="F2101" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(NC(=O)C4CCN(C(=O)CCCCOc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)sc23)cc(OC)c1CN(C)C.[H]C(=O)O</t>
+        </is>
+      </c>
+      <c r="G2101" t="inlineStr"/>
+      <c r="H2101" t="inlineStr"/>
+      <c r="I2101" t="n">
+        <v>0.8910364271240254</v>
+      </c>
+      <c r="J2101" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2101" t="inlineStr"/>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="1" t="n">
+        <v>2100</v>
+      </c>
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0547.png</t>
+        </is>
+      </c>
+      <c r="C2102" t="inlineStr"/>
+      <c r="D2102" t="inlineStr"/>
+      <c r="E2102" t="inlineStr"/>
+      <c r="F2102" t="inlineStr">
+        <is>
+          <t>COc1cc2cc(c1OC)OCCCC(OC(=O)c1cc(OC)c(OC)c(OCc3ccccc3)c1)CCN1CCCN(CCCOC2=O)CC1</t>
+        </is>
+      </c>
+      <c r="G2102" t="inlineStr"/>
+      <c r="H2102" t="inlineStr"/>
+      <c r="I2102" t="n">
+        <v>0.9120087027326216</v>
+      </c>
+      <c r="J2102" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2102" t="inlineStr"/>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="1" t="n">
+        <v>2101</v>
+      </c>
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0548.png</t>
+        </is>
+      </c>
+      <c r="C2103" t="inlineStr"/>
+      <c r="D2103" t="inlineStr"/>
+      <c r="E2103" t="inlineStr"/>
+      <c r="F2103" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccccc2C)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2103" t="inlineStr"/>
+      <c r="H2103" t="inlineStr"/>
+      <c r="I2103" t="n">
+        <v>0.8855863382692862</v>
+      </c>
+      <c r="J2103" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2103" t="inlineStr"/>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="1" t="n">
+        <v>2102</v>
+      </c>
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0549.png</t>
+        </is>
+      </c>
+      <c r="C2104" t="inlineStr"/>
+      <c r="D2104" t="inlineStr"/>
+      <c r="E2104" t="inlineStr"/>
+      <c r="F2104" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2(F)CC2)C(C)(C)C)c(OCCCCCCNC(=O)CN2CCN(C(=O)c3ccc(Nc4nc(C5CC5)cn5c(-c6cn[nH]c6)cnc45)c(F)c3)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G2104" t="inlineStr"/>
+      <c r="H2104" t="inlineStr"/>
+      <c r="I2104" t="n">
+        <v>0.8599425454870193</v>
+      </c>
+      <c r="J2104" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2104" t="inlineStr"/>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="1" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0550.png</t>
+        </is>
+      </c>
+      <c r="C2105" t="inlineStr"/>
+      <c r="D2105" t="inlineStr"/>
+      <c r="E2105" t="inlineStr"/>
+      <c r="F2105" t="inlineStr">
+        <is>
+          <t>[H]C12CC(C)(C)C(C(=O)NC3C4=C(C=CC=C4)CC3OCC#CC#CCO[CH]3=CC4=C(C=CC=C4)C3NC(=O)C3N4C(=O)C(NC(=O)C(C)NC)CCSC4([H])CC3(C)C)N1C(=O)C(NC(=O)C(C)NC)CCS2</t>
+        </is>
+      </c>
+      <c r="G2105" t="inlineStr"/>
+      <c r="H2105" t="inlineStr"/>
+      <c r="I2105" t="n">
+        <v>0.8453012866693328</v>
+      </c>
+      <c r="J2105" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2105" t="inlineStr"/>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="1" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0551.png</t>
+        </is>
+      </c>
+      <c r="C2106" t="inlineStr"/>
+      <c r="D2106" t="inlineStr"/>
+      <c r="E2106" t="inlineStr"/>
+      <c r="F2106" t="inlineStr">
+        <is>
+          <t>CC(C)[C@H](NC(=O)CCCCCCNC(=O)CN1CCN(C(=O)c2ccc(Nc3nc(C4CC4)cn4c(-c5cn[nH]c5)cnc34)c(Cl)c2)CC1)C(=O)N1C[C@@H](O)C[C@@H]1C(=O)N[C@@H](C)c1ccc(-c2cncs2)cc1</t>
+        </is>
+      </c>
+      <c r="G2106" t="inlineStr"/>
+      <c r="H2106" t="inlineStr"/>
+      <c r="I2106" t="n">
+        <v>0.8980056298945307</v>
+      </c>
+      <c r="J2106" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2106" t="inlineStr"/>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="1" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0552.png</t>
+        </is>
+      </c>
+      <c r="C2107" t="inlineStr"/>
+      <c r="D2107" t="inlineStr"/>
+      <c r="E2107" t="inlineStr"/>
+      <c r="F2107" t="inlineStr">
+        <is>
+          <t>[H][C@]12CC(C)(C)[C@@H](C(=O)N[C@H](CCOCC#CC#CCOCC[C@@H](NC(=O)[C@H]3N4C(=O)[C@@H](NC(=O)[C@H](C)NC)CCS[C@@]4([H])CC3(C)C)c3ccccc3)c3ccccc3)N1C(=O)[C@@H](NC(=O)[C@H](C)NC)CCS2</t>
+        </is>
+      </c>
+      <c r="G2107" t="inlineStr"/>
+      <c r="H2107" t="inlineStr"/>
+      <c r="I2107" t="n">
+        <v>0.8704495982409879</v>
+      </c>
+      <c r="J2107" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2107" t="inlineStr"/>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="1" t="n">
+        <v>2106</v>
+      </c>
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0553.png</t>
+        </is>
+      </c>
+      <c r="C2108" t="inlineStr"/>
+      <c r="D2108" t="inlineStr"/>
+      <c r="E2108" t="inlineStr"/>
+      <c r="F2108" t="inlineStr">
+        <is>
+          <t>CN1CCC(Oc2cc(C(=O)O)cc3c2nc(Cc2ccc4cc2OCCCc2cc(C#N)ccc2COc2cccc-4n2)n3C[C@@H]2CCO2)C1</t>
+        </is>
+      </c>
+      <c r="G2108" t="inlineStr"/>
+      <c r="H2108" t="inlineStr"/>
+      <c r="I2108" t="n">
+        <v>0.8739949378649005</v>
+      </c>
+      <c r="J2108" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2108" t="inlineStr"/>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="1" t="n">
+        <v>2107</v>
+      </c>
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0554.png</t>
+        </is>
+      </c>
+      <c r="C2109" t="inlineStr"/>
+      <c r="D2109" t="inlineStr"/>
+      <c r="E2109" t="inlineStr"/>
+      <c r="F2109" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NC4CC5(CCN(C(=O)CCN6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2109" t="inlineStr"/>
+      <c r="H2109" t="inlineStr"/>
+      <c r="I2109" t="n">
+        <v>0.9000435464406407</v>
+      </c>
+      <c r="J2109" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2109" t="inlineStr"/>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="1" t="n">
+        <v>2108</v>
+      </c>
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0555.png</t>
+        </is>
+      </c>
+      <c r="C2110" t="inlineStr"/>
+      <c r="D2110" t="inlineStr"/>
+      <c r="E2110" t="inlineStr"/>
+      <c r="F2110" t="inlineStr">
+        <is>
+          <t>CCCCCC(=O)N[C@H]1CC(=O)NCCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2cccc3ccccc23)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2110" t="inlineStr"/>
+      <c r="H2110" t="inlineStr"/>
+      <c r="I2110" t="n">
+        <v>0.8860733299909688</v>
+      </c>
+      <c r="J2110" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2110" t="inlineStr"/>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="1" t="n">
+        <v>2109</v>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0558.png</t>
+        </is>
+      </c>
+      <c r="C2111" t="inlineStr"/>
+      <c r="D2111" t="inlineStr"/>
+      <c r="E2111" t="inlineStr"/>
+      <c r="F2111" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CC(=O)NCCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccc(Cl)cc2)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2111" t="inlineStr"/>
+      <c r="H2111" t="inlineStr"/>
+      <c r="I2111" t="n">
+        <v>0.8875888785644509</v>
+      </c>
+      <c r="J2111" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2111" t="inlineStr"/>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="1" t="n">
+        <v>2110</v>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0559.png</t>
+        </is>
+      </c>
+      <c r="C2112" t="inlineStr"/>
+      <c r="D2112" t="inlineStr"/>
+      <c r="E2112" t="inlineStr"/>
+      <c r="F2112" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2cc(-c3c4ccc(=[N+](C)C)cc-4oc4cc(N(C)C)ccc34)c(C(=O)[O-])cc2OC)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G2112" t="inlineStr"/>
+      <c r="H2112" t="inlineStr"/>
+      <c r="I2112" t="n">
+        <v>0.8994092372472819</v>
+      </c>
+      <c r="J2112" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2112" t="inlineStr"/>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="1" t="n">
+        <v>2111</v>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0560.png</t>
+        </is>
+      </c>
+      <c r="C2113" t="inlineStr"/>
+      <c r="D2113" t="inlineStr"/>
+      <c r="E2113" t="inlineStr"/>
+      <c r="F2113" t="inlineStr">
+        <is>
+          <t>CNC(=O)c1cc2c(=O)n(C)cc(-c3cc(OC)c(CN4CCC5(CC4)CN(c4ccc6c(c4)C(=O)N(C4CCC(=O)NC4=O)C6)C5)c(OC)c3)c2s1</t>
+        </is>
+      </c>
+      <c r="G2113" t="inlineStr"/>
+      <c r="H2113" t="inlineStr"/>
+      <c r="I2113" t="n">
+        <v>0.9018473782069225</v>
+      </c>
+      <c r="J2113" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2113" t="inlineStr"/>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="1" t="n">
+        <v>2112</v>
+      </c>
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0561.png</t>
+        </is>
+      </c>
+      <c r="C2114" t="inlineStr"/>
+      <c r="D2114" t="inlineStr"/>
+      <c r="E2114" t="inlineStr"/>
+      <c r="F2114" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NC4CC5(CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7)CC5)C4)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2114" t="inlineStr"/>
+      <c r="H2114" t="inlineStr"/>
+      <c r="I2114" t="n">
+        <v>0.8603665995267586</v>
+      </c>
+      <c r="J2114" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2114" t="inlineStr"/>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="1" t="n">
+        <v>2113</v>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0562.png</t>
+        </is>
+      </c>
+      <c r="C2115" t="inlineStr"/>
+      <c r="D2115" t="inlineStr"/>
+      <c r="E2115" t="inlineStr"/>
+      <c r="F2115" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCCN)NC(=O)[C@H](CCCN)NCc2cccnc2Sc2c(Cl)ccc(-c3ccn4nc(C(=O)O)cc4c3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G2115" t="inlineStr"/>
+      <c r="H2115" t="inlineStr"/>
+      <c r="I2115" t="n">
+        <v>0.908953215576485</v>
+      </c>
+      <c r="J2115" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2115" t="inlineStr"/>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="1" t="n">
+        <v>2114</v>
+      </c>
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0563.png</t>
+        </is>
+      </c>
+      <c r="C2116" t="inlineStr"/>
+      <c r="D2116" t="inlineStr"/>
+      <c r="E2116" t="inlineStr"/>
+      <c r="F2116" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCN)NC(=O)[C@H](CCCN)NCc2cccnc2Sc2c(F)ccc(-c3ccc(C(=O)O)cc3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G2116" t="inlineStr"/>
+      <c r="H2116" t="inlineStr"/>
+      <c r="I2116" t="n">
+        <v>0.8914207014496056</v>
+      </c>
+      <c r="J2116" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2116" t="inlineStr"/>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="1" t="n">
+        <v>2115</v>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0565.png</t>
+        </is>
+      </c>
+      <c r="C2117" t="inlineStr"/>
+      <c r="D2117" t="inlineStr"/>
+      <c r="E2117" t="inlineStr"/>
+      <c r="F2117" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2cc3c(cc2OC)C2(OC3=O)c3ccc(OC(C)=O)cc3P(=O)(OC)c3cc(OC(C)=O)ccc32)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G2117" t="inlineStr"/>
+      <c r="H2117" t="inlineStr"/>
+      <c r="I2117" t="n">
+        <v>0.9053180615858006</v>
+      </c>
+      <c r="J2117" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2117" t="inlineStr"/>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="1" t="n">
+        <v>2116</v>
+      </c>
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0567.png</t>
+        </is>
+      </c>
+      <c r="C2118" t="inlineStr"/>
+      <c r="D2118" t="inlineStr"/>
+      <c r="E2118" t="inlineStr"/>
+      <c r="F2118" t="inlineStr">
+        <is>
+          <t>CN1C(=O)[C@H](CCCCN)NC(=O)[C@H](CCCN)NCc2cccnc2Sc2c(F)ccc(-c3ccn(/C=C/C(=O)O)c(=O)c3)c2CNC(=O)[C@@H]1Cc1c[nH]c2ccccc12</t>
+        </is>
+      </c>
+      <c r="G2118" t="inlineStr"/>
+      <c r="H2118" t="inlineStr"/>
+      <c r="I2118" t="n">
+        <v>0.9010490369768657</v>
+      </c>
+      <c r="J2118" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2118" t="inlineStr"/>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="1" t="n">
+        <v>2117</v>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0568.png</t>
+        </is>
+      </c>
+      <c r="C2119" t="inlineStr"/>
+      <c r="D2119" t="inlineStr"/>
+      <c r="E2119" t="inlineStr"/>
+      <c r="F2119" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2cccc3ccccc23)NC(=O)[C@H](CCS(C)(=O)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2119" t="inlineStr"/>
+      <c r="H2119" t="inlineStr"/>
+      <c r="I2119" t="n">
+        <v>0.881558679181409</v>
+      </c>
+      <c r="J2119" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2119" t="inlineStr"/>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="1" t="n">
+        <v>2118</v>
+      </c>
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0569.png</t>
+        </is>
+      </c>
+      <c r="C2120" t="inlineStr"/>
+      <c r="D2120" t="inlineStr"/>
+      <c r="E2120" t="inlineStr"/>
+      <c r="F2120" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(N)=O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CC)nc2cc(C(N)=O)cc(c21)OCC(CN1CCN(C)CC1)CO3</t>
+        </is>
+      </c>
+      <c r="G2120" t="inlineStr"/>
+      <c r="H2120" t="inlineStr"/>
+      <c r="I2120" t="n">
+        <v>0.9038346110660073</v>
+      </c>
+      <c r="J2120" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2120" t="inlineStr"/>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="1" t="n">
+        <v>2119</v>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0571.png</t>
+        </is>
+      </c>
+      <c r="C2121" t="inlineStr"/>
+      <c r="D2121" t="inlineStr"/>
+      <c r="E2121" t="inlineStr"/>
+      <c r="F2121" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(NC(=O)[C@H]4CCCN(C(=O)CCCCOc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2121" t="inlineStr"/>
+      <c r="H2121" t="inlineStr"/>
+      <c r="I2121" t="n">
+        <v>0.8959653553381359</v>
+      </c>
+      <c r="J2121" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2121" t="inlineStr"/>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="1" t="n">
+        <v>2120</v>
+      </c>
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0572.png</t>
+        </is>
+      </c>
+      <c r="C2122" t="inlineStr"/>
+      <c r="D2122" t="inlineStr"/>
+      <c r="E2122" t="inlineStr"/>
+      <c r="F2122" t="inlineStr">
+        <is>
+          <t>COCCOc1cc(C(=O)O)cc2c1nc(Cc1cc(F)c3cc1COCCc1cc(N)ccc1COc1ccc(F)c-3n1)n2C[C@@H]1CCO1</t>
+        </is>
+      </c>
+      <c r="G2122" t="inlineStr"/>
+      <c r="H2122" t="inlineStr"/>
+      <c r="I2122" t="n">
+        <v>0.8855148529097748</v>
+      </c>
+      <c r="J2122" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2122" t="inlineStr"/>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="1" t="n">
+        <v>2121</v>
+      </c>
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0574.png</t>
+        </is>
+      </c>
+      <c r="C2123" t="inlineStr"/>
+      <c r="D2123" t="inlineStr"/>
+      <c r="E2123" t="inlineStr"/>
+      <c r="F2123" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(N)=O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CC)nc2cc(C(N)=O)cc(c21)OCC(n1ccnc1)CO3</t>
+        </is>
+      </c>
+      <c r="G2123" t="inlineStr"/>
+      <c r="H2123" t="inlineStr"/>
+      <c r="I2123" t="n">
+        <v>0.901662242282937</v>
+      </c>
+      <c r="J2123" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2123" t="inlineStr"/>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="1" t="n">
+        <v>2122</v>
+      </c>
+      <c r="B2124" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0575.png</t>
+        </is>
+      </c>
+      <c r="C2124" t="inlineStr"/>
+      <c r="D2124" t="inlineStr"/>
+      <c r="E2124" t="inlineStr"/>
+      <c r="F2124" t="inlineStr">
+        <is>
+          <t>[H][C@]12CC(C)(C)[C@@H](C(=O)N[C@H]3c4ccccc4C[C@H]3OCc3ccc(CO[C@@H]4Cc5ccccc5[C@@H]4NC(=O)[C@H]4N5C(=O)[C@@H](NC(=O)[C@H](C)NC)CCS[C@@]5([H])CC4(C)C)cc3)N1C(=O)[C@@H](NC(=O)[C@H](C)NC)CCS2</t>
+        </is>
+      </c>
+      <c r="G2124" t="inlineStr"/>
+      <c r="H2124" t="inlineStr"/>
+      <c r="I2124" t="n">
+        <v>0.8843648749948265</v>
+      </c>
+      <c r="J2124" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2124" t="inlineStr"/>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="1" t="n">
+        <v>2123</v>
+      </c>
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0576.png</t>
+        </is>
+      </c>
+      <c r="C2125" t="inlineStr"/>
+      <c r="D2125" t="inlineStr"/>
+      <c r="E2125" t="inlineStr"/>
+      <c r="F2125" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NCC4CC5(CCN(CCCN6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2125" t="inlineStr"/>
+      <c r="H2125" t="inlineStr"/>
+      <c r="I2125" t="n">
+        <v>0.8555986401865193</v>
+      </c>
+      <c r="J2125" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2125" t="inlineStr"/>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="1" t="n">
+        <v>2124</v>
+      </c>
+      <c r="B2126" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0578.png</t>
+        </is>
+      </c>
+      <c r="C2126" t="inlineStr"/>
+      <c r="D2126" t="inlineStr"/>
+      <c r="E2126" t="inlineStr"/>
+      <c r="F2126" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NCC4CC5(CCN(CCCN6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)CO4)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G2126" t="inlineStr"/>
+      <c r="H2126" t="inlineStr"/>
+      <c r="I2126" t="n">
+        <v>0.8844391866319747</v>
+      </c>
+      <c r="J2126" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2126" t="inlineStr"/>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="1" t="n">
+        <v>2125</v>
+      </c>
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0583.png</t>
+        </is>
+      </c>
+      <c r="C2127" t="inlineStr"/>
+      <c r="D2127" t="inlineStr"/>
+      <c r="E2127" t="inlineStr"/>
+      <c r="F2127" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]C1CC(F)(F)CN1C(=O)CNC(=O)c1ccnc2ccc(OCCCN3CCN(C(=O)CN4CCN(CC(=O)O)CCN(CC(=O)O)CCN(CC(=O)O)CC4)CC3)cc12</t>
+        </is>
+      </c>
+      <c r="G2127" t="inlineStr"/>
+      <c r="H2127" t="inlineStr"/>
+      <c r="I2127" t="n">
+        <v>0.8682170466610961</v>
+      </c>
+      <c r="J2127" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2127" t="inlineStr"/>
+    </row>
+    <row r="2128">
+      <c r="A2128" s="1" t="n">
+        <v>2126</v>
+      </c>
+      <c r="B2128" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0584.png</t>
+        </is>
+      </c>
+      <c r="C2128" t="inlineStr"/>
+      <c r="D2128" t="inlineStr"/>
+      <c r="E2128" t="inlineStr"/>
+      <c r="F2128" t="inlineStr">
+        <is>
+          <t>[H][C@@]12/C=C\CCCCN(C)C(=O)[C@H]3C[C@H](Oc4cc(-c5nc(C(C)C)cs5)nc5c(C)c(OC)ccc45)C[C@@H]3C(=O)N[C@]1(C(=O)NS(=O)(=O)C1CC1)C2</t>
+        </is>
+      </c>
+      <c r="G2128" t="inlineStr"/>
+      <c r="H2128" t="inlineStr"/>
+      <c r="I2128" t="n">
+        <v>0.8904723748053179</v>
+      </c>
+      <c r="J2128" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2128" t="inlineStr"/>
+    </row>
+    <row r="2129">
+      <c r="A2129" s="1" t="n">
+        <v>2127</v>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0587.png</t>
+        </is>
+      </c>
+      <c r="C2129" t="inlineStr"/>
+      <c r="D2129" t="inlineStr"/>
+      <c r="E2129" t="inlineStr"/>
+      <c r="F2129" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCCCCCCCC(=O)N2CCN(C(=O)c3ccc(Nc4nc(C5CC5)cn5c(-c6cn[nH]c6)cnc45)c(F)c3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2129" t="inlineStr"/>
+      <c r="H2129" t="inlineStr"/>
+      <c r="I2129" t="n">
+        <v>0.8837239255523575</v>
+      </c>
+      <c r="J2129" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2129" t="inlineStr"/>
+    </row>
+    <row r="2130">
+      <c r="A2130" s="1" t="n">
+        <v>2128</v>
+      </c>
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0589.png</t>
+        </is>
+      </c>
+      <c r="C2130" t="inlineStr"/>
+      <c r="D2130" t="inlineStr"/>
+      <c r="E2130" t="inlineStr"/>
+      <c r="F2130" t="inlineStr">
+        <is>
+          <t>CNCc1c(OC)cc(-c2cn(C)c(=O)c3cc(C(=O)NC4CN(C5CCN(c6ccc7c(c6)CN(C6CCC(=O)NC6=O)C7=O)CC5)CC4(F)F)sc23)cc1OC</t>
+        </is>
+      </c>
+      <c r="G2130" t="inlineStr"/>
+      <c r="H2130" t="inlineStr"/>
+      <c r="I2130" t="n">
+        <v>0.8862915335702021</v>
+      </c>
+      <c r="J2130" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2130" t="inlineStr"/>
+    </row>
+    <row r="2131">
+      <c r="A2131" s="1" t="n">
+        <v>2129</v>
+      </c>
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0590.png</t>
+        </is>
+      </c>
+      <c r="C2131" t="inlineStr"/>
+      <c r="D2131" t="inlineStr"/>
+      <c r="E2131" t="inlineStr"/>
+      <c r="F2131" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCCCCCC(=O)N2CCN(C(=O)c3ccc(Nc4nc(C5CC5)cn5c(-c6cn[nH]c6)cnc45)c(F)c3)CC2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2131" t="inlineStr"/>
+      <c r="H2131" t="inlineStr"/>
+      <c r="I2131" t="n">
+        <v>0.8671151606121326</v>
+      </c>
+      <c r="J2131" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2131" t="inlineStr"/>
+    </row>
+    <row r="2132">
+      <c r="A2132" s="1" t="n">
+        <v>2130</v>
+      </c>
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0592.png</t>
+        </is>
+      </c>
+      <c r="C2132" t="inlineStr"/>
+      <c r="D2132" t="inlineStr"/>
+      <c r="E2132" t="inlineStr"/>
+      <c r="F2132" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCCCNC(=O)CN2CCN(C(=O)c3ccc(Nc4nc(C5CC5)cn5c(-c6cn[nH]c6)cnc45)c(F)c3)CC2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2132" t="inlineStr"/>
+      <c r="H2132" t="inlineStr"/>
+      <c r="I2132" t="n">
+        <v>0.887860916523232</v>
+      </c>
+      <c r="J2132" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2132" t="inlineStr"/>
+    </row>
+    <row r="2133">
+      <c r="A2133" s="1" t="n">
+        <v>2131</v>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0595.png</t>
+        </is>
+      </c>
+      <c r="C2133" t="inlineStr"/>
+      <c r="D2133" t="inlineStr"/>
+      <c r="E2133" t="inlineStr"/>
+      <c r="F2133" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2ccccc2C(F)(F)F)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2133" t="inlineStr"/>
+      <c r="H2133" t="inlineStr"/>
+      <c r="I2133" t="n">
+        <v>0.8846321325195994</v>
+      </c>
+      <c r="J2133" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2133" t="inlineStr"/>
+    </row>
+    <row r="2134">
+      <c r="A2134" s="1" t="n">
+        <v>2132</v>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0596.png</t>
+        </is>
+      </c>
+      <c r="C2134" t="inlineStr"/>
+      <c r="D2134" t="inlineStr"/>
+      <c r="E2134" t="inlineStr"/>
+      <c r="F2134" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(C)=O)C(=O)N[C@H]1CC(=O)NCCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](Cc2cccc3ccccc23)NC(=O)[C@H](Cc2c[nH]cn2)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2134" t="inlineStr"/>
+      <c r="H2134" t="inlineStr"/>
+      <c r="I2134" t="n">
+        <v>0.8833034208994214</v>
+      </c>
+      <c r="J2134" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2134" t="inlineStr"/>
+    </row>
+    <row r="2135">
+      <c r="A2135" s="1" t="n">
+        <v>2133</v>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0597.png</t>
+        </is>
+      </c>
+      <c r="C2135" t="inlineStr"/>
+      <c r="D2135" t="inlineStr"/>
+      <c r="E2135" t="inlineStr"/>
+      <c r="F2135" t="inlineStr">
+        <is>
+          <t>O=C(CN1CCN(C(=O)c2ccc(Nc3nc(C4CC4)cn4c(-c5cn[nH]c5)cnc34)c(F)c2)CC1)NCCOCCOCCOCCNC1=CCCC2=C1C(=O)N(C1CCC(=O)NC1=O)C2=O</t>
+        </is>
+      </c>
+      <c r="G2135" t="inlineStr"/>
+      <c r="H2135" t="inlineStr"/>
+      <c r="I2135" t="n">
+        <v>0.8989411043068729</v>
+      </c>
+      <c r="J2135" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2135" t="inlineStr"/>
+    </row>
+    <row r="2136">
+      <c r="A2136" s="1" t="n">
+        <v>2134</v>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0600.png</t>
+        </is>
+      </c>
+      <c r="C2136" t="inlineStr"/>
+      <c r="D2136" t="inlineStr"/>
+      <c r="E2136" t="inlineStr"/>
+      <c r="F2136" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccccc1C[C@H]1NC(=O)[C@H](Cc2c[nH]cn2)NC(=O)[C@@H](NC(=O)[C@H](CCCC)NC(C)=O)CCC(=O)NCCCCNC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](CCCNC(=N)N)NC1=O</t>
+        </is>
+      </c>
+      <c r="G2136" t="inlineStr"/>
+      <c r="H2136" t="inlineStr"/>
+      <c r="I2136" t="n">
+        <v>0.8836877394460909</v>
+      </c>
+      <c r="J2136" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2136" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_HighConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_HighConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2136"/>
+  <dimension ref="A1:K2304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62395,6 +62395,4878 @@
       </c>
       <c r="K2136" t="inlineStr"/>
     </row>
+    <row r="2137">
+      <c r="A2137" s="1" t="n">
+        <v>2135</v>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0605.png</t>
+        </is>
+      </c>
+      <c r="C2137" t="inlineStr"/>
+      <c r="D2137" t="inlineStr"/>
+      <c r="E2137" t="inlineStr"/>
+      <c r="F2137" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CCC5(CC4)CCN(C(=O)C4CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC4)CC5)nc3cc2OC)n1.[I-27] |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2137" t="inlineStr"/>
+      <c r="H2137" t="inlineStr"/>
+      <c r="I2137" t="n">
+        <v>0.8610171580958942</v>
+      </c>
+      <c r="J2137" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2137" t="inlineStr"/>
+    </row>
+    <row r="2138">
+      <c r="A2138" s="1" t="n">
+        <v>2136</v>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0613.png</t>
+        </is>
+      </c>
+      <c r="C2138" t="inlineStr"/>
+      <c r="D2138" t="inlineStr"/>
+      <c r="E2138" t="inlineStr"/>
+      <c r="F2138" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(C(=O)C6(O)CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2OC)n1.[I-33] |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2138" t="inlineStr"/>
+      <c r="H2138" t="inlineStr"/>
+      <c r="I2138" t="n">
+        <v>0.8565230705181638</v>
+      </c>
+      <c r="J2138" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2138" t="inlineStr"/>
+    </row>
+    <row r="2139">
+      <c r="A2139" s="1" t="n">
+        <v>2137</v>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0617.png</t>
+        </is>
+      </c>
+      <c r="C2139" t="inlineStr"/>
+      <c r="D2139" t="inlineStr"/>
+      <c r="E2139" t="inlineStr"/>
+      <c r="F2139" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)C3=C(C2=O)C(NCCNC(=O)C2=CC=C(NC(=O)C4NC5(CCCCC5)[CH]5(C(=O)NC6=CC(Cl)=CC=C65)C4C4=CC=CC(Cl)=C4F)C=C2)=CC=C3)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2139" t="inlineStr"/>
+      <c r="H2139" t="inlineStr"/>
+      <c r="I2139" t="n">
+        <v>0.8857879835284755</v>
+      </c>
+      <c r="J2139" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2139" t="inlineStr"/>
+    </row>
+    <row r="2140">
+      <c r="A2140" s="1" t="n">
+        <v>2138</v>
+      </c>
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0621.png</t>
+        </is>
+      </c>
+      <c r="C2140" t="inlineStr"/>
+      <c r="D2140" t="inlineStr"/>
+      <c r="E2140" t="inlineStr"/>
+      <c r="F2140" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)N(C)CCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)c2)cc1C=C[C@@H]1CC[C@@H](C(F)(F)F)CC1</t>
+        </is>
+      </c>
+      <c r="G2140" t="inlineStr"/>
+      <c r="H2140" t="inlineStr"/>
+      <c r="I2140" t="n">
+        <v>0.9049765300240314</v>
+      </c>
+      <c r="J2140" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2140" t="inlineStr"/>
+    </row>
+    <row r="2141">
+      <c r="A2141" s="1" t="n">
+        <v>2139</v>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0625.png</t>
+        </is>
+      </c>
+      <c r="C2141" t="inlineStr"/>
+      <c r="D2141" t="inlineStr"/>
+      <c r="E2141" t="inlineStr"/>
+      <c r="F2141" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCOCCOCCOCCN2CCC[C@@H](Nc3ncc(Cl)c(Nc4ccccc4S(=O)(=O)C(C)C)n3)C2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2141" t="inlineStr"/>
+      <c r="H2141" t="inlineStr"/>
+      <c r="I2141" t="n">
+        <v>0.8822048169708255</v>
+      </c>
+      <c r="J2141" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2141" t="inlineStr"/>
+    </row>
+    <row r="2142">
+      <c r="A2142" s="1" t="n">
+        <v>2140</v>
+      </c>
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0629.png</t>
+        </is>
+      </c>
+      <c r="C2142" t="inlineStr"/>
+      <c r="D2142" t="inlineStr"/>
+      <c r="E2142" t="inlineStr"/>
+      <c r="F2142" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCCCCCCCC(=O)N[C@H](C(=O)N3C[C@H](O)C[C@H]3C(=O)NCc3ccc(-c4cncs4)cc3)C(C)C)c2)cc1C=C[C@@H]1CC[C@@H](C(F)(F)F)CC1</t>
+        </is>
+      </c>
+      <c r="G2142" t="inlineStr"/>
+      <c r="H2142" t="inlineStr"/>
+      <c r="I2142" t="n">
+        <v>0.8862434679225574</v>
+      </c>
+      <c r="J2142" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2142" t="inlineStr"/>
+    </row>
+    <row r="2143">
+      <c r="A2143" s="1" t="n">
+        <v>2141</v>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0637.png</t>
+        </is>
+      </c>
+      <c r="C2143" t="inlineStr"/>
+      <c r="D2143" t="inlineStr"/>
+      <c r="E2143" t="inlineStr"/>
+      <c r="F2143" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCOCCOCCOCC(=O)N[C@H](C(=O)N3C[C@H](O)C[C@H]3C(=O)NCc3ccc(-c4scnc4C)cc3)C(C)(C)C)c2)cc1C=C[C@@H]1CC[C@@H](C(F)(F)F)CC1</t>
+        </is>
+      </c>
+      <c r="G2143" t="inlineStr"/>
+      <c r="H2143" t="inlineStr"/>
+      <c r="I2143" t="n">
+        <v>0.8611185673961723</v>
+      </c>
+      <c r="J2143" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2143" t="inlineStr"/>
+    </row>
+    <row r="2144">
+      <c r="A2144" s="1" t="n">
+        <v>2142</v>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0641.png</t>
+        </is>
+      </c>
+      <c r="C2144" t="inlineStr"/>
+      <c r="D2144" t="inlineStr"/>
+      <c r="E2144" t="inlineStr"/>
+      <c r="F2144" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCCCC(=O)N[C@H](C(=O)N3C[C@H](O)C[C@H]3C(=O)NCc3ccc(-c4cncs4)cc3)C(C)(C)C)c2)cc1C=C[C@@H]1CC[C@@H](C(F)(F)F)CC1</t>
+        </is>
+      </c>
+      <c r="G2144" t="inlineStr"/>
+      <c r="H2144" t="inlineStr"/>
+      <c r="I2144" t="n">
+        <v>0.8811884893677462</v>
+      </c>
+      <c r="J2144" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2144" t="inlineStr"/>
+    </row>
+    <row r="2145">
+      <c r="A2145" s="1" t="n">
+        <v>2143</v>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0649.png</t>
+        </is>
+      </c>
+      <c r="C2145" t="inlineStr"/>
+      <c r="D2145" t="inlineStr"/>
+      <c r="E2145" t="inlineStr"/>
+      <c r="F2145" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3cccc(NC(=O)CCOCCOCCOCCN4CCC(=C(c5ccc(F)cc5)c5ccc(F)cc5)CC4)c3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2145" t="inlineStr"/>
+      <c r="H2145" t="inlineStr"/>
+      <c r="I2145" t="n">
+        <v>0.9079939443219807</v>
+      </c>
+      <c r="J2145" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2145" t="inlineStr"/>
+    </row>
+    <row r="2146">
+      <c r="A2146" s="1" t="n">
+        <v>2144</v>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0653.png</t>
+        </is>
+      </c>
+      <c r="C2146" t="inlineStr"/>
+      <c r="D2146" t="inlineStr"/>
+      <c r="E2146" t="inlineStr"/>
+      <c r="F2146" t="inlineStr">
+        <is>
+          <t>C=C(Cl)C(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCCCCCCCCCCN4CCC(c5cc(F)cc6c5CN(C5CCC(=O)NC5=O)C6=O)CC4)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G2146" t="inlineStr"/>
+      <c r="H2146" t="inlineStr"/>
+      <c r="I2146" t="n">
+        <v>0.899838224186312</v>
+      </c>
+      <c r="J2146" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2146" t="inlineStr"/>
+    </row>
+    <row r="2147">
+      <c r="A2147" s="1" t="n">
+        <v>2145</v>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0661.png</t>
+        </is>
+      </c>
+      <c r="C2147" t="inlineStr"/>
+      <c r="D2147" t="inlineStr"/>
+      <c r="E2147" t="inlineStr"/>
+      <c r="F2147" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(C(=O)C6CCC(Nc7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2OC)n1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2147" t="inlineStr"/>
+      <c r="H2147" t="inlineStr"/>
+      <c r="I2147" t="n">
+        <v>0.8823459041713859</v>
+      </c>
+      <c r="J2147" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2147" t="inlineStr"/>
+    </row>
+    <row r="2148">
+      <c r="A2148" s="1" t="n">
+        <v>2146</v>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0669.png</t>
+        </is>
+      </c>
+      <c r="C2148" t="inlineStr"/>
+      <c r="D2148" t="inlineStr"/>
+      <c r="E2148" t="inlineStr"/>
+      <c r="F2148" t="inlineStr">
+        <is>
+          <t>COc1ccc2c(c1)CCCC(c1ccc(F)cc1)=C2c1ccc(N2CCC(CN3CCN(c4ccc5c(c4)CN([C@H]4CCC(=O)NC4=O)C5=O)CC3)CC2)cc1</t>
+        </is>
+      </c>
+      <c r="G2148" t="inlineStr"/>
+      <c r="H2148" t="inlineStr"/>
+      <c r="I2148" t="n">
+        <v>0.8889305101935889</v>
+      </c>
+      <c r="J2148" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2148" t="inlineStr"/>
+    </row>
+    <row r="2149">
+      <c r="A2149" s="1" t="n">
+        <v>2147</v>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0673.png</t>
+        </is>
+      </c>
+      <c r="C2149" t="inlineStr"/>
+      <c r="D2149" t="inlineStr"/>
+      <c r="E2149" t="inlineStr"/>
+      <c r="F2149" t="inlineStr">
+        <is>
+          <t>C=C(Cl)C(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCC4CCC(CN5CCC(c6cc(F)cc7c6CN(C6CCC(=O)NC6=O)C7=O)CC5)CC4)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G2149" t="inlineStr"/>
+      <c r="H2149" t="inlineStr"/>
+      <c r="I2149" t="n">
+        <v>0.8924391138341621</v>
+      </c>
+      <c r="J2149" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2149" t="inlineStr"/>
+    </row>
+    <row r="2150">
+      <c r="A2150" s="1" t="n">
+        <v>2148</v>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0681.png</t>
+        </is>
+      </c>
+      <c r="C2150" t="inlineStr"/>
+      <c r="D2150" t="inlineStr"/>
+      <c r="E2150" t="inlineStr"/>
+      <c r="F2150" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CCC5(CC4)CN(C(=O)C4CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC4)C5)nc3cc2OC)n1.[I-19] |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2150" t="inlineStr"/>
+      <c r="H2150" t="inlineStr"/>
+      <c r="I2150" t="n">
+        <v>0.8858068259670857</v>
+      </c>
+      <c r="J2150" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2150" t="inlineStr"/>
+    </row>
+    <row r="2151">
+      <c r="A2151" s="1" t="n">
+        <v>2149</v>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0689.png</t>
+        </is>
+      </c>
+      <c r="C2151" t="inlineStr"/>
+      <c r="D2151" t="inlineStr"/>
+      <c r="E2151" t="inlineStr"/>
+      <c r="F2151" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCOCCOCCOCCOCCOCC(=O)N[C@H](C(=O)N3C[C@H](O)C[C@H]3C(=O)NCc3ccc(-c4scnc4C)cc3)C(C)C)c2)cc1C=C[C@@H]1CC[C@@H](C(F)(F)F)CC1</t>
+        </is>
+      </c>
+      <c r="G2151" t="inlineStr"/>
+      <c r="H2151" t="inlineStr"/>
+      <c r="I2151" t="n">
+        <v>0.8679405596506941</v>
+      </c>
+      <c r="J2151" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2151" t="inlineStr"/>
+    </row>
+    <row r="2152">
+      <c r="A2152" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0693.png</t>
+        </is>
+      </c>
+      <c r="C2152" t="inlineStr"/>
+      <c r="D2152" t="inlineStr"/>
+      <c r="E2152" t="inlineStr"/>
+      <c r="F2152" t="inlineStr">
+        <is>
+          <t>*c1c(-c2c(F)cccc2OCCCCCCCCCCC(=O)N[C@H](C(=O)N2C[C@H](O)C[C@H]2C(=O)NCc2ccc(-c3cncs3)cc2)C(C)(C)C)c(Cl)cc2c(N3CCN(C(=O)C=C)CC3)ncnc12 |$*;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2152" t="inlineStr"/>
+      <c r="H2152" t="inlineStr"/>
+      <c r="I2152" t="n">
+        <v>0.8781890559428938</v>
+      </c>
+      <c r="J2152" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2152" t="inlineStr"/>
+    </row>
+    <row r="2153">
+      <c r="A2153" s="1" t="n">
+        <v>2151</v>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0697.png</t>
+        </is>
+      </c>
+      <c r="C2153" t="inlineStr"/>
+      <c r="D2153" t="inlineStr"/>
+      <c r="E2153" t="inlineStr"/>
+      <c r="F2153" t="inlineStr">
+        <is>
+          <t>O=C(COc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O)NCCCCCCN1CCC[C@@H](Nc2ncc(Cl)c(-c3c[nH]c4ccccc34)n2)C1</t>
+        </is>
+      </c>
+      <c r="G2153" t="inlineStr"/>
+      <c r="H2153" t="inlineStr"/>
+      <c r="I2153" t="n">
+        <v>0.8980319033641661</v>
+      </c>
+      <c r="J2153" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2153" t="inlineStr"/>
+    </row>
+    <row r="2154">
+      <c r="A2154" s="1" t="n">
+        <v>2152</v>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0709.png</t>
+        </is>
+      </c>
+      <c r="C2154" t="inlineStr"/>
+      <c r="D2154" t="inlineStr"/>
+      <c r="E2154" t="inlineStr"/>
+      <c r="F2154" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(C4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)CC3)CC2)c(C)cc1Nc1ncc(Br)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2154" t="inlineStr"/>
+      <c r="H2154" t="inlineStr"/>
+      <c r="I2154" t="n">
+        <v>0.8727068459575037</v>
+      </c>
+      <c r="J2154" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2154" t="inlineStr"/>
+    </row>
+    <row r="2155">
+      <c r="A2155" s="1" t="n">
+        <v>2153</v>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0713.png</t>
+        </is>
+      </c>
+      <c r="C2155" t="inlineStr"/>
+      <c r="D2155" t="inlineStr"/>
+      <c r="E2155" t="inlineStr"/>
+      <c r="F2155" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)N1CCc2cccc(Nc3nc(Nc4ccc(N5CCC(N6CCN(CCCC7CN(c8ccc9c(c8)C(=O)N(C8CCC(=O)NC8=O)C9=O)C7)CC6)CC5)c(F)c4)ncc3Cl)c21</t>
+        </is>
+      </c>
+      <c r="G2155" t="inlineStr"/>
+      <c r="H2155" t="inlineStr"/>
+      <c r="I2155" t="n">
+        <v>0.8609183891848223</v>
+      </c>
+      <c r="J2155" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2155" t="inlineStr"/>
+    </row>
+    <row r="2156">
+      <c r="A2156" s="1" t="n">
+        <v>2154</v>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0717.png</t>
+        </is>
+      </c>
+      <c r="C2156" t="inlineStr"/>
+      <c r="D2156" t="inlineStr"/>
+      <c r="E2156" t="inlineStr"/>
+      <c r="F2156" t="inlineStr">
+        <is>
+          <t>CC(C)[C@@H](CS(=O)(=O)C(C)C)N1C(=O)[C@@](C)(CC(=O)NCCOCCOCCNc2cccc3c2C(=O)N(C2CCC(=O)NC2=O)C3=O)C[C@H](c2cccc(Cl)c2)[C@H]1c1ccc(Cl)cc1</t>
+        </is>
+      </c>
+      <c r="G2156" t="inlineStr"/>
+      <c r="H2156" t="inlineStr"/>
+      <c r="I2156" t="n">
+        <v>0.8773367166569302</v>
+      </c>
+      <c r="J2156" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2156" t="inlineStr"/>
+    </row>
+    <row r="2157">
+      <c r="A2157" s="1" t="n">
+        <v>2155</v>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0725.png</t>
+        </is>
+      </c>
+      <c r="C2157" t="inlineStr"/>
+      <c r="D2157" t="inlineStr"/>
+      <c r="E2157" t="inlineStr"/>
+      <c r="F2157" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)N(C)CCCCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)c2)cc1CC[C@@H]1CC[C@@H](C(F)(F)F)CC1</t>
+        </is>
+      </c>
+      <c r="G2157" t="inlineStr"/>
+      <c r="H2157" t="inlineStr"/>
+      <c r="I2157" t="n">
+        <v>0.9034442877463904</v>
+      </c>
+      <c r="J2157" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2157" t="inlineStr"/>
+    </row>
+    <row r="2158">
+      <c r="A2158" s="1" t="n">
+        <v>2156</v>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0729.png</t>
+        </is>
+      </c>
+      <c r="C2158" t="inlineStr"/>
+      <c r="D2158" t="inlineStr"/>
+      <c r="E2158" t="inlineStr"/>
+      <c r="F2158" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(C(=O)C6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6(F)F)CC5)C4)nc3cc2OC)n1.[I-35] |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2158" t="inlineStr"/>
+      <c r="H2158" t="inlineStr"/>
+      <c r="I2158" t="n">
+        <v>0.8518958216137348</v>
+      </c>
+      <c r="J2158" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2158" t="inlineStr"/>
+    </row>
+    <row r="2159">
+      <c r="A2159" s="1" t="n">
+        <v>2157</v>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0737.png</t>
+        </is>
+      </c>
+      <c r="C2159" t="inlineStr"/>
+      <c r="D2159" t="inlineStr"/>
+      <c r="E2159" t="inlineStr"/>
+      <c r="F2159" t="inlineStr">
+        <is>
+          <t>Cc1nn(C)cc1C1=C(c2ccc(N3CCC(CN4CCN(c5ccc6c(c5)CN([C@H]5CCC(=O)NC5=O)C6=O)CC4)CC3)cc2)c2ccc(O)cc2CCC1</t>
+        </is>
+      </c>
+      <c r="G2159" t="inlineStr"/>
+      <c r="H2159" t="inlineStr"/>
+      <c r="I2159" t="n">
+        <v>0.8631264301344028</v>
+      </c>
+      <c r="J2159" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2159" t="inlineStr"/>
+    </row>
+    <row r="2160">
+      <c r="A2160" s="1" t="n">
+        <v>2158</v>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0745.png</t>
+        </is>
+      </c>
+      <c r="C2160" t="inlineStr"/>
+      <c r="D2160" t="inlineStr"/>
+      <c r="E2160" t="inlineStr"/>
+      <c r="F2160" t="inlineStr">
+        <is>
+          <t>COc1cc(Nc2nc(Nc3cccc4c3N(S(C)(=O)=O)CC4)c3cc[nH]c3n2)ccc1N1CCC(N2CCN(C(=O)C3CN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)C3)CC2)CC1</t>
+        </is>
+      </c>
+      <c r="G2160" t="inlineStr"/>
+      <c r="H2160" t="inlineStr"/>
+      <c r="I2160" t="n">
+        <v>0.8719890660955151</v>
+      </c>
+      <c r="J2160" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2160" t="inlineStr"/>
+    </row>
+    <row r="2161">
+      <c r="A2161" s="1" t="n">
+        <v>2159</v>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0753.png</t>
+        </is>
+      </c>
+      <c r="C2161" t="inlineStr"/>
+      <c r="D2161" t="inlineStr"/>
+      <c r="E2161" t="inlineStr"/>
+      <c r="F2161" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)N[C@@H](COCc2ccc(C(=O)N3CC(COc4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)C3)cc2)C(=O)Nc2nc(-c3ccccc3)cs2)c1</t>
+        </is>
+      </c>
+      <c r="G2161" t="inlineStr"/>
+      <c r="H2161" t="inlineStr"/>
+      <c r="I2161" t="n">
+        <v>0.9019008578077402</v>
+      </c>
+      <c r="J2161" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2161" t="inlineStr"/>
+    </row>
+    <row r="2162">
+      <c r="A2162" s="1" t="n">
+        <v>2160</v>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0761.png</t>
+        </is>
+      </c>
+      <c r="C2162" t="inlineStr"/>
+      <c r="D2162" t="inlineStr"/>
+      <c r="E2162" t="inlineStr"/>
+      <c r="F2162" t="inlineStr">
+        <is>
+          <t>*c1c(-c2c(F)cccc2OCCCCCN2CCC(c3cc(F)cc4c3CN(C3CCC(=O)NC3=O)C4=O)CC2)c(Cl)cc2c(N3CCN(C(=O)CC)CC3)ncnc12 |$*;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2162" t="inlineStr"/>
+      <c r="H2162" t="inlineStr"/>
+      <c r="I2162" t="n">
+        <v>0.9102852148863535</v>
+      </c>
+      <c r="J2162" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2162" t="inlineStr"/>
+    </row>
+    <row r="2163">
+      <c r="A2163" s="1" t="n">
+        <v>2161</v>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0773.png</t>
+        </is>
+      </c>
+      <c r="C2163" t="inlineStr"/>
+      <c r="D2163" t="inlineStr"/>
+      <c r="E2163" t="inlineStr"/>
+      <c r="F2163" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)N1CCc2cccc(Nc3nc(Nc4ccc(N5CCC(N6CCN(CC7CCN(c8ccc9c(c8)C(=O)N(C8CCC(=O)NC8=O)C9=O)CC7)CC6)CC5)c(F)c4)nc4[nH]ccc34)c21</t>
+        </is>
+      </c>
+      <c r="G2163" t="inlineStr"/>
+      <c r="H2163" t="inlineStr"/>
+      <c r="I2163" t="n">
+        <v>0.8789428049378561</v>
+      </c>
+      <c r="J2163" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2163" t="inlineStr"/>
+    </row>
+    <row r="2164">
+      <c r="A2164" s="1" t="n">
+        <v>2162</v>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0777.png</t>
+        </is>
+      </c>
+      <c r="C2164" t="inlineStr"/>
+      <c r="D2164" t="inlineStr"/>
+      <c r="E2164" t="inlineStr"/>
+      <c r="F2164" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCCCCCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)c2)cc1/C=C/C1CCCCC1</t>
+        </is>
+      </c>
+      <c r="G2164" t="inlineStr"/>
+      <c r="H2164" t="inlineStr"/>
+      <c r="I2164" t="n">
+        <v>0.9117992550866372</v>
+      </c>
+      <c r="J2164" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2164" t="inlineStr"/>
+    </row>
+    <row r="2165">
+      <c r="A2165" s="1" t="n">
+        <v>2163</v>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0785.png</t>
+        </is>
+      </c>
+      <c r="C2165" t="inlineStr"/>
+      <c r="D2165" t="inlineStr"/>
+      <c r="E2165" t="inlineStr"/>
+      <c r="F2165" t="inlineStr">
+        <is>
+          <t>CC1(C)N[C@@H](C(=O)N[C@@H]2CC[C@@H](C(=O)NCCOCCOCCOCCNc3cccc4c3CN(C3CCC(=O)NC3=O)C4=O)CC2)[C@H](c2ccccc2)[C@]12C(=O)Nc1cc(Cl)ccc12</t>
+        </is>
+      </c>
+      <c r="G2165" t="inlineStr"/>
+      <c r="H2165" t="inlineStr"/>
+      <c r="I2165" t="n">
+        <v>0.851800551829815</v>
+      </c>
+      <c r="J2165" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2165" t="inlineStr"/>
+    </row>
+    <row r="2166">
+      <c r="A2166" s="1" t="n">
+        <v>2164</v>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0789.png</t>
+        </is>
+      </c>
+      <c r="C2166" t="inlineStr"/>
+      <c r="D2166" t="inlineStr"/>
+      <c r="E2166" t="inlineStr"/>
+      <c r="F2166" t="inlineStr">
+        <is>
+          <t>CC(C)S(=O)(=O)c1ccccc1Nc1nc(N[C@@H]2CCCN(CCCCCCCNC(=O)COc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)C2)ncc1Cl</t>
+        </is>
+      </c>
+      <c r="G2166" t="inlineStr"/>
+      <c r="H2166" t="inlineStr"/>
+      <c r="I2166" t="n">
+        <v>0.9059069524785119</v>
+      </c>
+      <c r="J2166" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2166" t="inlineStr"/>
+    </row>
+    <row r="2167">
+      <c r="A2167" s="1" t="n">
+        <v>2165</v>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0793.png</t>
+        </is>
+      </c>
+      <c r="C2167" t="inlineStr"/>
+      <c r="D2167" t="inlineStr"/>
+      <c r="E2167" t="inlineStr"/>
+      <c r="F2167" t="inlineStr">
+        <is>
+          <t>O=C(COc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O)NCCCCCCCN1CCC[C@@H](Nc2ncc(Cl)c(-c3c[nH]c4ccccc34)n2)C1</t>
+        </is>
+      </c>
+      <c r="G2167" t="inlineStr"/>
+      <c r="H2167" t="inlineStr"/>
+      <c r="I2167" t="n">
+        <v>0.8860942463147978</v>
+      </c>
+      <c r="J2167" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2167" t="inlineStr"/>
+    </row>
+    <row r="2168">
+      <c r="A2168" s="1" t="n">
+        <v>2166</v>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0797.png</t>
+        </is>
+      </c>
+      <c r="C2168" t="inlineStr"/>
+      <c r="D2168" t="inlineStr"/>
+      <c r="E2168" t="inlineStr"/>
+      <c r="F2168" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)N[C@@H](CCCCNC(=O)C2CCN(CCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)CC2)C(=O)Nc2nc(-c3ccccc3)cs2)c1</t>
+        </is>
+      </c>
+      <c r="G2168" t="inlineStr"/>
+      <c r="H2168" t="inlineStr"/>
+      <c r="I2168" t="n">
+        <v>0.8979336674788291</v>
+      </c>
+      <c r="J2168" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2168" t="inlineStr"/>
+    </row>
+    <row r="2169">
+      <c r="A2169" s="1" t="n">
+        <v>2167</v>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0805.png</t>
+        </is>
+      </c>
+      <c r="C2169" t="inlineStr"/>
+      <c r="D2169" t="inlineStr"/>
+      <c r="E2169" t="inlineStr"/>
+      <c r="F2169" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCCCCCCCNc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G2169" t="inlineStr"/>
+      <c r="H2169" t="inlineStr"/>
+      <c r="I2169" t="n">
+        <v>0.8714756947854163</v>
+      </c>
+      <c r="J2169" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2169" t="inlineStr"/>
+    </row>
+    <row r="2170">
+      <c r="A2170" s="1" t="n">
+        <v>2168</v>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0809.png</t>
+        </is>
+      </c>
+      <c r="C2170" t="inlineStr"/>
+      <c r="D2170" t="inlineStr"/>
+      <c r="E2170" t="inlineStr"/>
+      <c r="F2170" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3cc(CCCCCNC(=O)c4ccc(NC(=O)[C@@H]5NC6(CCCCC6)[C@@]6(C(=O)Nc7cc(Cl)ccc76)[C@H]5c5cccc(Cl)c5F)cc4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2170" t="inlineStr"/>
+      <c r="H2170" t="inlineStr"/>
+      <c r="I2170" t="n">
+        <v>0.8895160041031596</v>
+      </c>
+      <c r="J2170" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2170" t="inlineStr"/>
+    </row>
+    <row r="2171">
+      <c r="A2171" s="1" t="n">
+        <v>2169</v>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0813.png</t>
+        </is>
+      </c>
+      <c r="C2171" t="inlineStr"/>
+      <c r="D2171" t="inlineStr"/>
+      <c r="E2171" t="inlineStr"/>
+      <c r="F2171" t="inlineStr">
+        <is>
+          <t>O=C(COc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O)NCCCCNC(=O)c1ccc(NC(=O)[C@@H]2NC3(CCCCC3)[C@@]3(C(=O)Nc4cc(Cl)ccc43)[C@H]2c2cccc(Cl)c2F)cc1</t>
+        </is>
+      </c>
+      <c r="G2171" t="inlineStr"/>
+      <c r="H2171" t="inlineStr"/>
+      <c r="I2171" t="n">
+        <v>0.8889638986568493</v>
+      </c>
+      <c r="J2171" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2171" t="inlineStr"/>
+    </row>
+    <row r="2172">
+      <c r="A2172" s="1" t="n">
+        <v>2170</v>
+      </c>
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0841.png</t>
+        </is>
+      </c>
+      <c r="C2172" t="inlineStr"/>
+      <c r="D2172" t="inlineStr"/>
+      <c r="E2172" t="inlineStr"/>
+      <c r="F2172" t="inlineStr">
+        <is>
+          <t>CCC(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCc4cn(CCN5CCC(c6cc(F)cc7c6CN(C6CCC(=O)NC6=O)C7=O)CC5)nn4)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G2172" t="inlineStr"/>
+      <c r="H2172" t="inlineStr"/>
+      <c r="I2172" t="n">
+        <v>0.8752021441380931</v>
+      </c>
+      <c r="J2172" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2172" t="inlineStr"/>
+    </row>
+    <row r="2173">
+      <c r="A2173" s="1" t="n">
+        <v>2171</v>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0845.png</t>
+        </is>
+      </c>
+      <c r="C2173" t="inlineStr"/>
+      <c r="D2173" t="inlineStr"/>
+      <c r="E2173" t="inlineStr"/>
+      <c r="F2173" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)NCC(=O)Nc2nc(-c3cccc(-c4cccc(CNC(=O)CCOCCOCCNc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)c4)c3)cs2)c1</t>
+        </is>
+      </c>
+      <c r="G2173" t="inlineStr"/>
+      <c r="H2173" t="inlineStr"/>
+      <c r="I2173" t="n">
+        <v>0.8958547932736132</v>
+      </c>
+      <c r="J2173" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2173" t="inlineStr"/>
+    </row>
+    <row r="2174">
+      <c r="A2174" s="1" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0849.png</t>
+        </is>
+      </c>
+      <c r="C2174" t="inlineStr"/>
+      <c r="D2174" t="inlineStr"/>
+      <c r="E2174" t="inlineStr"/>
+      <c r="F2174" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(C(=O)C4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)CC3)CC2)ccc1Nc1ncc(Cl)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2174" t="inlineStr"/>
+      <c r="H2174" t="inlineStr"/>
+      <c r="I2174" t="n">
+        <v>0.9130804319375601</v>
+      </c>
+      <c r="J2174" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2174" t="inlineStr"/>
+    </row>
+    <row r="2175">
+      <c r="A2175" s="1" t="n">
+        <v>2173</v>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0606.png</t>
+        </is>
+      </c>
+      <c r="C2175" t="inlineStr"/>
+      <c r="D2175" t="inlineStr"/>
+      <c r="E2175" t="inlineStr"/>
+      <c r="F2175" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(C(=O)C6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2F)n1.[I-35] |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2175" t="inlineStr"/>
+      <c r="H2175" t="inlineStr"/>
+      <c r="I2175" t="n">
+        <v>0.8644637594663227</v>
+      </c>
+      <c r="J2175" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2175" t="inlineStr"/>
+    </row>
+    <row r="2176">
+      <c r="A2176" s="1" t="n">
+        <v>2174</v>
+      </c>
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0618.png</t>
+        </is>
+      </c>
+      <c r="C2176" t="inlineStr"/>
+      <c r="D2176" t="inlineStr"/>
+      <c r="E2176" t="inlineStr"/>
+      <c r="F2176" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3c(NC(=O)CCOCCOCCNC(=O)c4ccc(NC(=O)[C@@H]5NC6(CCCCC6)[C@@]6(C(=O)Nc7cc(Cl)ccc76)[C@H]5c5cccc(Cl)c5F)cc4)cccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2176" t="inlineStr"/>
+      <c r="H2176" t="inlineStr"/>
+      <c r="I2176" t="n">
+        <v>0.8775696299245328</v>
+      </c>
+      <c r="J2176" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2176" t="inlineStr"/>
+    </row>
+    <row r="2177">
+      <c r="A2177" s="1" t="n">
+        <v>2175</v>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0626.png</t>
+        </is>
+      </c>
+      <c r="C2177" t="inlineStr"/>
+      <c r="D2177" t="inlineStr"/>
+      <c r="E2177" t="inlineStr"/>
+      <c r="F2177" t="inlineStr">
+        <is>
+          <t>[H]C(F)(F)[C@@H]1CC[C@@H](CCc2cc(C(=O)NCc3cccc(CC(=O)N(C)CCOCCOCCOCCOCCOc4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)c3)ncc2OC)CC1</t>
+        </is>
+      </c>
+      <c r="G2177" t="inlineStr"/>
+      <c r="H2177" t="inlineStr"/>
+      <c r="I2177" t="n">
+        <v>0.8879118246470079</v>
+      </c>
+      <c r="J2177" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2177" t="inlineStr"/>
+    </row>
+    <row r="2178">
+      <c r="A2178" s="1" t="n">
+        <v>2176</v>
+      </c>
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0630.png</t>
+        </is>
+      </c>
+      <c r="C2178" t="inlineStr"/>
+      <c r="D2178" t="inlineStr"/>
+      <c r="E2178" t="inlineStr"/>
+      <c r="F2178" t="inlineStr">
+        <is>
+          <t>COc1cc2nn(C3CC4(CCN(C(=O)C5CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)CC4)C3)cc2cc1NC(=O)c1coc(N2CCOCC2)n1</t>
+        </is>
+      </c>
+      <c r="G2178" t="inlineStr"/>
+      <c r="H2178" t="inlineStr"/>
+      <c r="I2178" t="n">
+        <v>0.8783881356705829</v>
+      </c>
+      <c r="J2178" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2178" t="inlineStr"/>
+    </row>
+    <row r="2179">
+      <c r="A2179" s="1" t="n">
+        <v>2177</v>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0634.png</t>
+        </is>
+      </c>
+      <c r="C2179" t="inlineStr"/>
+      <c r="D2179" t="inlineStr"/>
+      <c r="E2179" t="inlineStr"/>
+      <c r="F2179" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)N1CCc2cccc(Nc3nc(Nc4ccc(N5CCC(N6CCN(CC7CN(c8ccc9c(c8)CN(C8CCC(=O)NC8=O)C9=O)C7)CC6)CC5)c(F)c4)nc4[nH]ccc34)c21</t>
+        </is>
+      </c>
+      <c r="G2179" t="inlineStr"/>
+      <c r="H2179" t="inlineStr"/>
+      <c r="I2179" t="n">
+        <v>0.8615894446831001</v>
+      </c>
+      <c r="J2179" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2179" t="inlineStr"/>
+    </row>
+    <row r="2180">
+      <c r="A2180" s="1" t="n">
+        <v>2178</v>
+      </c>
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0642.png</t>
+        </is>
+      </c>
+      <c r="C2180" t="inlineStr"/>
+      <c r="D2180" t="inlineStr"/>
+      <c r="E2180" t="inlineStr"/>
+      <c r="F2180" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(C(=O)C6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2N2CC[C@@H](O)C2)n1.[I-10] |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2180" t="inlineStr"/>
+      <c r="H2180" t="inlineStr"/>
+      <c r="I2180" t="n">
+        <v>0.8860568642205224</v>
+      </c>
+      <c r="J2180" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2180" t="inlineStr"/>
+    </row>
+    <row r="2181">
+      <c r="A2181" s="1" t="n">
+        <v>2179</v>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0646.png</t>
+        </is>
+      </c>
+      <c r="C2181" t="inlineStr"/>
+      <c r="D2181" t="inlineStr"/>
+      <c r="E2181" t="inlineStr"/>
+      <c r="F2181" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CCN(C(=O)C5CCN(Cc6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)CC4)nc3cc2OC)n1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2181" t="inlineStr"/>
+      <c r="H2181" t="inlineStr"/>
+      <c r="I2181" t="n">
+        <v>0.8663828389947039</v>
+      </c>
+      <c r="J2181" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2181" t="inlineStr"/>
+    </row>
+    <row r="2182">
+      <c r="A2182" s="1" t="n">
+        <v>2180</v>
+      </c>
+      <c r="B2182" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0650.png</t>
+        </is>
+      </c>
+      <c r="C2182" t="inlineStr"/>
+      <c r="D2182" t="inlineStr"/>
+      <c r="E2182" t="inlineStr"/>
+      <c r="F2182" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3c(NCCOCCOCCNC(=O)c4ccc(NC(=O)[C@@H]5NC6(CCCCC6)[C@@]6(C(=O)Nc7cc(Cl)ccc76)[C@H]5c5cccc(Cl)c5F)cc4)cccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2182" t="inlineStr"/>
+      <c r="H2182" t="inlineStr"/>
+      <c r="I2182" t="n">
+        <v>0.872452252804597</v>
+      </c>
+      <c r="J2182" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2182" t="inlineStr"/>
+    </row>
+    <row r="2183">
+      <c r="A2183" s="1" t="n">
+        <v>2181</v>
+      </c>
+      <c r="B2183" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0654.png</t>
+        </is>
+      </c>
+      <c r="C2183" t="inlineStr"/>
+      <c r="D2183" t="inlineStr"/>
+      <c r="E2183" t="inlineStr"/>
+      <c r="F2183" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)N(C)CCOCCOCCOCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)c2)cc1/C=C/CCC1CC1</t>
+        </is>
+      </c>
+      <c r="G2183" t="inlineStr"/>
+      <c r="H2183" t="inlineStr"/>
+      <c r="I2183" t="n">
+        <v>0.8984976339985212</v>
+      </c>
+      <c r="J2183" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2183" t="inlineStr"/>
+    </row>
+    <row r="2184">
+      <c r="A2184" s="1" t="n">
+        <v>2182</v>
+      </c>
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0658.png</t>
+        </is>
+      </c>
+      <c r="C2184" t="inlineStr"/>
+      <c r="D2184" t="inlineStr"/>
+      <c r="E2184" t="inlineStr"/>
+      <c r="F2184" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCOCCOCCNC[C@@H](C(=O)N2CCN(c3ncnc4c3[C@H](C)C[C@H]4O)CC2)c2ccc(Cl)cc2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2184" t="inlineStr"/>
+      <c r="H2184" t="inlineStr"/>
+      <c r="I2184" t="n">
+        <v>0.8711184507314836</v>
+      </c>
+      <c r="J2184" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2184" t="inlineStr"/>
+    </row>
+    <row r="2185">
+      <c r="A2185" s="1" t="n">
+        <v>2183</v>
+      </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0662.png</t>
+        </is>
+      </c>
+      <c r="C2185" t="inlineStr"/>
+      <c r="D2185" t="inlineStr"/>
+      <c r="E2185" t="inlineStr"/>
+      <c r="F2185" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3c(CCc4cncn4CCCNC(=O)c4ccc(NC(=O)[C@@H]5NC6(CCCCC6)[C@@]6(C(=O)Nc7cc(Cl)ccc76)[C@H]5c5cccc(Cl)c5F)cc4)cccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2185" t="inlineStr"/>
+      <c r="H2185" t="inlineStr"/>
+      <c r="I2185" t="n">
+        <v>0.8743550837149585</v>
+      </c>
+      <c r="J2185" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2185" t="inlineStr"/>
+    </row>
+    <row r="2186">
+      <c r="A2186" s="1" t="n">
+        <v>2184</v>
+      </c>
+      <c r="B2186" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0666.png</t>
+        </is>
+      </c>
+      <c r="C2186" t="inlineStr"/>
+      <c r="D2186" t="inlineStr"/>
+      <c r="E2186" t="inlineStr"/>
+      <c r="F2186" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(C(=O)C4CCN(c5ccc6c(c5)CN(C5CCC(=O)NC5=O)C6=O)CC4)CC3)CC2)c(C)cc1Nc1ncc(Cl)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2186" t="inlineStr"/>
+      <c r="H2186" t="inlineStr"/>
+      <c r="I2186" t="n">
+        <v>0.9152467537508521</v>
+      </c>
+      <c r="J2186" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2186" t="inlineStr"/>
+    </row>
+    <row r="2187">
+      <c r="A2187" s="1" t="n">
+        <v>2185</v>
+      </c>
+      <c r="B2187" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0670.png</t>
+        </is>
+      </c>
+      <c r="C2187" t="inlineStr"/>
+      <c r="D2187" t="inlineStr"/>
+      <c r="E2187" t="inlineStr"/>
+      <c r="F2187" t="inlineStr">
+        <is>
+          <t>CC1(C)N[C@@H](C(=O)Nc2ccc(C(=O)NCCOCCOCCOCCNc3cccc4c3CN(C3CCC(=O)NC3=O)C4=O)cc2)[C@H](c2ccccc2)[C@]12C(=O)Nc1ccccc12</t>
+        </is>
+      </c>
+      <c r="G2187" t="inlineStr"/>
+      <c r="H2187" t="inlineStr"/>
+      <c r="I2187" t="n">
+        <v>0.8813313500957551</v>
+      </c>
+      <c r="J2187" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2187" t="inlineStr"/>
+    </row>
+    <row r="2188">
+      <c r="A2188" s="1" t="n">
+        <v>2186</v>
+      </c>
+      <c r="B2188" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0674.png</t>
+        </is>
+      </c>
+      <c r="C2188" t="inlineStr"/>
+      <c r="D2188" t="inlineStr"/>
+      <c r="E2188" t="inlineStr"/>
+      <c r="F2188" t="inlineStr">
+        <is>
+          <t>O=C1CC[C@H](N2Cc3cc(N4CCN(CCC5CCN(c6ccc(C7=C(c8ccccc8)CCCc8cc(C(=O)O)ccc87)cc6)CC5)CC4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2188" t="inlineStr"/>
+      <c r="H2188" t="inlineStr"/>
+      <c r="I2188" t="n">
+        <v>0.8653656790191515</v>
+      </c>
+      <c r="J2188" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2188" t="inlineStr"/>
+    </row>
+    <row r="2189">
+      <c r="A2189" s="1" t="n">
+        <v>2187</v>
+      </c>
+      <c r="B2189" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0678.png</t>
+        </is>
+      </c>
+      <c r="C2189" t="inlineStr"/>
+      <c r="D2189" t="inlineStr"/>
+      <c r="E2189" t="inlineStr"/>
+      <c r="F2189" t="inlineStr">
+        <is>
+          <t>CCC(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCCCCCCN4CCCC(c5cc(F)cc6c5CN(C5CCC(=O)NC5=O)C6=O)C4)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G2189" t="inlineStr"/>
+      <c r="H2189" t="inlineStr"/>
+      <c r="I2189" t="n">
+        <v>0.8890428769196772</v>
+      </c>
+      <c r="J2189" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2189" t="inlineStr"/>
+    </row>
+    <row r="2190">
+      <c r="A2190" s="1" t="n">
+        <v>2188</v>
+      </c>
+      <c r="B2190" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0682.png</t>
+        </is>
+      </c>
+      <c r="C2190" t="inlineStr"/>
+      <c r="D2190" t="inlineStr"/>
+      <c r="E2190" t="inlineStr"/>
+      <c r="F2190" t="inlineStr">
+        <is>
+          <t>COc1cc(Nc2nc(Nc3cccc4c3N(S(C)(=O)=O)CC4)c3cc[nH]c3n2)ccc1N1CCC(N2CCN(C(=O)[C@H]3CCN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)C3)CC2)CC1</t>
+        </is>
+      </c>
+      <c r="G2190" t="inlineStr"/>
+      <c r="H2190" t="inlineStr"/>
+      <c r="I2190" t="n">
+        <v>0.8535982195904276</v>
+      </c>
+      <c r="J2190" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2190" t="inlineStr"/>
+    </row>
+    <row r="2191">
+      <c r="A2191" s="1" t="n">
+        <v>2189</v>
+      </c>
+      <c r="B2191" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0686.png</t>
+        </is>
+      </c>
+      <c r="C2191" t="inlineStr"/>
+      <c r="D2191" t="inlineStr"/>
+      <c r="E2191" t="inlineStr"/>
+      <c r="F2191" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)NCC(=O)Nc2nc(-c3cccc(-c4ccnc(C5(C(=O)NCCNc6ccc7c(c6)CN(C6CCC(=O)NC6=O)C7=O)CC5)c4)c3)cs2)c1</t>
+        </is>
+      </c>
+      <c r="G2191" t="inlineStr"/>
+      <c r="H2191" t="inlineStr"/>
+      <c r="I2191" t="n">
+        <v>0.8932421499506348</v>
+      </c>
+      <c r="J2191" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2191" t="inlineStr"/>
+    </row>
+    <row r="2192">
+      <c r="A2192" s="1" t="n">
+        <v>2190</v>
+      </c>
+      <c r="B2192" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0690.png</t>
+        </is>
+      </c>
+      <c r="C2192" t="inlineStr"/>
+      <c r="D2192" t="inlineStr"/>
+      <c r="E2192" t="inlineStr"/>
+      <c r="F2192" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCCCCCCCCCN2CCC[C@@H](Nc3ncc(Cl)c(Nc4ccccc4S(=O)(=O)C(C)C)n3)C2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2192" t="inlineStr"/>
+      <c r="H2192" t="inlineStr"/>
+      <c r="I2192" t="n">
+        <v>0.8859283943259182</v>
+      </c>
+      <c r="J2192" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2192" t="inlineStr"/>
+    </row>
+    <row r="2193">
+      <c r="A2193" s="1" t="n">
+        <v>2191</v>
+      </c>
+      <c r="B2193" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0698.png</t>
+        </is>
+      </c>
+      <c r="C2193" t="inlineStr"/>
+      <c r="D2193" t="inlineStr"/>
+      <c r="E2193" t="inlineStr"/>
+      <c r="F2193" t="inlineStr">
+        <is>
+          <t>[H]C(F)(F)[C@@H]1CC[C@@H](C=Cc2cc(C(=O)NCc3cccc(CC(=O)NCCOCCOCCOCCOc4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)c3)ncc2OC)CC1</t>
+        </is>
+      </c>
+      <c r="G2193" t="inlineStr"/>
+      <c r="H2193" t="inlineStr"/>
+      <c r="I2193" t="n">
+        <v>0.8964250130111416</v>
+      </c>
+      <c r="J2193" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2193" t="inlineStr"/>
+    </row>
+    <row r="2194">
+      <c r="A2194" s="1" t="n">
+        <v>2192</v>
+      </c>
+      <c r="B2194" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0702.png</t>
+        </is>
+      </c>
+      <c r="C2194" t="inlineStr"/>
+      <c r="D2194" t="inlineStr"/>
+      <c r="E2194" t="inlineStr"/>
+      <c r="F2194" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(C(=O)C6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2C(C)(C)O)n1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2194" t="inlineStr"/>
+      <c r="H2194" t="inlineStr"/>
+      <c r="I2194" t="n">
+        <v>0.8853610558084996</v>
+      </c>
+      <c r="J2194" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2194" t="inlineStr"/>
+    </row>
+    <row r="2195">
+      <c r="A2195" s="1" t="n">
+        <v>2193</v>
+      </c>
+      <c r="B2195" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0710.png</t>
+        </is>
+      </c>
+      <c r="C2195" t="inlineStr"/>
+      <c r="D2195" t="inlineStr"/>
+      <c r="E2195" t="inlineStr"/>
+      <c r="F2195" t="inlineStr">
+        <is>
+          <t>CCC(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCCCCCCN4CCC(c5cc6c(cc5F)C(=O)N(C5CCC(=O)NC5=O)C6)CC4)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G2195" t="inlineStr"/>
+      <c r="H2195" t="inlineStr"/>
+      <c r="I2195" t="n">
+        <v>0.9059814255273025</v>
+      </c>
+      <c r="J2195" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2195" t="inlineStr"/>
+    </row>
+    <row r="2196">
+      <c r="A2196" s="1" t="n">
+        <v>2194</v>
+      </c>
+      <c r="B2196" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0714.png</t>
+        </is>
+      </c>
+      <c r="C2196" t="inlineStr"/>
+      <c r="D2196" t="inlineStr"/>
+      <c r="E2196" t="inlineStr"/>
+      <c r="F2196" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)N[C@@H](COCc2ccc(CNC(=O)CCN3CCN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)cc2)C(=O)Nc2nc(-c3ccccc3)cs2)c1</t>
+        </is>
+      </c>
+      <c r="G2196" t="inlineStr"/>
+      <c r="H2196" t="inlineStr"/>
+      <c r="I2196" t="n">
+        <v>0.8640804133229417</v>
+      </c>
+      <c r="J2196" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2196" t="inlineStr"/>
+    </row>
+    <row r="2197">
+      <c r="A2197" s="1" t="n">
+        <v>2195</v>
+      </c>
+      <c r="B2197" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0718.png</t>
+        </is>
+      </c>
+      <c r="C2197" t="inlineStr"/>
+      <c r="D2197" t="inlineStr"/>
+      <c r="E2197" t="inlineStr"/>
+      <c r="F2197" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3cccc(CCCOCCOCCNC(=O)c4ccc(NC(=O)[C@@H]5NC6(CCCCC6)[C@@]6(C(=O)Nc7cc(Cl)ccc76)[C@H]5c5cccc(Cl)c5F)cc4)c3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2197" t="inlineStr"/>
+      <c r="H2197" t="inlineStr"/>
+      <c r="I2197" t="n">
+        <v>0.8865130943516827</v>
+      </c>
+      <c r="J2197" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2197" t="inlineStr"/>
+    </row>
+    <row r="2198">
+      <c r="A2198" s="1" t="n">
+        <v>2196</v>
+      </c>
+      <c r="B2198" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0722.png</t>
+        </is>
+      </c>
+      <c r="C2198" t="inlineStr"/>
+      <c r="D2198" t="inlineStr"/>
+      <c r="E2198" t="inlineStr"/>
+      <c r="F2198" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)N(C)CCOCCOCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)c2)cc1C=C[C@@H]1CC[C@@H](C(F)(F)F)CC1</t>
+        </is>
+      </c>
+      <c r="G2198" t="inlineStr"/>
+      <c r="H2198" t="inlineStr"/>
+      <c r="I2198" t="n">
+        <v>0.9007503704739658</v>
+      </c>
+      <c r="J2198" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2198" t="inlineStr"/>
+    </row>
+    <row r="2199">
+      <c r="A2199" s="1" t="n">
+        <v>2197</v>
+      </c>
+      <c r="B2199" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0726.png</t>
+        </is>
+      </c>
+      <c r="C2199" t="inlineStr"/>
+      <c r="D2199" t="inlineStr"/>
+      <c r="E2199" t="inlineStr"/>
+      <c r="F2199" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3c(NCCCCNC(=O)c4ccc(NC(=O)[C@@H]5NC6(CCCCC6)[C@@]6(C(=O)Nc7cc(Cl)ccc76)[C@H]5c5cccc(Cl)c5F)cc4)cccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2199" t="inlineStr"/>
+      <c r="H2199" t="inlineStr"/>
+      <c r="I2199" t="n">
+        <v>0.8633235779996631</v>
+      </c>
+      <c r="J2199" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2199" t="inlineStr"/>
+    </row>
+    <row r="2200">
+      <c r="A2200" s="1" t="n">
+        <v>2198</v>
+      </c>
+      <c r="B2200" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0730.png</t>
+        </is>
+      </c>
+      <c r="C2200" t="inlineStr"/>
+      <c r="D2200" t="inlineStr"/>
+      <c r="E2200" t="inlineStr"/>
+      <c r="F2200" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3c(cc(F)cc3C3CCN(CCCCCCCOc4cccc(F)c4-c4c(Cl)cc5c(N6CCN(C(=O)c7cnc[nH]7)CC6)ncnc5c4F)CC3)C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2200" t="inlineStr"/>
+      <c r="H2200" t="inlineStr"/>
+      <c r="I2200" t="n">
+        <v>0.8698052483217701</v>
+      </c>
+      <c r="J2200" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2200" t="inlineStr"/>
+    </row>
+    <row r="2201">
+      <c r="A2201" s="1" t="n">
+        <v>2199</v>
+      </c>
+      <c r="B2201" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0738.png</t>
+        </is>
+      </c>
+      <c r="C2201" t="inlineStr"/>
+      <c r="D2201" t="inlineStr"/>
+      <c r="E2201" t="inlineStr"/>
+      <c r="F2201" t="inlineStr">
+        <is>
+          <t>C=C(Cl)C(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCCN4CCC(c5cc(F)cc6c5CN(C5CCC(=O)NC5=O)C6=O)CC4)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G2201" t="inlineStr"/>
+      <c r="H2201" t="inlineStr"/>
+      <c r="I2201" t="n">
+        <v>0.9106454010713649</v>
+      </c>
+      <c r="J2201" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2201" t="inlineStr"/>
+    </row>
+    <row r="2202">
+      <c r="A2202" s="1" t="n">
+        <v>2200</v>
+      </c>
+      <c r="B2202" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0742.png</t>
+        </is>
+      </c>
+      <c r="C2202" t="inlineStr"/>
+      <c r="D2202" t="inlineStr"/>
+      <c r="E2202" t="inlineStr"/>
+      <c r="F2202" t="inlineStr">
+        <is>
+          <t>C=C(Cl)C(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OC[C@@H]4CC[C@@H](CN5CCC(c6cc(F)cc7c6CN(C6CCC(=O)NC6=O)C7=O)CC5)CC4)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G2202" t="inlineStr"/>
+      <c r="H2202" t="inlineStr"/>
+      <c r="I2202" t="n">
+        <v>0.9044185868649373</v>
+      </c>
+      <c r="J2202" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2202" t="inlineStr"/>
+    </row>
+    <row r="2203">
+      <c r="A2203" s="1" t="n">
+        <v>2201</v>
+      </c>
+      <c r="B2203" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0746.png</t>
+        </is>
+      </c>
+      <c r="C2203" t="inlineStr"/>
+      <c r="D2203" t="inlineStr"/>
+      <c r="E2203" t="inlineStr"/>
+      <c r="F2203" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CCN(CC(=O)N5CCN(c6cccc7c6C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)CC4)nc3cc2OC)n1.I[I-22] |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2203" t="inlineStr"/>
+      <c r="H2203" t="inlineStr"/>
+      <c r="I2203" t="n">
+        <v>0.8947793338848076</v>
+      </c>
+      <c r="J2203" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2203" t="inlineStr"/>
+    </row>
+    <row r="2204">
+      <c r="A2204" s="1" t="n">
+        <v>2202</v>
+      </c>
+      <c r="B2204" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0750.png</t>
+        </is>
+      </c>
+      <c r="C2204" t="inlineStr"/>
+      <c r="D2204" t="inlineStr"/>
+      <c r="E2204" t="inlineStr"/>
+      <c r="F2204" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)N[C@@H](CCCCNC(=O)CCCCCCOc2cccc3c2C(=O)N(C2CCC(=O)NC2=O)C3=O)C(=O)Nc2nc(-c3ccccc3)cs2)c1</t>
+        </is>
+      </c>
+      <c r="G2204" t="inlineStr"/>
+      <c r="H2204" t="inlineStr"/>
+      <c r="I2204" t="n">
+        <v>0.9003473092132083</v>
+      </c>
+      <c r="J2204" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2204" t="inlineStr"/>
+    </row>
+    <row r="2205">
+      <c r="A2205" s="1" t="n">
+        <v>2203</v>
+      </c>
+      <c r="B2205" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0754.png</t>
+        </is>
+      </c>
+      <c r="C2205" t="inlineStr"/>
+      <c r="D2205" t="inlineStr"/>
+      <c r="E2205" t="inlineStr"/>
+      <c r="F2205" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(C(=O)[C@H]4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)CC3)CC2)ccc1Nc1ncc(Cl)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2205" t="inlineStr"/>
+      <c r="H2205" t="inlineStr"/>
+      <c r="I2205" t="n">
+        <v>0.9010725077197171</v>
+      </c>
+      <c r="J2205" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2205" t="inlineStr"/>
+    </row>
+    <row r="2206">
+      <c r="A2206" s="1" t="n">
+        <v>2204</v>
+      </c>
+      <c r="B2206" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0762.png</t>
+        </is>
+      </c>
+      <c r="C2206" t="inlineStr"/>
+      <c r="D2206" t="inlineStr"/>
+      <c r="E2206" t="inlineStr"/>
+      <c r="F2206" t="inlineStr">
+        <is>
+          <t>O=C1CC[C@H](N2Cc3cc(N4CCN(CC5CCN(c6ccc(C7=C(c8ccc(F)cc8)CCCc8cc(O)ccc87)cc6)CC5)CC4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2206" t="inlineStr"/>
+      <c r="H2206" t="inlineStr"/>
+      <c r="I2206" t="n">
+        <v>0.8878222046536792</v>
+      </c>
+      <c r="J2206" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2206" t="inlineStr"/>
+    </row>
+    <row r="2207">
+      <c r="A2207" s="1" t="n">
+        <v>2205</v>
+      </c>
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0766.png</t>
+        </is>
+      </c>
+      <c r="C2207" t="inlineStr"/>
+      <c r="D2207" t="inlineStr"/>
+      <c r="E2207" t="inlineStr"/>
+      <c r="F2207" t="inlineStr">
+        <is>
+          <t>COc1cc(Nc2nc(Nc3cccc4c3N(S(C)(=O)=O)CC4)c3cc[nH]c3n2)ccc1N1CCC(N2CCN(C(=O)[C@@H]3CCN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)C3)CC2)CC1</t>
+        </is>
+      </c>
+      <c r="G2207" t="inlineStr"/>
+      <c r="H2207" t="inlineStr"/>
+      <c r="I2207" t="n">
+        <v>0.894115863454783</v>
+      </c>
+      <c r="J2207" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2207" t="inlineStr"/>
+    </row>
+    <row r="2208">
+      <c r="A2208" s="1" t="n">
+        <v>2206</v>
+      </c>
+      <c r="B2208" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0770.png</t>
+        </is>
+      </c>
+      <c r="C2208" t="inlineStr"/>
+      <c r="D2208" t="inlineStr"/>
+      <c r="E2208" t="inlineStr"/>
+      <c r="F2208" t="inlineStr">
+        <is>
+          <t>Cc1c(C(=O)NCC(=O)Nc2nc(-c3cccc(-c4ccnc(N(C)CC(=O)NCCCCCNc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)c4)c3)cs2)cn(S(=O)(=O)C(C)C)c1C</t>
+        </is>
+      </c>
+      <c r="G2208" t="inlineStr"/>
+      <c r="H2208" t="inlineStr"/>
+      <c r="I2208" t="n">
+        <v>0.8912384392953568</v>
+      </c>
+      <c r="J2208" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2208" t="inlineStr"/>
+    </row>
+    <row r="2209">
+      <c r="A2209" s="1" t="n">
+        <v>2207</v>
+      </c>
+      <c r="B2209" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0778.png</t>
+        </is>
+      </c>
+      <c r="C2209" t="inlineStr"/>
+      <c r="D2209" t="inlineStr"/>
+      <c r="E2209" t="inlineStr"/>
+      <c r="F2209" t="inlineStr">
+        <is>
+          <t>O=C1CC[C@H](N2Cc3cc(N4CCN(CC5CCN(c6ccc(C7=C(c8ccc(C(F)(F)F)nc8)CCCc8cc(O)ccc87)cc6)CC5)CC4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2209" t="inlineStr"/>
+      <c r="H2209" t="inlineStr"/>
+      <c r="I2209" t="n">
+        <v>0.8800995760492952</v>
+      </c>
+      <c r="J2209" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2209" t="inlineStr"/>
+    </row>
+    <row r="2210">
+      <c r="A2210" s="1" t="n">
+        <v>2208</v>
+      </c>
+      <c r="B2210" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0786.png</t>
+        </is>
+      </c>
+      <c r="C2210" t="inlineStr"/>
+      <c r="D2210" t="inlineStr"/>
+      <c r="E2210" t="inlineStr"/>
+      <c r="F2210" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CCC5(CC4)CCN(C(=O)C4CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC4)CC5)nc3cc2OC)n1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2210" t="inlineStr"/>
+      <c r="H2210" t="inlineStr"/>
+      <c r="I2210" t="n">
+        <v>0.8929327918194094</v>
+      </c>
+      <c r="J2210" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2210" t="inlineStr"/>
+    </row>
+    <row r="2211">
+      <c r="A2211" s="1" t="n">
+        <v>2209</v>
+      </c>
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0790.png</t>
+        </is>
+      </c>
+      <c r="C2211" t="inlineStr"/>
+      <c r="D2211" t="inlineStr"/>
+      <c r="E2211" t="inlineStr"/>
+      <c r="F2211" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCC(C(=O)N6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2OC)n1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2211" t="inlineStr"/>
+      <c r="H2211" t="inlineStr"/>
+      <c r="I2211" t="n">
+        <v>0.8885233464200786</v>
+      </c>
+      <c r="J2211" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2211" t="inlineStr"/>
+    </row>
+    <row r="2212">
+      <c r="A2212" s="1" t="n">
+        <v>2210</v>
+      </c>
+      <c r="B2212" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0794.png</t>
+        </is>
+      </c>
+      <c r="C2212" t="inlineStr"/>
+      <c r="D2212" t="inlineStr"/>
+      <c r="E2212" t="inlineStr"/>
+      <c r="F2212" t="inlineStr">
+        <is>
+          <t>Nc1ncnc2c1c(-c1ccc(Oc3ccccc3)cc1)nn2C1CCN(CCOCCOCC(=O)Nc2ccc3c(c2)C(=O)N(C2CCC(=O)NC2=O)C3=O)CC1</t>
+        </is>
+      </c>
+      <c r="G2212" t="inlineStr"/>
+      <c r="H2212" t="inlineStr"/>
+      <c r="I2212" t="n">
+        <v>0.8994536651372642</v>
+      </c>
+      <c r="J2212" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2212" t="inlineStr"/>
+    </row>
+    <row r="2213">
+      <c r="A2213" s="1" t="n">
+        <v>2211</v>
+      </c>
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0798.png</t>
+        </is>
+      </c>
+      <c r="C2213" t="inlineStr"/>
+      <c r="D2213" t="inlineStr"/>
+      <c r="E2213" t="inlineStr"/>
+      <c r="F2213" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)NCC(=O)Nc2nc(-c3cccc(-c4ccnc(OCCNC(=O)CCOCCOCCNc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)c4)c3)co2)c1</t>
+        </is>
+      </c>
+      <c r="G2213" t="inlineStr"/>
+      <c r="H2213" t="inlineStr"/>
+      <c r="I2213" t="n">
+        <v>0.8846542742841519</v>
+      </c>
+      <c r="J2213" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2213" t="inlineStr"/>
+    </row>
+    <row r="2214">
+      <c r="A2214" s="1" t="n">
+        <v>2212</v>
+      </c>
+      <c r="B2214" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0810.png</t>
+        </is>
+      </c>
+      <c r="C2214" t="inlineStr"/>
+      <c r="D2214" t="inlineStr"/>
+      <c r="E2214" t="inlineStr"/>
+      <c r="F2214" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)NCC(=O)Nc2nc(-c3cccc(-c4cccc(CNC(=O)CCCCOc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)c4)c3)cs2)c1</t>
+        </is>
+      </c>
+      <c r="G2214" t="inlineStr"/>
+      <c r="H2214" t="inlineStr"/>
+      <c r="I2214" t="n">
+        <v>0.8919837781879983</v>
+      </c>
+      <c r="J2214" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2214" t="inlineStr"/>
+    </row>
+    <row r="2215">
+      <c r="A2215" s="1" t="n">
+        <v>2213</v>
+      </c>
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0822.png</t>
+        </is>
+      </c>
+      <c r="C2215" t="inlineStr"/>
+      <c r="D2215" t="inlineStr"/>
+      <c r="E2215" t="inlineStr"/>
+      <c r="F2215" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)NCC(=O)Nc2nc(C3CCCN(C(=O)CCCCOc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)C3)cs2)c1</t>
+        </is>
+      </c>
+      <c r="G2215" t="inlineStr"/>
+      <c r="H2215" t="inlineStr"/>
+      <c r="I2215" t="n">
+        <v>0.9079979875171748</v>
+      </c>
+      <c r="J2215" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2215" t="inlineStr"/>
+    </row>
+    <row r="2216">
+      <c r="A2216" s="1" t="n">
+        <v>2214</v>
+      </c>
+      <c r="B2216" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0826.png</t>
+        </is>
+      </c>
+      <c r="C2216" t="inlineStr"/>
+      <c r="D2216" t="inlineStr"/>
+      <c r="E2216" t="inlineStr"/>
+      <c r="F2216" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)N[C@@H](CCOCCCC(=O)N2CC(COc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)C2)C(=O)Nc2nc(-c3ccccc3)cs2)c1</t>
+        </is>
+      </c>
+      <c r="G2216" t="inlineStr"/>
+      <c r="H2216" t="inlineStr"/>
+      <c r="I2216" t="n">
+        <v>0.8895749979760114</v>
+      </c>
+      <c r="J2216" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2216" t="inlineStr"/>
+    </row>
+    <row r="2217">
+      <c r="A2217" s="1" t="n">
+        <v>2215</v>
+      </c>
+      <c r="B2217" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0830.png</t>
+        </is>
+      </c>
+      <c r="C2217" t="inlineStr"/>
+      <c r="D2217" t="inlineStr"/>
+      <c r="E2217" t="inlineStr"/>
+      <c r="F2217" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)N[C@@H](CCOCCCC(=O)N2CCN(CC3CN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)C3)CC2)C(=O)Nc2nc(-c3ccccc3)cs2)c1</t>
+        </is>
+      </c>
+      <c r="G2217" t="inlineStr"/>
+      <c r="H2217" t="inlineStr"/>
+      <c r="I2217" t="n">
+        <v>0.8899936196715675</v>
+      </c>
+      <c r="J2217" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2217" t="inlineStr"/>
+    </row>
+    <row r="2218">
+      <c r="A2218" s="1" t="n">
+        <v>2216</v>
+      </c>
+      <c r="B2218" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0834.png</t>
+        </is>
+      </c>
+      <c r="C2218" t="inlineStr"/>
+      <c r="D2218" t="inlineStr"/>
+      <c r="E2218" t="inlineStr"/>
+      <c r="F2218" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCOCCOCC(=O)N[C@H](C(=O)N3C[C@H](O)C[C@H]3C(=O)NCc3ccc(-c4scnc4C)cc3)C(C)C)c2)cc1CCC1CC2(CC2)C1</t>
+        </is>
+      </c>
+      <c r="G2218" t="inlineStr"/>
+      <c r="H2218" t="inlineStr"/>
+      <c r="I2218" t="n">
+        <v>0.8850017143831596</v>
+      </c>
+      <c r="J2218" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2218" t="inlineStr"/>
+    </row>
+    <row r="2219">
+      <c r="A2219" s="1" t="n">
+        <v>2217</v>
+      </c>
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0838.png</t>
+        </is>
+      </c>
+      <c r="C2219" t="inlineStr"/>
+      <c r="D2219" t="inlineStr"/>
+      <c r="E2219" t="inlineStr"/>
+      <c r="F2219" t="inlineStr">
+        <is>
+          <t>CNC(=O)c1ccccc1Nc1cc(Nc2ccc(N3CCN(CCOCCOCCOCCNC(=O)COc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)cc2OC)ncc1C(F)(F)F</t>
+        </is>
+      </c>
+      <c r="G2219" t="inlineStr"/>
+      <c r="H2219" t="inlineStr"/>
+      <c r="I2219" t="n">
+        <v>0.8997587084961858</v>
+      </c>
+      <c r="J2219" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2219" t="inlineStr"/>
+    </row>
+    <row r="2220">
+      <c r="A2220" s="1" t="n">
+        <v>2218</v>
+      </c>
+      <c r="B2220" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0842.png</t>
+        </is>
+      </c>
+      <c r="C2220" t="inlineStr"/>
+      <c r="D2220" t="inlineStr"/>
+      <c r="E2220" t="inlineStr"/>
+      <c r="F2220" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCCCCCCN4CCC(c5cc(F)cc6c5CN(C5CCC(=O)NC5=O)C6=O)CC4)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G2220" t="inlineStr"/>
+      <c r="H2220" t="inlineStr"/>
+      <c r="I2220" t="n">
+        <v>0.8803173809380918</v>
+      </c>
+      <c r="J2220" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2220" t="inlineStr"/>
+    </row>
+    <row r="2221">
+      <c r="A2221" s="1" t="n">
+        <v>2219</v>
+      </c>
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0603.png</t>
+        </is>
+      </c>
+      <c r="C2221" t="inlineStr"/>
+      <c r="D2221" t="inlineStr"/>
+      <c r="E2221" t="inlineStr"/>
+      <c r="F2221" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCCCCCC(=O)N[C@H](C(=O)N3C[C@H](O)C[C@H]3C(=O)NCc3ccc(-c4scnc4C)cc3)C(C)(C)C)c2)cc1CC[C@@H]1CC[C@@H](C(F)(F)F)CC1</t>
+        </is>
+      </c>
+      <c r="G2221" t="inlineStr"/>
+      <c r="H2221" t="inlineStr"/>
+      <c r="I2221" t="n">
+        <v>0.8655132648247157</v>
+      </c>
+      <c r="J2221" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2221" t="inlineStr"/>
+    </row>
+    <row r="2222">
+      <c r="A2222" s="1" t="n">
+        <v>2220</v>
+      </c>
+      <c r="B2222" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0607.png</t>
+        </is>
+      </c>
+      <c r="C2222" t="inlineStr"/>
+      <c r="D2222" t="inlineStr"/>
+      <c r="E2222" t="inlineStr"/>
+      <c r="F2222" t="inlineStr">
+        <is>
+          <t>O=C(COc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O)NCCCCCCN1CCC(C(=O)N2CCC[C@@H](Nc3ncc(Cl)c(-c4c[nH]c5ccccc45)n3)C2)CC1</t>
+        </is>
+      </c>
+      <c r="G2222" t="inlineStr"/>
+      <c r="H2222" t="inlineStr"/>
+      <c r="I2222" t="n">
+        <v>0.8863696534711821</v>
+      </c>
+      <c r="J2222" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2222" t="inlineStr"/>
+    </row>
+    <row r="2223">
+      <c r="A2223" s="1" t="n">
+        <v>2221</v>
+      </c>
+      <c r="B2223" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0611.png</t>
+        </is>
+      </c>
+      <c r="C2223" t="inlineStr"/>
+      <c r="D2223" t="inlineStr"/>
+      <c r="E2223" t="inlineStr"/>
+      <c r="F2223" t="inlineStr">
+        <is>
+          <t>COc1cc2nn(C3CC4(CCN(C(=O)C5CCN(c6cc7c(cc6F)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)CC4)C3)cc2cc1NC(=O)c1cccc(N2CCOCC2)n1</t>
+        </is>
+      </c>
+      <c r="G2223" t="inlineStr"/>
+      <c r="H2223" t="inlineStr"/>
+      <c r="I2223" t="n">
+        <v>0.8828157043890205</v>
+      </c>
+      <c r="J2223" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2223" t="inlineStr"/>
+    </row>
+    <row r="2224">
+      <c r="A2224" s="1" t="n">
+        <v>2222</v>
+      </c>
+      <c r="B2224" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0619.png</t>
+        </is>
+      </c>
+      <c r="C2224" t="inlineStr"/>
+      <c r="D2224" t="inlineStr"/>
+      <c r="E2224" t="inlineStr"/>
+      <c r="F2224" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2scnc2C)ccc1CNC(=O)[C@H]1C[C@@H](O)CN1C(=O)[C@H](NC(=O)CCC(=O)NCCCCOc1ccc(Oc2ccc(N(Cc3ccccc3)C(=O)CCl)cc2)cc1)C(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G2224" t="inlineStr"/>
+      <c r="H2224" t="inlineStr"/>
+      <c r="I2224" t="n">
+        <v>0.9002277069941788</v>
+      </c>
+      <c r="J2224" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2224" t="inlineStr"/>
+    </row>
+    <row r="2225">
+      <c r="A2225" s="1" t="n">
+        <v>2223</v>
+      </c>
+      <c r="B2225" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0623.png</t>
+        </is>
+      </c>
+      <c r="C2225" t="inlineStr"/>
+      <c r="D2225" t="inlineStr"/>
+      <c r="E2225" t="inlineStr"/>
+      <c r="F2225" t="inlineStr">
+        <is>
+          <t>C[C@@H]1C[C@@H](O)c2ncnc(N3CCN(C(=O)[C@H](CNC(=O)CCCCCCCCC#Cc4cccc5c4CN(C4CCC(=O)NC4=O)C5=O)c4ccc(Cl)cc4)CC3)c21</t>
+        </is>
+      </c>
+      <c r="G2225" t="inlineStr"/>
+      <c r="H2225" t="inlineStr"/>
+      <c r="I2225" t="n">
+        <v>0.8858344845690429</v>
+      </c>
+      <c r="J2225" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2225" t="inlineStr"/>
+    </row>
+    <row r="2226">
+      <c r="A2226" s="1" t="n">
+        <v>2224</v>
+      </c>
+      <c r="B2226" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0627.png</t>
+        </is>
+      </c>
+      <c r="C2226" t="inlineStr"/>
+      <c r="D2226" t="inlineStr"/>
+      <c r="E2226" t="inlineStr"/>
+      <c r="F2226" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3c(CCCOCCOCCNC(=O)c4ccc(NC(=O)[C@@H]5NC6(CCCCC6)[C@@]6(C(=O)Nc7cc(Cl)ccc76)[C@H]5c5cccc(Cl)c5F)cc4)cccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2226" t="inlineStr"/>
+      <c r="H2226" t="inlineStr"/>
+      <c r="I2226" t="n">
+        <v>0.8840712809926429</v>
+      </c>
+      <c r="J2226" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2226" t="inlineStr"/>
+    </row>
+    <row r="2227">
+      <c r="A2227" s="1" t="n">
+        <v>2225</v>
+      </c>
+      <c r="B2227" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0631.png</t>
+        </is>
+      </c>
+      <c r="C2227" t="inlineStr"/>
+      <c r="D2227" t="inlineStr"/>
+      <c r="E2227" t="inlineStr"/>
+      <c r="F2227" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(C(=O)[C@@H]4C[C@@H](N(C)c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)CC3)CC2)c(C)cc1Nc1ncc(Br)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2227" t="inlineStr"/>
+      <c r="H2227" t="inlineStr"/>
+      <c r="I2227" t="n">
+        <v>0.8931027579083716</v>
+      </c>
+      <c r="J2227" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2227" t="inlineStr"/>
+    </row>
+    <row r="2228">
+      <c r="A2228" s="1" t="n">
+        <v>2226</v>
+      </c>
+      <c r="B2228" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0639.png</t>
+        </is>
+      </c>
+      <c r="C2228" t="inlineStr"/>
+      <c r="D2228" t="inlineStr"/>
+      <c r="E2228" t="inlineStr"/>
+      <c r="F2228" t="inlineStr">
+        <is>
+          <t>CC(C)[C@H](NC(=O)COCCOCCOCCOCCNC(=O)Cc1cccc(CNC(=O)c2cc3c(cn2)OCc2cc(C4CC4)ccc2-3)c1)C(=O)N1C[C@H](O)C[C@H]1C(=O)NCc1ccc(-c2cncs2)cc1</t>
+        </is>
+      </c>
+      <c r="G2228" t="inlineStr"/>
+      <c r="H2228" t="inlineStr"/>
+      <c r="I2228" t="n">
+        <v>0.8790334215602335</v>
+      </c>
+      <c r="J2228" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2228" t="inlineStr"/>
+    </row>
+    <row r="2229">
+      <c r="A2229" s="1" t="n">
+        <v>2227</v>
+      </c>
+      <c r="B2229" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0647.png</t>
+        </is>
+      </c>
+      <c r="C2229" t="inlineStr"/>
+      <c r="D2229" t="inlineStr"/>
+      <c r="E2229" t="inlineStr"/>
+      <c r="F2229" t="inlineStr">
+        <is>
+          <t>C=C(Cl)C(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCOCc4ccc(COCCN5CCC(c6cc(F)cc7c6CN(C6CCC(=O)NC6=O)C7=O)CC5)cc4)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G2229" t="inlineStr"/>
+      <c r="H2229" t="inlineStr"/>
+      <c r="I2229" t="n">
+        <v>0.8680284560088778</v>
+      </c>
+      <c r="J2229" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2229" t="inlineStr"/>
+    </row>
+    <row r="2230">
+      <c r="A2230" s="1" t="n">
+        <v>2228</v>
+      </c>
+      <c r="B2230" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0655.png</t>
+        </is>
+      </c>
+      <c r="C2230" t="inlineStr"/>
+      <c r="D2230" t="inlineStr"/>
+      <c r="E2230" t="inlineStr"/>
+      <c r="F2230" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCCCCCCCC(=O)N[C@H](C(=O)N3C[C@H](O)C[C@H]3C(=O)NCc3ccc(-c4scnc4C)cc3)C(C)C)c2)cc1/C=C/C1CC(c2ccc(Cl)cc2)C1</t>
+        </is>
+      </c>
+      <c r="G2230" t="inlineStr"/>
+      <c r="H2230" t="inlineStr"/>
+      <c r="I2230" t="n">
+        <v>0.899985937952925</v>
+      </c>
+      <c r="J2230" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2230" t="inlineStr"/>
+    </row>
+    <row r="2231">
+      <c r="A2231" s="1" t="n">
+        <v>2229</v>
+      </c>
+      <c r="B2231" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0659.png</t>
+        </is>
+      </c>
+      <c r="C2231" t="inlineStr"/>
+      <c r="D2231" t="inlineStr"/>
+      <c r="E2231" t="inlineStr"/>
+      <c r="F2231" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(C(=O)C6CCC(C(=O)N[C@H](C(=O)N7C[C@H](O)C[C@H]7C(=O)N[C@@H](C)c7ccc(-c8scnc8C)cc7)C(C)(C)C)CC6)CC5)C4)nc3cc2OC)n1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2231" t="inlineStr"/>
+      <c r="H2231" t="inlineStr"/>
+      <c r="I2231" t="n">
+        <v>0.8777784349118143</v>
+      </c>
+      <c r="J2231" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2231" t="inlineStr"/>
+    </row>
+    <row r="2232">
+      <c r="A2232" s="1" t="n">
+        <v>2230</v>
+      </c>
+      <c r="B2232" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0663.png</t>
+        </is>
+      </c>
+      <c r="C2232" t="inlineStr"/>
+      <c r="D2232" t="inlineStr"/>
+      <c r="E2232" t="inlineStr"/>
+      <c r="F2232" t="inlineStr">
+        <is>
+          <t>O=C1CC[C@H](N2Cc3cc(N4CCN(CC5CCN(c6ccc(C7=C(c8ccc(OC(F)F)cc8)CCCc8cc(O)ccc87)cc6)CC5)CC4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2232" t="inlineStr"/>
+      <c r="H2232" t="inlineStr"/>
+      <c r="I2232" t="n">
+        <v>0.8883024555335121</v>
+      </c>
+      <c r="J2232" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2232" t="inlineStr"/>
+    </row>
+    <row r="2233">
+      <c r="A2233" s="1" t="n">
+        <v>2231</v>
+      </c>
+      <c r="B2233" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0671.png</t>
+        </is>
+      </c>
+      <c r="C2233" t="inlineStr"/>
+      <c r="D2233" t="inlineStr"/>
+      <c r="E2233" t="inlineStr"/>
+      <c r="F2233" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCOCCOCC(=O)N[C@H](C(=O)N3C[C@H](O)C[C@H]3C(=O)NCc3ccc(-c4scnc4C)cc3)C(C)C)c2)cc1C=C[C@@H]1CC[C@@H](C(F)(F)F)CC1</t>
+        </is>
+      </c>
+      <c r="G2233" t="inlineStr"/>
+      <c r="H2233" t="inlineStr"/>
+      <c r="I2233" t="n">
+        <v>0.8902973358232632</v>
+      </c>
+      <c r="J2233" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2233" t="inlineStr"/>
+    </row>
+    <row r="2234">
+      <c r="A2234" s="1" t="n">
+        <v>2232</v>
+      </c>
+      <c r="B2234" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0675.png</t>
+        </is>
+      </c>
+      <c r="C2234" t="inlineStr"/>
+      <c r="D2234" t="inlineStr"/>
+      <c r="E2234" t="inlineStr"/>
+      <c r="F2234" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3c(CCCNC(=O)c4ccc(NC(=O)[C@@H]5NC6(CCCCC6)[C@@]6(C(=O)Nc7cc(Cl)ccc76)[C@H]5c5cccc(Cl)c5F)cc4)cccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2234" t="inlineStr"/>
+      <c r="H2234" t="inlineStr"/>
+      <c r="I2234" t="n">
+        <v>0.8875348956691392</v>
+      </c>
+      <c r="J2234" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2234" t="inlineStr"/>
+    </row>
+    <row r="2235">
+      <c r="A2235" s="1" t="n">
+        <v>2233</v>
+      </c>
+      <c r="B2235" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0679.png</t>
+        </is>
+      </c>
+      <c r="C2235" t="inlineStr"/>
+      <c r="D2235" t="inlineStr"/>
+      <c r="E2235" t="inlineStr"/>
+      <c r="F2235" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(C(=O)C6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2C(=O)O)n1.[I-65] |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2235" t="inlineStr"/>
+      <c r="H2235" t="inlineStr"/>
+      <c r="I2235" t="n">
+        <v>0.8454845762908613</v>
+      </c>
+      <c r="J2235" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2235" t="inlineStr"/>
+    </row>
+    <row r="2236">
+      <c r="A2236" s="1" t="n">
+        <v>2234</v>
+      </c>
+      <c r="B2236" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0683.png</t>
+        </is>
+      </c>
+      <c r="C2236" t="inlineStr"/>
+      <c r="D2236" t="inlineStr"/>
+      <c r="E2236" t="inlineStr"/>
+      <c r="F2236" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)N[C@@H](CCCCNC(=O)C2CC2CNC(=O)COc2cccc3c2C(=O)N(C2CCC(=O)NC2=O)C3=O)C(=O)Nc2nc(-c3ccccc3)cs2)c1</t>
+        </is>
+      </c>
+      <c r="G2236" t="inlineStr"/>
+      <c r="H2236" t="inlineStr"/>
+      <c r="I2236" t="n">
+        <v>0.8964795950978239</v>
+      </c>
+      <c r="J2236" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2236" t="inlineStr"/>
+    </row>
+    <row r="2237">
+      <c r="A2237" s="1" t="n">
+        <v>2235</v>
+      </c>
+      <c r="B2237" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0691.png</t>
+        </is>
+      </c>
+      <c r="C2237" t="inlineStr"/>
+      <c r="D2237" t="inlineStr"/>
+      <c r="E2237" t="inlineStr"/>
+      <c r="F2237" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(CC6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2OC)n1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2237" t="inlineStr"/>
+      <c r="H2237" t="inlineStr"/>
+      <c r="I2237" t="n">
+        <v>0.8858021531998024</v>
+      </c>
+      <c r="J2237" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2237" t="inlineStr"/>
+    </row>
+    <row r="2238">
+      <c r="A2238" s="1" t="n">
+        <v>2236</v>
+      </c>
+      <c r="B2238" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0695.png</t>
+        </is>
+      </c>
+      <c r="C2238" t="inlineStr"/>
+      <c r="D2238" t="inlineStr"/>
+      <c r="E2238" t="inlineStr"/>
+      <c r="F2238" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCCCC(=O)N[C@H](C(=O)N3C[C@H](O)C[C@H]3C(=O)NCc3ccc(-c4cncs4)cc3)C(C)C)c2)cc1/C=C/C1CCCCC1</t>
+        </is>
+      </c>
+      <c r="G2238" t="inlineStr"/>
+      <c r="H2238" t="inlineStr"/>
+      <c r="I2238" t="n">
+        <v>0.8908196936906581</v>
+      </c>
+      <c r="J2238" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2238" t="inlineStr"/>
+    </row>
+    <row r="2239">
+      <c r="A2239" s="1" t="n">
+        <v>2237</v>
+      </c>
+      <c r="B2239" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0703.png</t>
+        </is>
+      </c>
+      <c r="C2239" t="inlineStr"/>
+      <c r="D2239" t="inlineStr"/>
+      <c r="E2239" t="inlineStr"/>
+      <c r="F2239" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(C(=O)C6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2OC)n1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2239" t="inlineStr"/>
+      <c r="H2239" t="inlineStr"/>
+      <c r="I2239" t="n">
+        <v>0.8824033861794084</v>
+      </c>
+      <c r="J2239" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2239" t="inlineStr"/>
+    </row>
+    <row r="2240">
+      <c r="A2240" s="1" t="n">
+        <v>2238</v>
+      </c>
+      <c r="B2240" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0711.png</t>
+        </is>
+      </c>
+      <c r="C2240" t="inlineStr"/>
+      <c r="D2240" t="inlineStr"/>
+      <c r="E2240" t="inlineStr"/>
+      <c r="F2240" t="inlineStr">
+        <is>
+          <t>CC1CN2C(=O)C=CC[CH]2(C)CN1C1=C2C=C(Cl)C(C3=C(F)C=CC=C3O)=C(F)C2=NC(OCCOCCOCCOCCNC2=CC=CC3=C2C(=O)N(C2CCC(=O)NC2=O)C3=O)=N1</t>
+        </is>
+      </c>
+      <c r="G2240" t="inlineStr"/>
+      <c r="H2240" t="inlineStr"/>
+      <c r="I2240" t="n">
+        <v>0.8647116504421858</v>
+      </c>
+      <c r="J2240" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2240" t="inlineStr"/>
+    </row>
+    <row r="2241">
+      <c r="A2241" s="1" t="n">
+        <v>2239</v>
+      </c>
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0715.png</t>
+        </is>
+      </c>
+      <c r="C2241" t="inlineStr"/>
+      <c r="D2241" t="inlineStr"/>
+      <c r="E2241" t="inlineStr"/>
+      <c r="F2241" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CC(c2nc3ccc(-c4cc(O)cc5ccccc45)cc3c(=O)n2CC(=O)NCCOCCOCCOCCNc2cccc3c2C(=O)N(C2CCC(=O)NC2=O)C3=O)C1</t>
+        </is>
+      </c>
+      <c r="G2241" t="inlineStr"/>
+      <c r="H2241" t="inlineStr"/>
+      <c r="I2241" t="n">
+        <v>0.9055532272819942</v>
+      </c>
+      <c r="J2241" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2241" t="inlineStr"/>
+    </row>
+    <row r="2242">
+      <c r="A2242" s="1" t="n">
+        <v>2240</v>
+      </c>
+      <c r="B2242" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0719.png</t>
+        </is>
+      </c>
+      <c r="C2242" t="inlineStr"/>
+      <c r="D2242" t="inlineStr"/>
+      <c r="E2242" t="inlineStr"/>
+      <c r="F2242" t="inlineStr">
+        <is>
+          <t>*c1c(-c2c(F)cccc2OCCCCCCCN2CCC(c3cc(F)cc4c3CN(C3CCC(=O)NC3=O)C4=O)CC2)c(Cl)cc2c(N3CCN(C(C)=O)CC3)ncnc12 |$*;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2242" t="inlineStr"/>
+      <c r="H2242" t="inlineStr"/>
+      <c r="I2242" t="n">
+        <v>0.899942451128915</v>
+      </c>
+      <c r="J2242" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2242" t="inlineStr"/>
+    </row>
+    <row r="2243">
+      <c r="A2243" s="1" t="n">
+        <v>2241</v>
+      </c>
+      <c r="B2243" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0723.png</t>
+        </is>
+      </c>
+      <c r="C2243" t="inlineStr"/>
+      <c r="D2243" t="inlineStr"/>
+      <c r="E2243" t="inlineStr"/>
+      <c r="F2243" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)N1CCc2cccc(Nc3nc(Nc4ccc(N5CCC(N6CCN(C(=O)[C@H]7CCN(c8ccc9c(c8)C(=O)N(C8CCC(=O)NC8=O)C9=O)C7)CC6)CC5)c(F)c4)nc4[nH]ccc34)c21</t>
+        </is>
+      </c>
+      <c r="G2243" t="inlineStr"/>
+      <c r="H2243" t="inlineStr"/>
+      <c r="I2243" t="n">
+        <v>0.8860171984946753</v>
+      </c>
+      <c r="J2243" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2243" t="inlineStr"/>
+    </row>
+    <row r="2244">
+      <c r="A2244" s="1" t="n">
+        <v>2242</v>
+      </c>
+      <c r="B2244" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0727.png</t>
+        </is>
+      </c>
+      <c r="C2244" t="inlineStr"/>
+      <c r="D2244" t="inlineStr"/>
+      <c r="E2244" t="inlineStr"/>
+      <c r="F2244" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3c(NC(=O)CCOCCOCCOCCNC(=O)c4ccc(NC(=O)[C@@H]5NC6(CCCCC6)[C@@]6(C(=O)Nc7cc(Cl)ccc76)[C@H]5c5cccc(Cl)c5F)cc4)cccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2244" t="inlineStr"/>
+      <c r="H2244" t="inlineStr"/>
+      <c r="I2244" t="n">
+        <v>0.855887958810358</v>
+      </c>
+      <c r="J2244" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2244" t="inlineStr"/>
+    </row>
+    <row r="2245">
+      <c r="A2245" s="1" t="n">
+        <v>2243</v>
+      </c>
+      <c r="B2245" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0731.png</t>
+        </is>
+      </c>
+      <c r="C2245" t="inlineStr"/>
+      <c r="D2245" t="inlineStr"/>
+      <c r="E2245" t="inlineStr"/>
+      <c r="F2245" t="inlineStr">
+        <is>
+          <t>CCC(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCCCCCCN4CC=C(c5cc(F)cc6c5CN(C5CCC(=O)NC5=O)C6=O)CC4)c(Cl)cc23)[C@@H](C)C1</t>
+        </is>
+      </c>
+      <c r="G2245" t="inlineStr"/>
+      <c r="H2245" t="inlineStr"/>
+      <c r="I2245" t="n">
+        <v>0.905749940962454</v>
+      </c>
+      <c r="J2245" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2245" t="inlineStr"/>
+    </row>
+    <row r="2246">
+      <c r="A2246" s="1" t="n">
+        <v>2244</v>
+      </c>
+      <c r="B2246" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0735.png</t>
+        </is>
+      </c>
+      <c r="C2246" t="inlineStr"/>
+      <c r="D2246" t="inlineStr"/>
+      <c r="E2246" t="inlineStr"/>
+      <c r="F2246" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCCCC(=O)N[C@H](C(=O)N3C[C@H](O)C[C@H]3C(=O)NCc3ccc(-c4scnc4C)cc3)C(C)C)c2)cc1CCC1CCC(F)(F)CC1</t>
+        </is>
+      </c>
+      <c r="G2246" t="inlineStr"/>
+      <c r="H2246" t="inlineStr"/>
+      <c r="I2246" t="n">
+        <v>0.8926856103367908</v>
+      </c>
+      <c r="J2246" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2246" t="inlineStr"/>
+    </row>
+    <row r="2247">
+      <c r="A2247" s="1" t="n">
+        <v>2245</v>
+      </c>
+      <c r="B2247" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0751.png</t>
+        </is>
+      </c>
+      <c r="C2247" t="inlineStr"/>
+      <c r="D2247" t="inlineStr"/>
+      <c r="E2247" t="inlineStr"/>
+      <c r="F2247" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(C[C@@H](O)NCCOCCOCCOCCOCC(=O)N[C@H](C(=O)N3C[C@H](O)C[C@H]3C(=O)NCc3ccc(-c4cncs4)cc3)C(C)(C)C)c2)cc1/C=C/c1ccc(Cl)cc1</t>
+        </is>
+      </c>
+      <c r="G2247" t="inlineStr"/>
+      <c r="H2247" t="inlineStr"/>
+      <c r="I2247" t="n">
+        <v>0.8608896874733709</v>
+      </c>
+      <c r="J2247" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2247" t="inlineStr"/>
+    </row>
+    <row r="2248">
+      <c r="A2248" s="1" t="n">
+        <v>2246</v>
+      </c>
+      <c r="B2248" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0755.png</t>
+        </is>
+      </c>
+      <c r="C2248" t="inlineStr"/>
+      <c r="D2248" t="inlineStr"/>
+      <c r="E2248" t="inlineStr"/>
+      <c r="F2248" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)N1CCc2cccc(Nc3nc(Nc4ccc(N5CCC(N6CCN(CC7CN(c8ccc9c(c8)C(=O)N(C8CCC(=O)NC8=O)C9=O)C7)CC6)CC5)c(F)c4)nc4[nH]ccc34)c21</t>
+        </is>
+      </c>
+      <c r="G2248" t="inlineStr"/>
+      <c r="H2248" t="inlineStr"/>
+      <c r="I2248" t="n">
+        <v>0.8726169205880004</v>
+      </c>
+      <c r="J2248" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2248" t="inlineStr"/>
+    </row>
+    <row r="2249">
+      <c r="A2249" s="1" t="n">
+        <v>2247</v>
+      </c>
+      <c r="B2249" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0759.png</t>
+        </is>
+      </c>
+      <c r="C2249" t="inlineStr"/>
+      <c r="D2249" t="inlineStr"/>
+      <c r="E2249" t="inlineStr"/>
+      <c r="F2249" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3c(NC(=O)CCOCCOCCOCCN4CCC(=C(c5ccc(F)cc5)c5ccc(F)cc5)CC4)cccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2249" t="inlineStr"/>
+      <c r="H2249" t="inlineStr"/>
+      <c r="I2249" t="n">
+        <v>0.9048016910855141</v>
+      </c>
+      <c r="J2249" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2249" t="inlineStr"/>
+    </row>
+    <row r="2250">
+      <c r="A2250" s="1" t="n">
+        <v>2248</v>
+      </c>
+      <c r="B2250" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0763.png</t>
+        </is>
+      </c>
+      <c r="C2250" t="inlineStr"/>
+      <c r="D2250" t="inlineStr"/>
+      <c r="E2250" t="inlineStr"/>
+      <c r="F2250" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(C[C@H]4C[C@H](N(C)c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)CC3)CC2)c(C)cc1Nc1ncc(Br)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2250" t="inlineStr"/>
+      <c r="H2250" t="inlineStr"/>
+      <c r="I2250" t="n">
+        <v>0.8810810446782894</v>
+      </c>
+      <c r="J2250" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2250" t="inlineStr"/>
+    </row>
+    <row r="2251">
+      <c r="A2251" s="1" t="n">
+        <v>2249</v>
+      </c>
+      <c r="B2251" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0771.png</t>
+        </is>
+      </c>
+      <c r="C2251" t="inlineStr"/>
+      <c r="D2251" t="inlineStr"/>
+      <c r="E2251" t="inlineStr"/>
+      <c r="F2251" t="inlineStr">
+        <is>
+          <t>COc1ccc2c(c1)OCCC(c1ccccc1)=C2c1ccc(N2CCC(CN3CCN(c4ccc5c(c4)CN([C@H]4CCC(=O)NC4=O)C5=O)CC3)CC2)cc1</t>
+        </is>
+      </c>
+      <c r="G2251" t="inlineStr"/>
+      <c r="H2251" t="inlineStr"/>
+      <c r="I2251" t="n">
+        <v>0.8973939460841507</v>
+      </c>
+      <c r="J2251" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2251" t="inlineStr"/>
+    </row>
+    <row r="2252">
+      <c r="A2252" s="1" t="n">
+        <v>2250</v>
+      </c>
+      <c r="B2252" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0783.png</t>
+        </is>
+      </c>
+      <c r="C2252" t="inlineStr"/>
+      <c r="D2252" t="inlineStr"/>
+      <c r="E2252" t="inlineStr"/>
+      <c r="F2252" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(C(=O)C6CCN(c7ccc8c(c7)CN(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2OC)n1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2252" t="inlineStr"/>
+      <c r="H2252" t="inlineStr"/>
+      <c r="I2252" t="n">
+        <v>0.8651679482188694</v>
+      </c>
+      <c r="J2252" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2252" t="inlineStr"/>
+    </row>
+    <row r="2253">
+      <c r="A2253" s="1" t="n">
+        <v>2251</v>
+      </c>
+      <c r="B2253" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0787.png</t>
+        </is>
+      </c>
+      <c r="C2253" t="inlineStr"/>
+      <c r="D2253" t="inlineStr"/>
+      <c r="E2253" t="inlineStr"/>
+      <c r="F2253" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCOCCOCCOCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)c2)cc1/C=C/Cc1ccccc1</t>
+        </is>
+      </c>
+      <c r="G2253" t="inlineStr"/>
+      <c r="H2253" t="inlineStr"/>
+      <c r="I2253" t="n">
+        <v>0.8989758790271409</v>
+      </c>
+      <c r="J2253" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2253" t="inlineStr"/>
+    </row>
+    <row r="2254">
+      <c r="A2254" s="1" t="n">
+        <v>2252</v>
+      </c>
+      <c r="B2254" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0791.png</t>
+        </is>
+      </c>
+      <c r="C2254" t="inlineStr"/>
+      <c r="D2254" t="inlineStr"/>
+      <c r="E2254" t="inlineStr"/>
+      <c r="F2254" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2scnc2C)ccc1CNC(=O)C1CC(O)CN1C(=O)C(NC(=O)CCC(=O)NCCCCOc1ccc(Oc2ccc(N(Cc3ccccc3)C(=O)CCl)cc2)cc1)C(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G2254" t="inlineStr"/>
+      <c r="H2254" t="inlineStr"/>
+      <c r="I2254" t="n">
+        <v>0.9095684678307264</v>
+      </c>
+      <c r="J2254" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2254" t="inlineStr"/>
+    </row>
+    <row r="2255">
+      <c r="A2255" s="1" t="n">
+        <v>2253</v>
+      </c>
+      <c r="B2255" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0795.png</t>
+        </is>
+      </c>
+      <c r="C2255" t="inlineStr"/>
+      <c r="D2255" t="inlineStr"/>
+      <c r="E2255" t="inlineStr"/>
+      <c r="F2255" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)N(C)CCCCCCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)c2)cc1C1CC(c2ccc(Cl)cc2)C1</t>
+        </is>
+      </c>
+      <c r="G2255" t="inlineStr"/>
+      <c r="H2255" t="inlineStr"/>
+      <c r="I2255" t="n">
+        <v>0.8958701775534571</v>
+      </c>
+      <c r="J2255" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2255" t="inlineStr"/>
+    </row>
+    <row r="2256">
+      <c r="A2256" s="1" t="n">
+        <v>2254</v>
+      </c>
+      <c r="B2256" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0799.png</t>
+        </is>
+      </c>
+      <c r="C2256" t="inlineStr"/>
+      <c r="D2256" t="inlineStr"/>
+      <c r="E2256" t="inlineStr"/>
+      <c r="F2256" t="inlineStr">
+        <is>
+          <t>COc1ccc2c(c1)CCCC(c1ccccc1)=C2c1ccc(N2CCC(CN3CCN(c4ccc5c(c4)CN([C@H]4CCC(=O)NC4=O)C5=O)CC3)CC2)cc1</t>
+        </is>
+      </c>
+      <c r="G2256" t="inlineStr"/>
+      <c r="H2256" t="inlineStr"/>
+      <c r="I2256" t="n">
+        <v>0.898767128717856</v>
+      </c>
+      <c r="J2256" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2256" t="inlineStr"/>
+    </row>
+    <row r="2257">
+      <c r="A2257" s="1" t="n">
+        <v>2255</v>
+      </c>
+      <c r="B2257" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0811.png</t>
+        </is>
+      </c>
+      <c r="C2257" t="inlineStr"/>
+      <c r="D2257" t="inlineStr"/>
+      <c r="E2257" t="inlineStr"/>
+      <c r="F2257" t="inlineStr">
+        <is>
+          <t>CCS(=O)(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCCCCCCN4CC=C(c5cc(F)cc6c5CN(C5CCC(=O)NC5=O)C6=O)CC4)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G2257" t="inlineStr"/>
+      <c r="H2257" t="inlineStr"/>
+      <c r="I2257" t="n">
+        <v>0.9041903111476202</v>
+      </c>
+      <c r="J2257" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2257" t="inlineStr"/>
+    </row>
+    <row r="2258">
+      <c r="A2258" s="1" t="n">
+        <v>2256</v>
+      </c>
+      <c r="B2258" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0815.png</t>
+        </is>
+      </c>
+      <c r="C2258" t="inlineStr"/>
+      <c r="D2258" t="inlineStr"/>
+      <c r="E2258" t="inlineStr"/>
+      <c r="F2258" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)N(C)CCOCCOCCOCCOCCOCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)c2)cc1C=C[C@@H]1CC[C@@H](C(F)(F)F)CC1</t>
+        </is>
+      </c>
+      <c r="G2258" t="inlineStr"/>
+      <c r="H2258" t="inlineStr"/>
+      <c r="I2258" t="n">
+        <v>0.8679184784769935</v>
+      </c>
+      <c r="J2258" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2258" t="inlineStr"/>
+    </row>
+    <row r="2259">
+      <c r="A2259" s="1" t="n">
+        <v>2257</v>
+      </c>
+      <c r="B2259" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0819.png</t>
+        </is>
+      </c>
+      <c r="C2259" t="inlineStr"/>
+      <c r="D2259" t="inlineStr"/>
+      <c r="E2259" t="inlineStr"/>
+      <c r="F2259" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)N[C@@H](COCCCC(=O)NCCCCS(=O)(=O)CCCNc2cccc3c2C(=O)N(C2CCC(=O)NC2=O)C3=O)C(=O)Nc2nc(-c3ccccc3)cs2)c1</t>
+        </is>
+      </c>
+      <c r="G2259" t="inlineStr"/>
+      <c r="H2259" t="inlineStr"/>
+      <c r="I2259" t="n">
+        <v>0.8908740907655459</v>
+      </c>
+      <c r="J2259" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2259" t="inlineStr"/>
+    </row>
+    <row r="2260">
+      <c r="A2260" s="1" t="n">
+        <v>2258</v>
+      </c>
+      <c r="B2260" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0823.png</t>
+        </is>
+      </c>
+      <c r="C2260" t="inlineStr"/>
+      <c r="D2260" t="inlineStr"/>
+      <c r="E2260" t="inlineStr"/>
+      <c r="F2260" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CCC5(CC4)CN(C(=O)C4CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC4)C5)nc3cc2OC)n1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2260" t="inlineStr"/>
+      <c r="H2260" t="inlineStr"/>
+      <c r="I2260" t="n">
+        <v>0.8873530942750222</v>
+      </c>
+      <c r="J2260" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2260" t="inlineStr"/>
+    </row>
+    <row r="2261">
+      <c r="A2261" s="1" t="n">
+        <v>2259</v>
+      </c>
+      <c r="B2261" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0827.png</t>
+        </is>
+      </c>
+      <c r="C2261" t="inlineStr"/>
+      <c r="D2261" t="inlineStr"/>
+      <c r="E2261" t="inlineStr"/>
+      <c r="F2261" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(CCNc4cccc5c4CN(C4CCC(=O)NC4=O)C5=O)CC3)CC2)c(C)cc1Nc1ncc(Br)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2261" t="inlineStr"/>
+      <c r="H2261" t="inlineStr"/>
+      <c r="I2261" t="n">
+        <v>0.9018317193592112</v>
+      </c>
+      <c r="J2261" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2261" t="inlineStr"/>
+    </row>
+    <row r="2262">
+      <c r="A2262" s="1" t="n">
+        <v>2260</v>
+      </c>
+      <c r="B2262" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0831.png</t>
+        </is>
+      </c>
+      <c r="C2262" t="inlineStr"/>
+      <c r="D2262" t="inlineStr"/>
+      <c r="E2262" t="inlineStr"/>
+      <c r="F2262" t="inlineStr">
+        <is>
+          <t>O=C(COc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O)NCCCCCN1CCC[C@@H](Nc2ncc(Cl)c(-c3c[nH]c4ccccc34)n2)C1</t>
+        </is>
+      </c>
+      <c r="G2262" t="inlineStr"/>
+      <c r="H2262" t="inlineStr"/>
+      <c r="I2262" t="n">
+        <v>0.8974302455171376</v>
+      </c>
+      <c r="J2262" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2262" t="inlineStr"/>
+    </row>
+    <row r="2263">
+      <c r="A2263" s="1" t="n">
+        <v>2261</v>
+      </c>
+      <c r="B2263" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0839.png</t>
+        </is>
+      </c>
+      <c r="C2263" t="inlineStr"/>
+      <c r="D2263" t="inlineStr"/>
+      <c r="E2263" t="inlineStr"/>
+      <c r="F2263" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(C(=O)CCN4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)CC3)CC2)c(C)cc1Nc1ncc(Br)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2263" t="inlineStr"/>
+      <c r="H2263" t="inlineStr"/>
+      <c r="I2263" t="n">
+        <v>0.897072924708909</v>
+      </c>
+      <c r="J2263" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2263" t="inlineStr"/>
+    </row>
+    <row r="2264">
+      <c r="A2264" s="1" t="n">
+        <v>2262</v>
+      </c>
+      <c r="B2264" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0843.png</t>
+        </is>
+      </c>
+      <c r="C2264" t="inlineStr"/>
+      <c r="D2264" t="inlineStr"/>
+      <c r="E2264" t="inlineStr"/>
+      <c r="F2264" t="inlineStr">
+        <is>
+          <t>CCC(=O)N1CCN(c2nc(OCCOCCOCCOCCNc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)nc3c2CCN(c2cccc4ccccc24)C3)C[C@H]1C</t>
+        </is>
+      </c>
+      <c r="G2264" t="inlineStr"/>
+      <c r="H2264" t="inlineStr"/>
+      <c r="I2264" t="n">
+        <v>0.8748938341200596</v>
+      </c>
+      <c r="J2264" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2264" t="inlineStr"/>
+    </row>
+    <row r="2265">
+      <c r="A2265" s="1" t="n">
+        <v>2263</v>
+      </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0847.png</t>
+        </is>
+      </c>
+      <c r="C2265" t="inlineStr"/>
+      <c r="D2265" t="inlineStr"/>
+      <c r="E2265" t="inlineStr"/>
+      <c r="F2265" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1C[C@@H]2C(=O)N(CCCCCCCN3CCC(c4cc(F)cc5c4CN(C4CCC(=O)NC4=O)C5=O)CC3)c3cnc4c(F)c(-c5c(O)cccc5F)c(Cl)cc4c3N2C[C@H]1C</t>
+        </is>
+      </c>
+      <c r="G2265" t="inlineStr"/>
+      <c r="H2265" t="inlineStr"/>
+      <c r="I2265" t="n">
+        <v>0.9037565120899138</v>
+      </c>
+      <c r="J2265" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2265" t="inlineStr"/>
+    </row>
+    <row r="2266">
+      <c r="A2266" s="1" t="n">
+        <v>2264</v>
+      </c>
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0604.png</t>
+        </is>
+      </c>
+      <c r="C2266" t="inlineStr"/>
+      <c r="D2266" t="inlineStr"/>
+      <c r="E2266" t="inlineStr"/>
+      <c r="F2266" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(C(=O)[C@@H]4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)CC3)CC2)ccc1Nc1ncc(Cl)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2266" t="inlineStr"/>
+      <c r="H2266" t="inlineStr"/>
+      <c r="I2266" t="n">
+        <v>0.9030112541060165</v>
+      </c>
+      <c r="J2266" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2266" t="inlineStr"/>
+    </row>
+    <row r="2267">
+      <c r="A2267" s="1" t="n">
+        <v>2265</v>
+      </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0608.png</t>
+        </is>
+      </c>
+      <c r="C2267" t="inlineStr"/>
+      <c r="D2267" t="inlineStr"/>
+      <c r="E2267" t="inlineStr"/>
+      <c r="F2267" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(C[C@@H]4CCN(c5ccc6c(c5)CN(C5CCC(=O)NC5=O)C6=O)C4)CC3)CC2)c(C)cc1Nc1ncc(Br)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2267" t="inlineStr"/>
+      <c r="H2267" t="inlineStr"/>
+      <c r="I2267" t="n">
+        <v>0.8801191003911513</v>
+      </c>
+      <c r="J2267" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2267" t="inlineStr"/>
+    </row>
+    <row r="2268">
+      <c r="A2268" s="1" t="n">
+        <v>2266</v>
+      </c>
+      <c r="B2268" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0612.png</t>
+        </is>
+      </c>
+      <c r="C2268" t="inlineStr"/>
+      <c r="D2268" t="inlineStr"/>
+      <c r="E2268" t="inlineStr"/>
+      <c r="F2268" t="inlineStr">
+        <is>
+          <t>C[C@@H]1C[C@@H](O)c2ncnc(N3CCN(C(=O)[C@H](CNCCOCCNC(=O)COc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)c4ccc(Cl)cc4)CC3)c21</t>
+        </is>
+      </c>
+      <c r="G2268" t="inlineStr"/>
+      <c r="H2268" t="inlineStr"/>
+      <c r="I2268" t="n">
+        <v>0.9004533929235652</v>
+      </c>
+      <c r="J2268" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2268" t="inlineStr"/>
+    </row>
+    <row r="2269">
+      <c r="A2269" s="1" t="n">
+        <v>2267</v>
+      </c>
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0616.png</t>
+        </is>
+      </c>
+      <c r="C2269" t="inlineStr"/>
+      <c r="D2269" t="inlineStr"/>
+      <c r="E2269" t="inlineStr"/>
+      <c r="F2269" t="inlineStr">
+        <is>
+          <t>O=C(COc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O)NCCCCN1CCC[C@@H](Nc2ncc(Cl)c(-c3c[nH]c4ccccc34)n2)C1</t>
+        </is>
+      </c>
+      <c r="G2269" t="inlineStr"/>
+      <c r="H2269" t="inlineStr"/>
+      <c r="I2269" t="n">
+        <v>0.8993762733904536</v>
+      </c>
+      <c r="J2269" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2269" t="inlineStr"/>
+    </row>
+    <row r="2270">
+      <c r="A2270" s="1" t="n">
+        <v>2268</v>
+      </c>
+      <c r="B2270" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0624.png</t>
+        </is>
+      </c>
+      <c r="C2270" t="inlineStr"/>
+      <c r="D2270" t="inlineStr"/>
+      <c r="E2270" t="inlineStr"/>
+      <c r="F2270" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3cc(N4CCN(CCCCCOc5ccc(C6=C(c7ccccc7)CCCc7cc(O)ccc76)cc5)CC4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2270" t="inlineStr"/>
+      <c r="H2270" t="inlineStr"/>
+      <c r="I2270" t="n">
+        <v>0.8971934775628068</v>
+      </c>
+      <c r="J2270" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2270" t="inlineStr"/>
+    </row>
+    <row r="2271">
+      <c r="A2271" s="1" t="n">
+        <v>2269</v>
+      </c>
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0628.png</t>
+        </is>
+      </c>
+      <c r="C2271" t="inlineStr"/>
+      <c r="D2271" t="inlineStr"/>
+      <c r="E2271" t="inlineStr"/>
+      <c r="F2271" t="inlineStr">
+        <is>
+          <t>O=C1CC[C@H](N2Cc3cc(N4CCN(CC5CCN(c6ccc(C7=C(c8ccccc8)CCCc8cc(O)ccc87)cc6)CC5)CC4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2271" t="inlineStr"/>
+      <c r="H2271" t="inlineStr"/>
+      <c r="I2271" t="n">
+        <v>0.8952374459754814</v>
+      </c>
+      <c r="J2271" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2271" t="inlineStr"/>
+    </row>
+    <row r="2272">
+      <c r="A2272" s="1" t="n">
+        <v>2270</v>
+      </c>
+      <c r="B2272" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0640.png</t>
+        </is>
+      </c>
+      <c r="C2272" t="inlineStr"/>
+      <c r="D2272" t="inlineStr"/>
+      <c r="E2272" t="inlineStr"/>
+      <c r="F2272" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)N1CCc2cccc(Nc3nc(Nc4ccc(N5CCC(N6CCN(C(=O)C7CN(c8ccc9c(c8)C(=O)N(C8CCC(=O)NC8=O)C9=O)C7)CC6)CC5)c(F)c4)ncc3Cl)c21</t>
+        </is>
+      </c>
+      <c r="G2272" t="inlineStr"/>
+      <c r="H2272" t="inlineStr"/>
+      <c r="I2272" t="n">
+        <v>0.8819621902171648</v>
+      </c>
+      <c r="J2272" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2272" t="inlineStr"/>
+    </row>
+    <row r="2273">
+      <c r="A2273" s="1" t="n">
+        <v>2271</v>
+      </c>
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0648.png</t>
+        </is>
+      </c>
+      <c r="C2273" t="inlineStr"/>
+      <c r="D2273" t="inlineStr"/>
+      <c r="E2273" t="inlineStr"/>
+      <c r="F2273" t="inlineStr">
+        <is>
+          <t>Cc1ccc(C2=C(c3ccc(N4CCC(CN5CCN(c6ccc7c(c6)CN([C@H]6CCC(=O)NC6=O)C7=O)CC5)CC4)cc3)c3ccc(O)cc3CCC2)cn1</t>
+        </is>
+      </c>
+      <c r="G2273" t="inlineStr"/>
+      <c r="H2273" t="inlineStr"/>
+      <c r="I2273" t="n">
+        <v>0.8947790372433228</v>
+      </c>
+      <c r="J2273" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2273" t="inlineStr"/>
+    </row>
+    <row r="2274">
+      <c r="A2274" s="1" t="n">
+        <v>2272</v>
+      </c>
+      <c r="B2274" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0652.png</t>
+        </is>
+      </c>
+      <c r="C2274" t="inlineStr"/>
+      <c r="D2274" t="inlineStr"/>
+      <c r="E2274" t="inlineStr"/>
+      <c r="F2274" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCCCCCCN4CCC(c5cc6c(cc5F)C(=O)N(C5CCC(=O)NC5=O)C6)CC4)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G2274" t="inlineStr"/>
+      <c r="H2274" t="inlineStr"/>
+      <c r="I2274" t="n">
+        <v>0.9062189123872439</v>
+      </c>
+      <c r="J2274" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2274" t="inlineStr"/>
+    </row>
+    <row r="2275">
+      <c r="A2275" s="1" t="n">
+        <v>2273</v>
+      </c>
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0664.png</t>
+        </is>
+      </c>
+      <c r="C2275" t="inlineStr"/>
+      <c r="D2275" t="inlineStr"/>
+      <c r="E2275" t="inlineStr"/>
+      <c r="F2275" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)NCC(=O)Nc2nc(-c3cccc(-c4cccc(CNC(=O)CCOCCOCCNc5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)c4)c3)co2)c1</t>
+        </is>
+      </c>
+      <c r="G2275" t="inlineStr"/>
+      <c r="H2275" t="inlineStr"/>
+      <c r="I2275" t="n">
+        <v>0.8723250575196625</v>
+      </c>
+      <c r="J2275" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2275" t="inlineStr"/>
+    </row>
+    <row r="2276">
+      <c r="A2276" s="1" t="n">
+        <v>2274</v>
+      </c>
+      <c r="B2276" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0676.png</t>
+        </is>
+      </c>
+      <c r="C2276" t="inlineStr"/>
+      <c r="D2276" t="inlineStr"/>
+      <c r="E2276" t="inlineStr"/>
+      <c r="F2276" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@H]2C[C@H](O)CN2C(=O)[C@@H](NC(=O)CCCCCCCCCCN2CCC[C@@H](Nc3ncc(Cl)c(Nc4ccccc4S(=O)(=O)C(C)C)n3)C2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2276" t="inlineStr"/>
+      <c r="H2276" t="inlineStr"/>
+      <c r="I2276" t="n">
+        <v>0.8850016273577715</v>
+      </c>
+      <c r="J2276" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2276" t="inlineStr"/>
+    </row>
+    <row r="2277">
+      <c r="A2277" s="1" t="n">
+        <v>2275</v>
+      </c>
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0684.png</t>
+        </is>
+      </c>
+      <c r="C2277" t="inlineStr"/>
+      <c r="D2277" t="inlineStr"/>
+      <c r="E2277" t="inlineStr"/>
+      <c r="F2277" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)NCC(=O)Nc2nc(-c3cccc(-c4cccc(CNC(=O)CCCCCCOc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)c4)c3)co2)c1</t>
+        </is>
+      </c>
+      <c r="G2277" t="inlineStr"/>
+      <c r="H2277" t="inlineStr"/>
+      <c r="I2277" t="n">
+        <v>0.9032794648596959</v>
+      </c>
+      <c r="J2277" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2277" t="inlineStr"/>
+    </row>
+    <row r="2278">
+      <c r="A2278" s="1" t="n">
+        <v>2276</v>
+      </c>
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0688.png</t>
+        </is>
+      </c>
+      <c r="C2278" t="inlineStr"/>
+      <c r="D2278" t="inlineStr"/>
+      <c r="E2278" t="inlineStr"/>
+      <c r="F2278" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCCCCCCCC(=O)N[C@H](C(=O)N3C[C@H](O)C[C@H]3C(=O)NCc3ccc(-c4scnc4C)cc3)C(C)(C)C)c2)cc1/C=C/C1CCCCC1</t>
+        </is>
+      </c>
+      <c r="G2278" t="inlineStr"/>
+      <c r="H2278" t="inlineStr"/>
+      <c r="I2278" t="n">
+        <v>0.88731110406892</v>
+      </c>
+      <c r="J2278" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2278" t="inlineStr"/>
+    </row>
+    <row r="2279">
+      <c r="A2279" s="1" t="n">
+        <v>2277</v>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0692.png</t>
+        </is>
+      </c>
+      <c r="C2279" t="inlineStr"/>
+      <c r="D2279" t="inlineStr"/>
+      <c r="E2279" t="inlineStr"/>
+      <c r="F2279" t="inlineStr">
+        <is>
+          <t>C=C(F)C(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCCCCCCN4CC=C(c5cc(F)cc6c5CN(C5CCC(=O)NC5=O)C6=O)CC4)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G2279" t="inlineStr"/>
+      <c r="H2279" t="inlineStr"/>
+      <c r="I2279" t="n">
+        <v>0.899606258227715</v>
+      </c>
+      <c r="J2279" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2279" t="inlineStr"/>
+    </row>
+    <row r="2280">
+      <c r="A2280" s="1" t="n">
+        <v>2278</v>
+      </c>
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0696.png</t>
+        </is>
+      </c>
+      <c r="C2280" t="inlineStr"/>
+      <c r="D2280" t="inlineStr"/>
+      <c r="E2280" t="inlineStr"/>
+      <c r="F2280" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CCN(C5CCN(C(=O)c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)CC4)nc3cc2OC)n1.[I-17] |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2280" t="inlineStr"/>
+      <c r="H2280" t="inlineStr"/>
+      <c r="I2280" t="n">
+        <v>0.8691031631289787</v>
+      </c>
+      <c r="J2280" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2280" t="inlineStr"/>
+    </row>
+    <row r="2281">
+      <c r="A2281" s="1" t="n">
+        <v>2279</v>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0704.png</t>
+        </is>
+      </c>
+      <c r="C2281" t="inlineStr"/>
+      <c r="D2281" t="inlineStr"/>
+      <c r="E2281" t="inlineStr"/>
+      <c r="F2281" t="inlineStr">
+        <is>
+          <t>COc1cc2nn(C3CC4(CCN(C(=O)C5CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)CC4)C3)cc2cc1NC(=O)c1cccc(C)n1</t>
+        </is>
+      </c>
+      <c r="G2281" t="inlineStr"/>
+      <c r="H2281" t="inlineStr"/>
+      <c r="I2281" t="n">
+        <v>0.8949182724697828</v>
+      </c>
+      <c r="J2281" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2281" t="inlineStr"/>
+    </row>
+    <row r="2282">
+      <c r="A2282" s="1" t="n">
+        <v>2280</v>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0708.png</t>
+        </is>
+      </c>
+      <c r="C2282" t="inlineStr"/>
+      <c r="D2282" t="inlineStr"/>
+      <c r="E2282" t="inlineStr"/>
+      <c r="F2282" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)N(C)CCCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)c2)cc1CCC1CCCCC1</t>
+        </is>
+      </c>
+      <c r="G2282" t="inlineStr"/>
+      <c r="H2282" t="inlineStr"/>
+      <c r="I2282" t="n">
+        <v>0.9155642590797736</v>
+      </c>
+      <c r="J2282" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2282" t="inlineStr"/>
+    </row>
+    <row r="2283">
+      <c r="A2283" s="1" t="n">
+        <v>2281</v>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0712.png</t>
+        </is>
+      </c>
+      <c r="C2283" t="inlineStr"/>
+      <c r="D2283" t="inlineStr"/>
+      <c r="E2283" t="inlineStr"/>
+      <c r="F2283" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCCCCCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)c2)cc1CC[C@@H]1CC[C@@H](C(F)(F)F)CC1</t>
+        </is>
+      </c>
+      <c r="G2283" t="inlineStr"/>
+      <c r="H2283" t="inlineStr"/>
+      <c r="I2283" t="n">
+        <v>0.8948262872422947</v>
+      </c>
+      <c r="J2283" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2283" t="inlineStr"/>
+    </row>
+    <row r="2284">
+      <c r="A2284" s="1" t="n">
+        <v>2282</v>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0720.png</t>
+        </is>
+      </c>
+      <c r="C2284" t="inlineStr"/>
+      <c r="D2284" t="inlineStr"/>
+      <c r="E2284" t="inlineStr"/>
+      <c r="F2284" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CCN(c2nc(OCCCCCCCN3CCC(c4cc(F)cc5c4CN(C4CCC(=O)NC4=O)C5=O)CC3)nc3c2CCN(c2cc(O)cc4ccccc24)C3)CC1</t>
+        </is>
+      </c>
+      <c r="G2284" t="inlineStr"/>
+      <c r="H2284" t="inlineStr"/>
+      <c r="I2284" t="n">
+        <v>0.8807255866415322</v>
+      </c>
+      <c r="J2284" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2284" t="inlineStr"/>
+    </row>
+    <row r="2285">
+      <c r="A2285" s="1" t="n">
+        <v>2283</v>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0728.png</t>
+        </is>
+      </c>
+      <c r="C2285" t="inlineStr"/>
+      <c r="D2285" t="inlineStr"/>
+      <c r="E2285" t="inlineStr"/>
+      <c r="F2285" t="inlineStr">
+        <is>
+          <t>O=C1CC[C@H](N2Cc3cc(N4CCN(CCC5CCN(c6ccc(C7=C(c8ccccc8)CCCc8cc(O)ccc87)cc6)CC5)CC4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2285" t="inlineStr"/>
+      <c r="H2285" t="inlineStr"/>
+      <c r="I2285" t="n">
+        <v>0.8619945775680758</v>
+      </c>
+      <c r="J2285" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2285" t="inlineStr"/>
+    </row>
+    <row r="2286">
+      <c r="A2286" s="1" t="n">
+        <v>2284</v>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0732.png</t>
+        </is>
+      </c>
+      <c r="C2286" t="inlineStr"/>
+      <c r="D2286" t="inlineStr"/>
+      <c r="E2286" t="inlineStr"/>
+      <c r="F2286" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3c(C#Cc4cncn4CCCNC(=O)c4ccc(NC(=O)[C@@H]5NC6(CCCCC6)[C@@]6(C(=O)Nc7cc(Cl)ccc76)[C@H]5c5cccc(Cl)c5F)cc4)cccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2286" t="inlineStr"/>
+      <c r="H2286" t="inlineStr"/>
+      <c r="I2286" t="n">
+        <v>0.8788689633302146</v>
+      </c>
+      <c r="J2286" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2286" t="inlineStr"/>
+    </row>
+    <row r="2287">
+      <c r="A2287" s="1" t="n">
+        <v>2285</v>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0736.png</t>
+        </is>
+      </c>
+      <c r="C2287" t="inlineStr"/>
+      <c r="D2287" t="inlineStr"/>
+      <c r="E2287" t="inlineStr"/>
+      <c r="F2287" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(C(=O)C6CCN(c7cc8c(cc7F)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2OC)n1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2287" t="inlineStr"/>
+      <c r="H2287" t="inlineStr"/>
+      <c r="I2287" t="n">
+        <v>0.8904066315914829</v>
+      </c>
+      <c r="J2287" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2287" t="inlineStr"/>
+    </row>
+    <row r="2288">
+      <c r="A2288" s="1" t="n">
+        <v>2286</v>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0748.png</t>
+        </is>
+      </c>
+      <c r="C2288" t="inlineStr"/>
+      <c r="D2288" t="inlineStr"/>
+      <c r="E2288" t="inlineStr"/>
+      <c r="F2288" t="inlineStr">
+        <is>
+          <t>CC(C)=C/C(Cl)=C(\O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCCCCCCN4CCC(c5cc(F)cc6c5CN(C5CCC(=O)NC5=O)C6=O)CC4)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G2288" t="inlineStr"/>
+      <c r="H2288" t="inlineStr"/>
+      <c r="I2288" t="n">
+        <v>0.900438444434281</v>
+      </c>
+      <c r="J2288" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2288" t="inlineStr"/>
+    </row>
+    <row r="2289">
+      <c r="A2289" s="1" t="n">
+        <v>2287</v>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0756.png</t>
+        </is>
+      </c>
+      <c r="C2289" t="inlineStr"/>
+      <c r="D2289" t="inlineStr"/>
+      <c r="E2289" t="inlineStr"/>
+      <c r="F2289" t="inlineStr">
+        <is>
+          <t>CCC(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCCCCCCCCN4CCC(c5cc(F)cc6c5CN(C5CCC(=O)NC5=O)C6=O)CC4)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G2289" t="inlineStr"/>
+      <c r="H2289" t="inlineStr"/>
+      <c r="I2289" t="n">
+        <v>0.9046471458075089</v>
+      </c>
+      <c r="J2289" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2289" t="inlineStr"/>
+    </row>
+    <row r="2290">
+      <c r="A2290" s="1" t="n">
+        <v>2288</v>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0772.png</t>
+        </is>
+      </c>
+      <c r="C2290" t="inlineStr"/>
+      <c r="D2290" t="inlineStr"/>
+      <c r="E2290" t="inlineStr"/>
+      <c r="F2290" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(C(=O)C6(F)CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2OC)n1.[I-34] |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2290" t="inlineStr"/>
+      <c r="H2290" t="inlineStr"/>
+      <c r="I2290" t="n">
+        <v>0.8441811118689947</v>
+      </c>
+      <c r="J2290" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2290" t="inlineStr"/>
+    </row>
+    <row r="2291">
+      <c r="A2291" s="1" t="n">
+        <v>2289</v>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0776.png</t>
+        </is>
+      </c>
+      <c r="C2291" t="inlineStr"/>
+      <c r="D2291" t="inlineStr"/>
+      <c r="E2291" t="inlineStr"/>
+      <c r="F2291" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(C[C@@H]4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)CC3)CC2)c(C)cc1Nc1ncc(Br)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2291" t="inlineStr"/>
+      <c r="H2291" t="inlineStr"/>
+      <c r="I2291" t="n">
+        <v>0.8874417627172276</v>
+      </c>
+      <c r="J2291" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2291" t="inlineStr"/>
+    </row>
+    <row r="2292">
+      <c r="A2292" s="1" t="n">
+        <v>2290</v>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0780.png</t>
+        </is>
+      </c>
+      <c r="C2292" t="inlineStr"/>
+      <c r="D2292" t="inlineStr"/>
+      <c r="E2292" t="inlineStr"/>
+      <c r="F2292" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CC(N2Cc3ccc(-c4cc(O)cc5ccccc45)cc3N(CCOCCC(=O)NCCOc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)C2=O)C1</t>
+        </is>
+      </c>
+      <c r="G2292" t="inlineStr"/>
+      <c r="H2292" t="inlineStr"/>
+      <c r="I2292" t="n">
+        <v>0.8731218940806282</v>
+      </c>
+      <c r="J2292" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2292" t="inlineStr"/>
+    </row>
+    <row r="2293">
+      <c r="A2293" s="1" t="n">
+        <v>2291</v>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0792.png</t>
+        </is>
+      </c>
+      <c r="C2293" t="inlineStr"/>
+      <c r="D2293" t="inlineStr"/>
+      <c r="E2293" t="inlineStr"/>
+      <c r="F2293" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)N1CCc2cccc(Nc3nc(Nc4ccc(N5CCC(N6CCN(CCOc7cccc8c7CN(C7CCC(=O)NC7=O)C8=O)CC6)CC5)c(F)c4)nc4[nH]ccc34)c21</t>
+        </is>
+      </c>
+      <c r="G2293" t="inlineStr"/>
+      <c r="H2293" t="inlineStr"/>
+      <c r="I2293" t="n">
+        <v>0.8891145582804182</v>
+      </c>
+      <c r="J2293" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2293" t="inlineStr"/>
+    </row>
+    <row r="2294">
+      <c r="A2294" s="1" t="n">
+        <v>2292</v>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0800.png</t>
+        </is>
+      </c>
+      <c r="C2294" t="inlineStr"/>
+      <c r="D2294" t="inlineStr"/>
+      <c r="E2294" t="inlineStr"/>
+      <c r="F2294" t="inlineStr">
+        <is>
+          <t>COc1cc2nn(C3CC4(CCN(C(=O)C5CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)CC4)C3)cc2cc1NC(=O)c1cccc(C(F)F)n1</t>
+        </is>
+      </c>
+      <c r="G2294" t="inlineStr"/>
+      <c r="H2294" t="inlineStr"/>
+      <c r="I2294" t="n">
+        <v>0.905644179806087</v>
+      </c>
+      <c r="J2294" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2294" t="inlineStr"/>
+    </row>
+    <row r="2295">
+      <c r="A2295" s="1" t="n">
+        <v>2293</v>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0804.png</t>
+        </is>
+      </c>
+      <c r="C2295" t="inlineStr"/>
+      <c r="D2295" t="inlineStr"/>
+      <c r="E2295" t="inlineStr"/>
+      <c r="F2295" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)NCC(=O)Nc2nc(-c3cccc(-c4ccnc(C5(C(=O)NCCNc6cccc7c6CN(C6CCC(=O)NC6=O)C7=O)CC5)c4)c3)cs2)c1</t>
+        </is>
+      </c>
+      <c r="G2295" t="inlineStr"/>
+      <c r="H2295" t="inlineStr"/>
+      <c r="I2295" t="n">
+        <v>0.8858315055395133</v>
+      </c>
+      <c r="J2295" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2295" t="inlineStr"/>
+    </row>
+    <row r="2296">
+      <c r="A2296" s="1" t="n">
+        <v>2294</v>
+      </c>
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0808.png</t>
+        </is>
+      </c>
+      <c r="C2296" t="inlineStr"/>
+      <c r="D2296" t="inlineStr"/>
+      <c r="E2296" t="inlineStr"/>
+      <c r="F2296" t="inlineStr">
+        <is>
+          <t>CN(CCC1CCN(c2ccc3c(c2)C(=O)N(C2CCC(=O)NC2=O)C3=O)CC1)C1CCN(c2ccc(Nc3ncc(Cl)c(Nc4cccc5c4N(S(C)(=O)=O)CC5)n3)c3c2CCO3)CC1</t>
+        </is>
+      </c>
+      <c r="G2296" t="inlineStr"/>
+      <c r="H2296" t="inlineStr"/>
+      <c r="I2296" t="n">
+        <v>0.89672425103116</v>
+      </c>
+      <c r="J2296" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2296" t="inlineStr"/>
+    </row>
+    <row r="2297">
+      <c r="A2297" s="1" t="n">
+        <v>2295</v>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0812.png</t>
+        </is>
+      </c>
+      <c r="C2297" t="inlineStr"/>
+      <c r="D2297" t="inlineStr"/>
+      <c r="E2297" t="inlineStr"/>
+      <c r="F2297" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(CC4CCN(c5ccc6c(c5)CN(C5CCC(=O)NC5=O)C6=O)CC4)CC3)CC2)c(C)cc1Nc1ncc(Br)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2297" t="inlineStr"/>
+      <c r="H2297" t="inlineStr"/>
+      <c r="I2297" t="n">
+        <v>0.9110121740754371</v>
+      </c>
+      <c r="J2297" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2297" t="inlineStr"/>
+    </row>
+    <row r="2298">
+      <c r="A2298" s="1" t="n">
+        <v>2296</v>
+      </c>
+      <c r="B2298" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0816.png</t>
+        </is>
+      </c>
+      <c r="C2298" t="inlineStr"/>
+      <c r="D2298" t="inlineStr"/>
+      <c r="E2298" t="inlineStr"/>
+      <c r="F2298" t="inlineStr">
+        <is>
+          <t>O=C1CC[C@H](N2Cc3cc(N4CCN(CC5CCN(c6ccc(C7=C(c8ccc(O)cc8)CCCc8cc(O)ccc87)cc6)CC5)CC4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2298" t="inlineStr"/>
+      <c r="H2298" t="inlineStr"/>
+      <c r="I2298" t="n">
+        <v>0.8931317846933091</v>
+      </c>
+      <c r="J2298" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2298" t="inlineStr"/>
+    </row>
+    <row r="2299">
+      <c r="A2299" s="1" t="n">
+        <v>2297</v>
+      </c>
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0820.png</t>
+        </is>
+      </c>
+      <c r="C2299" t="inlineStr"/>
+      <c r="D2299" t="inlineStr"/>
+      <c r="E2299" t="inlineStr"/>
+      <c r="F2299" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)N(C)CCOCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)c2)cc1C=C[C@@H]1CC[C@@H](C(F)(F)F)CC1</t>
+        </is>
+      </c>
+      <c r="G2299" t="inlineStr"/>
+      <c r="H2299" t="inlineStr"/>
+      <c r="I2299" t="n">
+        <v>0.9024408739004977</v>
+      </c>
+      <c r="J2299" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2299" t="inlineStr"/>
+    </row>
+    <row r="2300">
+      <c r="A2300" s="1" t="n">
+        <v>2298</v>
+      </c>
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0824.png</t>
+        </is>
+      </c>
+      <c r="C2300" t="inlineStr"/>
+      <c r="D2300" t="inlineStr"/>
+      <c r="E2300" t="inlineStr"/>
+      <c r="F2300" t="inlineStr">
+        <is>
+          <t>O=C1CC[C@H](N2Cc3cc(N4CCN(CC5CCN(c6ccc(C7=C(c8ccc(C9CC9)nc8)CCCc8cc(O)ccc87)cc6)CC5)CC4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2300" t="inlineStr"/>
+      <c r="H2300" t="inlineStr"/>
+      <c r="I2300" t="n">
+        <v>0.8890874847751512</v>
+      </c>
+      <c r="J2300" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2300" t="inlineStr"/>
+    </row>
+    <row r="2301">
+      <c r="A2301" s="1" t="n">
+        <v>2299</v>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0828.png</t>
+        </is>
+      </c>
+      <c r="C2301" t="inlineStr"/>
+      <c r="D2301" t="inlineStr"/>
+      <c r="E2301" t="inlineStr"/>
+      <c r="F2301" t="inlineStr">
+        <is>
+          <t>COc1cc(C(=O)NCCCCCc2cccc3c2CN(C2CCC(=O)NC2=O)C3=O)ccc1NC(=O)[C@@H]1N[C@@H](CC(C)(C)C)[C@](C#N)(c2ccc(Cl)cc2F)[C@H]1c1cccc(Cl)c1F</t>
+        </is>
+      </c>
+      <c r="G2301" t="inlineStr"/>
+      <c r="H2301" t="inlineStr"/>
+      <c r="I2301" t="n">
+        <v>0.887345842110477</v>
+      </c>
+      <c r="J2301" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2301" t="inlineStr"/>
+    </row>
+    <row r="2302">
+      <c r="A2302" s="1" t="n">
+        <v>2300</v>
+      </c>
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0840.png</t>
+        </is>
+      </c>
+      <c r="C2302" t="inlineStr"/>
+      <c r="D2302" t="inlineStr"/>
+      <c r="E2302" t="inlineStr"/>
+      <c r="F2302" t="inlineStr">
+        <is>
+          <t>O=C1CC[C@H](N2Cc3cc(N4CCN(CC5CCN(c6ccc(C7=C(c8ccc(OC(F)(F)F)cc8)CCCc8cc(O)ccc87)cc6)CC5)CC4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2302" t="inlineStr"/>
+      <c r="H2302" t="inlineStr"/>
+      <c r="I2302" t="n">
+        <v>0.869094610684758</v>
+      </c>
+      <c r="J2302" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2302" t="inlineStr"/>
+    </row>
+    <row r="2303">
+      <c r="A2303" s="1" t="n">
+        <v>2301</v>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0844.png</t>
+        </is>
+      </c>
+      <c r="C2303" t="inlineStr"/>
+      <c r="D2303" t="inlineStr"/>
+      <c r="E2303" t="inlineStr"/>
+      <c r="F2303" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3cc(N4CCN(CC5CCN(c6ccc(C7=C(c8ccccc8)CCCc8cc(O)ccc87)cc6)CC5)CC4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2303" t="inlineStr"/>
+      <c r="H2303" t="inlineStr"/>
+      <c r="I2303" t="n">
+        <v>0.896039843653586</v>
+      </c>
+      <c r="J2303" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2303" t="inlineStr"/>
+    </row>
+    <row r="2304">
+      <c r="A2304" s="1" t="n">
+        <v>2302</v>
+      </c>
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0848.png</t>
+        </is>
+      </c>
+      <c r="C2304" t="inlineStr"/>
+      <c r="D2304" t="inlineStr"/>
+      <c r="E2304" t="inlineStr"/>
+      <c r="F2304" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(C(=O)C6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2C(C)(C)O)n1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2304" t="inlineStr"/>
+      <c r="H2304" t="inlineStr"/>
+      <c r="I2304" t="n">
+        <v>0.8870646718504634</v>
+      </c>
+      <c r="J2304" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2304" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_HighConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_HighConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2304"/>
+  <dimension ref="A1:K2476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67267,6 +67267,4994 @@
       </c>
       <c r="K2304" t="inlineStr"/>
     </row>
+    <row r="2305">
+      <c r="A2305" s="1" t="n">
+        <v>2303</v>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0851.png</t>
+        </is>
+      </c>
+      <c r="C2305" t="inlineStr"/>
+      <c r="D2305" t="inlineStr"/>
+      <c r="E2305" t="inlineStr"/>
+      <c r="F2305" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4cnn(C5CN(CC6CCN(c7ccc8c(c7)C(=O)N([C@@H]7CCC(=O)NC7=O)C8=O)CC6)C5)c4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2305" t="inlineStr"/>
+      <c r="H2305" t="inlineStr"/>
+      <c r="I2305" t="n">
+        <v>0.8800156568610107</v>
+      </c>
+      <c r="J2305" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2305" t="inlineStr"/>
+    </row>
+    <row r="2306">
+      <c r="A2306" s="1" t="n">
+        <v>2304</v>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0859.png</t>
+        </is>
+      </c>
+      <c r="C2306" t="inlineStr"/>
+      <c r="D2306" t="inlineStr"/>
+      <c r="E2306" t="inlineStr"/>
+      <c r="F2306" t="inlineStr">
+        <is>
+          <t>O=C1CC[C@H](N2Cc3cc(N4CCN(CC5CCN(c6ccc(C7=C(c8ccc(Cl)cc8)CCCc8cc(O)ccc87)cc6)CC5)CC4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2306" t="inlineStr"/>
+      <c r="H2306" t="inlineStr"/>
+      <c r="I2306" t="n">
+        <v>0.8812739933204735</v>
+      </c>
+      <c r="J2306" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2306" t="inlineStr"/>
+    </row>
+    <row r="2307">
+      <c r="A2307" s="1" t="n">
+        <v>2305</v>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0863.png</t>
+        </is>
+      </c>
+      <c r="C2307" t="inlineStr"/>
+      <c r="D2307" t="inlineStr"/>
+      <c r="E2307" t="inlineStr"/>
+      <c r="F2307" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CCN(C(=O)COc6cccc7c6C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2307" t="inlineStr"/>
+      <c r="H2307" t="inlineStr"/>
+      <c r="I2307" t="n">
+        <v>0.8785078409109671</v>
+      </c>
+      <c r="J2307" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2307" t="inlineStr"/>
+    </row>
+    <row r="2308">
+      <c r="A2308" s="1" t="n">
+        <v>2306</v>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0867.png</t>
+        </is>
+      </c>
+      <c r="C2308" t="inlineStr"/>
+      <c r="D2308" t="inlineStr"/>
+      <c r="E2308" t="inlineStr"/>
+      <c r="F2308" t="inlineStr">
+        <is>
+          <t>CC1=C(c2ccc(CNC(=O)[C@@H]3C[C@@H](O)CN3C(=O)[C@@H](NC(=O)C3CC4(C3)CC(N3CCC(c5cnc(N6CCN(c7cc(-c8ccccc8O)nnc7N)CC6)nc5)CC3)C4)C(C)(C)C)cc2)SCN1</t>
+        </is>
+      </c>
+      <c r="G2308" t="inlineStr"/>
+      <c r="H2308" t="inlineStr"/>
+      <c r="I2308" t="n">
+        <v>0.8873208379024267</v>
+      </c>
+      <c r="J2308" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2308" t="inlineStr"/>
+    </row>
+    <row r="2309">
+      <c r="A2309" s="1" t="n">
+        <v>2307</v>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0871.png</t>
+        </is>
+      </c>
+      <c r="C2309" t="inlineStr"/>
+      <c r="D2309" t="inlineStr"/>
+      <c r="E2309" t="inlineStr"/>
+      <c r="F2309" t="inlineStr">
+        <is>
+          <t>COc1ccc2nc(-c3ccc(N4CC(OC5CCN(CCCCCOc6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)C4)cc3)sc2c1</t>
+        </is>
+      </c>
+      <c r="G2309" t="inlineStr"/>
+      <c r="H2309" t="inlineStr"/>
+      <c r="I2309" t="n">
+        <v>0.9084058266094072</v>
+      </c>
+      <c r="J2309" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2309" t="inlineStr"/>
+    </row>
+    <row r="2310">
+      <c r="A2310" s="1" t="n">
+        <v>2308</v>
+      </c>
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0875.png</t>
+        </is>
+      </c>
+      <c r="C2310" t="inlineStr"/>
+      <c r="D2310" t="inlineStr"/>
+      <c r="E2310" t="inlineStr"/>
+      <c r="F2310" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CCN(C[C@@H]6CC[C@@H](Nc7cccc8c7C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2310" t="inlineStr"/>
+      <c r="H2310" t="inlineStr"/>
+      <c r="I2310" t="n">
+        <v>0.8886077051616573</v>
+      </c>
+      <c r="J2310" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2310" t="inlineStr"/>
+    </row>
+    <row r="2311">
+      <c r="A2311" s="1" t="n">
+        <v>2309</v>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0879.png</t>
+        </is>
+      </c>
+      <c r="C2311" t="inlineStr"/>
+      <c r="D2311" t="inlineStr"/>
+      <c r="E2311" t="inlineStr"/>
+      <c r="F2311" t="inlineStr">
+        <is>
+          <t>Cc1cc(Nc2nc(N3CCC[C@@H](NC(=O)C4CCN(CC5CN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)C5)C4)C3)cnc2C(N)=O)sn1</t>
+        </is>
+      </c>
+      <c r="G2311" t="inlineStr"/>
+      <c r="H2311" t="inlineStr"/>
+      <c r="I2311" t="n">
+        <v>0.9016903762824725</v>
+      </c>
+      <c r="J2311" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2311" t="inlineStr"/>
+    </row>
+    <row r="2312">
+      <c r="A2312" s="1" t="n">
+        <v>2310</v>
+      </c>
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0883.png</t>
+        </is>
+      </c>
+      <c r="C2312" t="inlineStr"/>
+      <c r="D2312" t="inlineStr"/>
+      <c r="E2312" t="inlineStr"/>
+      <c r="F2312" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc5c(c4)CCN(C4CN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)C4)C5)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2312" t="inlineStr"/>
+      <c r="H2312" t="inlineStr"/>
+      <c r="I2312" t="n">
+        <v>0.8874295450945325</v>
+      </c>
+      <c r="J2312" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2312" t="inlineStr"/>
+    </row>
+    <row r="2313">
+      <c r="A2313" s="1" t="n">
+        <v>2311</v>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0887.png</t>
+        </is>
+      </c>
+      <c r="C2313" t="inlineStr"/>
+      <c r="D2313" t="inlineStr"/>
+      <c r="E2313" t="inlineStr"/>
+      <c r="F2313" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccc(N2C(=O)C(C)(C)N(c3cnc(-c4ccc(OCCNC(=O)COc5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)c(F)c4)c(F)c3)C2=S)c(F)c1OC</t>
+        </is>
+      </c>
+      <c r="G2313" t="inlineStr"/>
+      <c r="H2313" t="inlineStr"/>
+      <c r="I2313" t="n">
+        <v>0.8768074418836347</v>
+      </c>
+      <c r="J2313" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2313" t="inlineStr"/>
+    </row>
+    <row r="2314">
+      <c r="A2314" s="1" t="n">
+        <v>2312</v>
+      </c>
+      <c r="B2314" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0891.png</t>
+        </is>
+      </c>
+      <c r="C2314" t="inlineStr"/>
+      <c r="D2314" t="inlineStr"/>
+      <c r="E2314" t="inlineStr"/>
+      <c r="F2314" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(CC4CN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)CC3)CC2)ccc1Nc1ncc(Cl)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2314" t="inlineStr"/>
+      <c r="H2314" t="inlineStr"/>
+      <c r="I2314" t="n">
+        <v>0.8750030197913823</v>
+      </c>
+      <c r="J2314" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2314" t="inlineStr"/>
+    </row>
+    <row r="2315">
+      <c r="A2315" s="1" t="n">
+        <v>2313</v>
+      </c>
+      <c r="B2315" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0895.png</t>
+        </is>
+      </c>
+      <c r="C2315" t="inlineStr"/>
+      <c r="D2315" t="inlineStr"/>
+      <c r="E2315" t="inlineStr"/>
+      <c r="F2315" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(CC6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2OC)n1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2315" t="inlineStr"/>
+      <c r="H2315" t="inlineStr"/>
+      <c r="I2315" t="n">
+        <v>0.8856570532664731</v>
+      </c>
+      <c r="J2315" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2315" t="inlineStr"/>
+    </row>
+    <row r="2316">
+      <c r="A2316" s="1" t="n">
+        <v>2314</v>
+      </c>
+      <c r="B2316" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0903.png</t>
+        </is>
+      </c>
+      <c r="C2316" t="inlineStr"/>
+      <c r="D2316" t="inlineStr"/>
+      <c r="E2316" t="inlineStr"/>
+      <c r="F2316" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](c2cc(OCCCCN3CCC(c4cnc(N5C6CCC5CN(c5cc(-c7ccccc7O)nnc5N)C6)nc4)CC3)no2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2316" t="inlineStr"/>
+      <c r="H2316" t="inlineStr"/>
+      <c r="I2316" t="n">
+        <v>0.8650565642397587</v>
+      </c>
+      <c r="J2316" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2316" t="inlineStr"/>
+    </row>
+    <row r="2317">
+      <c r="A2317" s="1" t="n">
+        <v>2315</v>
+      </c>
+      <c r="B2317" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0911.png</t>
+        </is>
+      </c>
+      <c r="C2317" t="inlineStr"/>
+      <c r="D2317" t="inlineStr"/>
+      <c r="E2317" t="inlineStr"/>
+      <c r="F2317" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)COCCOCCOc2ccc(CN3C(=O)/C(=C\C=C\c4ccc([N+](=O)[O-])cc4)c4ccccc43)cc2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2317" t="inlineStr"/>
+      <c r="H2317" t="inlineStr"/>
+      <c r="I2317" t="n">
+        <v>0.8606746502942264</v>
+      </c>
+      <c r="J2317" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2317" t="inlineStr"/>
+    </row>
+    <row r="2318">
+      <c r="A2318" s="1" t="n">
+        <v>2316</v>
+      </c>
+      <c r="B2318" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0915.png</t>
+        </is>
+      </c>
+      <c r="C2318" t="inlineStr"/>
+      <c r="D2318" t="inlineStr"/>
+      <c r="E2318" t="inlineStr"/>
+      <c r="F2318" t="inlineStr">
+        <is>
+          <t>COc1cc(C2=CN(C)C(=O)N(C)C2)cc(OC)c1CN1CCC(CCN2CCN(c3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4)CC2)CC1</t>
+        </is>
+      </c>
+      <c r="G2318" t="inlineStr"/>
+      <c r="H2318" t="inlineStr"/>
+      <c r="I2318" t="n">
+        <v>0.9112066353553926</v>
+      </c>
+      <c r="J2318" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2318" t="inlineStr"/>
+    </row>
+    <row r="2319">
+      <c r="A2319" s="1" t="n">
+        <v>2317</v>
+      </c>
+      <c r="B2319" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0919.png</t>
+        </is>
+      </c>
+      <c r="C2319" t="inlineStr"/>
+      <c r="D2319" t="inlineStr"/>
+      <c r="E2319" t="inlineStr"/>
+      <c r="F2319" t="inlineStr">
+        <is>
+          <t>CCCCC(Cc1c[nH]c2ccccc12)NC(=O)c1cnc(N2CCN(CCOCCOCCOCC(=O)N[C@H](C(=O)N3C[C@H](O)C[C@H]3C(=O)N[C@@H](C)c3ccc(-c4scnc4C)cc3)C(C)(C)C)CC2)s1</t>
+        </is>
+      </c>
+      <c r="G2319" t="inlineStr"/>
+      <c r="H2319" t="inlineStr"/>
+      <c r="I2319" t="n">
+        <v>0.893431202373961</v>
+      </c>
+      <c r="J2319" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2319" t="inlineStr"/>
+    </row>
+    <row r="2320">
+      <c r="A2320" s="1" t="n">
+        <v>2318</v>
+      </c>
+      <c r="B2320" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0927.png</t>
+        </is>
+      </c>
+      <c r="C2320" t="inlineStr"/>
+      <c r="D2320" t="inlineStr"/>
+      <c r="E2320" t="inlineStr"/>
+      <c r="F2320" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)c2)cc1CC[C@@H]1CC[C@@H](C(F)(F)F)CC1</t>
+        </is>
+      </c>
+      <c r="G2320" t="inlineStr"/>
+      <c r="H2320" t="inlineStr"/>
+      <c r="I2320" t="n">
+        <v>0.9105292292008618</v>
+      </c>
+      <c r="J2320" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2320" t="inlineStr"/>
+    </row>
+    <row r="2321">
+      <c r="A2321" s="1" t="n">
+        <v>2319</v>
+      </c>
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0935.png</t>
+        </is>
+      </c>
+      <c r="C2321" t="inlineStr"/>
+      <c r="D2321" t="inlineStr"/>
+      <c r="E2321" t="inlineStr"/>
+      <c r="F2321" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(N5CCC6(CC5)CCN(c5ccc7c(c5)C(=O)N(C5CCC(=O)NC5=O)C7=O)CC6)cn4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2321" t="inlineStr"/>
+      <c r="H2321" t="inlineStr"/>
+      <c r="I2321" t="n">
+        <v>0.8722602968581674</v>
+      </c>
+      <c r="J2321" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2321" t="inlineStr"/>
+    </row>
+    <row r="2322">
+      <c r="A2322" s="1" t="n">
+        <v>2320</v>
+      </c>
+      <c r="B2322" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0939.png</t>
+        </is>
+      </c>
+      <c r="C2322" t="inlineStr"/>
+      <c r="D2322" t="inlineStr"/>
+      <c r="E2322" t="inlineStr"/>
+      <c r="F2322" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)COCCOCCOCCOCCOCCOCCOc2ccc3c(c2)Sc2cc(C(F)(F)F)ccc2N3)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2322" t="inlineStr"/>
+      <c r="H2322" t="inlineStr"/>
+      <c r="I2322" t="n">
+        <v>0.8465199819834056</v>
+      </c>
+      <c r="J2322" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2322" t="inlineStr"/>
+    </row>
+    <row r="2323">
+      <c r="A2323" s="1" t="n">
+        <v>2321</v>
+      </c>
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0943.png</t>
+        </is>
+      </c>
+      <c r="C2323" t="inlineStr"/>
+      <c r="D2323" t="inlineStr"/>
+      <c r="E2323" t="inlineStr"/>
+      <c r="F2323" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(OCCCNC(=O)[C@H]5C[C@@H](OCCCc6cccc7c6C(=O)N(C6CCC(=O)NC6=O)C7=O)C5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2323" t="inlineStr"/>
+      <c r="H2323" t="inlineStr"/>
+      <c r="I2323" t="n">
+        <v>0.8902821184403202</v>
+      </c>
+      <c r="J2323" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2323" t="inlineStr"/>
+    </row>
+    <row r="2324">
+      <c r="A2324" s="1" t="n">
+        <v>2322</v>
+      </c>
+      <c r="B2324" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0947.png</t>
+        </is>
+      </c>
+      <c r="C2324" t="inlineStr"/>
+      <c r="D2324" t="inlineStr"/>
+      <c r="E2324" t="inlineStr"/>
+      <c r="F2324" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)c1ccc(Nc2nc(N3CCC[C@@H](NC(=O)N4CC5(C4)CN(c4ccc6c(c4)C(=O)N(C4CCC(=O)NC4=O)C6=O)C5)C3)cnc2C(N)=O)cc1</t>
+        </is>
+      </c>
+      <c r="G2324" t="inlineStr"/>
+      <c r="H2324" t="inlineStr"/>
+      <c r="I2324" t="n">
+        <v>0.9118910282937324</v>
+      </c>
+      <c r="J2324" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2324" t="inlineStr"/>
+    </row>
+    <row r="2325">
+      <c r="A2325" s="1" t="n">
+        <v>2323</v>
+      </c>
+      <c r="B2325" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0967.png</t>
+        </is>
+      </c>
+      <c r="C2325" t="inlineStr"/>
+      <c r="D2325" t="inlineStr"/>
+      <c r="E2325" t="inlineStr"/>
+      <c r="F2325" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(CC4CN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)CC3)CC2)c(C)cc1Nc1ncc(Br)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2325" t="inlineStr"/>
+      <c r="H2325" t="inlineStr"/>
+      <c r="I2325" t="n">
+        <v>0.9078002182010143</v>
+      </c>
+      <c r="J2325" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2325" t="inlineStr"/>
+    </row>
+    <row r="2326">
+      <c r="A2326" s="1" t="n">
+        <v>2324</v>
+      </c>
+      <c r="B2326" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0975.png</t>
+        </is>
+      </c>
+      <c r="C2326" t="inlineStr"/>
+      <c r="D2326" t="inlineStr"/>
+      <c r="E2326" t="inlineStr"/>
+      <c r="F2326" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2CC=C(c3nccc(N4C5CCC4CN(c4cc(-c6ccccc6O)nnc4N)C5)n3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2326" t="inlineStr"/>
+      <c r="H2326" t="inlineStr"/>
+      <c r="I2326" t="n">
+        <v>0.8582888298737712</v>
+      </c>
+      <c r="J2326" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2326" t="inlineStr"/>
+    </row>
+    <row r="2327">
+      <c r="A2327" s="1" t="n">
+        <v>2325</v>
+      </c>
+      <c r="B2327" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0979.png</t>
+        </is>
+      </c>
+      <c r="C2327" t="inlineStr"/>
+      <c r="D2327" t="inlineStr"/>
+      <c r="E2327" t="inlineStr"/>
+      <c r="F2327" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CCN(C[C@@H]6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2327" t="inlineStr"/>
+      <c r="H2327" t="inlineStr"/>
+      <c r="I2327" t="n">
+        <v>0.8678510559489846</v>
+      </c>
+      <c r="J2327" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2327" t="inlineStr"/>
+    </row>
+    <row r="2328">
+      <c r="A2328" s="1" t="n">
+        <v>2326</v>
+      </c>
+      <c r="B2328" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0983.png</t>
+        </is>
+      </c>
+      <c r="C2328" t="inlineStr"/>
+      <c r="D2328" t="inlineStr"/>
+      <c r="E2328" t="inlineStr"/>
+      <c r="F2328" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(N5CCN(CCCCc6cccc7c6CN(C6CCC(=O)NC6=O)C7=O)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2328" t="inlineStr"/>
+      <c r="H2328" t="inlineStr"/>
+      <c r="I2328" t="n">
+        <v>0.8762545905943403</v>
+      </c>
+      <c r="J2328" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2328" t="inlineStr"/>
+    </row>
+    <row r="2329">
+      <c r="A2329" s="1" t="n">
+        <v>2327</v>
+      </c>
+      <c r="B2329" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0987.png</t>
+        </is>
+      </c>
+      <c r="C2329" t="inlineStr"/>
+      <c r="D2329" t="inlineStr"/>
+      <c r="E2329" t="inlineStr"/>
+      <c r="F2329" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5(C)CCN(C(=O)CCOCCC(=O)Nc6cccc7c6CN(C6CCC(=O)NC6=O)C7=O)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2329" t="inlineStr"/>
+      <c r="H2329" t="inlineStr"/>
+      <c r="I2329" t="n">
+        <v>0.860144964142862</v>
+      </c>
+      <c r="J2329" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2329" t="inlineStr"/>
+    </row>
+    <row r="2330">
+      <c r="A2330" s="1" t="n">
+        <v>2328</v>
+      </c>
+      <c r="B2330" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0991.png</t>
+        </is>
+      </c>
+      <c r="C2330" t="inlineStr"/>
+      <c r="D2330" t="inlineStr"/>
+      <c r="E2330" t="inlineStr"/>
+      <c r="F2330" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5(C)CCN(C(=O)CCCc6nnc(Nc7cccc8c7CN(C7CCC(=O)NC7=O)C8=O)o6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2330" t="inlineStr"/>
+      <c r="H2330" t="inlineStr"/>
+      <c r="I2330" t="n">
+        <v>0.8441361572236072</v>
+      </c>
+      <c r="J2330" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2330" t="inlineStr"/>
+    </row>
+    <row r="2331">
+      <c r="A2331" s="1" t="n">
+        <v>2329</v>
+      </c>
+      <c r="B2331" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0999.png</t>
+        </is>
+      </c>
+      <c r="C2331" t="inlineStr"/>
+      <c r="D2331" t="inlineStr"/>
+      <c r="E2331" t="inlineStr"/>
+      <c r="F2331" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CCN(C(=O)CCOCCOCCOCCNc6cccc7c6C(=O)N(C6=CCC(=O)NC6=O)C7=O)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2331" t="inlineStr"/>
+      <c r="H2331" t="inlineStr"/>
+      <c r="I2331" t="n">
+        <v>0.8998006594178317</v>
+      </c>
+      <c r="J2331" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2331" t="inlineStr"/>
+    </row>
+    <row r="2332">
+      <c r="A2332" s="1" t="n">
+        <v>2330</v>
+      </c>
+      <c r="B2332" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1003.png</t>
+        </is>
+      </c>
+      <c r="C2332" t="inlineStr"/>
+      <c r="D2332" t="inlineStr"/>
+      <c r="E2332" t="inlineStr"/>
+      <c r="F2332" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5(C)CCN(C6CN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2332" t="inlineStr"/>
+      <c r="H2332" t="inlineStr"/>
+      <c r="I2332" t="n">
+        <v>0.8651474991955674</v>
+      </c>
+      <c r="J2332" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2332" t="inlineStr"/>
+    </row>
+    <row r="2333">
+      <c r="A2333" s="1" t="n">
+        <v>2331</v>
+      </c>
+      <c r="B2333" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1007.png</t>
+        </is>
+      </c>
+      <c r="C2333" t="inlineStr"/>
+      <c r="D2333" t="inlineStr"/>
+      <c r="E2333" t="inlineStr"/>
+      <c r="F2333" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(N5CCCC6(CN(Cc7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)C5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2333" t="inlineStr"/>
+      <c r="H2333" t="inlineStr"/>
+      <c r="I2333" t="n">
+        <v>0.8944162014762213</v>
+      </c>
+      <c r="J2333" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2333" t="inlineStr"/>
+    </row>
+    <row r="2334">
+      <c r="A2334" s="1" t="n">
+        <v>2332</v>
+      </c>
+      <c r="B2334" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1011.png</t>
+        </is>
+      </c>
+      <c r="C2334" t="inlineStr"/>
+      <c r="D2334" t="inlineStr"/>
+      <c r="E2334" t="inlineStr"/>
+      <c r="F2334" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5(C)CCN(C(=O)CCOCCOCCOCCNc6cccc7c6C(=O)N(C6=CCC(=O)NC6=O)C7=O)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2334" t="inlineStr"/>
+      <c r="H2334" t="inlineStr"/>
+      <c r="I2334" t="n">
+        <v>0.8829813478069696</v>
+      </c>
+      <c r="J2334" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2334" t="inlineStr"/>
+    </row>
+    <row r="2335">
+      <c r="A2335" s="1" t="n">
+        <v>2333</v>
+      </c>
+      <c r="B2335" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1019.png</t>
+        </is>
+      </c>
+      <c r="C2335" t="inlineStr"/>
+      <c r="D2335" t="inlineStr"/>
+      <c r="E2335" t="inlineStr"/>
+      <c r="F2335" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(C(=O)C6CCN(c7cccc8c7C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2OC)n1.[I-55] |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2335" t="inlineStr"/>
+      <c r="H2335" t="inlineStr"/>
+      <c r="I2335" t="n">
+        <v>0.8902177405947107</v>
+      </c>
+      <c r="J2335" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2335" t="inlineStr"/>
+    </row>
+    <row r="2336">
+      <c r="A2336" s="1" t="n">
+        <v>2334</v>
+      </c>
+      <c r="B2336" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1027.png</t>
+        </is>
+      </c>
+      <c r="C2336" t="inlineStr"/>
+      <c r="D2336" t="inlineStr"/>
+      <c r="E2336" t="inlineStr"/>
+      <c r="F2336" t="inlineStr">
+        <is>
+          <t>Nc1ncnc2c1c(-c1ccc(Oc3ccccc3)cc1)nn2C1CCN(CCOCCOCCNc2ccc3c(c2)C(=O)N(C2CCC(=O)NC2=O)C3=O)CC1</t>
+        </is>
+      </c>
+      <c r="G2336" t="inlineStr"/>
+      <c r="H2336" t="inlineStr"/>
+      <c r="I2336" t="n">
+        <v>0.9007038207127008</v>
+      </c>
+      <c r="J2336" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2336" t="inlineStr"/>
+    </row>
+    <row r="2337">
+      <c r="A2337" s="1" t="n">
+        <v>2335</v>
+      </c>
+      <c r="B2337" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1031.png</t>
+        </is>
+      </c>
+      <c r="C2337" t="inlineStr"/>
+      <c r="D2337" t="inlineStr"/>
+      <c r="E2337" t="inlineStr"/>
+      <c r="F2337" t="inlineStr">
+        <is>
+          <t>C[C@@H]1C[C@@H](O)c2ncnc(N3CCN(C(=O)[C@H](CNCCCNC(=O)COc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)c4ccc(Cl)cc4)CC3)c21</t>
+        </is>
+      </c>
+      <c r="G2337" t="inlineStr"/>
+      <c r="H2337" t="inlineStr"/>
+      <c r="I2337" t="n">
+        <v>0.8983243425807873</v>
+      </c>
+      <c r="J2337" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2337" t="inlineStr"/>
+    </row>
+    <row r="2338">
+      <c r="A2338" s="1" t="n">
+        <v>2336</v>
+      </c>
+      <c r="B2338" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1035.png</t>
+        </is>
+      </c>
+      <c r="C2338" t="inlineStr"/>
+      <c r="D2338" t="inlineStr"/>
+      <c r="E2338" t="inlineStr"/>
+      <c r="F2338" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2CC3(CCN(Cc4cnc(N5C6CCC5CN(c5cc(-c7ccccc7O)nnc5N)C6)nc4)CC3)C2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2338" t="inlineStr"/>
+      <c r="H2338" t="inlineStr"/>
+      <c r="I2338" t="n">
+        <v>0.8798122103688564</v>
+      </c>
+      <c r="J2338" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2338" t="inlineStr"/>
+    </row>
+    <row r="2339">
+      <c r="A2339" s="1" t="n">
+        <v>2337</v>
+      </c>
+      <c r="B2339" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1039.png</t>
+        </is>
+      </c>
+      <c r="C2339" t="inlineStr"/>
+      <c r="D2339" t="inlineStr"/>
+      <c r="E2339" t="inlineStr"/>
+      <c r="F2339" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(C[C@H]4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)CC3)CC2)c(C)cc1Nc1ncc(Br)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2339" t="inlineStr"/>
+      <c r="H2339" t="inlineStr"/>
+      <c r="I2339" t="n">
+        <v>0.8984953266442945</v>
+      </c>
+      <c r="J2339" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2339" t="inlineStr"/>
+    </row>
+    <row r="2340">
+      <c r="A2340" s="1" t="n">
+        <v>2338</v>
+      </c>
+      <c r="B2340" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1043.png</t>
+        </is>
+      </c>
+      <c r="C2340" t="inlineStr"/>
+      <c r="D2340" t="inlineStr"/>
+      <c r="E2340" t="inlineStr"/>
+      <c r="F2340" t="inlineStr">
+        <is>
+          <t>Nc1ncnc2c1c(-c1ccc(Oc3ccccc3)cc1)nn2C1CCCN(CCOCCOCCOCCOCCNc2cccc3c2C(=O)N(C2CCC(=O)NC2=O)C3=O)C1</t>
+        </is>
+      </c>
+      <c r="G2340" t="inlineStr"/>
+      <c r="H2340" t="inlineStr"/>
+      <c r="I2340" t="n">
+        <v>0.8961317094874319</v>
+      </c>
+      <c r="J2340" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2340" t="inlineStr"/>
+    </row>
+    <row r="2341">
+      <c r="A2341" s="1" t="n">
+        <v>2339</v>
+      </c>
+      <c r="B2341" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1047.png</t>
+        </is>
+      </c>
+      <c r="C2341" t="inlineStr"/>
+      <c r="D2341" t="inlineStr"/>
+      <c r="E2341" t="inlineStr"/>
+      <c r="F2341" t="inlineStr">
+        <is>
+          <t>Cc1ncc(C2CCN(c3cc(C(C(=O)N4C[C@H](O)C[C@H]4C(=O)NCc4ccc(-c5scnc5C)cc4)C(C)C)on3)CC2)cn1.Nc1nnc(-c2ccccc2O)cc1N1CCCC1</t>
+        </is>
+      </c>
+      <c r="G2341" t="inlineStr"/>
+      <c r="H2341" t="inlineStr"/>
+      <c r="I2341" t="n">
+        <v>0.8698094404851652</v>
+      </c>
+      <c r="J2341" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2341" t="inlineStr"/>
+    </row>
+    <row r="2342">
+      <c r="A2342" s="1" t="n">
+        <v>2340</v>
+      </c>
+      <c r="B2342" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1059.png</t>
+        </is>
+      </c>
+      <c r="C2342" t="inlineStr"/>
+      <c r="D2342" t="inlineStr"/>
+      <c r="E2342" t="inlineStr"/>
+      <c r="F2342" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CN2CCC[C@@H](Cn3cc(-c4cc(-c5ccccc5O)nnc4N)cn3)C2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2342" t="inlineStr"/>
+      <c r="H2342" t="inlineStr"/>
+      <c r="I2342" t="n">
+        <v>0.8842013608233237</v>
+      </c>
+      <c r="J2342" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2342" t="inlineStr"/>
+    </row>
+    <row r="2343">
+      <c r="A2343" s="1" t="n">
+        <v>2341</v>
+      </c>
+      <c r="B2343" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1063.png</t>
+        </is>
+      </c>
+      <c r="C2343" t="inlineStr"/>
+      <c r="D2343" t="inlineStr"/>
+      <c r="E2343" t="inlineStr"/>
+      <c r="F2343" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CN2CCC[C@H](Cn3cc(-c4cc(-c5ccccc5O)nnc4N)cn3)C2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2343" t="inlineStr"/>
+      <c r="H2343" t="inlineStr"/>
+      <c r="I2343" t="n">
+        <v>0.8950922455743806</v>
+      </c>
+      <c r="J2343" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2343" t="inlineStr"/>
+    </row>
+    <row r="2344">
+      <c r="A2344" s="1" t="n">
+        <v>2342</v>
+      </c>
+      <c r="B2344" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1067.png</t>
+        </is>
+      </c>
+      <c r="C2344" t="inlineStr"/>
+      <c r="D2344" t="inlineStr"/>
+      <c r="E2344" t="inlineStr"/>
+      <c r="F2344" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)[C@H]2CC[C@@H](N(C)Cc3cnc(CN4C5CCC4CN(c4cc(-c6ccccc6O)nnc4N)C5)nc3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2344" t="inlineStr"/>
+      <c r="H2344" t="inlineStr"/>
+      <c r="I2344" t="n">
+        <v>0.8677611204309827</v>
+      </c>
+      <c r="J2344" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2344" t="inlineStr"/>
+    </row>
+    <row r="2345">
+      <c r="A2345" s="1" t="n">
+        <v>2343</v>
+      </c>
+      <c r="B2345" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1071.png</t>
+        </is>
+      </c>
+      <c r="C2345" t="inlineStr"/>
+      <c r="D2345" t="inlineStr"/>
+      <c r="E2345" t="inlineStr"/>
+      <c r="F2345" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CN2CCC(c3cnc(N4C5CCC4CN(c4cc(-c6ccccc6O)nnc4N)C5)nc3)CC2)C(C)(C)C)c(C(F)(F)F)c1</t>
+        </is>
+      </c>
+      <c r="G2345" t="inlineStr"/>
+      <c r="H2345" t="inlineStr"/>
+      <c r="I2345" t="n">
+        <v>0.8580021644903332</v>
+      </c>
+      <c r="J2345" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2345" t="inlineStr"/>
+    </row>
+    <row r="2346">
+      <c r="A2346" s="1" t="n">
+        <v>2344</v>
+      </c>
+      <c r="B2346" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1075.png</t>
+        </is>
+      </c>
+      <c r="C2346" t="inlineStr"/>
+      <c r="D2346" t="inlineStr"/>
+      <c r="E2346" t="inlineStr"/>
+      <c r="F2346" t="inlineStr">
+        <is>
+          <t>COc1cc(C2=CN(C)C(=O)N(C)C2)cc(OC)c1CN1CCN(CCC2CCN(c3ccc4c(c3)CN(C3CCC(=O)NC3=O)C4=O)CC2)CC1</t>
+        </is>
+      </c>
+      <c r="G2346" t="inlineStr"/>
+      <c r="H2346" t="inlineStr"/>
+      <c r="I2346" t="n">
+        <v>0.9138554409949439</v>
+      </c>
+      <c r="J2346" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2346" t="inlineStr"/>
+    </row>
+    <row r="2347">
+      <c r="A2347" s="1" t="n">
+        <v>2345</v>
+      </c>
+      <c r="B2347" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1079.png</t>
+        </is>
+      </c>
+      <c r="C2347" t="inlineStr"/>
+      <c r="D2347" t="inlineStr"/>
+      <c r="E2347" t="inlineStr"/>
+      <c r="F2347" t="inlineStr">
+        <is>
+          <t>CN(C)C(=O)c1cc2cnc(Nc3ccc(C(=O)NCC#Cc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)cc3)nc2n1C1CCCC1</t>
+        </is>
+      </c>
+      <c r="G2347" t="inlineStr"/>
+      <c r="H2347" t="inlineStr"/>
+      <c r="I2347" t="n">
+        <v>0.9050770406937049</v>
+      </c>
+      <c r="J2347" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2347" t="inlineStr"/>
+    </row>
+    <row r="2348">
+      <c r="A2348" s="1" t="n">
+        <v>2346</v>
+      </c>
+      <c r="B2348" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1083.png</t>
+        </is>
+      </c>
+      <c r="C2348" t="inlineStr"/>
+      <c r="D2348" t="inlineStr"/>
+      <c r="E2348" t="inlineStr"/>
+      <c r="F2348" t="inlineStr">
+        <is>
+          <t>Nc1ncnc2c1c(-c1ccc(Oc3ccccc3)cc1)nn2C1CCN(CCCCCCCCOc2ccc3c(c2)CN(C2CCC(=O)NC2=O)C3=O)CC1</t>
+        </is>
+      </c>
+      <c r="G2348" t="inlineStr"/>
+      <c r="H2348" t="inlineStr"/>
+      <c r="I2348" t="n">
+        <v>0.9077925019387793</v>
+      </c>
+      <c r="J2348" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2348" t="inlineStr"/>
+    </row>
+    <row r="2349">
+      <c r="A2349" s="1" t="n">
+        <v>2347</v>
+      </c>
+      <c r="B2349" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1095.png</t>
+        </is>
+      </c>
+      <c r="C2349" t="inlineStr"/>
+      <c r="D2349" t="inlineStr"/>
+      <c r="E2349" t="inlineStr"/>
+      <c r="F2349" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCOCCOCC(=O)N[C@H](C(=O)N3C[C@H](O)C[C@H]3C(=O)NCc3ccc(-c4scnc4C)cc3)C(C)C)c2)cc1CCCc1ccccc1</t>
+        </is>
+      </c>
+      <c r="G2349" t="inlineStr"/>
+      <c r="H2349" t="inlineStr"/>
+      <c r="I2349" t="n">
+        <v>0.8970111846655386</v>
+      </c>
+      <c r="J2349" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2349" t="inlineStr"/>
+    </row>
+    <row r="2350">
+      <c r="A2350" s="1" t="n">
+        <v>2348</v>
+      </c>
+      <c r="B2350" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0852.png</t>
+        </is>
+      </c>
+      <c r="C2350" t="inlineStr"/>
+      <c r="D2350" t="inlineStr"/>
+      <c r="E2350" t="inlineStr"/>
+      <c r="F2350" t="inlineStr">
+        <is>
+          <t>COc1cc(C2=CN(C)C(=O)N3CCCC23)cc(OC)c1CN1CCC2(CC1)CC(c1ccc3c(c1)C(=O)N(C1CCC(=O)NC1=O)C3=O)C2</t>
+        </is>
+      </c>
+      <c r="G2350" t="inlineStr"/>
+      <c r="H2350" t="inlineStr"/>
+      <c r="I2350" t="n">
+        <v>0.9162984295262578</v>
+      </c>
+      <c r="J2350" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2350" t="inlineStr"/>
+    </row>
+    <row r="2351">
+      <c r="A2351" s="1" t="n">
+        <v>2349</v>
+      </c>
+      <c r="B2351" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0856.png</t>
+        </is>
+      </c>
+      <c r="C2351" t="inlineStr"/>
+      <c r="D2351" t="inlineStr"/>
+      <c r="E2351" t="inlineStr"/>
+      <c r="F2351" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(N5CCC6(CC5)CN(c5ccc7c(c5)C(=O)N(C5CCC(=O)NC5=O)C7=O)C6)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2351" t="inlineStr"/>
+      <c r="H2351" t="inlineStr"/>
+      <c r="I2351" t="n">
+        <v>0.9069336944326933</v>
+      </c>
+      <c r="J2351" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2351" t="inlineStr"/>
+    </row>
+    <row r="2352">
+      <c r="A2352" s="1" t="n">
+        <v>2350</v>
+      </c>
+      <c r="B2352" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0860.png</t>
+        </is>
+      </c>
+      <c r="C2352" t="inlineStr"/>
+      <c r="D2352" t="inlineStr"/>
+      <c r="E2352" t="inlineStr"/>
+      <c r="F2352" t="inlineStr">
+        <is>
+          <t>CCCCC(Cc1c[nH]c2ccccc12)NC(=O)c1cnc(N2CCN(c3ccc(OCCOCCOCCOc4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)cc3)CC2)s1</t>
+        </is>
+      </c>
+      <c r="G2352" t="inlineStr"/>
+      <c r="H2352" t="inlineStr"/>
+      <c r="I2352" t="n">
+        <v>0.8988869556636492</v>
+      </c>
+      <c r="J2352" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2352" t="inlineStr"/>
+    </row>
+    <row r="2353">
+      <c r="A2353" s="1" t="n">
+        <v>2351</v>
+      </c>
+      <c r="B2353" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0864.png</t>
+        </is>
+      </c>
+      <c r="C2353" t="inlineStr"/>
+      <c r="D2353" t="inlineStr"/>
+      <c r="E2353" t="inlineStr"/>
+      <c r="F2353" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)[C@@H]2CC[C@@H](N(C)Cc3cnc(N4C5CCC4CN(c4cc(-c6ccccc6O)nnc4N)C5)nc3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2353" t="inlineStr"/>
+      <c r="H2353" t="inlineStr"/>
+      <c r="I2353" t="n">
+        <v>0.8911352351378017</v>
+      </c>
+      <c r="J2353" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2353" t="inlineStr"/>
+    </row>
+    <row r="2354">
+      <c r="A2354" s="1" t="n">
+        <v>2352</v>
+      </c>
+      <c r="B2354" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0872.png</t>
+        </is>
+      </c>
+      <c r="C2354" t="inlineStr"/>
+      <c r="D2354" t="inlineStr"/>
+      <c r="E2354" t="inlineStr"/>
+      <c r="F2354" t="inlineStr">
+        <is>
+          <t>CN(C)C(=O)c1cc2cnc(Nc3ccc(C(=O)NCCCc4cccc5c4CN(C4CCC(=O)NC4=O)C5=O)cc3)nc2n1C1CCCC1</t>
+        </is>
+      </c>
+      <c r="G2354" t="inlineStr"/>
+      <c r="H2354" t="inlineStr"/>
+      <c r="I2354" t="n">
+        <v>0.9061400345456071</v>
+      </c>
+      <c r="J2354" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2354" t="inlineStr"/>
+    </row>
+    <row r="2355">
+      <c r="A2355" s="1" t="n">
+        <v>2353</v>
+      </c>
+      <c r="B2355" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0880.png</t>
+        </is>
+      </c>
+      <c r="C2355" t="inlineStr"/>
+      <c r="D2355" t="inlineStr"/>
+      <c r="E2355" t="inlineStr"/>
+      <c r="F2355" t="inlineStr">
+        <is>
+          <t>Nc1ncnc2c1c(-c1ccc(Oc3ccccc3)cc1)nn2C1CCN(CCOCCOCCNc2ccc3c(c2)CN(C2CCC(=O)NC2=O)C3=O)CC1</t>
+        </is>
+      </c>
+      <c r="G2355" t="inlineStr"/>
+      <c r="H2355" t="inlineStr"/>
+      <c r="I2355" t="n">
+        <v>0.893638993841075</v>
+      </c>
+      <c r="J2355" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2355" t="inlineStr"/>
+    </row>
+    <row r="2356">
+      <c r="A2356" s="1" t="n">
+        <v>2354</v>
+      </c>
+      <c r="B2356" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0888.png</t>
+        </is>
+      </c>
+      <c r="C2356" t="inlineStr"/>
+      <c r="D2356" t="inlineStr"/>
+      <c r="E2356" t="inlineStr"/>
+      <c r="F2356" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CN2CCC(Cn3cc(-c4cc(-c5ccccc5O)nnc4N)cn3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2356" t="inlineStr"/>
+      <c r="H2356" t="inlineStr"/>
+      <c r="I2356" t="n">
+        <v>0.8949830601177746</v>
+      </c>
+      <c r="J2356" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2356" t="inlineStr"/>
+    </row>
+    <row r="2357">
+      <c r="A2357" s="1" t="n">
+        <v>2355</v>
+      </c>
+      <c r="B2357" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0892.png</t>
+        </is>
+      </c>
+      <c r="C2357" t="inlineStr"/>
+      <c r="D2357" t="inlineStr"/>
+      <c r="E2357" t="inlineStr"/>
+      <c r="F2357" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)C(NC(=O)C[C@H]2CC[C@@H](N3CCC(c4cnc(N5C6CCC5CN(c5cc(-c7ccccc7O)nnc5N)C6)nc4)CC3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2357" t="inlineStr"/>
+      <c r="H2357" t="inlineStr"/>
+      <c r="I2357" t="n">
+        <v>0.8446902536862927</v>
+      </c>
+      <c r="J2357" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2357" t="inlineStr"/>
+    </row>
+    <row r="2358">
+      <c r="A2358" s="1" t="n">
+        <v>2356</v>
+      </c>
+      <c r="B2358" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0896.png</t>
+        </is>
+      </c>
+      <c r="C2358" t="inlineStr"/>
+      <c r="D2358" t="inlineStr"/>
+      <c r="E2358" t="inlineStr"/>
+      <c r="F2358" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(N5CCN(CC#Cc6cccc7c6CN(C6CCC(=O)NC6=O)C7=O)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2358" t="inlineStr"/>
+      <c r="H2358" t="inlineStr"/>
+      <c r="I2358" t="n">
+        <v>0.8895034615534625</v>
+      </c>
+      <c r="J2358" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2358" t="inlineStr"/>
+    </row>
+    <row r="2359">
+      <c r="A2359" s="1" t="n">
+        <v>2357</v>
+      </c>
+      <c r="B2359" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0900.png</t>
+        </is>
+      </c>
+      <c r="C2359" t="inlineStr"/>
+      <c r="D2359" t="inlineStr"/>
+      <c r="E2359" t="inlineStr"/>
+      <c r="F2359" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)N(C)CCCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)c2)cc1/C=C/C1CCC(F)(F)CC1</t>
+        </is>
+      </c>
+      <c r="G2359" t="inlineStr"/>
+      <c r="H2359" t="inlineStr"/>
+      <c r="I2359" t="n">
+        <v>0.8955792156088828</v>
+      </c>
+      <c r="J2359" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2359" t="inlineStr"/>
+    </row>
+    <row r="2360">
+      <c r="A2360" s="1" t="n">
+        <v>2358</v>
+      </c>
+      <c r="B2360" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0904.png</t>
+        </is>
+      </c>
+      <c r="C2360" t="inlineStr"/>
+      <c r="D2360" t="inlineStr"/>
+      <c r="E2360" t="inlineStr"/>
+      <c r="F2360" t="inlineStr">
+        <is>
+          <t>NC(=O)c1ncc(N2CCC[C@@H](N3CCCC3=O)C2)nc1Nc1ccc(N2CC(C3CCN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)C2)cc1</t>
+        </is>
+      </c>
+      <c r="G2360" t="inlineStr"/>
+      <c r="H2360" t="inlineStr"/>
+      <c r="I2360" t="n">
+        <v>0.8466570197464612</v>
+      </c>
+      <c r="J2360" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2360" t="inlineStr"/>
+    </row>
+    <row r="2361">
+      <c r="A2361" s="1" t="n">
+        <v>2359</v>
+      </c>
+      <c r="B2361" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0908.png</t>
+        </is>
+      </c>
+      <c r="C2361" t="inlineStr"/>
+      <c r="D2361" t="inlineStr"/>
+      <c r="E2361" t="inlineStr"/>
+      <c r="F2361" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CCN(CC6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2361" t="inlineStr"/>
+      <c r="H2361" t="inlineStr"/>
+      <c r="I2361" t="n">
+        <v>0.8917202993800376</v>
+      </c>
+      <c r="J2361" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2361" t="inlineStr"/>
+    </row>
+    <row r="2362">
+      <c r="A2362" s="1" t="n">
+        <v>2360</v>
+      </c>
+      <c r="B2362" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0912.png</t>
+        </is>
+      </c>
+      <c r="C2362" t="inlineStr"/>
+      <c r="D2362" t="inlineStr"/>
+      <c r="E2362" t="inlineStr"/>
+      <c r="F2362" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@H]2CCCN(c3cnc(C(N)=O)c(Nc4cnn(C5CCN(CC6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)c4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2362" t="inlineStr"/>
+      <c r="H2362" t="inlineStr"/>
+      <c r="I2362" t="n">
+        <v>0.8976118180334012</v>
+      </c>
+      <c r="J2362" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2362" t="inlineStr"/>
+    </row>
+    <row r="2363">
+      <c r="A2363" s="1" t="n">
+        <v>2361</v>
+      </c>
+      <c r="B2363" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0920.png</t>
+        </is>
+      </c>
+      <c r="C2363" t="inlineStr"/>
+      <c r="D2363" t="inlineStr"/>
+      <c r="E2363" t="inlineStr"/>
+      <c r="F2363" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)C3C=CC=C(CC4CCN(C(=O)c5cccc(C#Cc6cc(NC(=O)Nc7ccnc(Cl)c7)ccn6)c5)CC4)C3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2363" t="inlineStr"/>
+      <c r="H2363" t="inlineStr"/>
+      <c r="I2363" t="n">
+        <v>0.8991888367449214</v>
+      </c>
+      <c r="J2363" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2363" t="inlineStr"/>
+    </row>
+    <row r="2364">
+      <c r="A2364" s="1" t="n">
+        <v>2362</v>
+      </c>
+      <c r="B2364" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0924.png</t>
+        </is>
+      </c>
+      <c r="C2364" t="inlineStr"/>
+      <c r="D2364" t="inlineStr"/>
+      <c r="E2364" t="inlineStr"/>
+      <c r="F2364" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cnn(C4CC5(CCC(C(=O)N6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)c3cc2OC)n1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2364" t="inlineStr"/>
+      <c r="H2364" t="inlineStr"/>
+      <c r="I2364" t="n">
+        <v>0.8953002182652078</v>
+      </c>
+      <c r="J2364" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2364" t="inlineStr"/>
+    </row>
+    <row r="2365">
+      <c r="A2365" s="1" t="n">
+        <v>2363</v>
+      </c>
+      <c r="B2365" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0940.png</t>
+        </is>
+      </c>
+      <c r="C2365" t="inlineStr"/>
+      <c r="D2365" t="inlineStr"/>
+      <c r="E2365" t="inlineStr"/>
+      <c r="F2365" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CCN(C[C@H]6CCCN6c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2365" t="inlineStr"/>
+      <c r="H2365" t="inlineStr"/>
+      <c r="I2365" t="n">
+        <v>0.8897002544338222</v>
+      </c>
+      <c r="J2365" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2365" t="inlineStr"/>
+    </row>
+    <row r="2366">
+      <c r="A2366" s="1" t="n">
+        <v>2364</v>
+      </c>
+      <c r="B2366" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0948.png</t>
+        </is>
+      </c>
+      <c r="C2366" t="inlineStr"/>
+      <c r="D2366" t="inlineStr"/>
+      <c r="E2366" t="inlineStr"/>
+      <c r="F2366" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)COCCOCCNCCOc2ccc(C(=O)Nc3ccc(N4CCN(c5cccnc5)CC4)cc3)cc2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2366" t="inlineStr"/>
+      <c r="H2366" t="inlineStr"/>
+      <c r="I2366" t="n">
+        <v>0.8807892807501856</v>
+      </c>
+      <c r="J2366" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2366" t="inlineStr"/>
+    </row>
+    <row r="2367">
+      <c r="A2367" s="1" t="n">
+        <v>2365</v>
+      </c>
+      <c r="B2367" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0956.png</t>
+        </is>
+      </c>
+      <c r="C2367" t="inlineStr"/>
+      <c r="D2367" t="inlineStr"/>
+      <c r="E2367" t="inlineStr"/>
+      <c r="F2367" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2(F)CC2)C2CCC(N(C)CCCC#Cc3cnc(N4C5CCC4CN(c4cc(-c6ccccc6O)nnc4N)C5)nc3)CC2)cc1</t>
+        </is>
+      </c>
+      <c r="G2367" t="inlineStr"/>
+      <c r="H2367" t="inlineStr"/>
+      <c r="I2367" t="n">
+        <v>0.8708724481948658</v>
+      </c>
+      <c r="J2367" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2367" t="inlineStr"/>
+    </row>
+    <row r="2368">
+      <c r="A2368" s="1" t="n">
+        <v>2366</v>
+      </c>
+      <c r="B2368" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0964.png</t>
+        </is>
+      </c>
+      <c r="C2368" t="inlineStr"/>
+      <c r="D2368" t="inlineStr"/>
+      <c r="E2368" t="inlineStr"/>
+      <c r="F2368" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3cccc(OCc4cn(Cc5cccc(N6C[C@H]7C[C@@H]6CN7/C=C/C(=O)c6ccccc6O)n5)nn4)c3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2368" t="inlineStr"/>
+      <c r="H2368" t="inlineStr"/>
+      <c r="I2368" t="n">
+        <v>0.8992229123073401</v>
+      </c>
+      <c r="J2368" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2368" t="inlineStr"/>
+    </row>
+    <row r="2369">
+      <c r="A2369" s="1" t="n">
+        <v>2367</v>
+      </c>
+      <c r="B2369" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0976.png</t>
+        </is>
+      </c>
+      <c r="C2369" t="inlineStr"/>
+      <c r="D2369" t="inlineStr"/>
+      <c r="E2369" t="inlineStr"/>
+      <c r="F2369" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@H](c2cc(OCCOCCOCCOc3ccc(CN4C(=O)/C(=C\C=C\c5ccc([N+](=O)[O-])cc5)c5ccccc54)cc3)no2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2369" t="inlineStr"/>
+      <c r="H2369" t="inlineStr"/>
+      <c r="I2369" t="n">
+        <v>0.8655665046975609</v>
+      </c>
+      <c r="J2369" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2369" t="inlineStr"/>
+    </row>
+    <row r="2370">
+      <c r="A2370" s="1" t="n">
+        <v>2368</v>
+      </c>
+      <c r="B2370" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0980.png</t>
+        </is>
+      </c>
+      <c r="C2370" t="inlineStr"/>
+      <c r="D2370" t="inlineStr"/>
+      <c r="E2370" t="inlineStr"/>
+      <c r="F2370" t="inlineStr">
+        <is>
+          <t>COc1ccc2nc(-c3ccc(N4CC(OC5CCN(CCN6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)cc3)sc2c1</t>
+        </is>
+      </c>
+      <c r="G2370" t="inlineStr"/>
+      <c r="H2370" t="inlineStr"/>
+      <c r="I2370" t="n">
+        <v>0.8918938762033259</v>
+      </c>
+      <c r="J2370" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2370" t="inlineStr"/>
+    </row>
+    <row r="2371">
+      <c r="A2371" s="1" t="n">
+        <v>2369</v>
+      </c>
+      <c r="B2371" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0984.png</t>
+        </is>
+      </c>
+      <c r="C2371" t="inlineStr"/>
+      <c r="D2371" t="inlineStr"/>
+      <c r="E2371" t="inlineStr"/>
+      <c r="F2371" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(N4CCN(CCCO[C@@H]5C[C@@H](Oc6ccc(CN7C(=O)/C(=C\C=C\c8ccc([N+](=O)[O-])cc8)c8ccccc87)cc6)C5)CC4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2371" t="inlineStr"/>
+      <c r="H2371" t="inlineStr"/>
+      <c r="I2371" t="n">
+        <v>0.8631163174345313</v>
+      </c>
+      <c r="J2371" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2371" t="inlineStr"/>
+    </row>
+    <row r="2372">
+      <c r="A2372" s="1" t="n">
+        <v>2370</v>
+      </c>
+      <c r="B2372" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0988.png</t>
+        </is>
+      </c>
+      <c r="C2372" t="inlineStr"/>
+      <c r="D2372" t="inlineStr"/>
+      <c r="E2372" t="inlineStr"/>
+      <c r="F2372" t="inlineStr">
+        <is>
+          <t>Nc1nnc(-c2ccccc2O)cc1-c1cnn(C2CCN(C3CCC(Nc4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G2372" t="inlineStr"/>
+      <c r="H2372" t="inlineStr"/>
+      <c r="I2372" t="n">
+        <v>0.9025855692058274</v>
+      </c>
+      <c r="J2372" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2372" t="inlineStr"/>
+    </row>
+    <row r="2373">
+      <c r="A2373" s="1" t="n">
+        <v>2371</v>
+      </c>
+      <c r="B2373" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0992.png</t>
+        </is>
+      </c>
+      <c r="C2373" t="inlineStr"/>
+      <c r="D2373" t="inlineStr"/>
+      <c r="E2373" t="inlineStr"/>
+      <c r="F2373" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)C(c2cc(OCCCCN3CCC(c4cnc(N5C6CCC5CN(c5cc(-c7ccccc7O)nnc5N)C6)nc4)CC3)no2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2373" t="inlineStr"/>
+      <c r="H2373" t="inlineStr"/>
+      <c r="I2373" t="n">
+        <v>0.8707110126117851</v>
+      </c>
+      <c r="J2373" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2373" t="inlineStr"/>
+    </row>
+    <row r="2374">
+      <c r="A2374" s="1" t="n">
+        <v>2372</v>
+      </c>
+      <c r="B2374" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0996.png</t>
+        </is>
+      </c>
+      <c r="C2374" t="inlineStr"/>
+      <c r="D2374" t="inlineStr"/>
+      <c r="E2374" t="inlineStr"/>
+      <c r="F2374" t="inlineStr">
+        <is>
+          <t>O=C(COc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O)NCCOCCOCCC(=O)N1CCC[C@@H](Nc2ncc(Cl)c(-c3c[nH]c4ccccc34)n2)C1</t>
+        </is>
+      </c>
+      <c r="G2374" t="inlineStr"/>
+      <c r="H2374" t="inlineStr"/>
+      <c r="I2374" t="n">
+        <v>0.8953224610785721</v>
+      </c>
+      <c r="J2374" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2374" t="inlineStr"/>
+    </row>
+    <row r="2375">
+      <c r="A2375" s="1" t="n">
+        <v>2373</v>
+      </c>
+      <c r="B2375" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1000.png</t>
+        </is>
+      </c>
+      <c r="C2375" t="inlineStr"/>
+      <c r="D2375" t="inlineStr"/>
+      <c r="E2375" t="inlineStr"/>
+      <c r="F2375" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(N5CCC6(CCCN(Cc7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2375" t="inlineStr"/>
+      <c r="H2375" t="inlineStr"/>
+      <c r="I2375" t="n">
+        <v>0.8801016968326852</v>
+      </c>
+      <c r="J2375" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2375" t="inlineStr"/>
+    </row>
+    <row r="2376">
+      <c r="A2376" s="1" t="n">
+        <v>2374</v>
+      </c>
+      <c r="B2376" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1004.png</t>
+        </is>
+      </c>
+      <c r="C2376" t="inlineStr"/>
+      <c r="D2376" t="inlineStr"/>
+      <c r="E2376" t="inlineStr"/>
+      <c r="F2376" t="inlineStr">
+        <is>
+          <t>O=C(COc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O)NCCOCCOCCN1CCC[C@@H](Nc2ncc(Cl)c(-c3c[nH]c4ccccc34)n2)C1</t>
+        </is>
+      </c>
+      <c r="G2376" t="inlineStr"/>
+      <c r="H2376" t="inlineStr"/>
+      <c r="I2376" t="n">
+        <v>0.8961455000141099</v>
+      </c>
+      <c r="J2376" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2376" t="inlineStr"/>
+    </row>
+    <row r="2377">
+      <c r="A2377" s="1" t="n">
+        <v>2375</v>
+      </c>
+      <c r="B2377" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1008.png</t>
+        </is>
+      </c>
+      <c r="C2377" t="inlineStr"/>
+      <c r="D2377" t="inlineStr"/>
+      <c r="E2377" t="inlineStr"/>
+      <c r="F2377" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3cccc(OCCCc4cn(Cc5cccc(N6C[C@H]7C[C@@H]6CN7/C=C/C(=O)c6ccccc6O)n5)nn4)c3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2377" t="inlineStr"/>
+      <c r="H2377" t="inlineStr"/>
+      <c r="I2377" t="n">
+        <v>0.8963919863585594</v>
+      </c>
+      <c r="J2377" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2377" t="inlineStr"/>
+    </row>
+    <row r="2378">
+      <c r="A2378" s="1" t="n">
+        <v>2376</v>
+      </c>
+      <c r="B2378" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1012.png</t>
+        </is>
+      </c>
+      <c r="C2378" t="inlineStr"/>
+      <c r="D2378" t="inlineStr"/>
+      <c r="E2378" t="inlineStr"/>
+      <c r="F2378" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(N4CCN(CCCO[C@@H]5C[C@@H](Oc6ccc(CN7C(=O)/C(=C/C=C/c8ccc([N+](=O)[O-])cc8)c8ccccc87)cc6)C5)CC4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2378" t="inlineStr"/>
+      <c r="H2378" t="inlineStr"/>
+      <c r="I2378" t="n">
+        <v>0.8887368737179159</v>
+      </c>
+      <c r="J2378" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2378" t="inlineStr"/>
+    </row>
+    <row r="2379">
+      <c r="A2379" s="1" t="n">
+        <v>2377</v>
+      </c>
+      <c r="B2379" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1016.png</t>
+        </is>
+      </c>
+      <c r="C2379" t="inlineStr"/>
+      <c r="D2379" t="inlineStr"/>
+      <c r="E2379" t="inlineStr"/>
+      <c r="F2379" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(N5CCN(C[C@H]6CCCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2379" t="inlineStr"/>
+      <c r="H2379" t="inlineStr"/>
+      <c r="I2379" t="n">
+        <v>0.9004922505501226</v>
+      </c>
+      <c r="J2379" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2379" t="inlineStr"/>
+    </row>
+    <row r="2380">
+      <c r="A2380" s="1" t="n">
+        <v>2378</v>
+      </c>
+      <c r="B2380" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1024.png</t>
+        </is>
+      </c>
+      <c r="C2380" t="inlineStr"/>
+      <c r="D2380" t="inlineStr"/>
+      <c r="E2380" t="inlineStr"/>
+      <c r="F2380" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CN(C)Cc2cnc(N3C4CCC3CN(c3cc(-c5ccccc5O)nnc3N)C4)nc2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2380" t="inlineStr"/>
+      <c r="H2380" t="inlineStr"/>
+      <c r="I2380" t="n">
+        <v>0.878474569755197</v>
+      </c>
+      <c r="J2380" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2380" t="inlineStr"/>
+    </row>
+    <row r="2381">
+      <c r="A2381" s="1" t="n">
+        <v>2379</v>
+      </c>
+      <c r="B2381" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1028.png</t>
+        </is>
+      </c>
+      <c r="C2381" t="inlineStr"/>
+      <c r="D2381" t="inlineStr"/>
+      <c r="E2381" t="inlineStr"/>
+      <c r="F2381" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CCN(C[C@H]6CCN(c7ccc8c(c7)C(=O)NC8=O)C6)CC5)nc4)n3)C2)C1=O.O=C1CCCC(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2381" t="inlineStr"/>
+      <c r="H2381" t="inlineStr"/>
+      <c r="I2381" t="n">
+        <v>0.8719555517788622</v>
+      </c>
+      <c r="J2381" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2381" t="inlineStr"/>
+    </row>
+    <row r="2382">
+      <c r="A2382" s="1" t="n">
+        <v>2380</v>
+      </c>
+      <c r="B2382" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1036.png</t>
+        </is>
+      </c>
+      <c r="C2382" t="inlineStr"/>
+      <c r="D2382" t="inlineStr"/>
+      <c r="E2382" t="inlineStr"/>
+      <c r="F2382" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCC(NC6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2OC)n1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G2382" t="inlineStr"/>
+      <c r="H2382" t="inlineStr"/>
+      <c r="I2382" t="n">
+        <v>0.8764121134147697</v>
+      </c>
+      <c r="J2382" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2382" t="inlineStr"/>
+    </row>
+    <row r="2383">
+      <c r="A2383" s="1" t="n">
+        <v>2381</v>
+      </c>
+      <c r="B2383" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1040.png</t>
+        </is>
+      </c>
+      <c r="C2383" t="inlineStr"/>
+      <c r="D2383" t="inlineStr"/>
+      <c r="E2383" t="inlineStr"/>
+      <c r="F2383" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)C(c2cc(O[C@H]3CC[C@@H](N4CCC(c5cnc(N)nc5)CC4)CC3)no2)C(C)C)cc1.Nc1nnc(-c2ccccc2O)cc1N1CCCCCC1</t>
+        </is>
+      </c>
+      <c r="G2383" t="inlineStr"/>
+      <c r="H2383" t="inlineStr"/>
+      <c r="I2383" t="n">
+        <v>0.8652772543683178</v>
+      </c>
+      <c r="J2383" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2383" t="inlineStr"/>
+    </row>
+    <row r="2384">
+      <c r="A2384" s="1" t="n">
+        <v>2382</v>
+      </c>
+      <c r="B2384" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1048.png</t>
+        </is>
+      </c>
+      <c r="C2384" t="inlineStr"/>
+      <c r="D2384" t="inlineStr"/>
+      <c r="E2384" t="inlineStr"/>
+      <c r="F2384" t="inlineStr">
+        <is>
+          <t>Cc1cc(C(C(=O)N2C[C@H](O)C[C@H]2C(=O)NCc2ccc(-c3scnc3C)cc2)C(C)CCN2CCC(c3cnc(N4C5CCC4CN(c4cc(-c6ccccc6O)nnc4N)C5)nc3)CC2)on1</t>
+        </is>
+      </c>
+      <c r="G2384" t="inlineStr"/>
+      <c r="H2384" t="inlineStr"/>
+      <c r="I2384" t="n">
+        <v>0.8870200797580483</v>
+      </c>
+      <c r="J2384" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2384" t="inlineStr"/>
+    </row>
+    <row r="2385">
+      <c r="A2385" s="1" t="n">
+        <v>2383</v>
+      </c>
+      <c r="B2385" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1056.png</t>
+        </is>
+      </c>
+      <c r="C2385" t="inlineStr"/>
+      <c r="D2385" t="inlineStr"/>
+      <c r="E2385" t="inlineStr"/>
+      <c r="F2385" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2(F)CC2)C(C)(C)C)c(OCCCCN2CCC(c3cnc(N4C5CCC4CN(c4cc(-c6ccccc6O)nnc4N)C5)nc3)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G2385" t="inlineStr"/>
+      <c r="H2385" t="inlineStr"/>
+      <c r="I2385" t="n">
+        <v>0.8621384511453518</v>
+      </c>
+      <c r="J2385" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2385" t="inlineStr"/>
+    </row>
+    <row r="2386">
+      <c r="A2386" s="1" t="n">
+        <v>2384</v>
+      </c>
+      <c r="B2386" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1060.png</t>
+        </is>
+      </c>
+      <c r="C2386" t="inlineStr"/>
+      <c r="D2386" t="inlineStr"/>
+      <c r="E2386" t="inlineStr"/>
+      <c r="F2386" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCCN2CCC(c3cccc(C#Cc4cc(NC(=O)Nc5cc(F)ncc5CO)ccn4)c3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2386" t="inlineStr"/>
+      <c r="H2386" t="inlineStr"/>
+      <c r="I2386" t="n">
+        <v>0.904930796518877</v>
+      </c>
+      <c r="J2386" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2386" t="inlineStr"/>
+    </row>
+    <row r="2387">
+      <c r="A2387" s="1" t="n">
+        <v>2385</v>
+      </c>
+      <c r="B2387" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1064.png</t>
+        </is>
+      </c>
+      <c r="C2387" t="inlineStr"/>
+      <c r="D2387" t="inlineStr"/>
+      <c r="E2387" t="inlineStr"/>
+      <c r="F2387" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc5c(c4)CCN(CC4CN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)C4)C5)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2387" t="inlineStr"/>
+      <c r="H2387" t="inlineStr"/>
+      <c r="I2387" t="n">
+        <v>0.8945653332964774</v>
+      </c>
+      <c r="J2387" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2387" t="inlineStr"/>
+    </row>
+    <row r="2388">
+      <c r="A2388" s="1" t="n">
+        <v>2386</v>
+      </c>
+      <c r="B2388" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1076.png</t>
+        </is>
+      </c>
+      <c r="C2388" t="inlineStr"/>
+      <c r="D2388" t="inlineStr"/>
+      <c r="E2388" t="inlineStr"/>
+      <c r="F2388" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(N4CCN(CCCO[C@@H]5C[C@@H](Oc6ccc(C(=O)Nc7ccc(N8CCN(c9ccccn9)CC8)cc7)c(F)c6)C5)CC4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2388" t="inlineStr"/>
+      <c r="H2388" t="inlineStr"/>
+      <c r="I2388" t="n">
+        <v>0.8673213907161366</v>
+      </c>
+      <c r="J2388" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2388" t="inlineStr"/>
+    </row>
+    <row r="2389">
+      <c r="A2389" s="1" t="n">
+        <v>2387</v>
+      </c>
+      <c r="B2389" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1084.png</t>
+        </is>
+      </c>
+      <c r="C2389" t="inlineStr"/>
+      <c r="D2389" t="inlineStr"/>
+      <c r="E2389" t="inlineStr"/>
+      <c r="F2389" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@H]2CCCN(c3cnc(C(N)=O)c(Nc4cnn(C5CCN(CCCc6cccc7c6CN(C6CCC(=O)NC6=O)C7=O)CC5)c4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2389" t="inlineStr"/>
+      <c r="H2389" t="inlineStr"/>
+      <c r="I2389" t="n">
+        <v>0.8954015112730895</v>
+      </c>
+      <c r="J2389" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2389" t="inlineStr"/>
+    </row>
+    <row r="2390">
+      <c r="A2390" s="1" t="n">
+        <v>2388</v>
+      </c>
+      <c r="B2390" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1088.png</t>
+        </is>
+      </c>
+      <c r="C2390" t="inlineStr"/>
+      <c r="D2390" t="inlineStr"/>
+      <c r="E2390" t="inlineStr"/>
+      <c r="F2390" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(N5CCN(C[C@@H]6[C@H]7CN(c8ccc9c(c8)C(=O)N(C8CCC(=O)NC8=O)C9=O)C[C@@H]67)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2390" t="inlineStr"/>
+      <c r="H2390" t="inlineStr"/>
+      <c r="I2390" t="n">
+        <v>0.8478375298383211</v>
+      </c>
+      <c r="J2390" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2390" t="inlineStr"/>
+    </row>
+    <row r="2391">
+      <c r="A2391" s="1" t="n">
+        <v>2389</v>
+      </c>
+      <c r="B2391" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1096.png</t>
+        </is>
+      </c>
+      <c r="C2391" t="inlineStr"/>
+      <c r="D2391" t="inlineStr"/>
+      <c r="E2391" t="inlineStr"/>
+      <c r="F2391" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CCN(C(=O)CCOCCNc6cccc7c6C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2391" t="inlineStr"/>
+      <c r="H2391" t="inlineStr"/>
+      <c r="I2391" t="n">
+        <v>0.8902804026436176</v>
+      </c>
+      <c r="J2391" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2391" t="inlineStr"/>
+    </row>
+    <row r="2392">
+      <c r="A2392" s="1" t="n">
+        <v>2390</v>
+      </c>
+      <c r="B2392" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1100.png</t>
+        </is>
+      </c>
+      <c r="C2392" t="inlineStr"/>
+      <c r="D2392" t="inlineStr"/>
+      <c r="E2392" t="inlineStr"/>
+      <c r="F2392" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)c1ccc(Nc2nc(N3CCC[C@@H](NC(=O)N4CC5(CN(Cc6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)C5)C4)C3)cnc2C(N)=O)cc1</t>
+        </is>
+      </c>
+      <c r="G2392" t="inlineStr"/>
+      <c r="H2392" t="inlineStr"/>
+      <c r="I2392" t="n">
+        <v>0.9103643561641684</v>
+      </c>
+      <c r="J2392" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2392" t="inlineStr"/>
+    </row>
+    <row r="2393">
+      <c r="A2393" s="1" t="n">
+        <v>2391</v>
+      </c>
+      <c r="B2393" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0853.png</t>
+        </is>
+      </c>
+      <c r="C2393" t="inlineStr"/>
+      <c r="D2393" t="inlineStr"/>
+      <c r="E2393" t="inlineStr"/>
+      <c r="F2393" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@H](c2cc(OCCOCCOCCOCCOc3ccc(CN4C(=O)/C(=C\C=C\c5ccc([N+](=O)[O-])cc5)c5ccccc54)cc3)no2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2393" t="inlineStr"/>
+      <c r="H2393" t="inlineStr"/>
+      <c r="I2393" t="n">
+        <v>0.8466753995794574</v>
+      </c>
+      <c r="J2393" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2393" t="inlineStr"/>
+    </row>
+    <row r="2394">
+      <c r="A2394" s="1" t="n">
+        <v>2392</v>
+      </c>
+      <c r="B2394" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0861.png</t>
+        </is>
+      </c>
+      <c r="C2394" t="inlineStr"/>
+      <c r="D2394" t="inlineStr"/>
+      <c r="E2394" t="inlineStr"/>
+      <c r="F2394" t="inlineStr">
+        <is>
+          <t>CCCCC(Cc1c[nH]c2ccccc12)NC(=O)c1cnc(N2CCN(c3ccc(OCCOCCOCCOCC(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)cc3)CC2)[nH]1</t>
+        </is>
+      </c>
+      <c r="G2394" t="inlineStr"/>
+      <c r="H2394" t="inlineStr"/>
+      <c r="I2394" t="n">
+        <v>0.8515662759401688</v>
+      </c>
+      <c r="J2394" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2394" t="inlineStr"/>
+    </row>
+    <row r="2395">
+      <c r="A2395" s="1" t="n">
+        <v>2393</v>
+      </c>
+      <c r="B2395" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0869.png</t>
+        </is>
+      </c>
+      <c r="C2395" t="inlineStr"/>
+      <c r="D2395" t="inlineStr"/>
+      <c r="E2395" t="inlineStr"/>
+      <c r="F2395" t="inlineStr">
+        <is>
+          <t>COc1cc(C2=CN(C)C(=O)N3CCCC23)cc(OC)c1CN1CCN(CCC2CCN(c3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)CC2)CC1</t>
+        </is>
+      </c>
+      <c r="G2395" t="inlineStr"/>
+      <c r="H2395" t="inlineStr"/>
+      <c r="I2395" t="n">
+        <v>0.919852428848787</v>
+      </c>
+      <c r="J2395" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2395" t="inlineStr"/>
+    </row>
+    <row r="2396">
+      <c r="A2396" s="1" t="n">
+        <v>2394</v>
+      </c>
+      <c r="B2396" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0873.png</t>
+        </is>
+      </c>
+      <c r="C2396" t="inlineStr"/>
+      <c r="D2396" t="inlineStr"/>
+      <c r="E2396" t="inlineStr"/>
+      <c r="F2396" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(N5CCN(C[C@H]6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2396" t="inlineStr"/>
+      <c r="H2396" t="inlineStr"/>
+      <c r="I2396" t="n">
+        <v>0.8857399258080914</v>
+      </c>
+      <c r="J2396" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2396" t="inlineStr"/>
+    </row>
+    <row r="2397">
+      <c r="A2397" s="1" t="n">
+        <v>2395</v>
+      </c>
+      <c r="B2397" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0877.png</t>
+        </is>
+      </c>
+      <c r="C2397" t="inlineStr"/>
+      <c r="D2397" t="inlineStr"/>
+      <c r="E2397" t="inlineStr"/>
+      <c r="F2397" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5(C)CCN(CCCc6cccc7c6CN(C6CCC(=O)NC6=O)C7=O)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2397" t="inlineStr"/>
+      <c r="H2397" t="inlineStr"/>
+      <c r="I2397" t="n">
+        <v>0.8882418061804578</v>
+      </c>
+      <c r="J2397" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2397" t="inlineStr"/>
+    </row>
+    <row r="2398">
+      <c r="A2398" s="1" t="n">
+        <v>2396</v>
+      </c>
+      <c r="B2398" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0885.png</t>
+        </is>
+      </c>
+      <c r="C2398" t="inlineStr"/>
+      <c r="D2398" t="inlineStr"/>
+      <c r="E2398" t="inlineStr"/>
+      <c r="F2398" t="inlineStr">
+        <is>
+          <t>Nc1nnc(-c2ccccc2O)cc1N1C[C@H]2C[C@@H]1CN2c1cccc(Cn2cc(CCCCOc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)nn2)n1</t>
+        </is>
+      </c>
+      <c r="G2398" t="inlineStr"/>
+      <c r="H2398" t="inlineStr"/>
+      <c r="I2398" t="n">
+        <v>0.8909117189725881</v>
+      </c>
+      <c r="J2398" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2398" t="inlineStr"/>
+    </row>
+    <row r="2399">
+      <c r="A2399" s="1" t="n">
+        <v>2397</v>
+      </c>
+      <c r="B2399" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0889.png</t>
+        </is>
+      </c>
+      <c r="C2399" t="inlineStr"/>
+      <c r="D2399" t="inlineStr"/>
+      <c r="E2399" t="inlineStr"/>
+      <c r="F2399" t="inlineStr">
+        <is>
+          <t>CN(C)C(=O)c1cc2cnc(Nc3ccc(C(=O)NCCCCCCOc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)cn3)nc2n1C1CCCC1</t>
+        </is>
+      </c>
+      <c r="G2399" t="inlineStr"/>
+      <c r="H2399" t="inlineStr"/>
+      <c r="I2399" t="n">
+        <v>0.9106409764499459</v>
+      </c>
+      <c r="J2399" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2399" t="inlineStr"/>
+    </row>
+    <row r="2400">
+      <c r="A2400" s="1" t="n">
+        <v>2398</v>
+      </c>
+      <c r="B2400" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0893.png</t>
+        </is>
+      </c>
+      <c r="C2400" t="inlineStr"/>
+      <c r="D2400" t="inlineStr"/>
+      <c r="E2400" t="inlineStr"/>
+      <c r="F2400" t="inlineStr">
+        <is>
+          <t>O=C(COc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O)NCCCCCCCCNC(=O)c1cccc(C#Cc2cc(NC(=O)Nc3ccnc(Cl)c3)ccn2)c1</t>
+        </is>
+      </c>
+      <c r="G2400" t="inlineStr"/>
+      <c r="H2400" t="inlineStr"/>
+      <c r="I2400" t="n">
+        <v>0.8996477825321679</v>
+      </c>
+      <c r="J2400" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2400" t="inlineStr"/>
+    </row>
+    <row r="2401">
+      <c r="A2401" s="1" t="n">
+        <v>2399</v>
+      </c>
+      <c r="B2401" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0897.png</t>
+        </is>
+      </c>
+      <c r="C2401" t="inlineStr"/>
+      <c r="D2401" t="inlineStr"/>
+      <c r="E2401" t="inlineStr"/>
+      <c r="F2401" t="inlineStr">
+        <is>
+          <t>CN(C)C(=O)c1cc2cnc(Nc3ccc(C(=O)NCCCC#Cc4cccc5c4CN(C4CCC(=O)NC4=O)C5=O)cc3)nc2n1C1CCCC1</t>
+        </is>
+      </c>
+      <c r="G2401" t="inlineStr"/>
+      <c r="H2401" t="inlineStr"/>
+      <c r="I2401" t="n">
+        <v>0.914999637988988</v>
+      </c>
+      <c r="J2401" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2401" t="inlineStr"/>
+    </row>
+    <row r="2402">
+      <c r="A2402" s="1" t="n">
+        <v>2400</v>
+      </c>
+      <c r="B2402" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0901.png</t>
+        </is>
+      </c>
+      <c r="C2402" t="inlineStr"/>
+      <c r="D2402" t="inlineStr"/>
+      <c r="E2402" t="inlineStr"/>
+      <c r="F2402" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(OCCOCCOCCOC4CCN(c5ccc(-c6nc7cc(-c8cccnc8)ccc7s6)cn5)C4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2402" t="inlineStr"/>
+      <c r="H2402" t="inlineStr"/>
+      <c r="I2402" t="n">
+        <v>0.8792618908387203</v>
+      </c>
+      <c r="J2402" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2402" t="inlineStr"/>
+    </row>
+    <row r="2403">
+      <c r="A2403" s="1" t="n">
+        <v>2401</v>
+      </c>
+      <c r="B2403" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0905.png</t>
+        </is>
+      </c>
+      <c r="C2403" t="inlineStr"/>
+      <c r="D2403" t="inlineStr"/>
+      <c r="E2403" t="inlineStr"/>
+      <c r="F2403" t="inlineStr">
+        <is>
+          <t>CNc1ccc(-c2nc3ccc(OCCOCCOCC(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)C)cc3s2)cc1</t>
+        </is>
+      </c>
+      <c r="G2403" t="inlineStr"/>
+      <c r="H2403" t="inlineStr"/>
+      <c r="I2403" t="n">
+        <v>0.8905005548170262</v>
+      </c>
+      <c r="J2403" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2403" t="inlineStr"/>
+    </row>
+    <row r="2404">
+      <c r="A2404" s="1" t="n">
+        <v>2402</v>
+      </c>
+      <c r="B2404" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0909.png</t>
+        </is>
+      </c>
+      <c r="C2404" t="inlineStr"/>
+      <c r="D2404" t="inlineStr"/>
+      <c r="E2404" t="inlineStr"/>
+      <c r="F2404" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(CCNc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2404" t="inlineStr"/>
+      <c r="H2404" t="inlineStr"/>
+      <c r="I2404" t="n">
+        <v>0.9085851516305709</v>
+      </c>
+      <c r="J2404" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2404" t="inlineStr"/>
+    </row>
+    <row r="2405">
+      <c r="A2405" s="1" t="n">
+        <v>2403</v>
+      </c>
+      <c r="B2405" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0917.png</t>
+        </is>
+      </c>
+      <c r="C2405" t="inlineStr"/>
+      <c r="D2405" t="inlineStr"/>
+      <c r="E2405" t="inlineStr"/>
+      <c r="F2405" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5(C)CCN(C(=O)CN6CCN(CCCc7cccc8c7CN(C7CCC(=O)NC7=O)C8=O)CC6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2405" t="inlineStr"/>
+      <c r="H2405" t="inlineStr"/>
+      <c r="I2405" t="n">
+        <v>0.863291984246128</v>
+      </c>
+      <c r="J2405" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2405" t="inlineStr"/>
+    </row>
+    <row r="2406">
+      <c r="A2406" s="1" t="n">
+        <v>2404</v>
+      </c>
+      <c r="B2406" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0925.png</t>
+        </is>
+      </c>
+      <c r="C2406" t="inlineStr"/>
+      <c r="D2406" t="inlineStr"/>
+      <c r="E2406" t="inlineStr"/>
+      <c r="F2406" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](c2cc(OCCOCCOCCOc3ccc(CN4C(=O)/C(=C\C=C\c5ccc([N+](=O)[O-])cc5)c5ccccc54)cc3)no2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2406" t="inlineStr"/>
+      <c r="H2406" t="inlineStr"/>
+      <c r="I2406" t="n">
+        <v>0.8674763219058576</v>
+      </c>
+      <c r="J2406" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2406" t="inlineStr"/>
+    </row>
+    <row r="2407">
+      <c r="A2407" s="1" t="n">
+        <v>2405</v>
+      </c>
+      <c r="B2407" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0929.png</t>
+        </is>
+      </c>
+      <c r="C2407" t="inlineStr"/>
+      <c r="D2407" t="inlineStr"/>
+      <c r="E2407" t="inlineStr"/>
+      <c r="F2407" t="inlineStr">
+        <is>
+          <t>NC(=O)c1ncc(-c2nccs2)nc1Nc1ccc(N2CCC3(CCN(Cc4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)CC2)cc1</t>
+        </is>
+      </c>
+      <c r="G2407" t="inlineStr"/>
+      <c r="H2407" t="inlineStr"/>
+      <c r="I2407" t="n">
+        <v>0.8964342366397184</v>
+      </c>
+      <c r="J2407" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2407" t="inlineStr"/>
+    </row>
+    <row r="2408">
+      <c r="A2408" s="1" t="n">
+        <v>2406</v>
+      </c>
+      <c r="B2408" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0937.png</t>
+        </is>
+      </c>
+      <c r="C2408" t="inlineStr"/>
+      <c r="D2408" t="inlineStr"/>
+      <c r="E2408" t="inlineStr"/>
+      <c r="F2408" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(N4CCN(CCN5CCC(O[C@@H]6C[C@@H](Oc7ccc(/C=C/c8cc(-c9nccs9)on8)cc7)C6)CC5)CC4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2408" t="inlineStr"/>
+      <c r="H2408" t="inlineStr"/>
+      <c r="I2408" t="n">
+        <v>0.8912308538098487</v>
+      </c>
+      <c r="J2408" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2408" t="inlineStr"/>
+    </row>
+    <row r="2409">
+      <c r="A2409" s="1" t="n">
+        <v>2407</v>
+      </c>
+      <c r="B2409" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0949.png</t>
+        </is>
+      </c>
+      <c r="C2409" t="inlineStr"/>
+      <c r="D2409" t="inlineStr"/>
+      <c r="E2409" t="inlineStr"/>
+      <c r="F2409" t="inlineStr">
+        <is>
+          <t>CCCCC(Cc1c[nH]c2ccccc12)NC(=O)c1cnc(N2CCN(CCOCCOCCOCCOCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)CC2)s1</t>
+        </is>
+      </c>
+      <c r="G2409" t="inlineStr"/>
+      <c r="H2409" t="inlineStr"/>
+      <c r="I2409" t="n">
+        <v>0.8868399185994743</v>
+      </c>
+      <c r="J2409" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2409" t="inlineStr"/>
+    </row>
+    <row r="2410">
+      <c r="A2410" s="1" t="n">
+        <v>2408</v>
+      </c>
+      <c r="B2410" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0953.png</t>
+        </is>
+      </c>
+      <c r="C2410" t="inlineStr"/>
+      <c r="D2410" t="inlineStr"/>
+      <c r="E2410" t="inlineStr"/>
+      <c r="F2410" t="inlineStr">
+        <is>
+          <t>Nc1nnc(-c2ccccc2O)cc1-c1cnn(C2CCN([C@@H]3CC[C@@H](CNc4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G2410" t="inlineStr"/>
+      <c r="H2410" t="inlineStr"/>
+      <c r="I2410" t="n">
+        <v>0.8887356444714017</v>
+      </c>
+      <c r="J2410" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2410" t="inlineStr"/>
+    </row>
+    <row r="2411">
+      <c r="A2411" s="1" t="n">
+        <v>2409</v>
+      </c>
+      <c r="B2411" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0957.png</t>
+        </is>
+      </c>
+      <c r="C2411" t="inlineStr"/>
+      <c r="D2411" t="inlineStr"/>
+      <c r="E2411" t="inlineStr"/>
+      <c r="F2411" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(N5CCN(CCCCc6cccc7c6CN(C6CCC(=O)NC6=O)C7=O)CC5)nc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2411" t="inlineStr"/>
+      <c r="H2411" t="inlineStr"/>
+      <c r="I2411" t="n">
+        <v>0.8604505266326453</v>
+      </c>
+      <c r="J2411" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2411" t="inlineStr"/>
+    </row>
+    <row r="2412">
+      <c r="A2412" s="1" t="n">
+        <v>2410</v>
+      </c>
+      <c r="B2412" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0969.png</t>
+        </is>
+      </c>
+      <c r="C2412" t="inlineStr"/>
+      <c r="D2412" t="inlineStr"/>
+      <c r="E2412" t="inlineStr"/>
+      <c r="F2412" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(N4CCN(CCCO[C@@H]5C[C@@H](Oc6ccc7c(c6)Sc6cc([N+](=O)[O-])ccc6N7)C5)CC4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2412" t="inlineStr"/>
+      <c r="H2412" t="inlineStr"/>
+      <c r="I2412" t="n">
+        <v>0.8516185566976728</v>
+      </c>
+      <c r="J2412" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2412" t="inlineStr"/>
+    </row>
+    <row r="2413">
+      <c r="A2413" s="1" t="n">
+        <v>2411</v>
+      </c>
+      <c r="B2413" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0977.png</t>
+        </is>
+      </c>
+      <c r="C2413" t="inlineStr"/>
+      <c r="D2413" t="inlineStr"/>
+      <c r="E2413" t="inlineStr"/>
+      <c r="F2413" t="inlineStr">
+        <is>
+          <t>Cc1cc(Nc2nc(N3CCC[C@@H](NC(=O)N4CCC5(CC4)CCN(c4ccc6c(c4)C(=O)N(C4CCC(=O)NC4=O)C6=O)CC5)C3)cnc2C(N)=O)sn1</t>
+        </is>
+      </c>
+      <c r="G2413" t="inlineStr"/>
+      <c r="H2413" t="inlineStr"/>
+      <c r="I2413" t="n">
+        <v>0.9068213004699242</v>
+      </c>
+      <c r="J2413" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2413" t="inlineStr"/>
+    </row>
+    <row r="2414">
+      <c r="A2414" s="1" t="n">
+        <v>2412</v>
+      </c>
+      <c r="B2414" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0981.png</t>
+        </is>
+      </c>
+      <c r="C2414" t="inlineStr"/>
+      <c r="D2414" t="inlineStr"/>
+      <c r="E2414" t="inlineStr"/>
+      <c r="F2414" t="inlineStr">
+        <is>
+          <t>COc1cc(C2=CN(C)C(=O)N(C)C2)cc(OC)c1CN1CCC(CCN2CCN(c3ccc4c(c3)CN(C3CCC(=O)NC3=O)C4=O)CC2)CC1</t>
+        </is>
+      </c>
+      <c r="G2414" t="inlineStr"/>
+      <c r="H2414" t="inlineStr"/>
+      <c r="I2414" t="n">
+        <v>0.9121547745689437</v>
+      </c>
+      <c r="J2414" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2414" t="inlineStr"/>
+    </row>
+    <row r="2415">
+      <c r="A2415" s="1" t="n">
+        <v>2413</v>
+      </c>
+      <c r="B2415" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0993.png</t>
+        </is>
+      </c>
+      <c r="C2415" t="inlineStr"/>
+      <c r="D2415" t="inlineStr"/>
+      <c r="E2415" t="inlineStr"/>
+      <c r="F2415" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@H]2CCCN(c3cnc(C(N)=O)c(Nc4cnn(C5CCN(CC6CN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)CC5)c4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2415" t="inlineStr"/>
+      <c r="H2415" t="inlineStr"/>
+      <c r="I2415" t="n">
+        <v>0.8947429194216854</v>
+      </c>
+      <c r="J2415" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2415" t="inlineStr"/>
+    </row>
+    <row r="2416">
+      <c r="A2416" s="1" t="n">
+        <v>2414</v>
+      </c>
+      <c r="B2416" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1005.png</t>
+        </is>
+      </c>
+      <c r="C2416" t="inlineStr"/>
+      <c r="D2416" t="inlineStr"/>
+      <c r="E2416" t="inlineStr"/>
+      <c r="F2416" t="inlineStr">
+        <is>
+          <t>O=C(COc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O)NCCOCCOCCOCCN1CCC[C@@H](Nc2ncc(Cl)c(-c3c[nH]c4ccccc34)n2)C1</t>
+        </is>
+      </c>
+      <c r="G2416" t="inlineStr"/>
+      <c r="H2416" t="inlineStr"/>
+      <c r="I2416" t="n">
+        <v>0.8917668323750861</v>
+      </c>
+      <c r="J2416" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2416" t="inlineStr"/>
+    </row>
+    <row r="2417">
+      <c r="A2417" s="1" t="n">
+        <v>2415</v>
+      </c>
+      <c r="B2417" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1013.png</t>
+        </is>
+      </c>
+      <c r="C2417" t="inlineStr"/>
+      <c r="D2417" t="inlineStr"/>
+      <c r="E2417" t="inlineStr"/>
+      <c r="F2417" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(N5CCCC6(C5)CN(c5cccc7c5C(=O)N(C5CCC(=O)NC5=O)C7=O)C6)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2417" t="inlineStr"/>
+      <c r="H2417" t="inlineStr"/>
+      <c r="I2417" t="n">
+        <v>0.8777285712399677</v>
+      </c>
+      <c r="J2417" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2417" t="inlineStr"/>
+    </row>
+    <row r="2418">
+      <c r="A2418" s="1" t="n">
+        <v>2416</v>
+      </c>
+      <c r="B2418" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1017.png</t>
+        </is>
+      </c>
+      <c r="C2418" t="inlineStr"/>
+      <c r="D2418" t="inlineStr"/>
+      <c r="E2418" t="inlineStr"/>
+      <c r="F2418" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CCN(C[C@H]6CCCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2418" t="inlineStr"/>
+      <c r="H2418" t="inlineStr"/>
+      <c r="I2418" t="n">
+        <v>0.8958822148129856</v>
+      </c>
+      <c r="J2418" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2418" t="inlineStr"/>
+    </row>
+    <row r="2419">
+      <c r="A2419" s="1" t="n">
+        <v>2417</v>
+      </c>
+      <c r="B2419" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1021.png</t>
+        </is>
+      </c>
+      <c r="C2419" t="inlineStr"/>
+      <c r="D2419" t="inlineStr"/>
+      <c r="E2419" t="inlineStr"/>
+      <c r="F2419" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)[C@@H]2CC[C@H](CN3CCC(n4cc(-c5cc(-c6ccccc6O)nnc5N)cn4)CC3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2419" t="inlineStr"/>
+      <c r="H2419" t="inlineStr"/>
+      <c r="I2419" t="n">
+        <v>0.8931944680978151</v>
+      </c>
+      <c r="J2419" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2419" t="inlineStr"/>
+    </row>
+    <row r="2420">
+      <c r="A2420" s="1" t="n">
+        <v>2418</v>
+      </c>
+      <c r="B2420" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1025.png</t>
+        </is>
+      </c>
+      <c r="C2420" t="inlineStr"/>
+      <c r="D2420" t="inlineStr"/>
+      <c r="E2420" t="inlineStr"/>
+      <c r="F2420" t="inlineStr">
+        <is>
+          <t>CC(C)(C)[C@H](NC(=O)C1(F)CC1)C(=O)N1C[C@H](O)C[C@H]1C(=O)NCc1ccc(-c2scnc2-c2ccc3cn[nH]c3c2)cc1OCCc1ccc(CN2CCN(c3cc(-c4ccccc4O)nnc3N)CC2)cc1</t>
+        </is>
+      </c>
+      <c r="G2420" t="inlineStr"/>
+      <c r="H2420" t="inlineStr"/>
+      <c r="I2420" t="n">
+        <v>0.89821042027687</v>
+      </c>
+      <c r="J2420" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2420" t="inlineStr"/>
+    </row>
+    <row r="2421">
+      <c r="A2421" s="1" t="n">
+        <v>2419</v>
+      </c>
+      <c r="B2421" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1029.png</t>
+        </is>
+      </c>
+      <c r="C2421" t="inlineStr"/>
+      <c r="D2421" t="inlineStr"/>
+      <c r="E2421" t="inlineStr"/>
+      <c r="F2421" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)C(c2cc(O[C@H]3CC[C@@H](N4CCC(c5cnc(N)nc5)CC4)CC3)no2)C(C)C)cc1.Nc1nnc(-c2ccccc2O)cc1N1CCCCCC1</t>
+        </is>
+      </c>
+      <c r="G2421" t="inlineStr"/>
+      <c r="H2421" t="inlineStr"/>
+      <c r="I2421" t="n">
+        <v>0.8782990724751671</v>
+      </c>
+      <c r="J2421" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2421" t="inlineStr"/>
+    </row>
+    <row r="2422">
+      <c r="A2422" s="1" t="n">
+        <v>2420</v>
+      </c>
+      <c r="B2422" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1033.png</t>
+        </is>
+      </c>
+      <c r="C2422" t="inlineStr"/>
+      <c r="D2422" t="inlineStr"/>
+      <c r="E2422" t="inlineStr"/>
+      <c r="F2422" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5(C)CCN(C6CC(Nc7cccc8c7C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2422" t="inlineStr"/>
+      <c r="H2422" t="inlineStr"/>
+      <c r="I2422" t="n">
+        <v>0.8664060143946055</v>
+      </c>
+      <c r="J2422" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2422" t="inlineStr"/>
+    </row>
+    <row r="2423">
+      <c r="A2423" s="1" t="n">
+        <v>2421</v>
+      </c>
+      <c r="B2423" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1041.png</t>
+        </is>
+      </c>
+      <c r="C2423" t="inlineStr"/>
+      <c r="D2423" t="inlineStr"/>
+      <c r="E2423" t="inlineStr"/>
+      <c r="F2423" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(OCCOCCOCCOC4CCN(c5ccc(-c6ccc7cc(-c8cccnc8)sc7n6)cn5)C4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2423" t="inlineStr"/>
+      <c r="H2423" t="inlineStr"/>
+      <c r="I2423" t="n">
+        <v>0.8857379057250647</v>
+      </c>
+      <c r="J2423" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2423" t="inlineStr"/>
+    </row>
+    <row r="2424">
+      <c r="A2424" s="1" t="n">
+        <v>2422</v>
+      </c>
+      <c r="B2424" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1045.png</t>
+        </is>
+      </c>
+      <c r="C2424" t="inlineStr"/>
+      <c r="D2424" t="inlineStr"/>
+      <c r="E2424" t="inlineStr"/>
+      <c r="F2424" t="inlineStr">
+        <is>
+          <t>CC(c1ccc(C(=O)NCCOCCOCCOCCNc2cccc3c2C(=O)N(C2CCC(=O)NC2=O)C3=O)cc1)n1cc(-c2cc(-c3ccccc3O)nnc2N)cn1</t>
+        </is>
+      </c>
+      <c r="G2424" t="inlineStr"/>
+      <c r="H2424" t="inlineStr"/>
+      <c r="I2424" t="n">
+        <v>0.8894290101392613</v>
+      </c>
+      <c r="J2424" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2424" t="inlineStr"/>
+    </row>
+    <row r="2425">
+      <c r="A2425" s="1" t="n">
+        <v>2423</v>
+      </c>
+      <c r="B2425" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1049.png</t>
+        </is>
+      </c>
+      <c r="C2425" t="inlineStr"/>
+      <c r="D2425" t="inlineStr"/>
+      <c r="E2425" t="inlineStr"/>
+      <c r="F2425" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccc(N2C(=O)C(C)(C)N(c3ccc(-c4ccc(OCCNC(=O)COc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)cc4)nc3)C2=S)c(F)c1OC</t>
+        </is>
+      </c>
+      <c r="G2425" t="inlineStr"/>
+      <c r="H2425" t="inlineStr"/>
+      <c r="I2425" t="n">
+        <v>0.855635124581425</v>
+      </c>
+      <c r="J2425" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2425" t="inlineStr"/>
+    </row>
+    <row r="2426">
+      <c r="A2426" s="1" t="n">
+        <v>2424</v>
+      </c>
+      <c r="B2426" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1061.png</t>
+        </is>
+      </c>
+      <c r="C2426" t="inlineStr"/>
+      <c r="D2426" t="inlineStr"/>
+      <c r="E2426" t="inlineStr"/>
+      <c r="F2426" t="inlineStr">
+        <is>
+          <t>Cc1nc(N2C3CCC2CN(c2cc(-c4ccccc4O)nnc2N)C3)ncc1[C@@H]1CC[C@@H](C(=O)N[C@H](C(=O)N2C[C@H](O)C[C@H]2C(=O)NCc2ccc(-c3scnc3C)cc2)C(C)(C)C)CC1</t>
+        </is>
+      </c>
+      <c r="G2426" t="inlineStr"/>
+      <c r="H2426" t="inlineStr"/>
+      <c r="I2426" t="n">
+        <v>0.8794271528741051</v>
+      </c>
+      <c r="J2426" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2426" t="inlineStr"/>
+    </row>
+    <row r="2427">
+      <c r="A2427" s="1" t="n">
+        <v>2425</v>
+      </c>
+      <c r="B2427" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1065.png</t>
+        </is>
+      </c>
+      <c r="C2427" t="inlineStr"/>
+      <c r="D2427" t="inlineStr"/>
+      <c r="E2427" t="inlineStr"/>
+      <c r="F2427" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@H]2CCCN(c3cnc(C(N)=O)c(Nc4cnn(C5CCN(C6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)c4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2427" t="inlineStr"/>
+      <c r="H2427" t="inlineStr"/>
+      <c r="I2427" t="n">
+        <v>0.8817714555086814</v>
+      </c>
+      <c r="J2427" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2427" t="inlineStr"/>
+    </row>
+    <row r="2428">
+      <c r="A2428" s="1" t="n">
+        <v>2426</v>
+      </c>
+      <c r="B2428" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1069.png</t>
+        </is>
+      </c>
+      <c r="C2428" t="inlineStr"/>
+      <c r="D2428" t="inlineStr"/>
+      <c r="E2428" t="inlineStr"/>
+      <c r="F2428" t="inlineStr">
+        <is>
+          <t>CN(C)C(=O)c1cc2cnc(Nc3ccc(C(=O)NCCCNC(=O)COc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)cc3)nc2n1C1CCCC1</t>
+        </is>
+      </c>
+      <c r="G2428" t="inlineStr"/>
+      <c r="H2428" t="inlineStr"/>
+      <c r="I2428" t="n">
+        <v>0.9119257161864824</v>
+      </c>
+      <c r="J2428" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2428" t="inlineStr"/>
+    </row>
+    <row r="2429">
+      <c r="A2429" s="1" t="n">
+        <v>2427</v>
+      </c>
+      <c r="B2429" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1085.png</t>
+        </is>
+      </c>
+      <c r="C2429" t="inlineStr"/>
+      <c r="D2429" t="inlineStr"/>
+      <c r="E2429" t="inlineStr"/>
+      <c r="F2429" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(C[C@H]4C[C@H](c5ccc6c(c5)CN(C5CCC(=O)NC5=O)C6=O)C4)CC3)CC2)c(C)cc1Nc1ncc(Br)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2429" t="inlineStr"/>
+      <c r="H2429" t="inlineStr"/>
+      <c r="I2429" t="n">
+        <v>0.897420716746503</v>
+      </c>
+      <c r="J2429" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2429" t="inlineStr"/>
+    </row>
+    <row r="2430">
+      <c r="A2430" s="1" t="n">
+        <v>2428</v>
+      </c>
+      <c r="B2430" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1093.png</t>
+        </is>
+      </c>
+      <c r="C2430" t="inlineStr"/>
+      <c r="D2430" t="inlineStr"/>
+      <c r="E2430" t="inlineStr"/>
+      <c r="F2430" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(OCCCCCN4CCC(O[C@@H]5C[C@@H](Oc6ccc7c(c6)Sc6cc([N+](=O)[O-])ccc6N7)C5)CC4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2430" t="inlineStr"/>
+      <c r="H2430" t="inlineStr"/>
+      <c r="I2430" t="n">
+        <v>0.8651184375359481</v>
+      </c>
+      <c r="J2430" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2430" t="inlineStr"/>
+    </row>
+    <row r="2431">
+      <c r="A2431" s="1" t="n">
+        <v>2429</v>
+      </c>
+      <c r="B2431" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1097.png</t>
+        </is>
+      </c>
+      <c r="C2431" t="inlineStr"/>
+      <c r="D2431" t="inlineStr"/>
+      <c r="E2431" t="inlineStr"/>
+      <c r="F2431" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(OCCOCCOCCOc4ccc(C(=O)Nc5ccc(N6CCN(c7cccnc7)CC6)cc5)cc4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2431" t="inlineStr"/>
+      <c r="H2431" t="inlineStr"/>
+      <c r="I2431" t="n">
+        <v>0.9028137036698931</v>
+      </c>
+      <c r="J2431" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2431" t="inlineStr"/>
+    </row>
+    <row r="2432">
+      <c r="A2432" s="1" t="n">
+        <v>2430</v>
+      </c>
+      <c r="B2432" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0854.png</t>
+        </is>
+      </c>
+      <c r="C2432" t="inlineStr"/>
+      <c r="D2432" t="inlineStr"/>
+      <c r="E2432" t="inlineStr"/>
+      <c r="F2432" t="inlineStr">
+        <is>
+          <t>NC(=O)c1ncc(N2CCCCC2)nc1Nc1ccc(C2CCN(C[C@@H]3CCN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)C3)CC2)cc1</t>
+        </is>
+      </c>
+      <c r="G2432" t="inlineStr"/>
+      <c r="H2432" t="inlineStr"/>
+      <c r="I2432" t="n">
+        <v>0.9069304511417354</v>
+      </c>
+      <c r="J2432" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2432" t="inlineStr"/>
+    </row>
+    <row r="2433">
+      <c r="A2433" s="1" t="n">
+        <v>2431</v>
+      </c>
+      <c r="B2433" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0858.png</t>
+        </is>
+      </c>
+      <c r="C2433" t="inlineStr"/>
+      <c r="D2433" t="inlineStr"/>
+      <c r="E2433" t="inlineStr"/>
+      <c r="F2433" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(OCCCCCN4CCC(O[C@@H]5C[C@@H](Oc6ccc(CN7C(=O)/C(=C\C=C\c8ccc([N+](=O)[O-])cc8)c8ccccc87)cc6)C5)CC4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2433" t="inlineStr"/>
+      <c r="H2433" t="inlineStr"/>
+      <c r="I2433" t="n">
+        <v>0.8585626818721126</v>
+      </c>
+      <c r="J2433" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2433" t="inlineStr"/>
+    </row>
+    <row r="2434">
+      <c r="A2434" s="1" t="n">
+        <v>2432</v>
+      </c>
+      <c r="B2434" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0862.png</t>
+        </is>
+      </c>
+      <c r="C2434" t="inlineStr"/>
+      <c r="D2434" t="inlineStr"/>
+      <c r="E2434" t="inlineStr"/>
+      <c r="F2434" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C23CCC(CN4CCC(c5cnc(N6C7CCC6CN(c6cc(-c8ccccc8O)nnc6N)C7)nc5)CC4)(CC2)CC3)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2434" t="inlineStr"/>
+      <c r="H2434" t="inlineStr"/>
+      <c r="I2434" t="n">
+        <v>0.8510292031765135</v>
+      </c>
+      <c r="J2434" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2434" t="inlineStr"/>
+    </row>
+    <row r="2435">
+      <c r="A2435" s="1" t="n">
+        <v>2433</v>
+      </c>
+      <c r="B2435" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0866.png</t>
+        </is>
+      </c>
+      <c r="C2435" t="inlineStr"/>
+      <c r="D2435" t="inlineStr"/>
+      <c r="E2435" t="inlineStr"/>
+      <c r="F2435" t="inlineStr">
+        <is>
+          <t>NC(=O)c1ncc(N2CCCC(N3CCCC3=O)C2)nc1Nc1ccc(C2CCN(C[C@@H]3CCN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)C3)CC2)cc1</t>
+        </is>
+      </c>
+      <c r="G2435" t="inlineStr"/>
+      <c r="H2435" t="inlineStr"/>
+      <c r="I2435" t="n">
+        <v>0.9006416450693644</v>
+      </c>
+      <c r="J2435" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2435" t="inlineStr"/>
+    </row>
+    <row r="2436">
+      <c r="A2436" s="1" t="n">
+        <v>2434</v>
+      </c>
+      <c r="B2436" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0874.png</t>
+        </is>
+      </c>
+      <c r="C2436" t="inlineStr"/>
+      <c r="D2436" t="inlineStr"/>
+      <c r="E2436" t="inlineStr"/>
+      <c r="F2436" t="inlineStr">
+        <is>
+          <t>NC(=O)c1ncc(N2CCC[C@H](N3CCOC3=O)C2)nc1Nc1ccc(N2CCC(C3CN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)C3)CC2)cc1</t>
+        </is>
+      </c>
+      <c r="G2436" t="inlineStr"/>
+      <c r="H2436" t="inlineStr"/>
+      <c r="I2436" t="n">
+        <v>0.8985894789446192</v>
+      </c>
+      <c r="J2436" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2436" t="inlineStr"/>
+    </row>
+    <row r="2437">
+      <c r="A2437" s="1" t="n">
+        <v>2435</v>
+      </c>
+      <c r="B2437" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0878.png</t>
+        </is>
+      </c>
+      <c r="C2437" t="inlineStr"/>
+      <c r="D2437" t="inlineStr"/>
+      <c r="E2437" t="inlineStr"/>
+      <c r="F2437" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(N4CCN(CCN5CCC(OC6CN(CCCN7c8ccccc8Sc8ccccc87)C6)CC5)CC4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2437" t="inlineStr"/>
+      <c r="H2437" t="inlineStr"/>
+      <c r="I2437" t="n">
+        <v>0.8877778105429337</v>
+      </c>
+      <c r="J2437" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2437" t="inlineStr"/>
+    </row>
+    <row r="2438">
+      <c r="A2438" s="1" t="n">
+        <v>2436</v>
+      </c>
+      <c r="B2438" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0882.png</t>
+        </is>
+      </c>
+      <c r="C2438" t="inlineStr"/>
+      <c r="D2438" t="inlineStr"/>
+      <c r="E2438" t="inlineStr"/>
+      <c r="F2438" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2CC3(C2)CN(C2CCC(c4cnc(N5C6CCC5CN(c5cc(-c7ccccc7O)nnc5N)C6)nc4)CC2)C3)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2438" t="inlineStr"/>
+      <c r="H2438" t="inlineStr"/>
+      <c r="I2438" t="n">
+        <v>0.8611977599442989</v>
+      </c>
+      <c r="J2438" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2438" t="inlineStr"/>
+    </row>
+    <row r="2439">
+      <c r="A2439" s="1" t="n">
+        <v>2437</v>
+      </c>
+      <c r="B2439" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0886.png</t>
+        </is>
+      </c>
+      <c r="C2439" t="inlineStr"/>
+      <c r="D2439" t="inlineStr"/>
+      <c r="E2439" t="inlineStr"/>
+      <c r="F2439" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C(=O)NCCOCCOCCOCCNc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2439" t="inlineStr"/>
+      <c r="H2439" t="inlineStr"/>
+      <c r="I2439" t="n">
+        <v>0.8847741641937547</v>
+      </c>
+      <c r="J2439" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2439" t="inlineStr"/>
+    </row>
+    <row r="2440">
+      <c r="A2440" s="1" t="n">
+        <v>2438</v>
+      </c>
+      <c r="B2440" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0890.png</t>
+        </is>
+      </c>
+      <c r="C2440" t="inlineStr"/>
+      <c r="D2440" t="inlineStr"/>
+      <c r="E2440" t="inlineStr"/>
+      <c r="F2440" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3cccc(NCCCCCCCCCCCC(=O)OCc4cnc(Cl)cc4NC(=O)Nc4cc(C(F)F)ns4)c3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2440" t="inlineStr"/>
+      <c r="H2440" t="inlineStr"/>
+      <c r="I2440" t="n">
+        <v>0.9016887376903401</v>
+      </c>
+      <c r="J2440" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2440" t="inlineStr"/>
+    </row>
+    <row r="2441">
+      <c r="A2441" s="1" t="n">
+        <v>2439</v>
+      </c>
+      <c r="B2441" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0894.png</t>
+        </is>
+      </c>
+      <c r="C2441" t="inlineStr"/>
+      <c r="D2441" t="inlineStr"/>
+      <c r="E2441" t="inlineStr"/>
+      <c r="F2441" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](c2cc(N3CCN(CCCO[C@@H]4C[C@@H](Oc5ccc6c(c5)Sc5cc([N+](=O)[O-])ccc5N6)C4)CC3)no2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2441" t="inlineStr"/>
+      <c r="H2441" t="inlineStr"/>
+      <c r="I2441" t="n">
+        <v>0.8625909356850991</v>
+      </c>
+      <c r="J2441" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2441" t="inlineStr"/>
+    </row>
+    <row r="2442">
+      <c r="A2442" s="1" t="n">
+        <v>2440</v>
+      </c>
+      <c r="B2442" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0906.png</t>
+        </is>
+      </c>
+      <c r="C2442" t="inlineStr"/>
+      <c r="D2442" t="inlineStr"/>
+      <c r="E2442" t="inlineStr"/>
+      <c r="F2442" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(OCCOCCOCCn4cnc(Sc5cc(NS(=O)(=O)c6cccs6)c6ccccc6c5O)n4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2442" t="inlineStr"/>
+      <c r="H2442" t="inlineStr"/>
+      <c r="I2442" t="n">
+        <v>0.8711447221305412</v>
+      </c>
+      <c r="J2442" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2442" t="inlineStr"/>
+    </row>
+    <row r="2443">
+      <c r="A2443" s="1" t="n">
+        <v>2441</v>
+      </c>
+      <c r="B2443" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0910.png</t>
+        </is>
+      </c>
+      <c r="C2443" t="inlineStr"/>
+      <c r="D2443" t="inlineStr"/>
+      <c r="E2443" t="inlineStr"/>
+      <c r="F2443" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CN(C[C@H]6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)C5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2443" t="inlineStr"/>
+      <c r="H2443" t="inlineStr"/>
+      <c r="I2443" t="n">
+        <v>0.8921671450832064</v>
+      </c>
+      <c r="J2443" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2443" t="inlineStr"/>
+    </row>
+    <row r="2444">
+      <c r="A2444" s="1" t="n">
+        <v>2442</v>
+      </c>
+      <c r="B2444" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0914.png</t>
+        </is>
+      </c>
+      <c r="C2444" t="inlineStr"/>
+      <c r="D2444" t="inlineStr"/>
+      <c r="E2444" t="inlineStr"/>
+      <c r="F2444" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(N5CCN(CCC6CN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2444" t="inlineStr"/>
+      <c r="H2444" t="inlineStr"/>
+      <c r="I2444" t="n">
+        <v>0.8674212141402926</v>
+      </c>
+      <c r="J2444" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2444" t="inlineStr"/>
+    </row>
+    <row r="2445">
+      <c r="A2445" s="1" t="n">
+        <v>2443</v>
+      </c>
+      <c r="B2445" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0918.png</t>
+        </is>
+      </c>
+      <c r="C2445" t="inlineStr"/>
+      <c r="D2445" t="inlineStr"/>
+      <c r="E2445" t="inlineStr"/>
+      <c r="F2445" t="inlineStr">
+        <is>
+          <t>Nc1ncnc2c1c(-c1ccc(Oc3ccccc3)cc1)nn2C1CCN(CCCCCOCCOc2ccc3c(c2)CN(C2CCC(=O)NC2=O)C3=O)CC1</t>
+        </is>
+      </c>
+      <c r="G2445" t="inlineStr"/>
+      <c r="H2445" t="inlineStr"/>
+      <c r="I2445" t="n">
+        <v>0.9086980651368326</v>
+      </c>
+      <c r="J2445" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2445" t="inlineStr"/>
+    </row>
+    <row r="2446">
+      <c r="A2446" s="1" t="n">
+        <v>2444</v>
+      </c>
+      <c r="B2446" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0922.png</t>
+        </is>
+      </c>
+      <c r="C2446" t="inlineStr"/>
+      <c r="D2446" t="inlineStr"/>
+      <c r="E2446" t="inlineStr"/>
+      <c r="F2446" t="inlineStr">
+        <is>
+          <t>NC(=O)c1ncc(N2CCC[C@H](N3CCCC3=O)C2)nc1Nc1ccc(C2CN(C[C@@H]3CCN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)C3)C2)cc1</t>
+        </is>
+      </c>
+      <c r="G2446" t="inlineStr"/>
+      <c r="H2446" t="inlineStr"/>
+      <c r="I2446" t="n">
+        <v>0.8876484725356328</v>
+      </c>
+      <c r="J2446" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2446" t="inlineStr"/>
+    </row>
+    <row r="2447">
+      <c r="A2447" s="1" t="n">
+        <v>2445</v>
+      </c>
+      <c r="B2447" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0926.png</t>
+        </is>
+      </c>
+      <c r="C2447" t="inlineStr"/>
+      <c r="D2447" t="inlineStr"/>
+      <c r="E2447" t="inlineStr"/>
+      <c r="F2447" t="inlineStr">
+        <is>
+          <t>COc1cc2nn(C3CC4(CCN(C(=O)C5CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)CC4)C3)cc2cc1NC(=O)c1cccc(C(F)F)n1</t>
+        </is>
+      </c>
+      <c r="G2447" t="inlineStr"/>
+      <c r="H2447" t="inlineStr"/>
+      <c r="I2447" t="n">
+        <v>0.8933809573260341</v>
+      </c>
+      <c r="J2447" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2447" t="inlineStr"/>
+    </row>
+    <row r="2448">
+      <c r="A2448" s="1" t="n">
+        <v>2446</v>
+      </c>
+      <c r="B2448" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0938.png</t>
+        </is>
+      </c>
+      <c r="C2448" t="inlineStr"/>
+      <c r="D2448" t="inlineStr"/>
+      <c r="E2448" t="inlineStr"/>
+      <c r="F2448" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(N5CCN(CC6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2448" t="inlineStr"/>
+      <c r="H2448" t="inlineStr"/>
+      <c r="I2448" t="n">
+        <v>0.8932747712612046</v>
+      </c>
+      <c r="J2448" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2448" t="inlineStr"/>
+    </row>
+    <row r="2449">
+      <c r="A2449" s="1" t="n">
+        <v>2447</v>
+      </c>
+      <c r="B2449" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0942.png</t>
+        </is>
+      </c>
+      <c r="C2449" t="inlineStr"/>
+      <c r="D2449" t="inlineStr"/>
+      <c r="E2449" t="inlineStr"/>
+      <c r="F2449" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5(C)CCN([C@H]6C[C@@H](Nc7cccc8c7C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2449" t="inlineStr"/>
+      <c r="H2449" t="inlineStr"/>
+      <c r="I2449" t="n">
+        <v>0.8885711349636168</v>
+      </c>
+      <c r="J2449" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2449" t="inlineStr"/>
+    </row>
+    <row r="2450">
+      <c r="A2450" s="1" t="n">
+        <v>2448</v>
+      </c>
+      <c r="B2450" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0946.png</t>
+        </is>
+      </c>
+      <c r="C2450" t="inlineStr"/>
+      <c r="D2450" t="inlineStr"/>
+      <c r="E2450" t="inlineStr"/>
+      <c r="F2450" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@H](c2cc(N3CCN(CCCO[C@@H]4C[C@@H](Oc5ccc6c(c5)Sc5cc([N+](=O)[O-])ccc5N6)C4)CC3)no2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2450" t="inlineStr"/>
+      <c r="H2450" t="inlineStr"/>
+      <c r="I2450" t="n">
+        <v>0.8619008481273934</v>
+      </c>
+      <c r="J2450" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2450" t="inlineStr"/>
+    </row>
+    <row r="2451">
+      <c r="A2451" s="1" t="n">
+        <v>2449</v>
+      </c>
+      <c r="B2451" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0950.png</t>
+        </is>
+      </c>
+      <c r="C2451" t="inlineStr"/>
+      <c r="D2451" t="inlineStr"/>
+      <c r="E2451" t="inlineStr"/>
+      <c r="F2451" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CCN(Cc6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2451" t="inlineStr"/>
+      <c r="H2451" t="inlineStr"/>
+      <c r="I2451" t="n">
+        <v>0.8804623750170856</v>
+      </c>
+      <c r="J2451" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2451" t="inlineStr"/>
+    </row>
+    <row r="2452">
+      <c r="A2452" s="1" t="n">
+        <v>2450</v>
+      </c>
+      <c r="B2452" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0954.png</t>
+        </is>
+      </c>
+      <c r="C2452" t="inlineStr"/>
+      <c r="D2452" t="inlineStr"/>
+      <c r="E2452" t="inlineStr"/>
+      <c r="F2452" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)COCCOCCOCCOc2ccc(N3CCc4nc(-c5ccc(N6CCCC6)nc5)sc4C3=O)cn2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2452" t="inlineStr"/>
+      <c r="H2452" t="inlineStr"/>
+      <c r="I2452" t="n">
+        <v>0.8823088657034199</v>
+      </c>
+      <c r="J2452" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2452" t="inlineStr"/>
+    </row>
+    <row r="2453">
+      <c r="A2453" s="1" t="n">
+        <v>2451</v>
+      </c>
+      <c r="B2453" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0962.png</t>
+        </is>
+      </c>
+      <c r="C2453" t="inlineStr"/>
+      <c r="D2453" t="inlineStr"/>
+      <c r="E2453" t="inlineStr"/>
+      <c r="F2453" t="inlineStr">
+        <is>
+          <t>CCCCC(Cc1c[nH]c2ccccc12)NC(=O)c1cnc(N2CCN(c3ccc(OCCOCCOc4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)cc3)CC2)s1</t>
+        </is>
+      </c>
+      <c r="G2453" t="inlineStr"/>
+      <c r="H2453" t="inlineStr"/>
+      <c r="I2453" t="n">
+        <v>0.8735335720722636</v>
+      </c>
+      <c r="J2453" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2453" t="inlineStr"/>
+    </row>
+    <row r="2454">
+      <c r="A2454" s="1" t="n">
+        <v>2452</v>
+      </c>
+      <c r="B2454" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0966.png</t>
+        </is>
+      </c>
+      <c r="C2454" t="inlineStr"/>
+      <c r="D2454" t="inlineStr"/>
+      <c r="E2454" t="inlineStr"/>
+      <c r="F2454" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)[C@@H]2CC3(C2)C[C@@H](N2CCN(c4cnc(N5C6CCC5CN(c5cc(-c7ccccc7O)nnc5N)C6)nc4)CC2)C3)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2454" t="inlineStr"/>
+      <c r="H2454" t="inlineStr"/>
+      <c r="I2454" t="n">
+        <v>0.8788955132904207</v>
+      </c>
+      <c r="J2454" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2454" t="inlineStr"/>
+    </row>
+    <row r="2455">
+      <c r="A2455" s="1" t="n">
+        <v>2453</v>
+      </c>
+      <c r="B2455" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0970.png</t>
+        </is>
+      </c>
+      <c r="C2455" t="inlineStr"/>
+      <c r="D2455" t="inlineStr"/>
+      <c r="E2455" t="inlineStr"/>
+      <c r="F2455" t="inlineStr">
+        <is>
+          <t>NC(=O)c1ncc(-c2nccs2)nc1Nc1ccc(C2CCN(C[C@@H]3CCN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)C3)CC2)cc1</t>
+        </is>
+      </c>
+      <c r="G2455" t="inlineStr"/>
+      <c r="H2455" t="inlineStr"/>
+      <c r="I2455" t="n">
+        <v>0.9040744970301162</v>
+      </c>
+      <c r="J2455" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2455" t="inlineStr"/>
+    </row>
+    <row r="2456">
+      <c r="A2456" s="1" t="n">
+        <v>2454</v>
+      </c>
+      <c r="B2456" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0974.png</t>
+        </is>
+      </c>
+      <c r="C2456" t="inlineStr"/>
+      <c r="D2456" t="inlineStr"/>
+      <c r="E2456" t="inlineStr"/>
+      <c r="F2456" t="inlineStr">
+        <is>
+          <t>O=C(COc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O)NCCCCCC(=O)N1CCC[C@@H](Nc2ncc(Cl)c(-c3c[nH]c4ccccc34)n2)C1</t>
+        </is>
+      </c>
+      <c r="G2456" t="inlineStr"/>
+      <c r="H2456" t="inlineStr"/>
+      <c r="I2456" t="n">
+        <v>0.9048950838625566</v>
+      </c>
+      <c r="J2456" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2456" t="inlineStr"/>
+    </row>
+    <row r="2457">
+      <c r="A2457" s="1" t="n">
+        <v>2455</v>
+      </c>
+      <c r="B2457" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0982.png</t>
+        </is>
+      </c>
+      <c r="C2457" t="inlineStr"/>
+      <c r="D2457" t="inlineStr"/>
+      <c r="E2457" t="inlineStr"/>
+      <c r="F2457" t="inlineStr">
+        <is>
+          <t>Nc1nnc(-c2ccccc2O)cc1-c1cnn(C2CCN([C@@H]3CC[C@H](CNc4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G2457" t="inlineStr"/>
+      <c r="H2457" t="inlineStr"/>
+      <c r="I2457" t="n">
+        <v>0.8746847025777333</v>
+      </c>
+      <c r="J2457" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2457" t="inlineStr"/>
+    </row>
+    <row r="2458">
+      <c r="A2458" s="1" t="n">
+        <v>2456</v>
+      </c>
+      <c r="B2458" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0986.png</t>
+        </is>
+      </c>
+      <c r="C2458" t="inlineStr"/>
+      <c r="D2458" t="inlineStr"/>
+      <c r="E2458" t="inlineStr"/>
+      <c r="F2458" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)NCCCCCCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)c2)cc1/C=C/c1ccc(Cl)cc1</t>
+        </is>
+      </c>
+      <c r="G2458" t="inlineStr"/>
+      <c r="H2458" t="inlineStr"/>
+      <c r="I2458" t="n">
+        <v>0.9063599937099274</v>
+      </c>
+      <c r="J2458" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2458" t="inlineStr"/>
+    </row>
+    <row r="2459">
+      <c r="A2459" s="1" t="n">
+        <v>2457</v>
+      </c>
+      <c r="B2459" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0994.png</t>
+        </is>
+      </c>
+      <c r="C2459" t="inlineStr"/>
+      <c r="D2459" t="inlineStr"/>
+      <c r="E2459" t="inlineStr"/>
+      <c r="F2459" t="inlineStr">
+        <is>
+          <t>COc1cc(C2=CN(C)C(=O)N(C)C2)cc(O)c1CN1CCN(CCN2CCN(c3ccc4c(c3)CN(C3CCC(=O)NC3=O)C4=O)CC2)CC1</t>
+        </is>
+      </c>
+      <c r="G2459" t="inlineStr"/>
+      <c r="H2459" t="inlineStr"/>
+      <c r="I2459" t="n">
+        <v>0.9144052942490697</v>
+      </c>
+      <c r="J2459" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2459" t="inlineStr"/>
+    </row>
+    <row r="2460">
+      <c r="A2460" s="1" t="n">
+        <v>2458</v>
+      </c>
+      <c r="B2460" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0998.png</t>
+        </is>
+      </c>
+      <c r="C2460" t="inlineStr"/>
+      <c r="D2460" t="inlineStr"/>
+      <c r="E2460" t="inlineStr"/>
+      <c r="F2460" t="inlineStr">
+        <is>
+          <t>Cn1cc(Nc2nc(N3CCCCC3)cnc2C(N)=O)cn1.O=C1CCC(N2C(=O)c3ccc(N4CCC(CN5CC6(CCNC6=O)C5)CC4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G2460" t="inlineStr"/>
+      <c r="H2460" t="inlineStr"/>
+      <c r="I2460" t="n">
+        <v>0.8476831963584213</v>
+      </c>
+      <c r="J2460" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2460" t="inlineStr"/>
+    </row>
+    <row r="2461">
+      <c r="A2461" s="1" t="n">
+        <v>2459</v>
+      </c>
+      <c r="B2461" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1006.png</t>
+        </is>
+      </c>
+      <c r="C2461" t="inlineStr"/>
+      <c r="D2461" t="inlineStr"/>
+      <c r="E2461" t="inlineStr"/>
+      <c r="F2461" t="inlineStr">
+        <is>
+          <t>CCCn1cc(-c2nc(Nc3ccc(C(=O)NCCCCCNc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)cc3)nc3[nH]ccc23)cn1</t>
+        </is>
+      </c>
+      <c r="G2461" t="inlineStr"/>
+      <c r="H2461" t="inlineStr"/>
+      <c r="I2461" t="n">
+        <v>0.910581312535195</v>
+      </c>
+      <c r="J2461" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2461" t="inlineStr"/>
+    </row>
+    <row r="2462">
+      <c r="A2462" s="1" t="n">
+        <v>2460</v>
+      </c>
+      <c r="B2462" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1010.png</t>
+        </is>
+      </c>
+      <c r="C2462" t="inlineStr"/>
+      <c r="D2462" t="inlineStr"/>
+      <c r="E2462" t="inlineStr"/>
+      <c r="F2462" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2CC(O)CN2C(=O)[C@H](c2cc(OCCOCCOc3ccc(CN4C(=O)/C(=C/C=C/c5ccc([N+](=O)[O-])cc5)c5ccccc54)cc3)no2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2462" t="inlineStr"/>
+      <c r="H2462" t="inlineStr"/>
+      <c r="I2462" t="n">
+        <v>0.853576812363668</v>
+      </c>
+      <c r="J2462" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2462" t="inlineStr"/>
+    </row>
+    <row r="2463">
+      <c r="A2463" s="1" t="n">
+        <v>2461</v>
+      </c>
+      <c r="B2463" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1014.png</t>
+        </is>
+      </c>
+      <c r="C2463" t="inlineStr"/>
+      <c r="D2463" t="inlineStr"/>
+      <c r="E2463" t="inlineStr"/>
+      <c r="F2463" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(CCC4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)CC3)CC2)ccc1Nc1ncc(Cl)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G2463" t="inlineStr"/>
+      <c r="H2463" t="inlineStr"/>
+      <c r="I2463" t="n">
+        <v>0.8953978340411021</v>
+      </c>
+      <c r="J2463" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2463" t="inlineStr"/>
+    </row>
+    <row r="2464">
+      <c r="A2464" s="1" t="n">
+        <v>2462</v>
+      </c>
+      <c r="B2464" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1018.png</t>
+        </is>
+      </c>
+      <c r="C2464" t="inlineStr"/>
+      <c r="D2464" t="inlineStr"/>
+      <c r="E2464" t="inlineStr"/>
+      <c r="F2464" t="inlineStr">
+        <is>
+          <t>COc1cc(C2=CN(C)C(=O)N3CCOCC23)cc(OC)c1CN1CCC2(CC1)CC(c1ccc3c(c1)C(=O)N(C1CCC(=O)NC1=O)C3=O)C2</t>
+        </is>
+      </c>
+      <c r="G2464" t="inlineStr"/>
+      <c r="H2464" t="inlineStr"/>
+      <c r="I2464" t="n">
+        <v>0.914536626818377</v>
+      </c>
+      <c r="J2464" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2464" t="inlineStr"/>
+    </row>
+    <row r="2465">
+      <c r="A2465" s="1" t="n">
+        <v>2463</v>
+      </c>
+      <c r="B2465" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1030.png</t>
+        </is>
+      </c>
+      <c r="C2465" t="inlineStr"/>
+      <c r="D2465" t="inlineStr"/>
+      <c r="E2465" t="inlineStr"/>
+      <c r="F2465" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5(C)CCN(C(=O)CCOCCNc6cccc7c6C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2465" t="inlineStr"/>
+      <c r="H2465" t="inlineStr"/>
+      <c r="I2465" t="n">
+        <v>0.9032810916354597</v>
+      </c>
+      <c r="J2465" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2465" t="inlineStr"/>
+    </row>
+    <row r="2466">
+      <c r="A2466" s="1" t="n">
+        <v>2464</v>
+      </c>
+      <c r="B2466" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1034.png</t>
+        </is>
+      </c>
+      <c r="C2466" t="inlineStr"/>
+      <c r="D2466" t="inlineStr"/>
+      <c r="E2466" t="inlineStr"/>
+      <c r="F2466" t="inlineStr">
+        <is>
+          <t>NC(=O)c1ncc(N2CCCCC2)nc1Nc1ccc(N2CCC3(CCN(Cc4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)CC2)cc1</t>
+        </is>
+      </c>
+      <c r="G2466" t="inlineStr"/>
+      <c r="H2466" t="inlineStr"/>
+      <c r="I2466" t="n">
+        <v>0.9016113108760238</v>
+      </c>
+      <c r="J2466" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2466" t="inlineStr"/>
+    </row>
+    <row r="2467">
+      <c r="A2467" s="1" t="n">
+        <v>2465</v>
+      </c>
+      <c r="B2467" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1038.png</t>
+        </is>
+      </c>
+      <c r="C2467" t="inlineStr"/>
+      <c r="D2467" t="inlineStr"/>
+      <c r="E2467" t="inlineStr"/>
+      <c r="F2467" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C(=O)NCCOCCOCCOCCCC5CC=CC6=C5CN(C5CCC(=O)NC5=O)C6=O)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2467" t="inlineStr"/>
+      <c r="H2467" t="inlineStr"/>
+      <c r="I2467" t="n">
+        <v>0.8764472306416241</v>
+      </c>
+      <c r="J2467" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2467" t="inlineStr"/>
+    </row>
+    <row r="2468">
+      <c r="A2468" s="1" t="n">
+        <v>2466</v>
+      </c>
+      <c r="B2468" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1042.png</t>
+        </is>
+      </c>
+      <c r="C2468" t="inlineStr"/>
+      <c r="D2468" t="inlineStr"/>
+      <c r="E2468" t="inlineStr"/>
+      <c r="F2468" t="inlineStr">
+        <is>
+          <t>Nc1ncnc2c1c(-c1ccc(Oc3ccccc3)cc1)nn2C1CCN(CCOCCCCCOc2ccc3c(c2)CN(C2CCC(=O)NC2=O)C3=O)CC1</t>
+        </is>
+      </c>
+      <c r="G2468" t="inlineStr"/>
+      <c r="H2468" t="inlineStr"/>
+      <c r="I2468" t="n">
+        <v>0.9065668565593671</v>
+      </c>
+      <c r="J2468" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2468" t="inlineStr"/>
+    </row>
+    <row r="2469">
+      <c r="A2469" s="1" t="n">
+        <v>2467</v>
+      </c>
+      <c r="B2469" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1046.png</t>
+        </is>
+      </c>
+      <c r="C2469" t="inlineStr"/>
+      <c r="D2469" t="inlineStr"/>
+      <c r="E2469" t="inlineStr"/>
+      <c r="F2469" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@H](c2cc(OCCCCN3CCC(c4cnc(N5C6CCC5CN(c5cc(-c7ccccc7O)nnc5N)C6)nc4)CC3)no2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2469" t="inlineStr"/>
+      <c r="H2469" t="inlineStr"/>
+      <c r="I2469" t="n">
+        <v>0.8701926062606588</v>
+      </c>
+      <c r="J2469" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2469" t="inlineStr"/>
+    </row>
+    <row r="2470">
+      <c r="A2470" s="1" t="n">
+        <v>2468</v>
+      </c>
+      <c r="B2470" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1050.png</t>
+        </is>
+      </c>
+      <c r="C2470" t="inlineStr"/>
+      <c r="D2470" t="inlineStr"/>
+      <c r="E2470" t="inlineStr"/>
+      <c r="F2470" t="inlineStr">
+        <is>
+          <t>COc1cc(C2=CN(C)C(=O)N3CCCCC23)cc(OC)c1CN1CCN(CCC2CCN(c3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)CC2)CC1</t>
+        </is>
+      </c>
+      <c r="G2470" t="inlineStr"/>
+      <c r="H2470" t="inlineStr"/>
+      <c r="I2470" t="n">
+        <v>0.9220117453020255</v>
+      </c>
+      <c r="J2470" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2470" t="inlineStr"/>
+    </row>
+    <row r="2471">
+      <c r="A2471" s="1" t="n">
+        <v>2469</v>
+      </c>
+      <c r="B2471" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1066.png</t>
+        </is>
+      </c>
+      <c r="C2471" t="inlineStr"/>
+      <c r="D2471" t="inlineStr"/>
+      <c r="E2471" t="inlineStr"/>
+      <c r="F2471" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)[C@@H]2CC[C@H](Cc3cnc(N4C5CCC4CN(c4cc(-c6ccccc6O)nnc4N)C5)nc3)CC2)C(C)(C)C)c(C(F)(F)F)c1</t>
+        </is>
+      </c>
+      <c r="G2471" t="inlineStr"/>
+      <c r="H2471" t="inlineStr"/>
+      <c r="I2471" t="n">
+        <v>0.883507830880916</v>
+      </c>
+      <c r="J2471" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2471" t="inlineStr"/>
+    </row>
+    <row r="2472">
+      <c r="A2472" s="1" t="n">
+        <v>2470</v>
+      </c>
+      <c r="B2472" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1074.png</t>
+        </is>
+      </c>
+      <c r="C2472" t="inlineStr"/>
+      <c r="D2472" t="inlineStr"/>
+      <c r="E2472" t="inlineStr"/>
+      <c r="F2472" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(N5CCC6CCN(c7cccc8c7C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6C5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2472" t="inlineStr"/>
+      <c r="H2472" t="inlineStr"/>
+      <c r="I2472" t="n">
+        <v>0.9033503555106929</v>
+      </c>
+      <c r="J2472" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2472" t="inlineStr"/>
+    </row>
+    <row r="2473">
+      <c r="A2473" s="1" t="n">
+        <v>2471</v>
+      </c>
+      <c r="B2473" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1078.png</t>
+        </is>
+      </c>
+      <c r="C2473" t="inlineStr"/>
+      <c r="D2473" t="inlineStr"/>
+      <c r="E2473" t="inlineStr"/>
+      <c r="F2473" t="inlineStr">
+        <is>
+          <t>Cn1cc(Nc2nc(N3CCCC(N4CC5(CN(CC6CN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)C5)OC4=O)C3)cnc2C(N)=O)cn1</t>
+        </is>
+      </c>
+      <c r="G2473" t="inlineStr"/>
+      <c r="H2473" t="inlineStr"/>
+      <c r="I2473" t="n">
+        <v>0.9001416760035215</v>
+      </c>
+      <c r="J2473" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2473" t="inlineStr"/>
+    </row>
+    <row r="2474">
+      <c r="A2474" s="1" t="n">
+        <v>2472</v>
+      </c>
+      <c r="B2474" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1082.png</t>
+        </is>
+      </c>
+      <c r="C2474" t="inlineStr"/>
+      <c r="D2474" t="inlineStr"/>
+      <c r="E2474" t="inlineStr"/>
+      <c r="F2474" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(N5CCC6(CC5)CCN(c5ccc7c(c5)C(=O)N(C5CCC(=O)NC5=O)C7=O)C6)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G2474" t="inlineStr"/>
+      <c r="H2474" t="inlineStr"/>
+      <c r="I2474" t="n">
+        <v>0.877535939455077</v>
+      </c>
+      <c r="J2474" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2474" t="inlineStr"/>
+    </row>
+    <row r="2475">
+      <c r="A2475" s="1" t="n">
+        <v>2473</v>
+      </c>
+      <c r="B2475" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1086.png</t>
+        </is>
+      </c>
+      <c r="C2475" t="inlineStr"/>
+      <c r="D2475" t="inlineStr"/>
+      <c r="E2475" t="inlineStr"/>
+      <c r="F2475" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCCC#Cc2cnc(N3C4CCC3CN(c3cc(-c5ccccc5O)nnc3N)C4)nc2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G2475" t="inlineStr"/>
+      <c r="H2475" t="inlineStr"/>
+      <c r="I2475" t="n">
+        <v>0.8733348019981719</v>
+      </c>
+      <c r="J2475" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2475" t="inlineStr"/>
+    </row>
+    <row r="2476">
+      <c r="A2476" s="1" t="n">
+        <v>2474</v>
+      </c>
+      <c r="B2476" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1098.png</t>
+        </is>
+      </c>
+      <c r="C2476" t="inlineStr"/>
+      <c r="D2476" t="inlineStr"/>
+      <c r="E2476" t="inlineStr"/>
+      <c r="F2476" t="inlineStr">
+        <is>
+          <t>Cc1nc2c(F)cc(-c3nc(Nc4ccc(C(=O)NCCCCCCOc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)cc4)ncc3F)cc2n1C(C)C</t>
+        </is>
+      </c>
+      <c r="G2476" t="inlineStr"/>
+      <c r="H2476" t="inlineStr"/>
+      <c r="I2476" t="n">
+        <v>0.8994047020171095</v>
+      </c>
+      <c r="J2476" t="inlineStr">
+        <is>
+          <t>High Confidence of SMILES being correct</t>
+        </is>
+      </c>
+      <c r="K2476" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
